--- a/NV Play Midweek League batting stats for season.xlsx
+++ b/NV Play Midweek League batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3539" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="720">
   <si>
     <t>Group</t>
   </si>
@@ -2135,6 +2135,51 @@
   <si>
     <t>Mohammed Sanobar</t>
   </si>
+  <si>
+    <t>Cliftonville Academy MW XI v Dunmurry MW2 XI, TBC - 16 July 2026</t>
+  </si>
+  <si>
+    <t>Santhan Reddy Gaddam</t>
+  </si>
+  <si>
+    <t>Suryakrishna Saneesh</t>
+  </si>
+  <si>
+    <t>Belfast Superkings MW XI v BISC MW XI, TBC - 16 July 2026</t>
+  </si>
+  <si>
+    <t>Mayur Nanjundaswamy</t>
+  </si>
+  <si>
+    <t>NIMACC MW XI v Dunmurry MW1 XI, TBC - 16 July 2026</t>
+  </si>
+  <si>
+    <t>Yashvanth Annaiah Vijayalakshmi</t>
+  </si>
+  <si>
+    <t>Lokesh Gehani</t>
+  </si>
+  <si>
+    <t>Fawad Uddin</t>
+  </si>
+  <si>
+    <t>Cregagh MW XI v Ardent Blues MW2 XI, Cregagh Memorial Recreation Ground - 17 July 2026</t>
+  </si>
+  <si>
+    <t>Thompson Dawson</t>
+  </si>
+  <si>
+    <t>Sandeep Ganesh Srinivasan</t>
+  </si>
+  <si>
+    <t>Harry Stone</t>
+  </si>
+  <si>
+    <t>Akshay Sunil</t>
+  </si>
+  <si>
+    <t>Joshy Thomas</t>
+  </si>
 </sst>
 </file>
 
@@ -2617,8 +2662,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2940,7 +2986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1561"/>
+  <dimension ref="A1:U1655"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="97.42578125" bestFit="1" customWidth="1"/>
@@ -96399,7 +96445,5253 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1562" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1562" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1562">
+        <v>1</v>
+      </c>
+      <c r="D1562">
+        <v>1</v>
+      </c>
+      <c r="E1562">
+        <v>0</v>
+      </c>
+      <c r="F1562">
+        <v>0</v>
+      </c>
+      <c r="G1562">
+        <v>0</v>
+      </c>
+      <c r="H1562">
+        <v>0</v>
+      </c>
+      <c r="I1562">
+        <v>0</v>
+      </c>
+      <c r="J1562">
+        <v>0</v>
+      </c>
+      <c r="K1562">
+        <v>0</v>
+      </c>
+      <c r="L1562">
+        <v>1</v>
+      </c>
+      <c r="M1562">
+        <v>1</v>
+      </c>
+      <c r="N1562">
+        <v>0</v>
+      </c>
+      <c r="O1562">
+        <v>0</v>
+      </c>
+      <c r="P1562">
+        <v>0</v>
+      </c>
+      <c r="Q1562">
+        <v>0</v>
+      </c>
+      <c r="R1562">
+        <v>0</v>
+      </c>
+      <c r="S1562">
+        <v>0</v>
+      </c>
+      <c r="T1562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1563" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>638</v>
+      </c>
+      <c r="C1563">
+        <v>1</v>
+      </c>
+      <c r="D1563">
+        <v>1</v>
+      </c>
+      <c r="E1563">
+        <v>0</v>
+      </c>
+      <c r="F1563">
+        <v>5</v>
+      </c>
+      <c r="G1563">
+        <v>5</v>
+      </c>
+      <c r="H1563">
+        <v>5</v>
+      </c>
+      <c r="I1563">
+        <v>0</v>
+      </c>
+      <c r="J1563">
+        <v>0</v>
+      </c>
+      <c r="K1563">
+        <v>45.45</v>
+      </c>
+      <c r="L1563">
+        <v>11</v>
+      </c>
+      <c r="M1563">
+        <v>7</v>
+      </c>
+      <c r="N1563">
+        <v>0</v>
+      </c>
+      <c r="O1563">
+        <v>0</v>
+      </c>
+      <c r="P1563">
+        <v>3.97</v>
+      </c>
+      <c r="Q1563">
+        <v>0</v>
+      </c>
+      <c r="R1563">
+        <v>0</v>
+      </c>
+      <c r="S1563">
+        <v>0</v>
+      </c>
+      <c r="T1563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1564" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1564">
+        <v>1</v>
+      </c>
+      <c r="D1564">
+        <v>1</v>
+      </c>
+      <c r="E1564">
+        <v>0</v>
+      </c>
+      <c r="F1564">
+        <v>9</v>
+      </c>
+      <c r="G1564">
+        <v>9</v>
+      </c>
+      <c r="H1564">
+        <v>9</v>
+      </c>
+      <c r="I1564">
+        <v>0</v>
+      </c>
+      <c r="J1564">
+        <v>0</v>
+      </c>
+      <c r="K1564">
+        <v>112.5</v>
+      </c>
+      <c r="L1564">
+        <v>8</v>
+      </c>
+      <c r="M1564">
+        <v>5</v>
+      </c>
+      <c r="N1564">
+        <v>2</v>
+      </c>
+      <c r="O1564">
+        <v>0</v>
+      </c>
+      <c r="P1564">
+        <v>7.14</v>
+      </c>
+      <c r="Q1564">
+        <v>0</v>
+      </c>
+      <c r="R1564">
+        <v>0</v>
+      </c>
+      <c r="S1564">
+        <v>0</v>
+      </c>
+      <c r="T1564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1565" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1565">
+        <v>1</v>
+      </c>
+      <c r="D1565">
+        <v>1</v>
+      </c>
+      <c r="E1565">
+        <v>0</v>
+      </c>
+      <c r="F1565">
+        <v>0</v>
+      </c>
+      <c r="G1565">
+        <v>0</v>
+      </c>
+      <c r="H1565">
+        <v>0</v>
+      </c>
+      <c r="I1565">
+        <v>0</v>
+      </c>
+      <c r="J1565">
+        <v>0</v>
+      </c>
+      <c r="K1565">
+        <v>0</v>
+      </c>
+      <c r="L1565">
+        <v>2</v>
+      </c>
+      <c r="M1565">
+        <v>2</v>
+      </c>
+      <c r="N1565">
+        <v>0</v>
+      </c>
+      <c r="O1565">
+        <v>0</v>
+      </c>
+      <c r="P1565">
+        <v>0</v>
+      </c>
+      <c r="Q1565">
+        <v>0</v>
+      </c>
+      <c r="R1565">
+        <v>0</v>
+      </c>
+      <c r="S1565">
+        <v>0</v>
+      </c>
+      <c r="T1565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1566" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>683</v>
+      </c>
+      <c r="C1566">
+        <v>1</v>
+      </c>
+      <c r="D1566">
+        <v>1</v>
+      </c>
+      <c r="E1566">
+        <v>0</v>
+      </c>
+      <c r="F1566">
+        <v>15</v>
+      </c>
+      <c r="G1566">
+        <v>15</v>
+      </c>
+      <c r="H1566">
+        <v>15</v>
+      </c>
+      <c r="I1566">
+        <v>0</v>
+      </c>
+      <c r="J1566">
+        <v>0</v>
+      </c>
+      <c r="K1566">
+        <v>136.36000000000001</v>
+      </c>
+      <c r="L1566">
+        <v>11</v>
+      </c>
+      <c r="M1566">
+        <v>3</v>
+      </c>
+      <c r="N1566">
+        <v>1</v>
+      </c>
+      <c r="O1566">
+        <v>0</v>
+      </c>
+      <c r="P1566">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="Q1566">
+        <v>0</v>
+      </c>
+      <c r="R1566">
+        <v>0</v>
+      </c>
+      <c r="S1566">
+        <v>0</v>
+      </c>
+      <c r="T1566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1567" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1567">
+        <v>1</v>
+      </c>
+      <c r="D1567">
+        <v>1</v>
+      </c>
+      <c r="E1567">
+        <v>0</v>
+      </c>
+      <c r="F1567">
+        <v>0</v>
+      </c>
+      <c r="G1567">
+        <v>0</v>
+      </c>
+      <c r="H1567">
+        <v>0</v>
+      </c>
+      <c r="I1567">
+        <v>0</v>
+      </c>
+      <c r="J1567">
+        <v>0</v>
+      </c>
+      <c r="K1567">
+        <v>0</v>
+      </c>
+      <c r="L1567">
+        <v>1</v>
+      </c>
+      <c r="M1567">
+        <v>1</v>
+      </c>
+      <c r="N1567">
+        <v>0</v>
+      </c>
+      <c r="O1567">
+        <v>0</v>
+      </c>
+      <c r="P1567">
+        <v>0</v>
+      </c>
+      <c r="Q1567">
+        <v>0</v>
+      </c>
+      <c r="R1567">
+        <v>0</v>
+      </c>
+      <c r="S1567">
+        <v>0</v>
+      </c>
+      <c r="T1567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1568" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>706</v>
+      </c>
+      <c r="C1568">
+        <v>1</v>
+      </c>
+      <c r="D1568">
+        <v>1</v>
+      </c>
+      <c r="E1568">
+        <v>1</v>
+      </c>
+      <c r="F1568">
+        <v>30</v>
+      </c>
+      <c r="H1568" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1568">
+        <v>0</v>
+      </c>
+      <c r="J1568">
+        <v>0</v>
+      </c>
+      <c r="K1568">
+        <v>120</v>
+      </c>
+      <c r="L1568">
+        <v>25</v>
+      </c>
+      <c r="M1568">
+        <v>13</v>
+      </c>
+      <c r="N1568">
+        <v>5</v>
+      </c>
+      <c r="O1568">
+        <v>0</v>
+      </c>
+      <c r="P1568">
+        <v>17.75</v>
+      </c>
+      <c r="Q1568">
+        <v>0</v>
+      </c>
+      <c r="R1568">
+        <v>0</v>
+      </c>
+      <c r="S1568">
+        <v>0</v>
+      </c>
+      <c r="T1568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1569" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1569">
+        <v>1</v>
+      </c>
+      <c r="D1569">
+        <v>1</v>
+      </c>
+      <c r="E1569">
+        <v>0</v>
+      </c>
+      <c r="F1569">
+        <v>2</v>
+      </c>
+      <c r="G1569">
+        <v>2</v>
+      </c>
+      <c r="H1569">
+        <v>2</v>
+      </c>
+      <c r="I1569">
+        <v>0</v>
+      </c>
+      <c r="J1569">
+        <v>0</v>
+      </c>
+      <c r="K1569">
+        <v>66.67</v>
+      </c>
+      <c r="L1569">
+        <v>3</v>
+      </c>
+      <c r="M1569">
+        <v>1</v>
+      </c>
+      <c r="N1569">
+        <v>0</v>
+      </c>
+      <c r="O1569">
+        <v>0</v>
+      </c>
+      <c r="P1569">
+        <v>1.59</v>
+      </c>
+      <c r="Q1569">
+        <v>0</v>
+      </c>
+      <c r="R1569">
+        <v>0</v>
+      </c>
+      <c r="S1569">
+        <v>0</v>
+      </c>
+      <c r="T1569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1570" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1570">
+        <v>1</v>
+      </c>
+      <c r="D1570">
+        <v>1</v>
+      </c>
+      <c r="E1570">
+        <v>0</v>
+      </c>
+      <c r="F1570">
+        <v>2</v>
+      </c>
+      <c r="G1570">
+        <v>2</v>
+      </c>
+      <c r="H1570">
+        <v>2</v>
+      </c>
+      <c r="I1570">
+        <v>0</v>
+      </c>
+      <c r="J1570">
+        <v>0</v>
+      </c>
+      <c r="K1570">
+        <v>66.67</v>
+      </c>
+      <c r="L1570">
+        <v>3</v>
+      </c>
+      <c r="M1570">
+        <v>2</v>
+      </c>
+      <c r="N1570">
+        <v>0</v>
+      </c>
+      <c r="O1570">
+        <v>0</v>
+      </c>
+      <c r="P1570">
+        <v>1.18</v>
+      </c>
+      <c r="Q1570">
+        <v>0</v>
+      </c>
+      <c r="R1570">
+        <v>0</v>
+      </c>
+      <c r="S1570">
+        <v>0</v>
+      </c>
+      <c r="T1570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1571" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1571">
+        <v>1</v>
+      </c>
+      <c r="D1571">
+        <v>1</v>
+      </c>
+      <c r="E1571">
+        <v>1</v>
+      </c>
+      <c r="F1571">
+        <v>5</v>
+      </c>
+      <c r="H1571" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1571">
+        <v>0</v>
+      </c>
+      <c r="J1571">
+        <v>0</v>
+      </c>
+      <c r="K1571">
+        <v>83.33</v>
+      </c>
+      <c r="L1571">
+        <v>6</v>
+      </c>
+      <c r="M1571">
+        <v>1</v>
+      </c>
+      <c r="N1571">
+        <v>0</v>
+      </c>
+      <c r="O1571">
+        <v>0</v>
+      </c>
+      <c r="P1571">
+        <v>2.96</v>
+      </c>
+      <c r="Q1571">
+        <v>0</v>
+      </c>
+      <c r="R1571">
+        <v>0</v>
+      </c>
+      <c r="S1571">
+        <v>0</v>
+      </c>
+      <c r="T1571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1572" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1572">
+        <v>1</v>
+      </c>
+      <c r="D1572">
+        <v>1</v>
+      </c>
+      <c r="E1572">
+        <v>0</v>
+      </c>
+      <c r="F1572">
+        <v>15</v>
+      </c>
+      <c r="G1572">
+        <v>15</v>
+      </c>
+      <c r="H1572">
+        <v>15</v>
+      </c>
+      <c r="I1572">
+        <v>0</v>
+      </c>
+      <c r="J1572">
+        <v>0</v>
+      </c>
+      <c r="K1572">
+        <v>93.75</v>
+      </c>
+      <c r="L1572">
+        <v>16</v>
+      </c>
+      <c r="M1572">
+        <v>5</v>
+      </c>
+      <c r="N1572">
+        <v>1</v>
+      </c>
+      <c r="O1572">
+        <v>0</v>
+      </c>
+      <c r="P1572">
+        <v>11.9</v>
+      </c>
+      <c r="Q1572">
+        <v>0</v>
+      </c>
+      <c r="R1572">
+        <v>0</v>
+      </c>
+      <c r="S1572">
+        <v>0</v>
+      </c>
+      <c r="T1572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1573" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1573">
+        <v>1</v>
+      </c>
+      <c r="D1573">
+        <v>1</v>
+      </c>
+      <c r="E1573">
+        <v>1</v>
+      </c>
+      <c r="F1573">
+        <v>30</v>
+      </c>
+      <c r="H1573" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1573">
+        <v>0</v>
+      </c>
+      <c r="J1573">
+        <v>0</v>
+      </c>
+      <c r="K1573">
+        <v>157.88999999999999</v>
+      </c>
+      <c r="L1573">
+        <v>19</v>
+      </c>
+      <c r="M1573">
+        <v>4</v>
+      </c>
+      <c r="N1573">
+        <v>4</v>
+      </c>
+      <c r="O1573">
+        <v>0</v>
+      </c>
+      <c r="P1573">
+        <v>17.75</v>
+      </c>
+      <c r="Q1573">
+        <v>0</v>
+      </c>
+      <c r="R1573">
+        <v>0</v>
+      </c>
+      <c r="S1573">
+        <v>0</v>
+      </c>
+      <c r="T1573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1574" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>507</v>
+      </c>
+      <c r="C1574">
+        <v>1</v>
+      </c>
+      <c r="D1574">
+        <v>1</v>
+      </c>
+      <c r="E1574">
+        <v>1</v>
+      </c>
+      <c r="F1574">
+        <v>30</v>
+      </c>
+      <c r="H1574" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1574">
+        <v>0</v>
+      </c>
+      <c r="J1574">
+        <v>0</v>
+      </c>
+      <c r="K1574">
+        <v>120</v>
+      </c>
+      <c r="L1574">
+        <v>25</v>
+      </c>
+      <c r="M1574">
+        <v>9</v>
+      </c>
+      <c r="N1574">
+        <v>4</v>
+      </c>
+      <c r="O1574">
+        <v>0</v>
+      </c>
+      <c r="P1574">
+        <v>23.81</v>
+      </c>
+      <c r="Q1574">
+        <v>0</v>
+      </c>
+      <c r="R1574">
+        <v>0</v>
+      </c>
+      <c r="S1574">
+        <v>0</v>
+      </c>
+      <c r="T1574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1575" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>707</v>
+      </c>
+      <c r="C1575">
+        <v>1</v>
+      </c>
+      <c r="D1575">
+        <v>1</v>
+      </c>
+      <c r="E1575">
+        <v>0</v>
+      </c>
+      <c r="F1575">
+        <v>4</v>
+      </c>
+      <c r="G1575">
+        <v>4</v>
+      </c>
+      <c r="H1575">
+        <v>4</v>
+      </c>
+      <c r="I1575">
+        <v>0</v>
+      </c>
+      <c r="J1575">
+        <v>0</v>
+      </c>
+      <c r="K1575">
+        <v>66.67</v>
+      </c>
+      <c r="L1575">
+        <v>6</v>
+      </c>
+      <c r="M1575">
+        <v>5</v>
+      </c>
+      <c r="N1575">
+        <v>1</v>
+      </c>
+      <c r="O1575">
+        <v>0</v>
+      </c>
+      <c r="P1575">
+        <v>3.17</v>
+      </c>
+      <c r="Q1575">
+        <v>0</v>
+      </c>
+      <c r="R1575">
+        <v>0</v>
+      </c>
+      <c r="S1575">
+        <v>0</v>
+      </c>
+      <c r="T1575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1576" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>510</v>
+      </c>
+      <c r="C1576">
+        <v>1</v>
+      </c>
+      <c r="D1576">
+        <v>1</v>
+      </c>
+      <c r="E1576">
+        <v>1</v>
+      </c>
+      <c r="F1576">
+        <v>30</v>
+      </c>
+      <c r="H1576" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1576">
+        <v>0</v>
+      </c>
+      <c r="J1576">
+        <v>0</v>
+      </c>
+      <c r="K1576">
+        <v>96.77</v>
+      </c>
+      <c r="L1576">
+        <v>31</v>
+      </c>
+      <c r="M1576">
+        <v>11</v>
+      </c>
+      <c r="N1576">
+        <v>2</v>
+      </c>
+      <c r="O1576">
+        <v>0</v>
+      </c>
+      <c r="P1576">
+        <v>23.81</v>
+      </c>
+      <c r="Q1576">
+        <v>0</v>
+      </c>
+      <c r="R1576">
+        <v>0</v>
+      </c>
+      <c r="S1576">
+        <v>0</v>
+      </c>
+      <c r="T1576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1577" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1577">
+        <v>1</v>
+      </c>
+      <c r="D1577">
+        <v>1</v>
+      </c>
+      <c r="E1577">
+        <v>0</v>
+      </c>
+      <c r="F1577">
+        <v>11</v>
+      </c>
+      <c r="G1577">
+        <v>11</v>
+      </c>
+      <c r="H1577">
+        <v>11</v>
+      </c>
+      <c r="I1577">
+        <v>0</v>
+      </c>
+      <c r="J1577">
+        <v>0</v>
+      </c>
+      <c r="K1577">
+        <v>91.67</v>
+      </c>
+      <c r="L1577">
+        <v>12</v>
+      </c>
+      <c r="M1577">
+        <v>8</v>
+      </c>
+      <c r="N1577">
+        <v>0</v>
+      </c>
+      <c r="O1577">
+        <v>1</v>
+      </c>
+      <c r="P1577">
+        <v>6.51</v>
+      </c>
+      <c r="Q1577">
+        <v>0</v>
+      </c>
+      <c r="R1577">
+        <v>0</v>
+      </c>
+      <c r="S1577">
+        <v>0</v>
+      </c>
+      <c r="T1577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1578" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1578">
+        <v>1</v>
+      </c>
+      <c r="D1578">
+        <v>1</v>
+      </c>
+      <c r="E1578">
+        <v>0</v>
+      </c>
+      <c r="F1578">
+        <v>9</v>
+      </c>
+      <c r="G1578">
+        <v>9</v>
+      </c>
+      <c r="H1578">
+        <v>9</v>
+      </c>
+      <c r="I1578">
+        <v>0</v>
+      </c>
+      <c r="J1578">
+        <v>0</v>
+      </c>
+      <c r="K1578">
+        <v>69.23</v>
+      </c>
+      <c r="L1578">
+        <v>13</v>
+      </c>
+      <c r="M1578">
+        <v>8</v>
+      </c>
+      <c r="N1578">
+        <v>1</v>
+      </c>
+      <c r="O1578">
+        <v>0</v>
+      </c>
+      <c r="P1578">
+        <v>5.33</v>
+      </c>
+      <c r="Q1578">
+        <v>0</v>
+      </c>
+      <c r="R1578">
+        <v>0</v>
+      </c>
+      <c r="S1578">
+        <v>0</v>
+      </c>
+      <c r="T1578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1579" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1579">
+        <v>1</v>
+      </c>
+      <c r="D1579">
+        <v>1</v>
+      </c>
+      <c r="E1579">
+        <v>1</v>
+      </c>
+      <c r="F1579">
+        <v>3</v>
+      </c>
+      <c r="H1579" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1579">
+        <v>0</v>
+      </c>
+      <c r="J1579">
+        <v>0</v>
+      </c>
+      <c r="K1579">
+        <v>37.5</v>
+      </c>
+      <c r="L1579">
+        <v>8</v>
+      </c>
+      <c r="M1579">
+        <v>6</v>
+      </c>
+      <c r="N1579">
+        <v>0</v>
+      </c>
+      <c r="O1579">
+        <v>0</v>
+      </c>
+      <c r="P1579">
+        <v>2.38</v>
+      </c>
+      <c r="Q1579">
+        <v>0</v>
+      </c>
+      <c r="R1579">
+        <v>0</v>
+      </c>
+      <c r="S1579">
+        <v>0</v>
+      </c>
+      <c r="T1579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1580" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1580">
+        <v>1</v>
+      </c>
+      <c r="D1580">
+        <v>1</v>
+      </c>
+      <c r="E1580">
+        <v>0</v>
+      </c>
+      <c r="F1580">
+        <v>0</v>
+      </c>
+      <c r="G1580">
+        <v>0</v>
+      </c>
+      <c r="H1580">
+        <v>0</v>
+      </c>
+      <c r="I1580">
+        <v>0</v>
+      </c>
+      <c r="J1580">
+        <v>0</v>
+      </c>
+      <c r="K1580">
+        <v>0</v>
+      </c>
+      <c r="L1580">
+        <v>3</v>
+      </c>
+      <c r="M1580">
+        <v>3</v>
+      </c>
+      <c r="N1580">
+        <v>0</v>
+      </c>
+      <c r="O1580">
+        <v>0</v>
+      </c>
+      <c r="P1580">
+        <v>0</v>
+      </c>
+      <c r="Q1580">
+        <v>0</v>
+      </c>
+      <c r="R1580">
+        <v>0</v>
+      </c>
+      <c r="S1580">
+        <v>0</v>
+      </c>
+      <c r="T1580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1581" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>684</v>
+      </c>
+      <c r="C1581">
+        <v>1</v>
+      </c>
+      <c r="D1581">
+        <v>1</v>
+      </c>
+      <c r="E1581">
+        <v>1</v>
+      </c>
+      <c r="F1581">
+        <v>32</v>
+      </c>
+      <c r="H1581" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1581">
+        <v>0</v>
+      </c>
+      <c r="J1581">
+        <v>0</v>
+      </c>
+      <c r="K1581">
+        <v>123.08</v>
+      </c>
+      <c r="L1581">
+        <v>26</v>
+      </c>
+      <c r="M1581">
+        <v>14</v>
+      </c>
+      <c r="N1581">
+        <v>3</v>
+      </c>
+      <c r="O1581">
+        <v>1</v>
+      </c>
+      <c r="P1581">
+        <v>18.93</v>
+      </c>
+      <c r="Q1581">
+        <v>0</v>
+      </c>
+      <c r="R1581">
+        <v>0</v>
+      </c>
+      <c r="S1581">
+        <v>0</v>
+      </c>
+      <c r="T1581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1582" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1582">
+        <v>1</v>
+      </c>
+      <c r="D1582">
+        <v>1</v>
+      </c>
+      <c r="E1582">
+        <v>0</v>
+      </c>
+      <c r="F1582">
+        <v>7</v>
+      </c>
+      <c r="G1582">
+        <v>7</v>
+      </c>
+      <c r="H1582">
+        <v>7</v>
+      </c>
+      <c r="I1582">
+        <v>0</v>
+      </c>
+      <c r="J1582">
+        <v>0</v>
+      </c>
+      <c r="K1582">
+        <v>116.67</v>
+      </c>
+      <c r="L1582">
+        <v>6</v>
+      </c>
+      <c r="M1582">
+        <v>3</v>
+      </c>
+      <c r="N1582">
+        <v>1</v>
+      </c>
+      <c r="O1582">
+        <v>0</v>
+      </c>
+      <c r="P1582">
+        <v>5.56</v>
+      </c>
+      <c r="Q1582">
+        <v>0</v>
+      </c>
+      <c r="R1582">
+        <v>0</v>
+      </c>
+      <c r="S1582">
+        <v>0</v>
+      </c>
+      <c r="T1582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1583" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1583">
+        <v>1</v>
+      </c>
+      <c r="D1583">
+        <v>1</v>
+      </c>
+      <c r="E1583">
+        <v>0</v>
+      </c>
+      <c r="F1583">
+        <v>0</v>
+      </c>
+      <c r="G1583">
+        <v>0</v>
+      </c>
+      <c r="H1583">
+        <v>0</v>
+      </c>
+      <c r="I1583">
+        <v>0</v>
+      </c>
+      <c r="J1583">
+        <v>0</v>
+      </c>
+      <c r="K1583">
+        <v>0</v>
+      </c>
+      <c r="L1583">
+        <v>1</v>
+      </c>
+      <c r="M1583">
+        <v>1</v>
+      </c>
+      <c r="N1583">
+        <v>0</v>
+      </c>
+      <c r="O1583">
+        <v>0</v>
+      </c>
+      <c r="P1583">
+        <v>0</v>
+      </c>
+      <c r="Q1583">
+        <v>1</v>
+      </c>
+      <c r="R1583">
+        <v>0</v>
+      </c>
+      <c r="S1583">
+        <v>0</v>
+      </c>
+      <c r="T1583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1584" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1584">
+        <v>1</v>
+      </c>
+      <c r="D1584">
+        <v>1</v>
+      </c>
+      <c r="E1584">
+        <v>1</v>
+      </c>
+      <c r="F1584">
+        <v>30</v>
+      </c>
+      <c r="H1584" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1584">
+        <v>0</v>
+      </c>
+      <c r="J1584">
+        <v>0</v>
+      </c>
+      <c r="K1584">
+        <v>187.5</v>
+      </c>
+      <c r="L1584">
+        <v>16</v>
+      </c>
+      <c r="M1584">
+        <v>4</v>
+      </c>
+      <c r="N1584">
+        <v>4</v>
+      </c>
+      <c r="O1584">
+        <v>1</v>
+      </c>
+      <c r="P1584">
+        <v>17.75</v>
+      </c>
+      <c r="Q1584">
+        <v>0</v>
+      </c>
+      <c r="R1584">
+        <v>0</v>
+      </c>
+      <c r="S1584">
+        <v>0</v>
+      </c>
+      <c r="T1584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1585" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1585">
+        <v>1</v>
+      </c>
+      <c r="D1585">
+        <v>1</v>
+      </c>
+      <c r="E1585">
+        <v>0</v>
+      </c>
+      <c r="F1585">
+        <v>11</v>
+      </c>
+      <c r="G1585">
+        <v>11</v>
+      </c>
+      <c r="H1585">
+        <v>11</v>
+      </c>
+      <c r="I1585">
+        <v>0</v>
+      </c>
+      <c r="J1585">
+        <v>0</v>
+      </c>
+      <c r="K1585">
+        <v>84.62</v>
+      </c>
+      <c r="L1585">
+        <v>13</v>
+      </c>
+      <c r="M1585">
+        <v>8</v>
+      </c>
+      <c r="N1585">
+        <v>2</v>
+      </c>
+      <c r="O1585">
+        <v>0</v>
+      </c>
+      <c r="P1585">
+        <v>6.55</v>
+      </c>
+      <c r="Q1585">
+        <v>0</v>
+      </c>
+      <c r="R1585">
+        <v>0</v>
+      </c>
+      <c r="S1585">
+        <v>0</v>
+      </c>
+      <c r="T1585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1586" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1586">
+        <v>1</v>
+      </c>
+      <c r="D1586">
+        <v>1</v>
+      </c>
+      <c r="E1586">
+        <v>1</v>
+      </c>
+      <c r="F1586">
+        <v>35</v>
+      </c>
+      <c r="H1586" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1586">
+        <v>0</v>
+      </c>
+      <c r="J1586">
+        <v>0</v>
+      </c>
+      <c r="K1586">
+        <v>166.67</v>
+      </c>
+      <c r="L1586">
+        <v>21</v>
+      </c>
+      <c r="M1586">
+        <v>8</v>
+      </c>
+      <c r="N1586">
+        <v>0</v>
+      </c>
+      <c r="O1586">
+        <v>4</v>
+      </c>
+      <c r="P1586">
+        <v>20.71</v>
+      </c>
+      <c r="Q1586">
+        <v>0</v>
+      </c>
+      <c r="R1586">
+        <v>0</v>
+      </c>
+      <c r="S1586">
+        <v>0</v>
+      </c>
+      <c r="T1586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1587" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1587">
+        <v>1</v>
+      </c>
+      <c r="D1587">
+        <v>1</v>
+      </c>
+      <c r="E1587">
+        <v>0</v>
+      </c>
+      <c r="F1587">
+        <v>3</v>
+      </c>
+      <c r="G1587">
+        <v>3</v>
+      </c>
+      <c r="H1587">
+        <v>3</v>
+      </c>
+      <c r="I1587">
+        <v>0</v>
+      </c>
+      <c r="J1587">
+        <v>0</v>
+      </c>
+      <c r="K1587">
+        <v>42.86</v>
+      </c>
+      <c r="L1587">
+        <v>7</v>
+      </c>
+      <c r="M1587">
+        <v>4</v>
+      </c>
+      <c r="N1587">
+        <v>0</v>
+      </c>
+      <c r="O1587">
+        <v>0</v>
+      </c>
+      <c r="P1587">
+        <v>1.79</v>
+      </c>
+      <c r="Q1587">
+        <v>0</v>
+      </c>
+      <c r="R1587">
+        <v>0</v>
+      </c>
+      <c r="S1587">
+        <v>0</v>
+      </c>
+      <c r="T1587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1588" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1588">
+        <v>1</v>
+      </c>
+      <c r="D1588">
+        <v>1</v>
+      </c>
+      <c r="E1588">
+        <v>1</v>
+      </c>
+      <c r="F1588">
+        <v>30</v>
+      </c>
+      <c r="H1588" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1588">
+        <v>0</v>
+      </c>
+      <c r="J1588">
+        <v>0</v>
+      </c>
+      <c r="K1588">
+        <v>375</v>
+      </c>
+      <c r="L1588">
+        <v>8</v>
+      </c>
+      <c r="M1588">
+        <v>1</v>
+      </c>
+      <c r="N1588">
+        <v>1</v>
+      </c>
+      <c r="O1588">
+        <v>4</v>
+      </c>
+      <c r="P1588">
+        <v>17.86</v>
+      </c>
+      <c r="Q1588">
+        <v>0</v>
+      </c>
+      <c r="R1588">
+        <v>0</v>
+      </c>
+      <c r="S1588">
+        <v>0</v>
+      </c>
+      <c r="T1588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1589" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>618</v>
+      </c>
+      <c r="C1589">
+        <v>1</v>
+      </c>
+      <c r="D1589">
+        <v>1</v>
+      </c>
+      <c r="E1589">
+        <v>0</v>
+      </c>
+      <c r="F1589">
+        <v>21</v>
+      </c>
+      <c r="G1589">
+        <v>21</v>
+      </c>
+      <c r="H1589">
+        <v>21</v>
+      </c>
+      <c r="I1589">
+        <v>0</v>
+      </c>
+      <c r="J1589">
+        <v>0</v>
+      </c>
+      <c r="K1589">
+        <v>161.54</v>
+      </c>
+      <c r="L1589">
+        <v>13</v>
+      </c>
+      <c r="M1589">
+        <v>6</v>
+      </c>
+      <c r="N1589">
+        <v>3</v>
+      </c>
+      <c r="O1589">
+        <v>1</v>
+      </c>
+      <c r="P1589">
+        <v>12.43</v>
+      </c>
+      <c r="Q1589">
+        <v>0</v>
+      </c>
+      <c r="R1589">
+        <v>0</v>
+      </c>
+      <c r="S1589">
+        <v>0</v>
+      </c>
+      <c r="T1589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1590" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1590">
+        <v>1</v>
+      </c>
+      <c r="D1590">
+        <v>1</v>
+      </c>
+      <c r="E1590">
+        <v>0</v>
+      </c>
+      <c r="F1590">
+        <v>13</v>
+      </c>
+      <c r="G1590">
+        <v>13</v>
+      </c>
+      <c r="H1590">
+        <v>13</v>
+      </c>
+      <c r="I1590">
+        <v>0</v>
+      </c>
+      <c r="J1590">
+        <v>0</v>
+      </c>
+      <c r="K1590">
+        <v>72.22</v>
+      </c>
+      <c r="L1590">
+        <v>18</v>
+      </c>
+      <c r="M1590">
+        <v>9</v>
+      </c>
+      <c r="N1590">
+        <v>1</v>
+      </c>
+      <c r="O1590">
+        <v>0</v>
+      </c>
+      <c r="P1590">
+        <v>7.74</v>
+      </c>
+      <c r="Q1590">
+        <v>0</v>
+      </c>
+      <c r="R1590">
+        <v>0</v>
+      </c>
+      <c r="S1590">
+        <v>0</v>
+      </c>
+      <c r="T1590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1591" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>522</v>
+      </c>
+      <c r="C1591">
+        <v>1</v>
+      </c>
+      <c r="D1591">
+        <v>0</v>
+      </c>
+      <c r="E1591">
+        <v>0</v>
+      </c>
+      <c r="F1591">
+        <v>0</v>
+      </c>
+      <c r="I1591">
+        <v>0</v>
+      </c>
+      <c r="J1591">
+        <v>0</v>
+      </c>
+      <c r="L1591">
+        <v>0</v>
+      </c>
+      <c r="M1591">
+        <v>0</v>
+      </c>
+      <c r="N1591">
+        <v>0</v>
+      </c>
+      <c r="O1591">
+        <v>0</v>
+      </c>
+      <c r="P1591">
+        <v>0</v>
+      </c>
+      <c r="Q1591">
+        <v>0</v>
+      </c>
+      <c r="R1591">
+        <v>0</v>
+      </c>
+      <c r="S1591">
+        <v>0</v>
+      </c>
+      <c r="T1591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1592" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1592">
+        <v>1</v>
+      </c>
+      <c r="D1592">
+        <v>1</v>
+      </c>
+      <c r="E1592">
+        <v>1</v>
+      </c>
+      <c r="F1592">
+        <v>1</v>
+      </c>
+      <c r="H1592" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1592">
+        <v>0</v>
+      </c>
+      <c r="J1592">
+        <v>0</v>
+      </c>
+      <c r="K1592">
+        <v>100</v>
+      </c>
+      <c r="L1592">
+        <v>1</v>
+      </c>
+      <c r="M1592">
+        <v>0</v>
+      </c>
+      <c r="N1592">
+        <v>0</v>
+      </c>
+      <c r="O1592">
+        <v>0</v>
+      </c>
+      <c r="P1592">
+        <v>0.6</v>
+      </c>
+      <c r="Q1592">
+        <v>0</v>
+      </c>
+      <c r="R1592">
+        <v>0</v>
+      </c>
+      <c r="S1592">
+        <v>0</v>
+      </c>
+      <c r="T1592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1593" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>709</v>
+      </c>
+      <c r="C1593">
+        <v>1</v>
+      </c>
+      <c r="D1593">
+        <v>1</v>
+      </c>
+      <c r="E1593">
+        <v>1</v>
+      </c>
+      <c r="F1593">
+        <v>31</v>
+      </c>
+      <c r="H1593" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1593">
+        <v>0</v>
+      </c>
+      <c r="J1593">
+        <v>0</v>
+      </c>
+      <c r="K1593">
+        <v>258.33</v>
+      </c>
+      <c r="L1593">
+        <v>12</v>
+      </c>
+      <c r="M1593">
+        <v>5</v>
+      </c>
+      <c r="N1593">
+        <v>3</v>
+      </c>
+      <c r="O1593">
+        <v>3</v>
+      </c>
+      <c r="P1593">
+        <v>18.45</v>
+      </c>
+      <c r="Q1593">
+        <v>0</v>
+      </c>
+      <c r="R1593">
+        <v>0</v>
+      </c>
+      <c r="S1593">
+        <v>0</v>
+      </c>
+      <c r="T1593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1594" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1594">
+        <v>1</v>
+      </c>
+      <c r="D1594">
+        <v>1</v>
+      </c>
+      <c r="E1594">
+        <v>1</v>
+      </c>
+      <c r="F1594">
+        <v>14</v>
+      </c>
+      <c r="H1594" t="s">
+        <v>205</v>
+      </c>
+      <c r="I1594">
+        <v>0</v>
+      </c>
+      <c r="J1594">
+        <v>0</v>
+      </c>
+      <c r="K1594">
+        <v>280</v>
+      </c>
+      <c r="L1594">
+        <v>5</v>
+      </c>
+      <c r="M1594">
+        <v>2</v>
+      </c>
+      <c r="N1594">
+        <v>2</v>
+      </c>
+      <c r="O1594">
+        <v>1</v>
+      </c>
+      <c r="P1594">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="Q1594">
+        <v>0</v>
+      </c>
+      <c r="R1594">
+        <v>0</v>
+      </c>
+      <c r="S1594">
+        <v>0</v>
+      </c>
+      <c r="T1594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1595" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1595">
+        <v>1</v>
+      </c>
+      <c r="D1595">
+        <v>1</v>
+      </c>
+      <c r="E1595">
+        <v>0</v>
+      </c>
+      <c r="F1595">
+        <v>6</v>
+      </c>
+      <c r="G1595">
+        <v>6</v>
+      </c>
+      <c r="H1595">
+        <v>6</v>
+      </c>
+      <c r="I1595">
+        <v>0</v>
+      </c>
+      <c r="J1595">
+        <v>0</v>
+      </c>
+      <c r="K1595">
+        <v>120</v>
+      </c>
+      <c r="L1595">
+        <v>5</v>
+      </c>
+      <c r="M1595">
+        <v>2</v>
+      </c>
+      <c r="N1595">
+        <v>1</v>
+      </c>
+      <c r="O1595">
+        <v>0</v>
+      </c>
+      <c r="P1595">
+        <v>3.57</v>
+      </c>
+      <c r="Q1595">
+        <v>0</v>
+      </c>
+      <c r="R1595">
+        <v>0</v>
+      </c>
+      <c r="S1595">
+        <v>0</v>
+      </c>
+      <c r="T1595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1596" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1596">
+        <v>1</v>
+      </c>
+      <c r="D1596">
+        <v>1</v>
+      </c>
+      <c r="E1596">
+        <v>0</v>
+      </c>
+      <c r="F1596">
+        <v>11</v>
+      </c>
+      <c r="G1596">
+        <v>11</v>
+      </c>
+      <c r="H1596">
+        <v>11</v>
+      </c>
+      <c r="I1596">
+        <v>0</v>
+      </c>
+      <c r="J1596">
+        <v>0</v>
+      </c>
+      <c r="K1596">
+        <v>64.709999999999994</v>
+      </c>
+      <c r="L1596">
+        <v>17</v>
+      </c>
+      <c r="M1596">
+        <v>8</v>
+      </c>
+      <c r="N1596">
+        <v>0</v>
+      </c>
+      <c r="O1596">
+        <v>0</v>
+      </c>
+      <c r="P1596">
+        <v>6.51</v>
+      </c>
+      <c r="Q1596">
+        <v>0</v>
+      </c>
+      <c r="R1596">
+        <v>0</v>
+      </c>
+      <c r="S1596">
+        <v>0</v>
+      </c>
+      <c r="T1596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1597" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1597">
+        <v>1</v>
+      </c>
+      <c r="D1597">
+        <v>1</v>
+      </c>
+      <c r="E1597">
+        <v>0</v>
+      </c>
+      <c r="F1597">
+        <v>6</v>
+      </c>
+      <c r="G1597">
+        <v>6</v>
+      </c>
+      <c r="H1597">
+        <v>6</v>
+      </c>
+      <c r="I1597">
+        <v>0</v>
+      </c>
+      <c r="J1597">
+        <v>0</v>
+      </c>
+      <c r="K1597">
+        <v>150</v>
+      </c>
+      <c r="L1597">
+        <v>4</v>
+      </c>
+      <c r="M1597">
+        <v>1</v>
+      </c>
+      <c r="N1597">
+        <v>1</v>
+      </c>
+      <c r="O1597">
+        <v>0</v>
+      </c>
+      <c r="P1597">
+        <v>3.57</v>
+      </c>
+      <c r="Q1597">
+        <v>0</v>
+      </c>
+      <c r="R1597">
+        <v>0</v>
+      </c>
+      <c r="S1597">
+        <v>0</v>
+      </c>
+      <c r="T1597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1598" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>523</v>
+      </c>
+      <c r="C1598">
+        <v>1</v>
+      </c>
+      <c r="D1598">
+        <v>1</v>
+      </c>
+      <c r="E1598">
+        <v>0</v>
+      </c>
+      <c r="F1598">
+        <v>18</v>
+      </c>
+      <c r="G1598">
+        <v>18</v>
+      </c>
+      <c r="H1598">
+        <v>18</v>
+      </c>
+      <c r="I1598">
+        <v>0</v>
+      </c>
+      <c r="J1598">
+        <v>0</v>
+      </c>
+      <c r="K1598">
+        <v>163.63999999999999</v>
+      </c>
+      <c r="L1598">
+        <v>11</v>
+      </c>
+      <c r="M1598">
+        <v>6</v>
+      </c>
+      <c r="N1598">
+        <v>1</v>
+      </c>
+      <c r="O1598">
+        <v>2</v>
+      </c>
+      <c r="P1598">
+        <v>10.65</v>
+      </c>
+      <c r="Q1598">
+        <v>0</v>
+      </c>
+      <c r="R1598">
+        <v>1</v>
+      </c>
+      <c r="S1598">
+        <v>0</v>
+      </c>
+      <c r="T1598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1599" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>619</v>
+      </c>
+      <c r="C1599">
+        <v>1</v>
+      </c>
+      <c r="D1599">
+        <v>1</v>
+      </c>
+      <c r="E1599">
+        <v>0</v>
+      </c>
+      <c r="F1599">
+        <v>0</v>
+      </c>
+      <c r="G1599">
+        <v>0</v>
+      </c>
+      <c r="H1599">
+        <v>0</v>
+      </c>
+      <c r="I1599">
+        <v>0</v>
+      </c>
+      <c r="J1599">
+        <v>0</v>
+      </c>
+      <c r="K1599">
+        <v>0</v>
+      </c>
+      <c r="L1599">
+        <v>2</v>
+      </c>
+      <c r="M1599">
+        <v>2</v>
+      </c>
+      <c r="N1599">
+        <v>0</v>
+      </c>
+      <c r="O1599">
+        <v>0</v>
+      </c>
+      <c r="P1599">
+        <v>0</v>
+      </c>
+      <c r="Q1599">
+        <v>0</v>
+      </c>
+      <c r="R1599">
+        <v>0</v>
+      </c>
+      <c r="S1599">
+        <v>0</v>
+      </c>
+      <c r="T1599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1600" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>526</v>
+      </c>
+      <c r="C1600">
+        <v>1</v>
+      </c>
+      <c r="D1600">
+        <v>1</v>
+      </c>
+      <c r="E1600">
+        <v>1</v>
+      </c>
+      <c r="F1600">
+        <v>27</v>
+      </c>
+      <c r="H1600" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1600">
+        <v>0</v>
+      </c>
+      <c r="J1600">
+        <v>0</v>
+      </c>
+      <c r="K1600">
+        <v>117.39</v>
+      </c>
+      <c r="L1600">
+        <v>23</v>
+      </c>
+      <c r="M1600">
+        <v>10</v>
+      </c>
+      <c r="N1600">
+        <v>3</v>
+      </c>
+      <c r="O1600">
+        <v>1</v>
+      </c>
+      <c r="P1600">
+        <v>15.98</v>
+      </c>
+      <c r="Q1600">
+        <v>0</v>
+      </c>
+      <c r="R1600">
+        <v>0</v>
+      </c>
+      <c r="S1600">
+        <v>0</v>
+      </c>
+      <c r="T1600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1601" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1601">
+        <v>1</v>
+      </c>
+      <c r="D1601">
+        <v>0</v>
+      </c>
+      <c r="E1601">
+        <v>0</v>
+      </c>
+      <c r="F1601">
+        <v>0</v>
+      </c>
+      <c r="I1601">
+        <v>0</v>
+      </c>
+      <c r="J1601">
+        <v>0</v>
+      </c>
+      <c r="L1601">
+        <v>0</v>
+      </c>
+      <c r="M1601">
+        <v>0</v>
+      </c>
+      <c r="N1601">
+        <v>0</v>
+      </c>
+      <c r="O1601">
+        <v>0</v>
+      </c>
+      <c r="P1601">
+        <v>0</v>
+      </c>
+      <c r="Q1601">
+        <v>0</v>
+      </c>
+      <c r="R1601">
+        <v>0</v>
+      </c>
+      <c r="S1601">
+        <v>0</v>
+      </c>
+      <c r="T1601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1602" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1602">
+        <v>1</v>
+      </c>
+      <c r="D1602">
+        <v>1</v>
+      </c>
+      <c r="E1602">
+        <v>1</v>
+      </c>
+      <c r="F1602">
+        <v>31</v>
+      </c>
+      <c r="H1602" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1602">
+        <v>0</v>
+      </c>
+      <c r="J1602">
+        <v>0</v>
+      </c>
+      <c r="K1602">
+        <v>140.91</v>
+      </c>
+      <c r="L1602">
+        <v>22</v>
+      </c>
+      <c r="M1602">
+        <v>7</v>
+      </c>
+      <c r="N1602">
+        <v>5</v>
+      </c>
+      <c r="O1602">
+        <v>0</v>
+      </c>
+      <c r="P1602">
+        <v>18.45</v>
+      </c>
+      <c r="Q1602">
+        <v>0</v>
+      </c>
+      <c r="R1602">
+        <v>0</v>
+      </c>
+      <c r="S1602">
+        <v>0</v>
+      </c>
+      <c r="T1602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1603" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>428</v>
+      </c>
+      <c r="C1603">
+        <v>1</v>
+      </c>
+      <c r="D1603">
+        <v>1</v>
+      </c>
+      <c r="E1603">
+        <v>0</v>
+      </c>
+      <c r="F1603">
+        <v>12</v>
+      </c>
+      <c r="G1603">
+        <v>12</v>
+      </c>
+      <c r="H1603">
+        <v>12</v>
+      </c>
+      <c r="I1603">
+        <v>0</v>
+      </c>
+      <c r="J1603">
+        <v>0</v>
+      </c>
+      <c r="K1603">
+        <v>120</v>
+      </c>
+      <c r="L1603">
+        <v>10</v>
+      </c>
+      <c r="M1603">
+        <v>5</v>
+      </c>
+      <c r="N1603">
+        <v>2</v>
+      </c>
+      <c r="O1603">
+        <v>0</v>
+      </c>
+      <c r="P1603">
+        <v>7.14</v>
+      </c>
+      <c r="Q1603">
+        <v>0</v>
+      </c>
+      <c r="R1603">
+        <v>0</v>
+      </c>
+      <c r="S1603">
+        <v>0</v>
+      </c>
+      <c r="T1603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1604" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>429</v>
+      </c>
+      <c r="C1604">
+        <v>1</v>
+      </c>
+      <c r="D1604">
+        <v>1</v>
+      </c>
+      <c r="E1604">
+        <v>0</v>
+      </c>
+      <c r="F1604">
+        <v>6</v>
+      </c>
+      <c r="G1604">
+        <v>6</v>
+      </c>
+      <c r="H1604">
+        <v>6</v>
+      </c>
+      <c r="I1604">
+        <v>0</v>
+      </c>
+      <c r="J1604">
+        <v>0</v>
+      </c>
+      <c r="K1604">
+        <v>85.71</v>
+      </c>
+      <c r="L1604">
+        <v>7</v>
+      </c>
+      <c r="M1604">
+        <v>4</v>
+      </c>
+      <c r="N1604">
+        <v>1</v>
+      </c>
+      <c r="O1604">
+        <v>0</v>
+      </c>
+      <c r="P1604">
+        <v>3.57</v>
+      </c>
+      <c r="Q1604">
+        <v>0</v>
+      </c>
+      <c r="R1604">
+        <v>0</v>
+      </c>
+      <c r="S1604">
+        <v>0</v>
+      </c>
+      <c r="T1604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1605" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>575</v>
+      </c>
+      <c r="C1605">
+        <v>1</v>
+      </c>
+      <c r="D1605">
+        <v>0</v>
+      </c>
+      <c r="E1605">
+        <v>0</v>
+      </c>
+      <c r="F1605">
+        <v>0</v>
+      </c>
+      <c r="I1605">
+        <v>0</v>
+      </c>
+      <c r="J1605">
+        <v>0</v>
+      </c>
+      <c r="L1605">
+        <v>0</v>
+      </c>
+      <c r="M1605">
+        <v>0</v>
+      </c>
+      <c r="N1605">
+        <v>0</v>
+      </c>
+      <c r="O1605">
+        <v>0</v>
+      </c>
+      <c r="P1605">
+        <v>0</v>
+      </c>
+      <c r="Q1605">
+        <v>0</v>
+      </c>
+      <c r="R1605">
+        <v>0</v>
+      </c>
+      <c r="S1605">
+        <v>0</v>
+      </c>
+      <c r="T1605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1606" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1606">
+        <v>1</v>
+      </c>
+      <c r="D1606">
+        <v>1</v>
+      </c>
+      <c r="E1606">
+        <v>0</v>
+      </c>
+      <c r="F1606">
+        <v>6</v>
+      </c>
+      <c r="G1606">
+        <v>6</v>
+      </c>
+      <c r="H1606">
+        <v>6</v>
+      </c>
+      <c r="I1606">
+        <v>0</v>
+      </c>
+      <c r="J1606">
+        <v>0</v>
+      </c>
+      <c r="K1606">
+        <v>30</v>
+      </c>
+      <c r="L1606">
+        <v>20</v>
+      </c>
+      <c r="M1606">
+        <v>14</v>
+      </c>
+      <c r="N1606">
+        <v>0</v>
+      </c>
+      <c r="O1606">
+        <v>0</v>
+      </c>
+      <c r="P1606">
+        <v>5.22</v>
+      </c>
+      <c r="Q1606">
+        <v>0</v>
+      </c>
+      <c r="R1606">
+        <v>0</v>
+      </c>
+      <c r="S1606">
+        <v>0</v>
+      </c>
+      <c r="T1606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1607" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>517</v>
+      </c>
+      <c r="C1607">
+        <v>1</v>
+      </c>
+      <c r="D1607">
+        <v>1</v>
+      </c>
+      <c r="E1607">
+        <v>1</v>
+      </c>
+      <c r="F1607">
+        <v>17</v>
+      </c>
+      <c r="H1607" t="s">
+        <v>261</v>
+      </c>
+      <c r="I1607">
+        <v>0</v>
+      </c>
+      <c r="J1607">
+        <v>0</v>
+      </c>
+      <c r="K1607">
+        <v>85</v>
+      </c>
+      <c r="L1607">
+        <v>20</v>
+      </c>
+      <c r="M1607">
+        <v>10</v>
+      </c>
+      <c r="N1607">
+        <v>2</v>
+      </c>
+      <c r="O1607">
+        <v>0</v>
+      </c>
+      <c r="P1607">
+        <v>14.91</v>
+      </c>
+      <c r="Q1607">
+        <v>0</v>
+      </c>
+      <c r="R1607">
+        <v>0</v>
+      </c>
+      <c r="S1607">
+        <v>0</v>
+      </c>
+      <c r="T1607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1608" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1608">
+        <v>1</v>
+      </c>
+      <c r="D1608">
+        <v>1</v>
+      </c>
+      <c r="E1608">
+        <v>1</v>
+      </c>
+      <c r="F1608">
+        <v>0</v>
+      </c>
+      <c r="H1608" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1608">
+        <v>0</v>
+      </c>
+      <c r="J1608">
+        <v>0</v>
+      </c>
+      <c r="K1608">
+        <v>0</v>
+      </c>
+      <c r="L1608">
+        <v>3</v>
+      </c>
+      <c r="M1608">
+        <v>3</v>
+      </c>
+      <c r="N1608">
+        <v>0</v>
+      </c>
+      <c r="O1608">
+        <v>0</v>
+      </c>
+      <c r="P1608">
+        <v>0</v>
+      </c>
+      <c r="Q1608">
+        <v>0</v>
+      </c>
+      <c r="R1608">
+        <v>0</v>
+      </c>
+      <c r="S1608">
+        <v>0</v>
+      </c>
+      <c r="T1608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1609" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>711</v>
+      </c>
+      <c r="C1609">
+        <v>1</v>
+      </c>
+      <c r="D1609">
+        <v>0</v>
+      </c>
+      <c r="E1609">
+        <v>0</v>
+      </c>
+      <c r="F1609">
+        <v>0</v>
+      </c>
+      <c r="I1609">
+        <v>0</v>
+      </c>
+      <c r="J1609">
+        <v>0</v>
+      </c>
+      <c r="L1609">
+        <v>0</v>
+      </c>
+      <c r="M1609">
+        <v>0</v>
+      </c>
+      <c r="N1609">
+        <v>0</v>
+      </c>
+      <c r="O1609">
+        <v>0</v>
+      </c>
+      <c r="P1609">
+        <v>0</v>
+      </c>
+      <c r="Q1609">
+        <v>0</v>
+      </c>
+      <c r="R1609">
+        <v>0</v>
+      </c>
+      <c r="S1609">
+        <v>0</v>
+      </c>
+      <c r="T1609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1610" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>518</v>
+      </c>
+      <c r="C1610">
+        <v>1</v>
+      </c>
+      <c r="D1610">
+        <v>1</v>
+      </c>
+      <c r="E1610">
+        <v>0</v>
+      </c>
+      <c r="F1610">
+        <v>8</v>
+      </c>
+      <c r="G1610">
+        <v>8</v>
+      </c>
+      <c r="H1610">
+        <v>8</v>
+      </c>
+      <c r="I1610">
+        <v>0</v>
+      </c>
+      <c r="J1610">
+        <v>0</v>
+      </c>
+      <c r="K1610">
+        <v>57.14</v>
+      </c>
+      <c r="L1610">
+        <v>14</v>
+      </c>
+      <c r="M1610">
+        <v>7</v>
+      </c>
+      <c r="N1610">
+        <v>0</v>
+      </c>
+      <c r="O1610">
+        <v>0</v>
+      </c>
+      <c r="P1610">
+        <v>7.02</v>
+      </c>
+      <c r="Q1610">
+        <v>0</v>
+      </c>
+      <c r="R1610">
+        <v>0</v>
+      </c>
+      <c r="S1610">
+        <v>0</v>
+      </c>
+      <c r="T1610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1611" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1611">
+        <v>1</v>
+      </c>
+      <c r="D1611">
+        <v>1</v>
+      </c>
+      <c r="E1611">
+        <v>1</v>
+      </c>
+      <c r="F1611">
+        <v>0</v>
+      </c>
+      <c r="H1611" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1611">
+        <v>0</v>
+      </c>
+      <c r="J1611">
+        <v>0</v>
+      </c>
+      <c r="L1611">
+        <v>0</v>
+      </c>
+      <c r="M1611">
+        <v>0</v>
+      </c>
+      <c r="N1611">
+        <v>0</v>
+      </c>
+      <c r="O1611">
+        <v>0</v>
+      </c>
+      <c r="P1611">
+        <v>0</v>
+      </c>
+      <c r="Q1611">
+        <v>0</v>
+      </c>
+      <c r="R1611">
+        <v>0</v>
+      </c>
+      <c r="S1611">
+        <v>0</v>
+      </c>
+      <c r="T1611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1612" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>712</v>
+      </c>
+      <c r="C1612">
+        <v>1</v>
+      </c>
+      <c r="D1612">
+        <v>0</v>
+      </c>
+      <c r="E1612">
+        <v>0</v>
+      </c>
+      <c r="F1612">
+        <v>0</v>
+      </c>
+      <c r="I1612">
+        <v>0</v>
+      </c>
+      <c r="J1612">
+        <v>0</v>
+      </c>
+      <c r="L1612">
+        <v>0</v>
+      </c>
+      <c r="M1612">
+        <v>0</v>
+      </c>
+      <c r="N1612">
+        <v>0</v>
+      </c>
+      <c r="O1612">
+        <v>0</v>
+      </c>
+      <c r="P1612">
+        <v>0</v>
+      </c>
+      <c r="Q1612">
+        <v>0</v>
+      </c>
+      <c r="R1612">
+        <v>0</v>
+      </c>
+      <c r="S1612">
+        <v>0</v>
+      </c>
+      <c r="T1612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1613" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1613">
+        <v>1</v>
+      </c>
+      <c r="D1613">
+        <v>1</v>
+      </c>
+      <c r="E1613">
+        <v>1</v>
+      </c>
+      <c r="F1613">
+        <v>30</v>
+      </c>
+      <c r="H1613" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1613">
+        <v>0</v>
+      </c>
+      <c r="J1613">
+        <v>0</v>
+      </c>
+      <c r="K1613">
+        <v>63.83</v>
+      </c>
+      <c r="L1613">
+        <v>47</v>
+      </c>
+      <c r="M1613">
+        <v>27</v>
+      </c>
+      <c r="N1613">
+        <v>3</v>
+      </c>
+      <c r="O1613">
+        <v>0</v>
+      </c>
+      <c r="P1613">
+        <v>26.32</v>
+      </c>
+      <c r="Q1613">
+        <v>0</v>
+      </c>
+      <c r="R1613">
+        <v>0</v>
+      </c>
+      <c r="S1613">
+        <v>0</v>
+      </c>
+      <c r="T1613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1614" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1614">
+        <v>1</v>
+      </c>
+      <c r="D1614">
+        <v>0</v>
+      </c>
+      <c r="E1614">
+        <v>0</v>
+      </c>
+      <c r="F1614">
+        <v>0</v>
+      </c>
+      <c r="I1614">
+        <v>0</v>
+      </c>
+      <c r="J1614">
+        <v>0</v>
+      </c>
+      <c r="L1614">
+        <v>0</v>
+      </c>
+      <c r="M1614">
+        <v>0</v>
+      </c>
+      <c r="N1614">
+        <v>0</v>
+      </c>
+      <c r="O1614">
+        <v>0</v>
+      </c>
+      <c r="P1614">
+        <v>0</v>
+      </c>
+      <c r="Q1614">
+        <v>0</v>
+      </c>
+      <c r="R1614">
+        <v>0</v>
+      </c>
+      <c r="S1614">
+        <v>0</v>
+      </c>
+      <c r="T1614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1615" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1615">
+        <v>1</v>
+      </c>
+      <c r="D1615">
+        <v>1</v>
+      </c>
+      <c r="E1615">
+        <v>1</v>
+      </c>
+      <c r="F1615">
+        <v>30</v>
+      </c>
+      <c r="H1615" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1615">
+        <v>0</v>
+      </c>
+      <c r="J1615">
+        <v>0</v>
+      </c>
+      <c r="K1615">
+        <v>103.45</v>
+      </c>
+      <c r="L1615">
+        <v>29</v>
+      </c>
+      <c r="M1615">
+        <v>14</v>
+      </c>
+      <c r="N1615">
+        <v>3</v>
+      </c>
+      <c r="O1615">
+        <v>0</v>
+      </c>
+      <c r="P1615">
+        <v>26.09</v>
+      </c>
+      <c r="Q1615">
+        <v>0</v>
+      </c>
+      <c r="R1615">
+        <v>0</v>
+      </c>
+      <c r="S1615">
+        <v>0</v>
+      </c>
+      <c r="T1615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1616" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1616">
+        <v>1</v>
+      </c>
+      <c r="D1616">
+        <v>0</v>
+      </c>
+      <c r="E1616">
+        <v>0</v>
+      </c>
+      <c r="F1616">
+        <v>0</v>
+      </c>
+      <c r="I1616">
+        <v>0</v>
+      </c>
+      <c r="J1616">
+        <v>0</v>
+      </c>
+      <c r="L1616">
+        <v>0</v>
+      </c>
+      <c r="M1616">
+        <v>0</v>
+      </c>
+      <c r="N1616">
+        <v>0</v>
+      </c>
+      <c r="O1616">
+        <v>0</v>
+      </c>
+      <c r="P1616">
+        <v>0</v>
+      </c>
+      <c r="Q1616">
+        <v>0</v>
+      </c>
+      <c r="R1616">
+        <v>0</v>
+      </c>
+      <c r="S1616">
+        <v>0</v>
+      </c>
+      <c r="T1616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1617" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1617">
+        <v>1</v>
+      </c>
+      <c r="D1617">
+        <v>0</v>
+      </c>
+      <c r="E1617">
+        <v>0</v>
+      </c>
+      <c r="F1617">
+        <v>0</v>
+      </c>
+      <c r="I1617">
+        <v>0</v>
+      </c>
+      <c r="J1617">
+        <v>0</v>
+      </c>
+      <c r="L1617">
+        <v>0</v>
+      </c>
+      <c r="M1617">
+        <v>0</v>
+      </c>
+      <c r="N1617">
+        <v>0</v>
+      </c>
+      <c r="O1617">
+        <v>0</v>
+      </c>
+      <c r="P1617">
+        <v>0</v>
+      </c>
+      <c r="Q1617">
+        <v>0</v>
+      </c>
+      <c r="R1617">
+        <v>0</v>
+      </c>
+      <c r="S1617">
+        <v>0</v>
+      </c>
+      <c r="T1617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1618" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1618">
+        <v>1</v>
+      </c>
+      <c r="D1618">
+        <v>1</v>
+      </c>
+      <c r="E1618">
+        <v>1</v>
+      </c>
+      <c r="F1618">
+        <v>30</v>
+      </c>
+      <c r="H1618" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1618">
+        <v>0</v>
+      </c>
+      <c r="J1618">
+        <v>0</v>
+      </c>
+      <c r="K1618">
+        <v>111.11</v>
+      </c>
+      <c r="L1618">
+        <v>27</v>
+      </c>
+      <c r="M1618">
+        <v>12</v>
+      </c>
+      <c r="N1618">
+        <v>4</v>
+      </c>
+      <c r="O1618">
+        <v>0</v>
+      </c>
+      <c r="P1618">
+        <v>26.32</v>
+      </c>
+      <c r="Q1618">
+        <v>0</v>
+      </c>
+      <c r="R1618">
+        <v>0</v>
+      </c>
+      <c r="S1618">
+        <v>0</v>
+      </c>
+      <c r="T1618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1619" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1619">
+        <v>1</v>
+      </c>
+      <c r="D1619">
+        <v>0</v>
+      </c>
+      <c r="E1619">
+        <v>0</v>
+      </c>
+      <c r="F1619">
+        <v>0</v>
+      </c>
+      <c r="I1619">
+        <v>0</v>
+      </c>
+      <c r="J1619">
+        <v>0</v>
+      </c>
+      <c r="L1619">
+        <v>0</v>
+      </c>
+      <c r="M1619">
+        <v>0</v>
+      </c>
+      <c r="N1619">
+        <v>0</v>
+      </c>
+      <c r="O1619">
+        <v>0</v>
+      </c>
+      <c r="P1619">
+        <v>0</v>
+      </c>
+      <c r="Q1619">
+        <v>0</v>
+      </c>
+      <c r="R1619">
+        <v>0</v>
+      </c>
+      <c r="S1619">
+        <v>0</v>
+      </c>
+      <c r="T1619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1620" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1620">
+        <v>1</v>
+      </c>
+      <c r="D1620">
+        <v>0</v>
+      </c>
+      <c r="E1620">
+        <v>0</v>
+      </c>
+      <c r="F1620">
+        <v>0</v>
+      </c>
+      <c r="I1620">
+        <v>0</v>
+      </c>
+      <c r="J1620">
+        <v>0</v>
+      </c>
+      <c r="L1620">
+        <v>0</v>
+      </c>
+      <c r="M1620">
+        <v>0</v>
+      </c>
+      <c r="N1620">
+        <v>0</v>
+      </c>
+      <c r="O1620">
+        <v>0</v>
+      </c>
+      <c r="P1620">
+        <v>0</v>
+      </c>
+      <c r="Q1620">
+        <v>0</v>
+      </c>
+      <c r="R1620">
+        <v>0</v>
+      </c>
+      <c r="S1620">
+        <v>0</v>
+      </c>
+      <c r="T1620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1621" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1621">
+        <v>1</v>
+      </c>
+      <c r="D1621">
+        <v>1</v>
+      </c>
+      <c r="E1621">
+        <v>0</v>
+      </c>
+      <c r="F1621">
+        <v>33</v>
+      </c>
+      <c r="G1621">
+        <v>33</v>
+      </c>
+      <c r="H1621">
+        <v>33</v>
+      </c>
+      <c r="I1621">
+        <v>0</v>
+      </c>
+      <c r="J1621">
+        <v>0</v>
+      </c>
+      <c r="K1621">
+        <v>143.47999999999999</v>
+      </c>
+      <c r="L1621">
+        <v>23</v>
+      </c>
+      <c r="M1621">
+        <v>10</v>
+      </c>
+      <c r="N1621">
+        <v>6</v>
+      </c>
+      <c r="O1621">
+        <v>0</v>
+      </c>
+      <c r="P1621">
+        <v>28.7</v>
+      </c>
+      <c r="Q1621">
+        <v>0</v>
+      </c>
+      <c r="R1621">
+        <v>0</v>
+      </c>
+      <c r="S1621">
+        <v>0</v>
+      </c>
+      <c r="T1621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1622" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>388</v>
+      </c>
+      <c r="C1622">
+        <v>1</v>
+      </c>
+      <c r="D1622">
+        <v>0</v>
+      </c>
+      <c r="E1622">
+        <v>0</v>
+      </c>
+      <c r="F1622">
+        <v>0</v>
+      </c>
+      <c r="I1622">
+        <v>0</v>
+      </c>
+      <c r="J1622">
+        <v>0</v>
+      </c>
+      <c r="L1622">
+        <v>0</v>
+      </c>
+      <c r="M1622">
+        <v>0</v>
+      </c>
+      <c r="N1622">
+        <v>0</v>
+      </c>
+      <c r="O1622">
+        <v>0</v>
+      </c>
+      <c r="P1622">
+        <v>0</v>
+      </c>
+      <c r="Q1622">
+        <v>0</v>
+      </c>
+      <c r="R1622">
+        <v>0</v>
+      </c>
+      <c r="S1622">
+        <v>0</v>
+      </c>
+      <c r="T1622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1623" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1623">
+        <v>1</v>
+      </c>
+      <c r="D1623">
+        <v>1</v>
+      </c>
+      <c r="E1623">
+        <v>1</v>
+      </c>
+      <c r="F1623">
+        <v>8</v>
+      </c>
+      <c r="H1623" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1623">
+        <v>0</v>
+      </c>
+      <c r="J1623">
+        <v>0</v>
+      </c>
+      <c r="K1623">
+        <v>88.89</v>
+      </c>
+      <c r="L1623">
+        <v>9</v>
+      </c>
+      <c r="M1623">
+        <v>4</v>
+      </c>
+      <c r="N1623">
+        <v>0</v>
+      </c>
+      <c r="O1623">
+        <v>0</v>
+      </c>
+      <c r="P1623">
+        <v>6.96</v>
+      </c>
+      <c r="Q1623">
+        <v>0</v>
+      </c>
+      <c r="R1623">
+        <v>0</v>
+      </c>
+      <c r="S1623">
+        <v>0</v>
+      </c>
+      <c r="T1623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1624" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>476</v>
+      </c>
+      <c r="C1624">
+        <v>1</v>
+      </c>
+      <c r="D1624">
+        <v>1</v>
+      </c>
+      <c r="E1624">
+        <v>0</v>
+      </c>
+      <c r="F1624">
+        <v>0</v>
+      </c>
+      <c r="G1624">
+        <v>0</v>
+      </c>
+      <c r="H1624">
+        <v>0</v>
+      </c>
+      <c r="I1624">
+        <v>0</v>
+      </c>
+      <c r="J1624">
+        <v>0</v>
+      </c>
+      <c r="L1624">
+        <v>0</v>
+      </c>
+      <c r="M1624">
+        <v>0</v>
+      </c>
+      <c r="N1624">
+        <v>0</v>
+      </c>
+      <c r="O1624">
+        <v>0</v>
+      </c>
+      <c r="P1624">
+        <v>0</v>
+      </c>
+      <c r="Q1624">
+        <v>0</v>
+      </c>
+      <c r="R1624">
+        <v>0</v>
+      </c>
+      <c r="S1624">
+        <v>0</v>
+      </c>
+      <c r="T1624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1625" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>321</v>
+      </c>
+      <c r="C1625">
+        <v>1</v>
+      </c>
+      <c r="D1625">
+        <v>1</v>
+      </c>
+      <c r="E1625">
+        <v>0</v>
+      </c>
+      <c r="F1625">
+        <v>16</v>
+      </c>
+      <c r="G1625">
+        <v>16</v>
+      </c>
+      <c r="H1625">
+        <v>16</v>
+      </c>
+      <c r="I1625">
+        <v>0</v>
+      </c>
+      <c r="J1625">
+        <v>0</v>
+      </c>
+      <c r="K1625">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1625">
+        <v>12</v>
+      </c>
+      <c r="M1625">
+        <v>6</v>
+      </c>
+      <c r="N1625">
+        <v>3</v>
+      </c>
+      <c r="O1625">
+        <v>0</v>
+      </c>
+      <c r="P1625">
+        <v>13.91</v>
+      </c>
+      <c r="Q1625">
+        <v>0</v>
+      </c>
+      <c r="R1625">
+        <v>0</v>
+      </c>
+      <c r="S1625">
+        <v>0</v>
+      </c>
+      <c r="T1625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1626" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1626">
+        <v>1</v>
+      </c>
+      <c r="D1626">
+        <v>1</v>
+      </c>
+      <c r="E1626">
+        <v>0</v>
+      </c>
+      <c r="F1626">
+        <v>6</v>
+      </c>
+      <c r="G1626">
+        <v>6</v>
+      </c>
+      <c r="H1626">
+        <v>6</v>
+      </c>
+      <c r="I1626">
+        <v>0</v>
+      </c>
+      <c r="J1626">
+        <v>0</v>
+      </c>
+      <c r="K1626">
+        <v>100</v>
+      </c>
+      <c r="L1626">
+        <v>6</v>
+      </c>
+      <c r="M1626">
+        <v>3</v>
+      </c>
+      <c r="N1626">
+        <v>1</v>
+      </c>
+      <c r="O1626">
+        <v>0</v>
+      </c>
+      <c r="P1626">
+        <v>5.26</v>
+      </c>
+      <c r="Q1626">
+        <v>0</v>
+      </c>
+      <c r="R1626">
+        <v>0</v>
+      </c>
+      <c r="S1626">
+        <v>0</v>
+      </c>
+      <c r="T1626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1627" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1627" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C1627">
+        <v>1</v>
+      </c>
+      <c r="D1627">
+        <v>1</v>
+      </c>
+      <c r="E1627">
+        <v>0</v>
+      </c>
+      <c r="F1627">
+        <v>5</v>
+      </c>
+      <c r="G1627">
+        <v>5</v>
+      </c>
+      <c r="H1627">
+        <v>5</v>
+      </c>
+      <c r="I1627">
+        <v>0</v>
+      </c>
+      <c r="J1627">
+        <v>0</v>
+      </c>
+      <c r="K1627">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="L1627">
+        <v>7</v>
+      </c>
+      <c r="M1627">
+        <v>2</v>
+      </c>
+      <c r="N1627">
+        <v>0</v>
+      </c>
+      <c r="O1627">
+        <v>0</v>
+      </c>
+      <c r="P1627">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="Q1627">
+        <v>0</v>
+      </c>
+      <c r="R1627">
+        <v>0</v>
+      </c>
+      <c r="S1627">
+        <v>0</v>
+      </c>
+      <c r="T1627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1628" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1628" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C1628">
+        <v>1</v>
+      </c>
+      <c r="D1628">
+        <v>1</v>
+      </c>
+      <c r="E1628">
+        <v>0</v>
+      </c>
+      <c r="F1628">
+        <v>3</v>
+      </c>
+      <c r="G1628">
+        <v>3</v>
+      </c>
+      <c r="H1628">
+        <v>3</v>
+      </c>
+      <c r="I1628">
+        <v>0</v>
+      </c>
+      <c r="J1628">
+        <v>0</v>
+      </c>
+      <c r="K1628">
+        <v>42.86</v>
+      </c>
+      <c r="L1628">
+        <v>7</v>
+      </c>
+      <c r="M1628">
+        <v>4</v>
+      </c>
+      <c r="N1628">
+        <v>0</v>
+      </c>
+      <c r="O1628">
+        <v>0</v>
+      </c>
+      <c r="P1628">
+        <v>2.17</v>
+      </c>
+      <c r="Q1628">
+        <v>0</v>
+      </c>
+      <c r="R1628">
+        <v>0</v>
+      </c>
+      <c r="S1628">
+        <v>0</v>
+      </c>
+      <c r="T1628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1629" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1629" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C1629">
+        <v>1</v>
+      </c>
+      <c r="D1629">
+        <v>0</v>
+      </c>
+      <c r="E1629">
+        <v>0</v>
+      </c>
+      <c r="F1629">
+        <v>0</v>
+      </c>
+      <c r="I1629">
+        <v>0</v>
+      </c>
+      <c r="J1629">
+        <v>0</v>
+      </c>
+      <c r="L1629">
+        <v>0</v>
+      </c>
+      <c r="M1629">
+        <v>0</v>
+      </c>
+      <c r="N1629">
+        <v>0</v>
+      </c>
+      <c r="O1629">
+        <v>0</v>
+      </c>
+      <c r="P1629">
+        <v>0</v>
+      </c>
+      <c r="Q1629">
+        <v>0</v>
+      </c>
+      <c r="R1629">
+        <v>0</v>
+      </c>
+      <c r="S1629">
+        <v>0</v>
+      </c>
+      <c r="T1629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1630" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1630" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1630">
+        <v>1</v>
+      </c>
+      <c r="D1630">
+        <v>0</v>
+      </c>
+      <c r="E1630">
+        <v>0</v>
+      </c>
+      <c r="F1630">
+        <v>0</v>
+      </c>
+      <c r="I1630">
+        <v>0</v>
+      </c>
+      <c r="J1630">
+        <v>0</v>
+      </c>
+      <c r="L1630">
+        <v>0</v>
+      </c>
+      <c r="M1630">
+        <v>0</v>
+      </c>
+      <c r="N1630">
+        <v>0</v>
+      </c>
+      <c r="O1630">
+        <v>0</v>
+      </c>
+      <c r="P1630">
+        <v>0</v>
+      </c>
+      <c r="Q1630">
+        <v>0</v>
+      </c>
+      <c r="R1630">
+        <v>0</v>
+      </c>
+      <c r="S1630">
+        <v>0</v>
+      </c>
+      <c r="T1630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1631" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1631" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1631">
+        <v>1</v>
+      </c>
+      <c r="D1631">
+        <v>1</v>
+      </c>
+      <c r="E1631">
+        <v>0</v>
+      </c>
+      <c r="F1631">
+        <v>25</v>
+      </c>
+      <c r="G1631">
+        <v>25</v>
+      </c>
+      <c r="H1631">
+        <v>25</v>
+      </c>
+      <c r="I1631">
+        <v>0</v>
+      </c>
+      <c r="J1631">
+        <v>0</v>
+      </c>
+      <c r="K1631">
+        <v>86.21</v>
+      </c>
+      <c r="L1631">
+        <v>29</v>
+      </c>
+      <c r="M1631">
+        <v>13</v>
+      </c>
+      <c r="N1631">
+        <v>2</v>
+      </c>
+      <c r="O1631">
+        <v>0</v>
+      </c>
+      <c r="P1631">
+        <v>18.12</v>
+      </c>
+      <c r="Q1631">
+        <v>1</v>
+      </c>
+      <c r="R1631">
+        <v>0</v>
+      </c>
+      <c r="S1631">
+        <v>0</v>
+      </c>
+      <c r="T1631">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1632" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1632" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1632">
+        <v>1</v>
+      </c>
+      <c r="D1632">
+        <v>0</v>
+      </c>
+      <c r="E1632">
+        <v>0</v>
+      </c>
+      <c r="F1632">
+        <v>0</v>
+      </c>
+      <c r="I1632">
+        <v>0</v>
+      </c>
+      <c r="J1632">
+        <v>0</v>
+      </c>
+      <c r="L1632">
+        <v>0</v>
+      </c>
+      <c r="M1632">
+        <v>0</v>
+      </c>
+      <c r="N1632">
+        <v>0</v>
+      </c>
+      <c r="O1632">
+        <v>0</v>
+      </c>
+      <c r="P1632">
+        <v>0</v>
+      </c>
+      <c r="Q1632">
+        <v>0</v>
+      </c>
+      <c r="R1632">
+        <v>0</v>
+      </c>
+      <c r="S1632">
+        <v>0</v>
+      </c>
+      <c r="T1632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1633" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1633" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C1633">
+        <v>1</v>
+      </c>
+      <c r="D1633">
+        <v>1</v>
+      </c>
+      <c r="E1633">
+        <v>1</v>
+      </c>
+      <c r="F1633">
+        <v>31</v>
+      </c>
+      <c r="H1633" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1633">
+        <v>0</v>
+      </c>
+      <c r="J1633">
+        <v>0</v>
+      </c>
+      <c r="K1633">
+        <v>221.43</v>
+      </c>
+      <c r="L1633">
+        <v>14</v>
+      </c>
+      <c r="M1633">
+        <v>5</v>
+      </c>
+      <c r="N1633">
+        <v>5</v>
+      </c>
+      <c r="O1633">
+        <v>1</v>
+      </c>
+      <c r="P1633">
+        <v>22.46</v>
+      </c>
+      <c r="Q1633">
+        <v>1</v>
+      </c>
+      <c r="R1633">
+        <v>0</v>
+      </c>
+      <c r="S1633">
+        <v>0</v>
+      </c>
+      <c r="T1633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1634" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1634" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C1634">
+        <v>1</v>
+      </c>
+      <c r="D1634">
+        <v>1</v>
+      </c>
+      <c r="E1634">
+        <v>1</v>
+      </c>
+      <c r="F1634">
+        <v>13</v>
+      </c>
+      <c r="H1634" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1634">
+        <v>0</v>
+      </c>
+      <c r="J1634">
+        <v>0</v>
+      </c>
+      <c r="K1634">
+        <v>61.9</v>
+      </c>
+      <c r="L1634">
+        <v>21</v>
+      </c>
+      <c r="M1634">
+        <v>11</v>
+      </c>
+      <c r="N1634">
+        <v>1</v>
+      </c>
+      <c r="O1634">
+        <v>0</v>
+      </c>
+      <c r="P1634">
+        <v>9.42</v>
+      </c>
+      <c r="Q1634">
+        <v>0</v>
+      </c>
+      <c r="R1634">
+        <v>0</v>
+      </c>
+      <c r="S1634">
+        <v>0</v>
+      </c>
+      <c r="T1634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1635" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1635" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C1635">
+        <v>1</v>
+      </c>
+      <c r="D1635">
+        <v>0</v>
+      </c>
+      <c r="E1635">
+        <v>0</v>
+      </c>
+      <c r="F1635">
+        <v>0</v>
+      </c>
+      <c r="I1635">
+        <v>0</v>
+      </c>
+      <c r="J1635">
+        <v>0</v>
+      </c>
+      <c r="L1635">
+        <v>0</v>
+      </c>
+      <c r="M1635">
+        <v>0</v>
+      </c>
+      <c r="N1635">
+        <v>0</v>
+      </c>
+      <c r="O1635">
+        <v>0</v>
+      </c>
+      <c r="P1635">
+        <v>0</v>
+      </c>
+      <c r="Q1635">
+        <v>0</v>
+      </c>
+      <c r="R1635">
+        <v>0</v>
+      </c>
+      <c r="S1635">
+        <v>0</v>
+      </c>
+      <c r="T1635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1636" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1636" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1636">
+        <v>1</v>
+      </c>
+      <c r="D1636">
+        <v>1</v>
+      </c>
+      <c r="E1636">
+        <v>0</v>
+      </c>
+      <c r="F1636">
+        <v>1</v>
+      </c>
+      <c r="G1636">
+        <v>1</v>
+      </c>
+      <c r="H1636">
+        <v>1</v>
+      </c>
+      <c r="I1636">
+        <v>0</v>
+      </c>
+      <c r="J1636">
+        <v>0</v>
+      </c>
+      <c r="K1636">
+        <v>50</v>
+      </c>
+      <c r="L1636">
+        <v>2</v>
+      </c>
+      <c r="M1636">
+        <v>1</v>
+      </c>
+      <c r="N1636">
+        <v>0</v>
+      </c>
+      <c r="O1636">
+        <v>0</v>
+      </c>
+      <c r="P1636">
+        <v>0.74</v>
+      </c>
+      <c r="Q1636">
+        <v>0</v>
+      </c>
+      <c r="R1636">
+        <v>0</v>
+      </c>
+      <c r="S1636">
+        <v>0</v>
+      </c>
+      <c r="T1636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1637" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1637" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1637">
+        <v>1</v>
+      </c>
+      <c r="D1637">
+        <v>1</v>
+      </c>
+      <c r="E1637">
+        <v>0</v>
+      </c>
+      <c r="F1637">
+        <v>9</v>
+      </c>
+      <c r="G1637">
+        <v>9</v>
+      </c>
+      <c r="H1637">
+        <v>9</v>
+      </c>
+      <c r="I1637">
+        <v>0</v>
+      </c>
+      <c r="J1637">
+        <v>0</v>
+      </c>
+      <c r="K1637">
+        <v>47.37</v>
+      </c>
+      <c r="L1637">
+        <v>19</v>
+      </c>
+      <c r="M1637">
+        <v>14</v>
+      </c>
+      <c r="N1637">
+        <v>1</v>
+      </c>
+      <c r="O1637">
+        <v>0</v>
+      </c>
+      <c r="P1637">
+        <v>6.62</v>
+      </c>
+      <c r="Q1637">
+        <v>0</v>
+      </c>
+      <c r="R1637">
+        <v>0</v>
+      </c>
+      <c r="S1637">
+        <v>0</v>
+      </c>
+      <c r="T1637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1638" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1638" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="C1638">
+        <v>1</v>
+      </c>
+      <c r="D1638">
+        <v>1</v>
+      </c>
+      <c r="E1638">
+        <v>1</v>
+      </c>
+      <c r="F1638">
+        <v>7</v>
+      </c>
+      <c r="H1638" t="s">
+        <v>316</v>
+      </c>
+      <c r="I1638">
+        <v>0</v>
+      </c>
+      <c r="J1638">
+        <v>0</v>
+      </c>
+      <c r="K1638">
+        <v>77.78</v>
+      </c>
+      <c r="L1638">
+        <v>9</v>
+      </c>
+      <c r="M1638">
+        <v>5</v>
+      </c>
+      <c r="N1638">
+        <v>1</v>
+      </c>
+      <c r="O1638">
+        <v>0</v>
+      </c>
+      <c r="P1638">
+        <v>5.15</v>
+      </c>
+      <c r="Q1638">
+        <v>0</v>
+      </c>
+      <c r="R1638">
+        <v>0</v>
+      </c>
+      <c r="S1638">
+        <v>0</v>
+      </c>
+      <c r="T1638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1639" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1639" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C1639">
+        <v>1</v>
+      </c>
+      <c r="D1639">
+        <v>1</v>
+      </c>
+      <c r="E1639">
+        <v>0</v>
+      </c>
+      <c r="F1639">
+        <v>6</v>
+      </c>
+      <c r="G1639">
+        <v>6</v>
+      </c>
+      <c r="H1639">
+        <v>6</v>
+      </c>
+      <c r="I1639">
+        <v>0</v>
+      </c>
+      <c r="J1639">
+        <v>0</v>
+      </c>
+      <c r="K1639">
+        <v>85.71</v>
+      </c>
+      <c r="L1639">
+        <v>7</v>
+      </c>
+      <c r="M1639">
+        <v>4</v>
+      </c>
+      <c r="N1639">
+        <v>1</v>
+      </c>
+      <c r="O1639">
+        <v>0</v>
+      </c>
+      <c r="P1639">
+        <v>4.41</v>
+      </c>
+      <c r="Q1639">
+        <v>0</v>
+      </c>
+      <c r="R1639">
+        <v>0</v>
+      </c>
+      <c r="S1639">
+        <v>0</v>
+      </c>
+      <c r="T1639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1640" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1640" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C1640">
+        <v>1</v>
+      </c>
+      <c r="D1640">
+        <v>1</v>
+      </c>
+      <c r="E1640">
+        <v>0</v>
+      </c>
+      <c r="F1640">
+        <v>0</v>
+      </c>
+      <c r="G1640">
+        <v>0</v>
+      </c>
+      <c r="H1640">
+        <v>0</v>
+      </c>
+      <c r="I1640">
+        <v>0</v>
+      </c>
+      <c r="J1640">
+        <v>0</v>
+      </c>
+      <c r="K1640">
+        <v>0</v>
+      </c>
+      <c r="L1640">
+        <v>5</v>
+      </c>
+      <c r="M1640">
+        <v>5</v>
+      </c>
+      <c r="N1640">
+        <v>0</v>
+      </c>
+      <c r="O1640">
+        <v>0</v>
+      </c>
+      <c r="P1640">
+        <v>0</v>
+      </c>
+      <c r="Q1640">
+        <v>0</v>
+      </c>
+      <c r="R1640">
+        <v>0</v>
+      </c>
+      <c r="S1640">
+        <v>0</v>
+      </c>
+      <c r="T1640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1641" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1641" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1641">
+        <v>1</v>
+      </c>
+      <c r="D1641">
+        <v>1</v>
+      </c>
+      <c r="E1641">
+        <v>1</v>
+      </c>
+      <c r="F1641">
+        <v>16</v>
+      </c>
+      <c r="H1641" t="s">
+        <v>283</v>
+      </c>
+      <c r="I1641">
+        <v>0</v>
+      </c>
+      <c r="J1641">
+        <v>0</v>
+      </c>
+      <c r="K1641">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1641">
+        <v>12</v>
+      </c>
+      <c r="M1641">
+        <v>5</v>
+      </c>
+      <c r="N1641">
+        <v>3</v>
+      </c>
+      <c r="O1641">
+        <v>0</v>
+      </c>
+      <c r="P1641">
+        <v>11.59</v>
+      </c>
+      <c r="Q1641">
+        <v>0</v>
+      </c>
+      <c r="R1641">
+        <v>0</v>
+      </c>
+      <c r="S1641">
+        <v>0</v>
+      </c>
+      <c r="T1641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1642" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1642" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1642">
+        <v>1</v>
+      </c>
+      <c r="D1642">
+        <v>1</v>
+      </c>
+      <c r="E1642">
+        <v>0</v>
+      </c>
+      <c r="F1642">
+        <v>20</v>
+      </c>
+      <c r="G1642">
+        <v>20</v>
+      </c>
+      <c r="H1642">
+        <v>20</v>
+      </c>
+      <c r="I1642">
+        <v>0</v>
+      </c>
+      <c r="J1642">
+        <v>0</v>
+      </c>
+      <c r="K1642">
+        <v>95.24</v>
+      </c>
+      <c r="L1642">
+        <v>21</v>
+      </c>
+      <c r="M1642">
+        <v>7</v>
+      </c>
+      <c r="N1642">
+        <v>2</v>
+      </c>
+      <c r="O1642">
+        <v>0</v>
+      </c>
+      <c r="P1642">
+        <v>14.71</v>
+      </c>
+      <c r="Q1642">
+        <v>0</v>
+      </c>
+      <c r="R1642">
+        <v>0</v>
+      </c>
+      <c r="S1642">
+        <v>0</v>
+      </c>
+      <c r="T1642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1643" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1643" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C1643">
+        <v>1</v>
+      </c>
+      <c r="D1643">
+        <v>1</v>
+      </c>
+      <c r="E1643">
+        <v>0</v>
+      </c>
+      <c r="F1643">
+        <v>10</v>
+      </c>
+      <c r="G1643">
+        <v>10</v>
+      </c>
+      <c r="H1643">
+        <v>10</v>
+      </c>
+      <c r="I1643">
+        <v>0</v>
+      </c>
+      <c r="J1643">
+        <v>0</v>
+      </c>
+      <c r="K1643">
+        <v>125</v>
+      </c>
+      <c r="L1643">
+        <v>8</v>
+      </c>
+      <c r="M1643">
+        <v>2</v>
+      </c>
+      <c r="N1643">
+        <v>1</v>
+      </c>
+      <c r="O1643">
+        <v>0</v>
+      </c>
+      <c r="P1643">
+        <v>7.35</v>
+      </c>
+      <c r="Q1643">
+        <v>0</v>
+      </c>
+      <c r="R1643">
+        <v>0</v>
+      </c>
+      <c r="S1643">
+        <v>0</v>
+      </c>
+      <c r="T1643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1644" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1644" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1644">
+        <v>1</v>
+      </c>
+      <c r="D1644">
+        <v>1</v>
+      </c>
+      <c r="E1644">
+        <v>0</v>
+      </c>
+      <c r="F1644">
+        <v>16</v>
+      </c>
+      <c r="G1644">
+        <v>16</v>
+      </c>
+      <c r="H1644">
+        <v>16</v>
+      </c>
+      <c r="I1644">
+        <v>0</v>
+      </c>
+      <c r="J1644">
+        <v>0</v>
+      </c>
+      <c r="K1644">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1644">
+        <v>12</v>
+      </c>
+      <c r="M1644">
+        <v>5</v>
+      </c>
+      <c r="N1644">
+        <v>1</v>
+      </c>
+      <c r="O1644">
+        <v>1</v>
+      </c>
+      <c r="P1644">
+        <v>11.59</v>
+      </c>
+      <c r="Q1644">
+        <v>2</v>
+      </c>
+      <c r="R1644">
+        <v>0</v>
+      </c>
+      <c r="S1644">
+        <v>0</v>
+      </c>
+      <c r="T1644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1645" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1645" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="C1645">
+        <v>1</v>
+      </c>
+      <c r="D1645">
+        <v>1</v>
+      </c>
+      <c r="E1645">
+        <v>0</v>
+      </c>
+      <c r="F1645">
+        <v>0</v>
+      </c>
+      <c r="G1645">
+        <v>0</v>
+      </c>
+      <c r="H1645">
+        <v>0</v>
+      </c>
+      <c r="I1645">
+        <v>0</v>
+      </c>
+      <c r="J1645">
+        <v>0</v>
+      </c>
+      <c r="K1645">
+        <v>0</v>
+      </c>
+      <c r="L1645">
+        <v>2</v>
+      </c>
+      <c r="M1645">
+        <v>2</v>
+      </c>
+      <c r="N1645">
+        <v>0</v>
+      </c>
+      <c r="O1645">
+        <v>0</v>
+      </c>
+      <c r="P1645">
+        <v>0</v>
+      </c>
+      <c r="Q1645">
+        <v>0</v>
+      </c>
+      <c r="R1645">
+        <v>0</v>
+      </c>
+      <c r="S1645">
+        <v>0</v>
+      </c>
+      <c r="T1645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1646" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1646" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1646">
+        <v>1</v>
+      </c>
+      <c r="D1646">
+        <v>1</v>
+      </c>
+      <c r="E1646">
+        <v>0</v>
+      </c>
+      <c r="F1646">
+        <v>26</v>
+      </c>
+      <c r="G1646">
+        <v>26</v>
+      </c>
+      <c r="H1646">
+        <v>26</v>
+      </c>
+      <c r="I1646">
+        <v>0</v>
+      </c>
+      <c r="J1646">
+        <v>0</v>
+      </c>
+      <c r="K1646">
+        <v>100</v>
+      </c>
+      <c r="L1646">
+        <v>26</v>
+      </c>
+      <c r="M1646">
+        <v>9</v>
+      </c>
+      <c r="N1646">
+        <v>2</v>
+      </c>
+      <c r="O1646">
+        <v>0</v>
+      </c>
+      <c r="P1646">
+        <v>19.12</v>
+      </c>
+      <c r="Q1646">
+        <v>0</v>
+      </c>
+      <c r="R1646">
+        <v>0</v>
+      </c>
+      <c r="S1646">
+        <v>0</v>
+      </c>
+      <c r="T1646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1647" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1647" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="C1647">
+        <v>1</v>
+      </c>
+      <c r="D1647">
+        <v>0</v>
+      </c>
+      <c r="E1647">
+        <v>0</v>
+      </c>
+      <c r="F1647">
+        <v>0</v>
+      </c>
+      <c r="I1647">
+        <v>0</v>
+      </c>
+      <c r="J1647">
+        <v>0</v>
+      </c>
+      <c r="L1647">
+        <v>0</v>
+      </c>
+      <c r="M1647">
+        <v>0</v>
+      </c>
+      <c r="N1647">
+        <v>0</v>
+      </c>
+      <c r="O1647">
+        <v>0</v>
+      </c>
+      <c r="P1647">
+        <v>0</v>
+      </c>
+      <c r="Q1647">
+        <v>0</v>
+      </c>
+      <c r="R1647">
+        <v>0</v>
+      </c>
+      <c r="S1647">
+        <v>0</v>
+      </c>
+      <c r="T1647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1648" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1648" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1648">
+        <v>1</v>
+      </c>
+      <c r="D1648">
+        <v>1</v>
+      </c>
+      <c r="E1648">
+        <v>0</v>
+      </c>
+      <c r="F1648">
+        <v>0</v>
+      </c>
+      <c r="G1648">
+        <v>0</v>
+      </c>
+      <c r="H1648">
+        <v>0</v>
+      </c>
+      <c r="I1648">
+        <v>0</v>
+      </c>
+      <c r="J1648">
+        <v>0</v>
+      </c>
+      <c r="K1648">
+        <v>0</v>
+      </c>
+      <c r="L1648">
+        <v>3</v>
+      </c>
+      <c r="M1648">
+        <v>3</v>
+      </c>
+      <c r="N1648">
+        <v>0</v>
+      </c>
+      <c r="O1648">
+        <v>0</v>
+      </c>
+      <c r="P1648">
+        <v>0</v>
+      </c>
+      <c r="Q1648">
+        <v>0</v>
+      </c>
+      <c r="R1648">
+        <v>0</v>
+      </c>
+      <c r="S1648">
+        <v>0</v>
+      </c>
+      <c r="T1648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1649" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1649" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1649">
+        <v>1</v>
+      </c>
+      <c r="D1649">
+        <v>1</v>
+      </c>
+      <c r="E1649">
+        <v>1</v>
+      </c>
+      <c r="F1649">
+        <v>33</v>
+      </c>
+      <c r="H1649" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1649">
+        <v>0</v>
+      </c>
+      <c r="J1649">
+        <v>0</v>
+      </c>
+      <c r="K1649">
+        <v>157.13999999999999</v>
+      </c>
+      <c r="L1649">
+        <v>21</v>
+      </c>
+      <c r="M1649">
+        <v>9</v>
+      </c>
+      <c r="N1649">
+        <v>5</v>
+      </c>
+      <c r="O1649">
+        <v>1</v>
+      </c>
+      <c r="P1649">
+        <v>24.26</v>
+      </c>
+      <c r="Q1649">
+        <v>0</v>
+      </c>
+      <c r="R1649">
+        <v>0</v>
+      </c>
+      <c r="S1649">
+        <v>0</v>
+      </c>
+      <c r="T1649">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B1650" s="1"/>
+    </row>
+    <row r="1651" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B1651" s="1"/>
+    </row>
+    <row r="1652" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B1652" s="1"/>
+    </row>
+    <row r="1653" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B1653" s="1"/>
+    </row>
+    <row r="1654" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B1654" s="1"/>
+    </row>
+    <row r="1655" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B1655" s="1"/>
+    </row>
   </sheetData>
+  <sortState ref="A1628:T1656">
+    <sortCondition ref="B1628:B1656"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/NV Play Midweek League batting stats for season.xlsx
+++ b/NV Play Midweek League batting stats for season.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="20260529-000138-batting-stats-g" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="718">
   <si>
     <t>Group</t>
   </si>
@@ -1869,9 +1869,6 @@
     <t>Mahesh Maniyan Baby</t>
   </si>
   <si>
-    <t>Pawan Thakur</t>
-  </si>
-  <si>
     <t>Belfast Superkings MW XI v PSNI MW XI, TBC - 2 July 2026</t>
   </si>
   <si>
@@ -1975,9 +1972,6 @@
   </si>
   <si>
     <t>Muckamore MW2 XI v Arches MW XI, Moylena - 8 July 2026</t>
-  </si>
-  <si>
-    <t>Pavan Kumar</t>
   </si>
   <si>
     <t>Rohan Labade</t>
@@ -2088,9 +2082,6 @@
     <t>Aryan Thakur</t>
   </si>
   <si>
-    <t>Pavan Thakur</t>
-  </si>
-  <si>
     <t>Robin Varkey</t>
   </si>
   <si>
@@ -2179,6 +2170,9 @@
   </si>
   <si>
     <t>Joshy Thomas</t>
+  </si>
+  <si>
+    <t>Pawan Kumar</t>
   </si>
 </sst>
 </file>
@@ -14226,7 +14220,7 @@
         <v>198</v>
       </c>
       <c r="B188" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -58033,7 +58027,7 @@
         <v>542</v>
       </c>
       <c r="B919" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C919">
         <v>1</v>
@@ -59665,7 +59659,7 @@
         <v>546</v>
       </c>
       <c r="B946" t="s">
-        <v>616</v>
+        <v>717</v>
       </c>
       <c r="C946">
         <v>1</v>
@@ -67667,7 +67661,7 @@
     </row>
     <row r="1080" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1080" t="s">
         <v>441</v>
@@ -67732,7 +67726,7 @@
     </row>
     <row r="1081" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1081" t="s">
         <v>218</v>
@@ -67794,7 +67788,7 @@
     </row>
     <row r="1082" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1082" t="s">
         <v>222</v>
@@ -67853,7 +67847,7 @@
     </row>
     <row r="1083" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1083" t="s">
         <v>23</v>
@@ -67918,7 +67912,7 @@
     </row>
     <row r="1084" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1084" t="s">
         <v>24</v>
@@ -67977,7 +67971,7 @@
     </row>
     <row r="1085" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1085" t="s">
         <v>339</v>
@@ -68039,7 +68033,7 @@
     </row>
     <row r="1086" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1086" t="s">
         <v>26</v>
@@ -68101,7 +68095,7 @@
     </row>
     <row r="1087" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1087" t="s">
         <v>31</v>
@@ -68163,10 +68157,10 @@
     </row>
     <row r="1088" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1088" t="s">
         <v>617</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>618</v>
       </c>
       <c r="C1088">
         <v>1</v>
@@ -68225,7 +68219,7 @@
     </row>
     <row r="1089" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1089" t="s">
         <v>522</v>
@@ -68278,7 +68272,7 @@
     </row>
     <row r="1090" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1090" t="s">
         <v>32</v>
@@ -68340,7 +68334,7 @@
     </row>
     <row r="1091" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1091" t="s">
         <v>36</v>
@@ -68405,7 +68399,7 @@
     </row>
     <row r="1092" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1092" t="s">
         <v>37</v>
@@ -68458,7 +68452,7 @@
     </row>
     <row r="1093" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1093" t="s">
         <v>523</v>
@@ -68520,7 +68514,7 @@
     </row>
     <row r="1094" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1094" t="s">
         <v>524</v>
@@ -68576,10 +68570,10 @@
     </row>
     <row r="1095" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1095" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C1095">
         <v>1</v>
@@ -68641,10 +68635,10 @@
     </row>
     <row r="1096" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1096" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C1096">
         <v>1</v>
@@ -68694,7 +68688,7 @@
     </row>
     <row r="1097" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1097" t="s">
         <v>526</v>
@@ -68756,7 +68750,7 @@
     </row>
     <row r="1098" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1098" t="s">
         <v>437</v>
@@ -68812,7 +68806,7 @@
     </row>
     <row r="1099" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1099" t="s">
         <v>565</v>
@@ -68871,7 +68865,7 @@
     </row>
     <row r="1100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1100" t="s">
         <v>527</v>
@@ -68924,7 +68918,7 @@
     </row>
     <row r="1101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B1101" t="s">
         <v>575</v>
@@ -70948,7 +70942,7 @@
         <v>600</v>
       </c>
       <c r="B1135" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C1135">
         <v>1</v>
@@ -71063,7 +71057,7 @@
         <v>600</v>
       </c>
       <c r="B1137" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C1137">
         <v>1</v>
@@ -71972,7 +71966,7 @@
         <v>603</v>
       </c>
       <c r="B1152" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C1152">
         <v>1</v>
@@ -72928,7 +72922,7 @@
     </row>
     <row r="1168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1168" t="s">
         <v>469</v>
@@ -72990,7 +72984,7 @@
     </row>
     <row r="1169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1169" t="s">
         <v>135</v>
@@ -73049,7 +73043,7 @@
     </row>
     <row r="1170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1170" t="s">
         <v>518</v>
@@ -73108,7 +73102,7 @@
     </row>
     <row r="1171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1171" t="s">
         <v>302</v>
@@ -73170,7 +73164,7 @@
     </row>
     <row r="1172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1172" t="s">
         <v>50</v>
@@ -73232,10 +73226,10 @@
     </row>
     <row r="1173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
+        <v>622</v>
+      </c>
+      <c r="B1173" t="s">
         <v>623</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>624</v>
       </c>
       <c r="C1173">
         <v>1</v>
@@ -73294,7 +73288,7 @@
     </row>
     <row r="1174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1174" t="s">
         <v>56</v>
@@ -73347,7 +73341,7 @@
     </row>
     <row r="1175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1175" t="s">
         <v>439</v>
@@ -73406,7 +73400,7 @@
     </row>
     <row r="1176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1176" t="s">
         <v>460</v>
@@ -73468,7 +73462,7 @@
     </row>
     <row r="1177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1177" t="s">
         <v>533</v>
@@ -73530,7 +73524,7 @@
     </row>
     <row r="1178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1178" t="s">
         <v>304</v>
@@ -73592,10 +73586,10 @@
     </row>
     <row r="1179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1179" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C1179">
         <v>1</v>
@@ -73654,7 +73648,7 @@
     </row>
     <row r="1180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1180" t="s">
         <v>305</v>
@@ -73716,7 +73710,7 @@
     </row>
     <row r="1181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1181" t="s">
         <v>148</v>
@@ -73778,7 +73772,7 @@
     </row>
     <row r="1182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1182" t="s">
         <v>308</v>
@@ -73840,7 +73834,7 @@
     </row>
     <row r="1183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1183" t="s">
         <v>568</v>
@@ -73899,7 +73893,7 @@
     </row>
     <row r="1184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1184" t="s">
         <v>488</v>
@@ -73961,7 +73955,7 @@
     </row>
     <row r="1185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1185" t="s">
         <v>462</v>
@@ -74020,7 +74014,7 @@
     </row>
     <row r="1186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1186" t="s">
         <v>476</v>
@@ -74082,7 +74076,7 @@
     </row>
     <row r="1187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1187" t="s">
         <v>599</v>
@@ -74135,7 +74129,7 @@
     </row>
     <row r="1188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1188" t="s">
         <v>61</v>
@@ -74197,7 +74191,7 @@
     </row>
     <row r="1189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B1189" t="s">
         <v>151</v>
@@ -74259,7 +74253,7 @@
     </row>
     <row r="1190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1190" t="s">
         <v>382</v>
@@ -74321,10 +74315,10 @@
     </row>
     <row r="1191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
+        <v>625</v>
+      </c>
+      <c r="B1191" t="s">
         <v>626</v>
-      </c>
-      <c r="B1191" t="s">
-        <v>627</v>
       </c>
       <c r="C1191">
         <v>1</v>
@@ -74383,7 +74377,7 @@
     </row>
     <row r="1192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1192" t="s">
         <v>312</v>
@@ -74445,7 +74439,7 @@
     </row>
     <row r="1193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1193" t="s">
         <v>46</v>
@@ -74504,7 +74498,7 @@
     </row>
     <row r="1194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1194" t="s">
         <v>384</v>
@@ -74563,10 +74557,10 @@
     </row>
     <row r="1195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1195" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C1195">
         <v>1</v>
@@ -74625,7 +74619,7 @@
     </row>
     <row r="1196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1196" t="s">
         <v>303</v>
@@ -74687,7 +74681,7 @@
     </row>
     <row r="1197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1197" t="s">
         <v>315</v>
@@ -74749,7 +74743,7 @@
     </row>
     <row r="1198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1198" t="s">
         <v>615</v>
@@ -74802,7 +74796,7 @@
     </row>
     <row r="1199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1199" t="s">
         <v>317</v>
@@ -74864,7 +74858,7 @@
     </row>
     <row r="1200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1200" t="s">
         <v>495</v>
@@ -74926,7 +74920,7 @@
     </row>
     <row r="1201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1201" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1201" t="s">
         <v>306</v>
@@ -74985,7 +74979,7 @@
     </row>
     <row r="1202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1202" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1202" t="s">
         <v>60</v>
@@ -75044,10 +75038,10 @@
     </row>
     <row r="1203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1203" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C1203">
         <v>1</v>
@@ -75106,10 +75100,10 @@
     </row>
     <row r="1204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1204" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C1204">
         <v>1</v>
@@ -75168,7 +75162,7 @@
     </row>
     <row r="1205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1205" t="s">
         <v>389</v>
@@ -75230,7 +75224,7 @@
     </row>
     <row r="1206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1206" t="s">
         <v>322</v>
@@ -75292,10 +75286,10 @@
     </row>
     <row r="1207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1207" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C1207">
         <v>1</v>
@@ -75354,7 +75348,7 @@
     </row>
     <row r="1208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1208" t="s">
         <v>64</v>
@@ -75416,7 +75410,7 @@
     </row>
     <row r="1209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1209" t="s">
         <v>65</v>
@@ -75475,10 +75469,10 @@
     </row>
     <row r="1210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1210" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1210" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C1210">
         <v>1</v>
@@ -75537,7 +75531,7 @@
     </row>
     <row r="1211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1211" t="s">
         <v>311</v>
@@ -75599,7 +75593,7 @@
     </row>
     <row r="1212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1212" t="s">
         <v>441</v>
@@ -75661,7 +75655,7 @@
     </row>
     <row r="1213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1213" t="s">
         <v>23</v>
@@ -75723,7 +75717,7 @@
     </row>
     <row r="1214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1214" t="s">
         <v>161</v>
@@ -75785,7 +75779,7 @@
     </row>
     <row r="1215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1215" t="s">
         <v>24</v>
@@ -75847,7 +75841,7 @@
     </row>
     <row r="1216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1216" t="s">
         <v>339</v>
@@ -75909,7 +75903,7 @@
     </row>
     <row r="1217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1217" t="s">
         <v>26</v>
@@ -75971,7 +75965,7 @@
     </row>
     <row r="1218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1218" t="s">
         <v>31</v>
@@ -76033,7 +76027,7 @@
     </row>
     <row r="1219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1219" t="s">
         <v>228</v>
@@ -76092,10 +76086,10 @@
     </row>
     <row r="1220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
+        <v>632</v>
+      </c>
+      <c r="B1220" t="s">
         <v>633</v>
-      </c>
-      <c r="B1220" t="s">
-        <v>634</v>
       </c>
       <c r="C1220">
         <v>1</v>
@@ -76151,7 +76145,7 @@
     </row>
     <row r="1221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1221" t="s">
         <v>230</v>
@@ -76213,7 +76207,7 @@
     </row>
     <row r="1222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1222" t="s">
         <v>231</v>
@@ -76275,7 +76269,7 @@
     </row>
     <row r="1223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1223" t="s">
         <v>232</v>
@@ -76337,7 +76331,7 @@
     </row>
     <row r="1224" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1224" t="s">
         <v>554</v>
@@ -76390,7 +76384,7 @@
     </row>
     <row r="1225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1225" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1225" t="s">
         <v>32</v>
@@ -76452,7 +76446,7 @@
     </row>
     <row r="1226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1226" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1226" t="s">
         <v>34</v>
@@ -76511,7 +76505,7 @@
     </row>
     <row r="1227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1227" t="s">
         <v>235</v>
@@ -76573,7 +76567,7 @@
     </row>
     <row r="1228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1228" t="s">
         <v>36</v>
@@ -76632,10 +76626,10 @@
     </row>
     <row r="1229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1229" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1229" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C1229">
         <v>1</v>
@@ -76685,7 +76679,7 @@
     </row>
     <row r="1230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1230" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1230" t="s">
         <v>239</v>
@@ -76744,7 +76738,7 @@
     </row>
     <row r="1231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1231" t="s">
         <v>480</v>
@@ -76806,10 +76800,10 @@
     </row>
     <row r="1232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1232" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C1232">
         <v>1</v>
@@ -76868,7 +76862,7 @@
     </row>
     <row r="1233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1233" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1233" t="s">
         <v>134</v>
@@ -76930,10 +76924,10 @@
     </row>
     <row r="1234" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1234" t="s">
+        <v>636</v>
+      </c>
+      <c r="B1234" t="s">
         <v>637</v>
-      </c>
-      <c r="B1234" t="s">
-        <v>638</v>
       </c>
       <c r="C1234">
         <v>1</v>
@@ -76983,7 +76977,7 @@
     </row>
     <row r="1235" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1235" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1235" t="s">
         <v>583</v>
@@ -77045,7 +77039,7 @@
     </row>
     <row r="1236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1236" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1236" t="s">
         <v>71</v>
@@ -77107,7 +77101,7 @@
     </row>
     <row r="1237" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1237" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1237" t="s">
         <v>138</v>
@@ -77169,7 +77163,7 @@
     </row>
     <row r="1238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1238" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1238" t="s">
         <v>72</v>
@@ -77228,7 +77222,7 @@
     </row>
     <row r="1239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1239" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1239" t="s">
         <v>434</v>
@@ -77290,7 +77284,7 @@
     </row>
     <row r="1240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1240" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1240" t="s">
         <v>140</v>
@@ -77352,7 +77346,7 @@
     </row>
     <row r="1241" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1241" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1241" t="s">
         <v>78</v>
@@ -77414,10 +77408,10 @@
     </row>
     <row r="1242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1242" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1242" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C1242">
         <v>1</v>
@@ -77473,10 +77467,10 @@
     </row>
     <row r="1243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1243" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1243" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C1243">
         <v>1</v>
@@ -77526,7 +77520,7 @@
     </row>
     <row r="1244" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1244" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1244" t="s">
         <v>144</v>
@@ -77585,10 +77579,10 @@
     </row>
     <row r="1245" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1245" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1245" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C1245">
         <v>1</v>
@@ -77647,7 +77641,7 @@
     </row>
     <row r="1246" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1246" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1246" t="s">
         <v>175</v>
@@ -77706,7 +77700,7 @@
     </row>
     <row r="1247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1247" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1247" t="s">
         <v>247</v>
@@ -77768,7 +77762,7 @@
     </row>
     <row r="1248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1248" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1248" t="s">
         <v>42</v>
@@ -77821,7 +77815,7 @@
     </row>
     <row r="1249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1249" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1249" t="s">
         <v>288</v>
@@ -77874,10 +77868,10 @@
     </row>
     <row r="1250" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1250" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1250" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C1250">
         <v>1</v>
@@ -77936,7 +77930,7 @@
     </row>
     <row r="1251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1251" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1251" t="s">
         <v>154</v>
@@ -77998,10 +77992,10 @@
     </row>
     <row r="1252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1252" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1252" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C1252">
         <v>1</v>
@@ -78051,7 +78045,7 @@
     </row>
     <row r="1253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1253" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1253" t="s">
         <v>585</v>
@@ -78110,7 +78104,7 @@
     </row>
     <row r="1254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1254" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B1254" t="s">
         <v>289</v>
@@ -78172,7 +78166,7 @@
     </row>
     <row r="1255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1255" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1255" t="s">
         <v>22</v>
@@ -78231,10 +78225,10 @@
     </row>
     <row r="1256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1256" t="s">
+        <v>643</v>
+      </c>
+      <c r="B1256" t="s">
         <v>644</v>
-      </c>
-      <c r="B1256" t="s">
-        <v>645</v>
       </c>
       <c r="C1256">
         <v>1</v>
@@ -78293,7 +78287,7 @@
     </row>
     <row r="1257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1257" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1257" t="s">
         <v>252</v>
@@ -78352,7 +78346,7 @@
     </row>
     <row r="1258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1258" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1258" t="s">
         <v>254</v>
@@ -78411,7 +78405,7 @@
     </row>
     <row r="1259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1259" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1259" t="s">
         <v>206</v>
@@ -78464,7 +78458,7 @@
     </row>
     <row r="1260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1260" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1260" t="s">
         <v>378</v>
@@ -78526,7 +78520,7 @@
     </row>
     <row r="1261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1261" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1261" t="s">
         <v>294</v>
@@ -78579,10 +78573,10 @@
     </row>
     <row r="1262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1262" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1262" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C1262">
         <v>1</v>
@@ -78638,10 +78632,10 @@
     </row>
     <row r="1263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1263" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1263" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C1263">
         <v>1</v>
@@ -78700,10 +78694,10 @@
     </row>
     <row r="1264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1264" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1264" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C1264">
         <v>1</v>
@@ -78759,7 +78753,7 @@
     </row>
     <row r="1265" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1265" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1265" t="s">
         <v>427</v>
@@ -78812,7 +78806,7 @@
     </row>
     <row r="1266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1266" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1266" t="s">
         <v>245</v>
@@ -78874,7 +78868,7 @@
     </row>
     <row r="1267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1267" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1267" t="s">
         <v>379</v>
@@ -78933,7 +78927,7 @@
     </row>
     <row r="1268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1268" t="s">
         <v>210</v>
@@ -78995,10 +78989,10 @@
     </row>
     <row r="1269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1269" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1269" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C1269">
         <v>1</v>
@@ -79057,7 +79051,7 @@
     </row>
     <row r="1270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1270" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1270" t="s">
         <v>38</v>
@@ -79119,10 +79113,10 @@
     </row>
     <row r="1271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1271" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1271" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C1271">
         <v>1</v>
@@ -79181,10 +79175,10 @@
     </row>
     <row r="1272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1272" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C1272">
         <v>1</v>
@@ -79243,7 +79237,7 @@
     </row>
     <row r="1273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1273" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1273" t="s">
         <v>297</v>
@@ -79296,7 +79290,7 @@
     </row>
     <row r="1274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1274" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1274" t="s">
         <v>43</v>
@@ -79358,7 +79352,7 @@
     </row>
     <row r="1275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1275" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B1275" t="s">
         <v>298</v>
@@ -79420,7 +79414,7 @@
     </row>
     <row r="1276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1276" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1276" t="s">
         <v>249</v>
@@ -79482,7 +79476,7 @@
     </row>
     <row r="1277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1277" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1277" t="s">
         <v>163</v>
@@ -79535,7 +79529,7 @@
     </row>
     <row r="1278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1278" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1278" t="s">
         <v>251</v>
@@ -79594,7 +79588,7 @@
     </row>
     <row r="1279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1279" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1279" t="s">
         <v>253</v>
@@ -79653,7 +79647,7 @@
     </row>
     <row r="1280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1280" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1280" t="s">
         <v>370</v>
@@ -79715,10 +79709,10 @@
     </row>
     <row r="1281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1281" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1281" t="s">
-        <v>652</v>
+        <v>717</v>
       </c>
       <c r="C1281">
         <v>1</v>
@@ -79771,10 +79765,10 @@
     </row>
     <row r="1282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1282" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1282" t="s">
         <v>651</v>
-      </c>
-      <c r="B1282" t="s">
-        <v>653</v>
       </c>
       <c r="C1282">
         <v>1</v>
@@ -79830,7 +79824,7 @@
     </row>
     <row r="1283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1283" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1283" t="s">
         <v>256</v>
@@ -79892,7 +79886,7 @@
     </row>
     <row r="1284" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1284" t="s">
         <v>452</v>
@@ -79951,7 +79945,7 @@
     </row>
     <row r="1285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1285" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1285" t="s">
         <v>258</v>
@@ -80013,7 +80007,7 @@
     </row>
     <row r="1286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1286" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1286" t="s">
         <v>259</v>
@@ -80075,7 +80069,7 @@
     </row>
     <row r="1287" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1287" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1287" t="s">
         <v>171</v>
@@ -80137,7 +80131,7 @@
     </row>
     <row r="1288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1288" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1288" t="s">
         <v>173</v>
@@ -80199,7 +80193,7 @@
     </row>
     <row r="1289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1289" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1289" t="s">
         <v>262</v>
@@ -80261,7 +80255,7 @@
     </row>
     <row r="1290" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1290" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1290" t="s">
         <v>263</v>
@@ -80314,7 +80308,7 @@
     </row>
     <row r="1291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1291" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1291" t="s">
         <v>176</v>
@@ -80373,7 +80367,7 @@
     </row>
     <row r="1292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1292" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1292" t="s">
         <v>178</v>
@@ -80426,7 +80420,7 @@
     </row>
     <row r="1293" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1293" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1293" t="s">
         <v>265</v>
@@ -80488,7 +80482,7 @@
     </row>
     <row r="1294" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1294" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1294" t="s">
         <v>180</v>
@@ -80541,7 +80535,7 @@
     </row>
     <row r="1295" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1295" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1295" t="s">
         <v>421</v>
@@ -80594,10 +80588,10 @@
     </row>
     <row r="1296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1296" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1296" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C1296">
         <v>1</v>
@@ -80656,7 +80650,7 @@
     </row>
     <row r="1297" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1297" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B1297" t="s">
         <v>512</v>
@@ -80709,7 +80703,7 @@
     </row>
     <row r="1298" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1298" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1298" t="s">
         <v>135</v>
@@ -80762,7 +80756,7 @@
     </row>
     <row r="1299" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1299" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1299" t="s">
         <v>160</v>
@@ -80821,10 +80815,10 @@
     </row>
     <row r="1300" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1300" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1300" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C1300">
         <v>1</v>
@@ -80880,7 +80874,7 @@
     </row>
     <row r="1301" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1301" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1301" t="s">
         <v>163</v>
@@ -80942,7 +80936,7 @@
     </row>
     <row r="1302" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1302" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1302" t="s">
         <v>142</v>
@@ -81001,7 +80995,7 @@
     </row>
     <row r="1303" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1303" t="s">
         <v>421</v>
@@ -81063,10 +81057,10 @@
     </row>
     <row r="1304" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1304" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1304" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C1304">
         <v>1</v>
@@ -81125,10 +81119,10 @@
     </row>
     <row r="1305" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1305" t="s">
+        <v>653</v>
+      </c>
+      <c r="B1305" t="s">
         <v>655</v>
-      </c>
-      <c r="B1305" t="s">
-        <v>657</v>
       </c>
       <c r="C1305">
         <v>1</v>
@@ -81184,7 +81178,7 @@
     </row>
     <row r="1306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1306" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1306" t="s">
         <v>147</v>
@@ -81243,7 +81237,7 @@
     </row>
     <row r="1307" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1307" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1307" t="s">
         <v>171</v>
@@ -81305,7 +81299,7 @@
     </row>
     <row r="1308" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1308" t="s">
         <v>59</v>
@@ -81364,10 +81358,10 @@
     </row>
     <row r="1309" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1309" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1309" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C1309">
         <v>1</v>
@@ -81426,7 +81420,7 @@
     </row>
     <row r="1310" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1310" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1310" t="s">
         <v>173</v>
@@ -81488,7 +81482,7 @@
     </row>
     <row r="1311" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1311" t="s">
         <v>149</v>
@@ -81541,7 +81535,7 @@
     </row>
     <row r="1312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1312" t="s">
         <v>488</v>
@@ -81603,7 +81597,7 @@
     </row>
     <row r="1313" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1313" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1313" t="s">
         <v>176</v>
@@ -81665,7 +81659,7 @@
     </row>
     <row r="1314" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1314" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1314" t="s">
         <v>61</v>
@@ -81718,7 +81712,7 @@
     </row>
     <row r="1315" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1315" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1315" t="s">
         <v>180</v>
@@ -81777,7 +81771,7 @@
     </row>
     <row r="1316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1316" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1316" t="s">
         <v>62</v>
@@ -81839,7 +81833,7 @@
     </row>
     <row r="1317" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1317" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1317" t="s">
         <v>151</v>
@@ -81892,10 +81886,10 @@
     </row>
     <row r="1318" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1318" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C1318">
         <v>1</v>
@@ -81951,7 +81945,7 @@
     </row>
     <row r="1319" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1319" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B1319" t="s">
         <v>156</v>
@@ -82013,7 +82007,7 @@
     </row>
     <row r="1320" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1320" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1320" t="s">
         <v>21</v>
@@ -82075,7 +82069,7 @@
     </row>
     <row r="1321" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1321" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1321" t="s">
         <v>22</v>
@@ -82128,7 +82122,7 @@
     </row>
     <row r="1322" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1322" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1322" t="s">
         <v>202</v>
@@ -82190,10 +82184,10 @@
     </row>
     <row r="1323" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1323" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1323" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C1323">
         <v>1</v>
@@ -82252,7 +82246,7 @@
     </row>
     <row r="1324" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1324" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1324" t="s">
         <v>203</v>
@@ -82314,7 +82308,7 @@
     </row>
     <row r="1325" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1325" t="s">
         <v>341</v>
@@ -82373,7 +82367,7 @@
     </row>
     <row r="1326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1326" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1326" t="s">
         <v>342</v>
@@ -82435,7 +82429,7 @@
     </row>
     <row r="1327" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1327" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1327" t="s">
         <v>140</v>
@@ -82488,10 +82482,10 @@
     </row>
     <row r="1328" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1328" t="s">
+        <v>657</v>
+      </c>
+      <c r="B1328" t="s">
         <v>659</v>
-      </c>
-      <c r="B1328" t="s">
-        <v>661</v>
       </c>
       <c r="C1328">
         <v>1</v>
@@ -82541,7 +82535,7 @@
     </row>
     <row r="1329" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1329" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1329" t="s">
         <v>212</v>
@@ -82603,7 +82597,7 @@
     </row>
     <row r="1330" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1330" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1330" t="s">
         <v>38</v>
@@ -82662,10 +82656,10 @@
     </row>
     <row r="1331" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1331" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1331" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C1331">
         <v>1</v>
@@ -82724,7 +82718,7 @@
     </row>
     <row r="1332" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1332" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1332" t="s">
         <v>213</v>
@@ -82777,7 +82771,7 @@
     </row>
     <row r="1333" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1333" t="s">
         <v>466</v>
@@ -82836,7 +82830,7 @@
     </row>
     <row r="1334" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1334" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1334" t="s">
         <v>175</v>
@@ -82889,7 +82883,7 @@
     </row>
     <row r="1335" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1335" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1335" t="s">
         <v>247</v>
@@ -82948,7 +82942,7 @@
     </row>
     <row r="1336" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1336" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1336" t="s">
         <v>503</v>
@@ -83010,10 +83004,10 @@
     </row>
     <row r="1337" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1337" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1337" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C1337">
         <v>1</v>
@@ -83069,7 +83063,7 @@
     </row>
     <row r="1338" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1338" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1338" t="s">
         <v>216</v>
@@ -83122,7 +83116,7 @@
     </row>
     <row r="1339" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1339" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1339" t="s">
         <v>43</v>
@@ -83175,7 +83169,7 @@
     </row>
     <row r="1340" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1340" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1340" t="s">
         <v>428</v>
@@ -83234,7 +83228,7 @@
     </row>
     <row r="1341" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1341" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B1341" t="s">
         <v>429</v>
@@ -83296,7 +83290,7 @@
     </row>
     <row r="1342" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1342" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1342" t="s">
         <v>218</v>
@@ -83355,7 +83349,7 @@
     </row>
     <row r="1343" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1343" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1343" t="s">
         <v>222</v>
@@ -83417,7 +83411,7 @@
     </row>
     <row r="1344" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1344" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1344" t="s">
         <v>223</v>
@@ -83479,10 +83473,10 @@
     </row>
     <row r="1345" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1345" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1345" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C1345">
         <v>1</v>
@@ -83541,10 +83535,10 @@
     </row>
     <row r="1346" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1346" t="s">
+        <v>662</v>
+      </c>
+      <c r="B1346" t="s">
         <v>664</v>
-      </c>
-      <c r="B1346" t="s">
-        <v>666</v>
       </c>
       <c r="C1346">
         <v>1</v>
@@ -83594,7 +83588,7 @@
     </row>
     <row r="1347" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1347" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1347" t="s">
         <v>120</v>
@@ -83656,7 +83650,7 @@
     </row>
     <row r="1348" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1348" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1348" t="s">
         <v>417</v>
@@ -83718,10 +83712,10 @@
     </row>
     <row r="1349" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1349" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1349" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C1349">
         <v>1</v>
@@ -83777,7 +83771,7 @@
     </row>
     <row r="1350" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1350" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1350" t="s">
         <v>233</v>
@@ -83839,10 +83833,10 @@
     </row>
     <row r="1351" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1351" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1351" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C1351">
         <v>1</v>
@@ -83898,7 +83892,7 @@
     </row>
     <row r="1352" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1352" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1352" t="s">
         <v>124</v>
@@ -83954,7 +83948,7 @@
     </row>
     <row r="1353" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1353" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1353" t="s">
         <v>328</v>
@@ -84016,7 +84010,7 @@
     </row>
     <row r="1354" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1354" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1354" t="s">
         <v>125</v>
@@ -84078,7 +84072,7 @@
     </row>
     <row r="1355" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1355" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1355" t="s">
         <v>329</v>
@@ -84131,10 +84125,10 @@
     </row>
     <row r="1356" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1356" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1356" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C1356">
         <v>1</v>
@@ -84193,7 +84187,7 @@
     </row>
     <row r="1357" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1357" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1357" t="s">
         <v>126</v>
@@ -84252,7 +84246,7 @@
     </row>
     <row r="1358" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1358" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1358" t="s">
         <v>330</v>
@@ -84314,7 +84308,7 @@
     </row>
     <row r="1359" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1359" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1359" t="s">
         <v>523</v>
@@ -84373,7 +84367,7 @@
     </row>
     <row r="1360" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1360" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1360" t="s">
         <v>526</v>
@@ -84432,7 +84426,7 @@
     </row>
     <row r="1361" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1361" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1361" t="s">
         <v>437</v>
@@ -84494,10 +84488,10 @@
     </row>
     <row r="1362" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1362" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1362" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C1362">
         <v>1</v>
@@ -84547,7 +84541,7 @@
     </row>
     <row r="1363" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1363" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B1363" t="s">
         <v>575</v>
@@ -84600,7 +84594,7 @@
     </row>
     <row r="1364" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1364" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1364" t="s">
         <v>382</v>
@@ -84662,7 +84656,7 @@
     </row>
     <row r="1365" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1365" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1365" t="s">
         <v>182</v>
@@ -84724,7 +84718,7 @@
     </row>
     <row r="1366" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1366" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1366" t="s">
         <v>312</v>
@@ -84783,7 +84777,7 @@
     </row>
     <row r="1367" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1367" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1367" t="s">
         <v>183</v>
@@ -84842,7 +84836,7 @@
     </row>
     <row r="1368" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1368" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1368" t="s">
         <v>184</v>
@@ -84904,7 +84898,7 @@
     </row>
     <row r="1369" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1369" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1369" t="s">
         <v>391</v>
@@ -84957,7 +84951,7 @@
     </row>
     <row r="1370" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1370" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1370" t="s">
         <v>185</v>
@@ -85016,7 +85010,7 @@
     </row>
     <row r="1371" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1371" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1371" t="s">
         <v>348</v>
@@ -85078,10 +85072,10 @@
     </row>
     <row r="1372" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1372" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1372" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C1372">
         <v>1</v>
@@ -85140,7 +85134,7 @@
     </row>
     <row r="1373" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1373" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1373" t="s">
         <v>315</v>
@@ -85199,7 +85193,7 @@
     </row>
     <row r="1374" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1374" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1374" t="s">
         <v>189</v>
@@ -85261,7 +85255,7 @@
     </row>
     <row r="1375" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1375" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1375" t="s">
         <v>190</v>
@@ -85323,7 +85317,7 @@
     </row>
     <row r="1376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1376" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1376" t="s">
         <v>317</v>
@@ -85376,7 +85370,7 @@
     </row>
     <row r="1377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1377" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1377" t="s">
         <v>366</v>
@@ -85438,7 +85432,7 @@
     </row>
     <row r="1378" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1378" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1378" t="s">
         <v>318</v>
@@ -85500,10 +85494,10 @@
     </row>
     <row r="1379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1379" t="s">
+        <v>667</v>
+      </c>
+      <c r="B1379" t="s">
         <v>669</v>
-      </c>
-      <c r="B1379" t="s">
-        <v>671</v>
       </c>
       <c r="C1379">
         <v>1</v>
@@ -85562,7 +85556,7 @@
     </row>
     <row r="1380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1380" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1380" t="s">
         <v>388</v>
@@ -85621,7 +85615,7 @@
     </row>
     <row r="1381" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1381" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1381" t="s">
         <v>389</v>
@@ -85680,7 +85674,7 @@
     </row>
     <row r="1382" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1382" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1382" t="s">
         <v>395</v>
@@ -85742,7 +85736,7 @@
     </row>
     <row r="1383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1383" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1383" t="s">
         <v>322</v>
@@ -85795,10 +85789,10 @@
     </row>
     <row r="1384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1384" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1384" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C1384">
         <v>1</v>
@@ -85857,7 +85851,7 @@
     </row>
     <row r="1385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1385" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B1385" t="s">
         <v>396</v>
@@ -85910,7 +85904,7 @@
     </row>
     <row r="1386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1386" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1386" t="s">
         <v>441</v>
@@ -85963,7 +85957,7 @@
     </row>
     <row r="1387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1387" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1387" t="s">
         <v>118</v>
@@ -86025,7 +86019,7 @@
     </row>
     <row r="1388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1388" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1388" t="s">
         <v>375</v>
@@ -86087,7 +86081,7 @@
     </row>
     <row r="1389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1389" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1389" t="s">
         <v>23</v>
@@ -86149,7 +86143,7 @@
     </row>
     <row r="1390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1390" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1390" t="s">
         <v>24</v>
@@ -86211,7 +86205,7 @@
     </row>
     <row r="1391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1391" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1391" t="s">
         <v>339</v>
@@ -86273,7 +86267,7 @@
     </row>
     <row r="1392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1392" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1392" t="s">
         <v>119</v>
@@ -86332,7 +86326,7 @@
     </row>
     <row r="1393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1393" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1393" t="s">
         <v>31</v>
@@ -86394,7 +86388,7 @@
     </row>
     <row r="1394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1394" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1394" t="s">
         <v>123</v>
@@ -86456,7 +86450,7 @@
     </row>
     <row r="1395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1395" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1395" t="s">
         <v>32</v>
@@ -86515,7 +86509,7 @@
     </row>
     <row r="1396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1396" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1396" t="s">
         <v>34</v>
@@ -86574,7 +86568,7 @@
     </row>
     <row r="1397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1397" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1397" t="s">
         <v>343</v>
@@ -86633,10 +86627,10 @@
     </row>
     <row r="1398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1398" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C1398">
         <v>1</v>
@@ -86695,7 +86689,7 @@
     </row>
     <row r="1399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1399" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1399" t="s">
         <v>431</v>
@@ -86757,10 +86751,10 @@
     </row>
     <row r="1400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1400" t="s">
+        <v>675</v>
+      </c>
+      <c r="B1400" t="s">
         <v>677</v>
-      </c>
-      <c r="B1400" t="s">
-        <v>679</v>
       </c>
       <c r="C1400">
         <v>1</v>
@@ -86819,7 +86813,7 @@
     </row>
     <row r="1401" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1401" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1401" t="s">
         <v>128</v>
@@ -86881,10 +86875,10 @@
     </row>
     <row r="1402" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1402" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1402" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C1402">
         <v>1</v>
@@ -86940,7 +86934,7 @@
     </row>
     <row r="1403" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1403" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1403" t="s">
         <v>402</v>
@@ -87002,7 +86996,7 @@
     </row>
     <row r="1404" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1404" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1404" t="s">
         <v>504</v>
@@ -87061,7 +87055,7 @@
     </row>
     <row r="1405" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1405" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1405" t="s">
         <v>480</v>
@@ -87120,10 +87114,10 @@
     </row>
     <row r="1406" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1406" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1406" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C1406">
         <v>1</v>
@@ -87182,7 +87176,7 @@
     </row>
     <row r="1407" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1407" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B1407" t="s">
         <v>44</v>
@@ -87244,7 +87238,7 @@
     </row>
     <row r="1408" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1408" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1408" t="s">
         <v>135</v>
@@ -87303,7 +87297,7 @@
     </row>
     <row r="1409" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1409" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1409" t="s">
         <v>249</v>
@@ -87365,10 +87359,10 @@
     </row>
     <row r="1410" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1410" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1410" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C1410">
         <v>1</v>
@@ -87427,7 +87421,7 @@
     </row>
     <row r="1411" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1411" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1411" t="s">
         <v>251</v>
@@ -87486,7 +87480,7 @@
     </row>
     <row r="1412" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1412" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1412" t="s">
         <v>253</v>
@@ -87548,7 +87542,7 @@
     </row>
     <row r="1413" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1413" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1413" t="s">
         <v>335</v>
@@ -87607,7 +87601,7 @@
     </row>
     <row r="1414" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1414" t="s">
         <v>370</v>
@@ -87666,7 +87660,7 @@
     </row>
     <row r="1415" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1415" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1415" t="s">
         <v>54</v>
@@ -87728,7 +87722,7 @@
     </row>
     <row r="1416" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1416" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1416" t="s">
         <v>256</v>
@@ -87781,7 +87775,7 @@
     </row>
     <row r="1417" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1417" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1417" t="s">
         <v>452</v>
@@ -87840,7 +87834,7 @@
     </row>
     <row r="1418" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1418" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1418" t="s">
         <v>258</v>
@@ -87902,7 +87896,7 @@
     </row>
     <row r="1419" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1419" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1419" t="s">
         <v>259</v>
@@ -87964,7 +87958,7 @@
     </row>
     <row r="1420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1420" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1420" t="s">
         <v>147</v>
@@ -88023,7 +88017,7 @@
     </row>
     <row r="1421" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1421" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1421" t="s">
         <v>262</v>
@@ -88082,7 +88076,7 @@
     </row>
     <row r="1422" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1422" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1422" t="s">
         <v>149</v>
@@ -88135,7 +88129,7 @@
     </row>
     <row r="1423" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1423" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1423" t="s">
         <v>488</v>
@@ -88197,7 +88191,7 @@
     </row>
     <row r="1424" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1424" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1424" t="s">
         <v>263</v>
@@ -88250,7 +88244,7 @@
     </row>
     <row r="1425" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1425" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1425" t="s">
         <v>265</v>
@@ -88312,7 +88306,7 @@
     </row>
     <row r="1426" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1426" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1426" t="s">
         <v>61</v>
@@ -88374,7 +88368,7 @@
     </row>
     <row r="1427" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1427" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1427" t="s">
         <v>62</v>
@@ -88436,7 +88430,7 @@
     </row>
     <row r="1428" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1428" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B1428" t="s">
         <v>151</v>
@@ -88498,10 +88492,10 @@
     </row>
     <row r="1429" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1429" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1429" t="s">
         <v>682</v>
-      </c>
-      <c r="B1429" t="s">
-        <v>684</v>
       </c>
       <c r="C1429">
         <v>1</v>
@@ -88560,7 +88554,7 @@
     </row>
     <row r="1430" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1430" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1430" t="s">
         <v>134</v>
@@ -88619,10 +88613,10 @@
     </row>
     <row r="1431" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1431" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1431" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C1431">
         <v>1</v>
@@ -88672,7 +88666,7 @@
     </row>
     <row r="1432" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1432" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1432" t="s">
         <v>250</v>
@@ -88734,7 +88728,7 @@
     </row>
     <row r="1433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1433" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1433" t="s">
         <v>138</v>
@@ -88796,7 +88790,7 @@
     </row>
     <row r="1434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1434" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1434" t="s">
         <v>163</v>
@@ -88849,7 +88843,7 @@
     </row>
     <row r="1435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1435" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1435" t="s">
         <v>140</v>
@@ -88911,7 +88905,7 @@
     </row>
     <row r="1436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1436" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1436" t="s">
         <v>169</v>
@@ -88964,10 +88958,10 @@
     </row>
     <row r="1437" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1437" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1437" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C1437">
         <v>1</v>
@@ -89026,7 +89020,7 @@
     </row>
     <row r="1438" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1438" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1438" t="s">
         <v>245</v>
@@ -89088,10 +89082,10 @@
     </row>
     <row r="1439" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1439" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1439" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C1439">
         <v>1</v>
@@ -89150,7 +89144,7 @@
     </row>
     <row r="1440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1440" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1440" t="s">
         <v>607</v>
@@ -89212,10 +89206,10 @@
     </row>
     <row r="1441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1441" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1441" t="s">
         <v>685</v>
-      </c>
-      <c r="B1441" t="s">
-        <v>687</v>
       </c>
       <c r="C1441">
         <v>1</v>
@@ -89274,7 +89268,7 @@
     </row>
     <row r="1442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1442" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1442" t="s">
         <v>171</v>
@@ -89336,7 +89330,7 @@
     </row>
     <row r="1443" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1443" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1443" t="s">
         <v>173</v>
@@ -89398,7 +89392,7 @@
     </row>
     <row r="1444" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1444" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1444" t="s">
         <v>176</v>
@@ -89457,7 +89451,7 @@
     </row>
     <row r="1445" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1445" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1445" t="s">
         <v>511</v>
@@ -89510,7 +89504,7 @@
     </row>
     <row r="1446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1446" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1446" t="s">
         <v>42</v>
@@ -89569,7 +89563,7 @@
     </row>
     <row r="1447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1447" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1447" t="s">
         <v>180</v>
@@ -89628,10 +89622,10 @@
     </row>
     <row r="1448" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1448" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1448" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C1448">
         <v>1</v>
@@ -89681,10 +89675,10 @@
     </row>
     <row r="1449" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1449" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1449" t="s">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="C1449">
         <v>1</v>
@@ -89740,7 +89734,7 @@
     </row>
     <row r="1450" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1450" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1450" t="s">
         <v>152</v>
@@ -89802,10 +89796,10 @@
     </row>
     <row r="1451" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1451" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1451" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C1451">
         <v>1</v>
@@ -89864,7 +89858,7 @@
     </row>
     <row r="1452" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1452" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1452" t="s">
         <v>572</v>
@@ -89926,7 +89920,7 @@
     </row>
     <row r="1453" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1453" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1453" t="s">
         <v>412</v>
@@ -89985,7 +89979,7 @@
     </row>
     <row r="1454" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1454" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1454" t="s">
         <v>590</v>
@@ -90044,10 +90038,10 @@
     </row>
     <row r="1455" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1455" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1455" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C1455">
         <v>1</v>
@@ -90106,7 +90100,7 @@
     </row>
     <row r="1456" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1456" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1456" t="s">
         <v>98</v>
@@ -90168,7 +90162,7 @@
     </row>
     <row r="1457" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1457" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1457" t="s">
         <v>482</v>
@@ -90230,7 +90224,7 @@
     </row>
     <row r="1458" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1458" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1458" t="s">
         <v>549</v>
@@ -90289,7 +90283,7 @@
     </row>
     <row r="1459" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1459" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1459" t="s">
         <v>73</v>
@@ -90351,10 +90345,10 @@
     </row>
     <row r="1460" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1460" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1460" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C1460">
         <v>1</v>
@@ -90410,7 +90404,7 @@
     </row>
     <row r="1461" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1461" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1461" t="s">
         <v>465</v>
@@ -90469,7 +90463,7 @@
     </row>
     <row r="1462" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1462" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1462" t="s">
         <v>75</v>
@@ -90522,7 +90516,7 @@
     </row>
     <row r="1463" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1463" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1463" t="s">
         <v>413</v>
@@ -90584,7 +90578,7 @@
     </row>
     <row r="1464" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1464" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1464" t="s">
         <v>551</v>
@@ -90646,7 +90640,7 @@
     </row>
     <row r="1465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1465" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1465" t="s">
         <v>277</v>
@@ -90708,7 +90702,7 @@
     </row>
     <row r="1466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1466" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1466" t="s">
         <v>515</v>
@@ -90770,7 +90764,7 @@
     </row>
     <row r="1467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1467" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1467" t="s">
         <v>278</v>
@@ -90823,7 +90817,7 @@
     </row>
     <row r="1468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1468" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1468" t="s">
         <v>108</v>
@@ -90885,7 +90879,7 @@
     </row>
     <row r="1469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1469" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1469" t="s">
         <v>489</v>
@@ -90944,10 +90938,10 @@
     </row>
     <row r="1470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1470" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1470" t="s">
         <v>691</v>
-      </c>
-      <c r="B1470" t="s">
-        <v>694</v>
       </c>
       <c r="C1470">
         <v>1</v>
@@ -91003,7 +90997,7 @@
     </row>
     <row r="1471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1471" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1471" t="s">
         <v>592</v>
@@ -91065,7 +91059,7 @@
     </row>
     <row r="1472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1472" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1472" t="s">
         <v>110</v>
@@ -91127,7 +91121,7 @@
     </row>
     <row r="1473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1473" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1473" t="s">
         <v>88</v>
@@ -91180,7 +91174,7 @@
     </row>
     <row r="1474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1474" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1474" t="s">
         <v>312</v>
@@ -91239,7 +91233,7 @@
     </row>
     <row r="1475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1475" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1475" t="s">
         <v>594</v>
@@ -91298,10 +91292,10 @@
     </row>
     <row r="1476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1476" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1476" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C1476">
         <v>1</v>
@@ -91360,7 +91354,7 @@
     </row>
     <row r="1477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1477" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1477" t="s">
         <v>313</v>
@@ -91422,7 +91416,7 @@
     </row>
     <row r="1478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1478" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1478" t="s">
         <v>383</v>
@@ -91484,7 +91478,7 @@
     </row>
     <row r="1479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1479" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1479" t="s">
         <v>384</v>
@@ -91543,7 +91537,7 @@
     </row>
     <row r="1480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1480" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1480" t="s">
         <v>576</v>
@@ -91602,7 +91596,7 @@
     </row>
     <row r="1481" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1481" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1481" t="s">
         <v>387</v>
@@ -91664,7 +91658,7 @@
     </row>
     <row r="1482" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1482" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1482" t="s">
         <v>315</v>
@@ -91717,7 +91711,7 @@
     </row>
     <row r="1483" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1483" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1483" t="s">
         <v>439</v>
@@ -91776,7 +91770,7 @@
     </row>
     <row r="1484" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1484" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1484" t="s">
         <v>460</v>
@@ -91838,7 +91832,7 @@
     </row>
     <row r="1485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1485" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1485" t="s">
         <v>533</v>
@@ -91897,7 +91891,7 @@
     </row>
     <row r="1486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1486" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1486" t="s">
         <v>305</v>
@@ -91950,7 +91944,7 @@
     </row>
     <row r="1487" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1487" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1487" t="s">
         <v>409</v>
@@ -92012,7 +92006,7 @@
     </row>
     <row r="1488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1488" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1488" t="s">
         <v>307</v>
@@ -92071,7 +92065,7 @@
     </row>
     <row r="1489" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1489" t="s">
         <v>308</v>
@@ -92124,7 +92118,7 @@
     </row>
     <row r="1490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1490" t="s">
         <v>568</v>
@@ -92186,10 +92180,10 @@
     </row>
     <row r="1491" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1491" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C1491">
         <v>1</v>
@@ -92248,7 +92242,7 @@
     </row>
     <row r="1492" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1492" t="s">
         <v>389</v>
@@ -92310,7 +92304,7 @@
     </row>
     <row r="1493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1493" t="s">
         <v>309</v>
@@ -92363,7 +92357,7 @@
     </row>
     <row r="1494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1494" t="s">
         <v>462</v>
@@ -92416,10 +92410,10 @@
     </row>
     <row r="1495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1495" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C1495">
         <v>1</v>
@@ -92478,7 +92472,7 @@
     </row>
     <row r="1496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1496" t="s">
         <v>46</v>
@@ -92540,10 +92534,10 @@
     </row>
     <row r="1497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1497" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C1497">
         <v>1</v>
@@ -92599,7 +92593,7 @@
     </row>
     <row r="1498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1498" t="s">
         <v>183</v>
@@ -92661,7 +92655,7 @@
     </row>
     <row r="1499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1499" t="s">
         <v>184</v>
@@ -92723,7 +92717,7 @@
     </row>
     <row r="1500" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1500" t="s">
         <v>391</v>
@@ -92785,7 +92779,7 @@
     </row>
     <row r="1501" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1501" t="s">
         <v>185</v>
@@ -92847,7 +92841,7 @@
     </row>
     <row r="1502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1502" t="s">
         <v>187</v>
@@ -92909,7 +92903,7 @@
     </row>
     <row r="1503" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1503" t="s">
         <v>303</v>
@@ -92968,7 +92962,7 @@
     </row>
     <row r="1504" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1504" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1504" t="s">
         <v>189</v>
@@ -93030,7 +93024,7 @@
     </row>
     <row r="1505" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1505" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1505" t="s">
         <v>190</v>
@@ -93092,7 +93086,7 @@
     </row>
     <row r="1506" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1506" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1506" t="s">
         <v>615</v>
@@ -93145,7 +93139,7 @@
     </row>
     <row r="1507" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1507" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1507" t="s">
         <v>495</v>
@@ -93204,7 +93198,7 @@
     </row>
     <row r="1508" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1508" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1508" t="s">
         <v>366</v>
@@ -93266,7 +93260,7 @@
     </row>
     <row r="1509" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1509" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1509" t="s">
         <v>306</v>
@@ -93328,10 +93322,10 @@
     </row>
     <row r="1510" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1510" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1510" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C1510">
         <v>1</v>
@@ -93390,7 +93384,7 @@
     </row>
     <row r="1511" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1511" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1511" t="s">
         <v>60</v>
@@ -93452,7 +93446,7 @@
     </row>
     <row r="1512" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1512" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1512" t="s">
         <v>445</v>
@@ -93514,7 +93508,7 @@
     </row>
     <row r="1513" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1513" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1513" t="s">
         <v>395</v>
@@ -93576,7 +93570,7 @@
     </row>
     <row r="1514" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1514" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1514" t="s">
         <v>64</v>
@@ -93629,7 +93623,7 @@
     </row>
     <row r="1515" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1515" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1515" t="s">
         <v>65</v>
@@ -93691,7 +93685,7 @@
     </row>
     <row r="1516" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1516" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1516" t="s">
         <v>588</v>
@@ -93753,7 +93747,7 @@
     </row>
     <row r="1517" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1517" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B1517" t="s">
         <v>311</v>
@@ -93815,7 +93809,7 @@
     </row>
     <row r="1518" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1518" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1518" t="s">
         <v>115</v>
@@ -93877,7 +93871,7 @@
     </row>
     <row r="1519" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1519" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1519" t="s">
         <v>116</v>
@@ -93939,7 +93933,7 @@
     </row>
     <row r="1520" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1520" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1520" t="s">
         <v>201</v>
@@ -93992,10 +93986,10 @@
     </row>
     <row r="1521" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1521" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1521" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C1521">
         <v>1</v>
@@ -94054,7 +94048,7 @@
     </row>
     <row r="1522" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1522" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1522" t="s">
         <v>560</v>
@@ -94113,7 +94107,7 @@
     </row>
     <row r="1523" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1523" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1523" t="s">
         <v>120</v>
@@ -94175,7 +94169,7 @@
     </row>
     <row r="1524" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1524" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1524" t="s">
         <v>417</v>
@@ -94234,7 +94228,7 @@
     </row>
     <row r="1525" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1525" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1525" t="s">
         <v>206</v>
@@ -94296,10 +94290,10 @@
     </row>
     <row r="1526" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1526" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1526" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C1526">
         <v>1</v>
@@ -94358,10 +94352,10 @@
     </row>
     <row r="1527" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1527" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1527" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C1527">
         <v>1</v>
@@ -94417,7 +94411,7 @@
     </row>
     <row r="1528" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1528" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1528" t="s">
         <v>328</v>
@@ -94476,7 +94470,7 @@
     </row>
     <row r="1529" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1529" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1529" t="s">
         <v>378</v>
@@ -94538,7 +94532,7 @@
     </row>
     <row r="1530" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1530" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1530" t="s">
         <v>125</v>
@@ -94600,7 +94594,7 @@
     </row>
     <row r="1531" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1531" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1531" t="s">
         <v>294</v>
@@ -94659,10 +94653,10 @@
     </row>
     <row r="1532" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1532" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1532" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C1532">
         <v>1</v>
@@ -94721,10 +94715,10 @@
     </row>
     <row r="1533" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1533" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1533" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C1533">
         <v>1</v>
@@ -94774,7 +94768,7 @@
     </row>
     <row r="1534" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1534" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1534" t="s">
         <v>126</v>
@@ -94836,7 +94830,7 @@
     </row>
     <row r="1535" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1535" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1535" t="s">
         <v>208</v>
@@ -94898,7 +94892,7 @@
     </row>
     <row r="1536" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1536" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1536" t="s">
         <v>379</v>
@@ -94960,7 +94954,7 @@
     </row>
     <row r="1537" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1537" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1537" t="s">
         <v>210</v>
@@ -95019,7 +95013,7 @@
     </row>
     <row r="1538" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1538" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1538" t="s">
         <v>130</v>
@@ -95081,7 +95075,7 @@
     </row>
     <row r="1539" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1539" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B1539" t="s">
         <v>571</v>
@@ -95143,7 +95137,7 @@
     </row>
     <row r="1540" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1540" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1540" t="s">
         <v>22</v>
@@ -95205,7 +95199,7 @@
     </row>
     <row r="1541" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1541" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1541" t="s">
         <v>134</v>
@@ -95264,7 +95258,7 @@
     </row>
     <row r="1542" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1542" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1542" t="s">
         <v>224</v>
@@ -95323,7 +95317,7 @@
     </row>
     <row r="1543" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1543" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1543" t="s">
         <v>250</v>
@@ -95382,7 +95376,7 @@
     </row>
     <row r="1544" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1544" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1544" t="s">
         <v>227</v>
@@ -95441,7 +95435,7 @@
     </row>
     <row r="1545" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1545" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1545" t="s">
         <v>228</v>
@@ -95494,7 +95488,7 @@
     </row>
     <row r="1546" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1546" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1546" t="s">
         <v>230</v>
@@ -95547,7 +95541,7 @@
     </row>
     <row r="1547" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1547" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1547" t="s">
         <v>231</v>
@@ -95609,7 +95603,7 @@
     </row>
     <row r="1548" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1548" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1548" t="s">
         <v>232</v>
@@ -95668,7 +95662,7 @@
     </row>
     <row r="1549" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1549" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1549" t="s">
         <v>255</v>
@@ -95730,10 +95724,10 @@
     </row>
     <row r="1550" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1550" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1550" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C1550">
         <v>1</v>
@@ -95792,7 +95786,7 @@
     </row>
     <row r="1551" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1551" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1551" t="s">
         <v>235</v>
@@ -95854,7 +95848,7 @@
     </row>
     <row r="1552" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1552" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1552" t="s">
         <v>236</v>
@@ -95907,7 +95901,7 @@
     </row>
     <row r="1553" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1553" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1553" t="s">
         <v>144</v>
@@ -95969,10 +95963,10 @@
     </row>
     <row r="1554" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1554" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1554" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C1554">
         <v>1</v>
@@ -96028,7 +96022,7 @@
     </row>
     <row r="1555" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1555" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1555" t="s">
         <v>245</v>
@@ -96090,10 +96084,10 @@
     </row>
     <row r="1556" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1556" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1556" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C1556">
         <v>1</v>
@@ -96149,7 +96143,7 @@
     </row>
     <row r="1557" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1557" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1557" t="s">
         <v>38</v>
@@ -96208,7 +96202,7 @@
     </row>
     <row r="1558" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1558" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1558" t="s">
         <v>40</v>
@@ -96270,7 +96264,7 @@
     </row>
     <row r="1559" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1559" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1559" t="s">
         <v>239</v>
@@ -96332,7 +96326,7 @@
     </row>
     <row r="1560" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1560" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1560" t="s">
         <v>578</v>
@@ -96385,7 +96379,7 @@
     </row>
     <row r="1561" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1561" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B1561" t="s">
         <v>43</v>
@@ -96447,7 +96441,7 @@
     </row>
     <row r="1562" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1562" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1562" t="s">
         <v>135</v>
@@ -96509,10 +96503,10 @@
     </row>
     <row r="1563" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1563" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1563" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C1563">
         <v>1</v>
@@ -96571,7 +96565,7 @@
     </row>
     <row r="1564" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1564" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1564" t="s">
         <v>69</v>
@@ -96633,7 +96627,7 @@
     </row>
     <row r="1565" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1565" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1565" t="s">
         <v>137</v>
@@ -96695,10 +96689,10 @@
     </row>
     <row r="1566" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1566" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1566" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C1566">
         <v>1</v>
@@ -96757,7 +96751,7 @@
     </row>
     <row r="1567" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1567" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1567" t="s">
         <v>285</v>
@@ -96819,10 +96813,10 @@
     </row>
     <row r="1568" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1568" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1568" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C1568">
         <v>1</v>
@@ -96878,7 +96872,7 @@
     </row>
     <row r="1569" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1569" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1569" t="s">
         <v>434</v>
@@ -96940,7 +96934,7 @@
     </row>
     <row r="1570" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1570" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1570" t="s">
         <v>335</v>
@@ -97002,7 +96996,7 @@
     </row>
     <row r="1571" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1571" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1571" t="s">
         <v>54</v>
@@ -97061,7 +97055,7 @@
     </row>
     <row r="1572" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1572" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1572" t="s">
         <v>78</v>
@@ -97123,7 +97117,7 @@
     </row>
     <row r="1573" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1573" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1573" t="s">
         <v>147</v>
@@ -97182,7 +97176,7 @@
     </row>
     <row r="1574" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1574" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1574" t="s">
         <v>507</v>
@@ -97241,10 +97235,10 @@
     </row>
     <row r="1575" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1575" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1575" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C1575">
         <v>1</v>
@@ -97303,7 +97297,7 @@
     </row>
     <row r="1576" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1576" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1576" t="s">
         <v>510</v>
@@ -97362,7 +97356,7 @@
     </row>
     <row r="1577" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1577" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1577" t="s">
         <v>62</v>
@@ -97424,7 +97418,7 @@
     </row>
     <row r="1578" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1578" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1578" t="s">
         <v>151</v>
@@ -97486,7 +97480,7 @@
     </row>
     <row r="1579" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1579" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1579" t="s">
         <v>288</v>
@@ -97545,7 +97539,7 @@
     </row>
     <row r="1580" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1580" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1580" t="s">
         <v>156</v>
@@ -97607,10 +97601,10 @@
     </row>
     <row r="1581" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1581" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1581" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C1581">
         <v>1</v>
@@ -97666,7 +97660,7 @@
     </row>
     <row r="1582" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1582" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1582" t="s">
         <v>89</v>
@@ -97728,7 +97722,7 @@
     </row>
     <row r="1583" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1583" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B1583" t="s">
         <v>289</v>
@@ -97790,7 +97784,7 @@
     </row>
     <row r="1584" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1584" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1584" t="s">
         <v>223</v>
@@ -97849,7 +97843,7 @@
     </row>
     <row r="1585" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1585" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1585" t="s">
         <v>202</v>
@@ -97911,7 +97905,7 @@
     </row>
     <row r="1586" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1586" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1586" t="s">
         <v>521</v>
@@ -97970,7 +97964,7 @@
     </row>
     <row r="1587" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1587" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1587" t="s">
         <v>203</v>
@@ -98032,7 +98026,7 @@
     </row>
     <row r="1588" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1588" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1588" t="s">
         <v>341</v>
@@ -98091,10 +98085,10 @@
     </row>
     <row r="1589" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1589" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1589" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C1589">
         <v>1</v>
@@ -98153,7 +98147,7 @@
     </row>
     <row r="1590" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1590" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1590" t="s">
         <v>204</v>
@@ -98215,7 +98209,7 @@
     </row>
     <row r="1591" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1591" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1591" t="s">
         <v>522</v>
@@ -98268,7 +98262,7 @@
     </row>
     <row r="1592" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1592" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1592" t="s">
         <v>342</v>
@@ -98327,10 +98321,10 @@
     </row>
     <row r="1593" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1593" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1593" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C1593">
         <v>1</v>
@@ -98386,7 +98380,7 @@
     </row>
     <row r="1594" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1594" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1594" t="s">
         <v>233</v>
@@ -98445,7 +98439,7 @@
     </row>
     <row r="1595" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1595" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1595" t="s">
         <v>212</v>
@@ -98507,7 +98501,7 @@
     </row>
     <row r="1596" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1596" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1596" t="s">
         <v>238</v>
@@ -98569,7 +98563,7 @@
     </row>
     <row r="1597" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1597" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1597" t="s">
         <v>213</v>
@@ -98631,7 +98625,7 @@
     </row>
     <row r="1598" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1598" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1598" t="s">
         <v>523</v>
@@ -98693,10 +98687,10 @@
     </row>
     <row r="1599" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1599" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1599" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C1599">
         <v>1</v>
@@ -98755,7 +98749,7 @@
     </row>
     <row r="1600" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1600" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1600" t="s">
         <v>526</v>
@@ -98814,7 +98808,7 @@
     </row>
     <row r="1601" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1601" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1601" t="s">
         <v>437</v>
@@ -98867,7 +98861,7 @@
     </row>
     <row r="1602" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1602" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1602" t="s">
         <v>503</v>
@@ -98926,7 +98920,7 @@
     </row>
     <row r="1603" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1603" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1603" t="s">
         <v>428</v>
@@ -98988,7 +98982,7 @@
     </row>
     <row r="1604" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1604" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1604" t="s">
         <v>429</v>
@@ -99050,7 +99044,7 @@
     </row>
     <row r="1605" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1605" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B1605" t="s">
         <v>575</v>
@@ -99103,7 +99097,7 @@
     </row>
     <row r="1606" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1606" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1606" t="s">
         <v>382</v>
@@ -99165,7 +99159,7 @@
     </row>
     <row r="1607" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1607" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1607" t="s">
         <v>517</v>
@@ -99224,7 +99218,7 @@
     </row>
     <row r="1608" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1608" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1608" t="s">
         <v>312</v>
@@ -99283,10 +99277,10 @@
     </row>
     <row r="1609" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1609" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1609" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C1609">
         <v>1</v>
@@ -99336,7 +99330,7 @@
     </row>
     <row r="1610" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1610" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1610" t="s">
         <v>518</v>
@@ -99398,7 +99392,7 @@
     </row>
     <row r="1611" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1611" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1611" t="s">
         <v>48</v>
@@ -99454,10 +99448,10 @@
     </row>
     <row r="1612" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1612" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1612" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C1612">
         <v>1</v>
@@ -99507,7 +99501,7 @@
     </row>
     <row r="1613" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1613" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1613" t="s">
         <v>50</v>
@@ -99566,7 +99560,7 @@
     </row>
     <row r="1614" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1614" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1614" t="s">
         <v>386</v>
@@ -99619,7 +99613,7 @@
     </row>
     <row r="1615" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1615" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1615" t="s">
         <v>387</v>
@@ -99678,10 +99672,10 @@
     </row>
     <row r="1616" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1616" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1616" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C1616">
         <v>1</v>
@@ -99731,7 +99725,7 @@
     </row>
     <row r="1617" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1617" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1617" t="s">
         <v>315</v>
@@ -99784,7 +99778,7 @@
     </row>
     <row r="1618" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1618" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1618" t="s">
         <v>411</v>
@@ -99843,7 +99837,7 @@
     </row>
     <row r="1619" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1619" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1619" t="s">
         <v>56</v>
@@ -99896,7 +99890,7 @@
     </row>
     <row r="1620" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1620" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1620" t="s">
         <v>318</v>
@@ -99949,7 +99943,7 @@
     </row>
     <row r="1621" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1621" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1621" t="s">
         <v>409</v>
@@ -100011,7 +100005,7 @@
     </row>
     <row r="1622" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1622" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1622" t="s">
         <v>388</v>
@@ -100064,7 +100058,7 @@
     </row>
     <row r="1623" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1623" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1623" t="s">
         <v>389</v>
@@ -100123,7 +100117,7 @@
     </row>
     <row r="1624" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1624" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1624" t="s">
         <v>476</v>
@@ -100182,7 +100176,7 @@
     </row>
     <row r="1625" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1625" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1625" t="s">
         <v>321</v>
@@ -100244,7 +100238,7 @@
     </row>
     <row r="1626" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1626" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B1626" t="s">
         <v>61</v>
@@ -100306,10 +100300,10 @@
     </row>
     <row r="1627" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1627" t="s">
+        <v>707</v>
+      </c>
+      <c r="B1627" s="1" t="s">
         <v>710</v>
-      </c>
-      <c r="B1627" s="1" t="s">
-        <v>713</v>
       </c>
       <c r="C1627">
         <v>1</v>
@@ -100368,10 +100362,10 @@
     </row>
     <row r="1628" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1628" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1628" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C1628">
         <v>1</v>
@@ -100430,10 +100424,10 @@
     </row>
     <row r="1629" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1629" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1629" s="1" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C1629">
         <v>1</v>
@@ -100483,7 +100477,7 @@
     </row>
     <row r="1630" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1630" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1630" s="1" t="s">
         <v>97</v>
@@ -100536,7 +100530,7 @@
     </row>
     <row r="1631" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1631" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1631" s="1" t="s">
         <v>284</v>
@@ -100598,7 +100592,7 @@
     </row>
     <row r="1632" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1632" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1632" s="1" t="s">
         <v>101</v>
@@ -100651,7 +100645,7 @@
     </row>
     <row r="1633" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1633" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1633" s="1" t="s">
         <v>449</v>
@@ -100710,7 +100704,7 @@
     </row>
     <row r="1634" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1634" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1634" s="1" t="s">
         <v>606</v>
@@ -100769,10 +100763,10 @@
     </row>
     <row r="1635" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1635" t="s">
+        <v>711</v>
+      </c>
+      <c r="B1635" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="B1635" s="1" t="s">
-        <v>717</v>
       </c>
       <c r="C1635">
         <v>1</v>
@@ -100822,7 +100816,7 @@
     </row>
     <row r="1636" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1636" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1636" s="1" t="s">
         <v>245</v>
@@ -100884,7 +100878,7 @@
     </row>
     <row r="1637" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1637" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1637" s="1" t="s">
         <v>140</v>
@@ -100946,10 +100940,10 @@
     </row>
     <row r="1638" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1638" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1638" s="1" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C1638">
         <v>1</v>
@@ -101005,10 +100999,10 @@
     </row>
     <row r="1639" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1639" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1639" s="1" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C1639">
         <v>1</v>
@@ -101067,7 +101061,7 @@
     </row>
     <row r="1640" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1640" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1640" s="1" t="s">
         <v>591</v>
@@ -101129,7 +101123,7 @@
     </row>
     <row r="1641" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1641" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1641" s="1" t="s">
         <v>448</v>
@@ -101188,7 +101182,7 @@
     </row>
     <row r="1642" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1642" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1642" s="1" t="s">
         <v>134</v>
@@ -101250,10 +101244,10 @@
     </row>
     <row r="1643" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1643" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1643" s="1" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C1643">
         <v>1</v>
@@ -101312,7 +101306,7 @@
     </row>
     <row r="1644" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1644" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1644" s="1" t="s">
         <v>100</v>
@@ -101374,10 +101368,10 @@
     </row>
     <row r="1645" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1645" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1645" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C1645">
         <v>1</v>
@@ -101436,7 +101430,7 @@
     </row>
     <row r="1646" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1646" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1646" s="1" t="s">
         <v>143</v>
@@ -101498,10 +101492,10 @@
     </row>
     <row r="1647" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1647" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1647" s="1" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C1647">
         <v>1</v>
@@ -101551,7 +101545,7 @@
     </row>
     <row r="1648" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1648" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1648" s="1" t="s">
         <v>152</v>
@@ -101613,7 +101607,7 @@
     </row>
     <row r="1649" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1649" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B1649" s="1" t="s">
         <v>43</v>

--- a/NV Play Midweek League batting stats for season.xlsx
+++ b/NV Play Midweek League batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3989" uniqueCount="733">
   <si>
     <t>Group</t>
   </si>
@@ -2174,6 +2174,51 @@
   <si>
     <t>Pawan Kumar</t>
   </si>
+  <si>
+    <t>CSNI MW XI v Arches MW XI, Stormont - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Richard Gould Hocking</t>
+  </si>
+  <si>
+    <t>Dunmurry MW2 XI v Cooke Collegians MW XI, Fullerton Park - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Sam Cave</t>
+  </si>
+  <si>
+    <t>Billy Foster</t>
+  </si>
+  <si>
+    <t>Ali Quadri</t>
+  </si>
+  <si>
+    <t>Satyen Shukla</t>
+  </si>
+  <si>
+    <t>Muckamore MW1 XI v Amigos Belfast MW XI, Moylena - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Arjun Sasidharan</t>
+  </si>
+  <si>
+    <t>Don Thomas</t>
+  </si>
+  <si>
+    <t>BISC MW XI v Ballymena MW XI, TBC - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Rajendrakumar Patil</t>
+  </si>
+  <si>
+    <t>NIMACC MW XI v Instonians MW XI, TBC - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Byjo Varghese</t>
+  </si>
+  <si>
+    <t>Roshan Varghese</t>
+  </si>
 </sst>
 </file>
 
@@ -2980,7 +3025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1655"/>
+  <dimension ref="A1:U1759"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="97.42578125" bestFit="1" customWidth="1"/>
@@ -101665,22 +101710,6644 @@
       </c>
     </row>
     <row r="1650" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B1650" s="1"/>
+      <c r="A1650" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1650">
+        <v>1</v>
+      </c>
+      <c r="D1650">
+        <v>1</v>
+      </c>
+      <c r="E1650">
+        <v>1</v>
+      </c>
+      <c r="F1650">
+        <v>26</v>
+      </c>
+      <c r="H1650" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1650">
+        <v>0</v>
+      </c>
+      <c r="J1650">
+        <v>0</v>
+      </c>
+      <c r="K1650">
+        <v>288.89</v>
+      </c>
+      <c r="L1650">
+        <v>9</v>
+      </c>
+      <c r="M1650">
+        <v>1</v>
+      </c>
+      <c r="N1650">
+        <v>0</v>
+      </c>
+      <c r="O1650">
+        <v>3</v>
+      </c>
+      <c r="P1650">
+        <v>14.61</v>
+      </c>
+      <c r="Q1650">
+        <v>0</v>
+      </c>
+      <c r="R1650">
+        <v>0</v>
+      </c>
+      <c r="S1650">
+        <v>0</v>
+      </c>
+      <c r="T1650">
+        <v>0</v>
+      </c>
     </row>
     <row r="1651" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B1651" s="1"/>
+      <c r="A1651" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>482</v>
+      </c>
+      <c r="C1651">
+        <v>1</v>
+      </c>
+      <c r="D1651">
+        <v>1</v>
+      </c>
+      <c r="E1651">
+        <v>0</v>
+      </c>
+      <c r="F1651">
+        <v>15</v>
+      </c>
+      <c r="G1651">
+        <v>15</v>
+      </c>
+      <c r="H1651">
+        <v>15</v>
+      </c>
+      <c r="I1651">
+        <v>0</v>
+      </c>
+      <c r="J1651">
+        <v>0</v>
+      </c>
+      <c r="K1651">
+        <v>107.14</v>
+      </c>
+      <c r="L1651">
+        <v>14</v>
+      </c>
+      <c r="M1651">
+        <v>6</v>
+      </c>
+      <c r="N1651">
+        <v>2</v>
+      </c>
+      <c r="O1651">
+        <v>0</v>
+      </c>
+      <c r="P1651">
+        <v>11.72</v>
+      </c>
+      <c r="Q1651">
+        <v>0</v>
+      </c>
+      <c r="R1651">
+        <v>0</v>
+      </c>
+      <c r="S1651">
+        <v>0</v>
+      </c>
+      <c r="T1651">
+        <v>0</v>
+      </c>
     </row>
     <row r="1652" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B1652" s="1"/>
+      <c r="A1652" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>549</v>
+      </c>
+      <c r="C1652">
+        <v>1</v>
+      </c>
+      <c r="D1652">
+        <v>1</v>
+      </c>
+      <c r="E1652">
+        <v>0</v>
+      </c>
+      <c r="F1652">
+        <v>1</v>
+      </c>
+      <c r="G1652">
+        <v>1</v>
+      </c>
+      <c r="H1652">
+        <v>1</v>
+      </c>
+      <c r="I1652">
+        <v>0</v>
+      </c>
+      <c r="J1652">
+        <v>0</v>
+      </c>
+      <c r="K1652">
+        <v>25</v>
+      </c>
+      <c r="L1652">
+        <v>4</v>
+      </c>
+      <c r="M1652">
+        <v>3</v>
+      </c>
+      <c r="N1652">
+        <v>0</v>
+      </c>
+      <c r="O1652">
+        <v>0</v>
+      </c>
+      <c r="P1652">
+        <v>0.78</v>
+      </c>
+      <c r="Q1652">
+        <v>0</v>
+      </c>
+      <c r="R1652">
+        <v>0</v>
+      </c>
+      <c r="S1652">
+        <v>0</v>
+      </c>
+      <c r="T1652">
+        <v>0</v>
+      </c>
     </row>
     <row r="1653" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B1653" s="1"/>
+      <c r="A1653" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1653">
+        <v>1</v>
+      </c>
+      <c r="D1653">
+        <v>1</v>
+      </c>
+      <c r="E1653">
+        <v>0</v>
+      </c>
+      <c r="F1653">
+        <v>7</v>
+      </c>
+      <c r="G1653">
+        <v>7</v>
+      </c>
+      <c r="H1653">
+        <v>7</v>
+      </c>
+      <c r="I1653">
+        <v>0</v>
+      </c>
+      <c r="J1653">
+        <v>0</v>
+      </c>
+      <c r="K1653">
+        <v>100</v>
+      </c>
+      <c r="L1653">
+        <v>7</v>
+      </c>
+      <c r="M1653">
+        <v>3</v>
+      </c>
+      <c r="N1653">
+        <v>1</v>
+      </c>
+      <c r="O1653">
+        <v>0</v>
+      </c>
+      <c r="P1653">
+        <v>5.47</v>
+      </c>
+      <c r="Q1653">
+        <v>1</v>
+      </c>
+      <c r="R1653">
+        <v>0</v>
+      </c>
+      <c r="S1653">
+        <v>0</v>
+      </c>
+      <c r="T1653">
+        <v>0</v>
+      </c>
     </row>
     <row r="1654" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B1654" s="1"/>
+      <c r="A1654" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1654">
+        <v>1</v>
+      </c>
+      <c r="D1654">
+        <v>1</v>
+      </c>
+      <c r="E1654">
+        <v>0</v>
+      </c>
+      <c r="F1654">
+        <v>0</v>
+      </c>
+      <c r="G1654">
+        <v>0</v>
+      </c>
+      <c r="H1654">
+        <v>0</v>
+      </c>
+      <c r="I1654">
+        <v>0</v>
+      </c>
+      <c r="J1654">
+        <v>0</v>
+      </c>
+      <c r="K1654">
+        <v>0</v>
+      </c>
+      <c r="L1654">
+        <v>1</v>
+      </c>
+      <c r="M1654">
+        <v>1</v>
+      </c>
+      <c r="N1654">
+        <v>0</v>
+      </c>
+      <c r="O1654">
+        <v>0</v>
+      </c>
+      <c r="P1654">
+        <v>0</v>
+      </c>
+      <c r="Q1654">
+        <v>0</v>
+      </c>
+      <c r="R1654">
+        <v>0</v>
+      </c>
+      <c r="S1654">
+        <v>0</v>
+      </c>
+      <c r="T1654">
+        <v>0</v>
+      </c>
     </row>
     <row r="1655" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B1655" s="1"/>
+      <c r="A1655" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>719</v>
+      </c>
+      <c r="C1655">
+        <v>1</v>
+      </c>
+      <c r="D1655">
+        <v>1</v>
+      </c>
+      <c r="E1655">
+        <v>0</v>
+      </c>
+      <c r="F1655">
+        <v>1</v>
+      </c>
+      <c r="G1655">
+        <v>1</v>
+      </c>
+      <c r="H1655">
+        <v>1</v>
+      </c>
+      <c r="I1655">
+        <v>0</v>
+      </c>
+      <c r="J1655">
+        <v>0</v>
+      </c>
+      <c r="K1655">
+        <v>25</v>
+      </c>
+      <c r="L1655">
+        <v>4</v>
+      </c>
+      <c r="M1655">
+        <v>3</v>
+      </c>
+      <c r="N1655">
+        <v>0</v>
+      </c>
+      <c r="O1655">
+        <v>0</v>
+      </c>
+      <c r="P1655">
+        <v>0.78</v>
+      </c>
+      <c r="Q1655">
+        <v>0</v>
+      </c>
+      <c r="R1655">
+        <v>0</v>
+      </c>
+      <c r="S1655">
+        <v>0</v>
+      </c>
+      <c r="T1655">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1656" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1656">
+        <v>1</v>
+      </c>
+      <c r="D1656">
+        <v>1</v>
+      </c>
+      <c r="E1656">
+        <v>1</v>
+      </c>
+      <c r="F1656">
+        <v>30</v>
+      </c>
+      <c r="H1656" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1656">
+        <v>0</v>
+      </c>
+      <c r="J1656">
+        <v>0</v>
+      </c>
+      <c r="K1656">
+        <v>107.14</v>
+      </c>
+      <c r="L1656">
+        <v>28</v>
+      </c>
+      <c r="M1656">
+        <v>13</v>
+      </c>
+      <c r="N1656">
+        <v>2</v>
+      </c>
+      <c r="O1656">
+        <v>1</v>
+      </c>
+      <c r="P1656">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="Q1656">
+        <v>0</v>
+      </c>
+      <c r="R1656">
+        <v>0</v>
+      </c>
+      <c r="S1656">
+        <v>0</v>
+      </c>
+      <c r="T1656">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1657" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1657">
+        <v>1</v>
+      </c>
+      <c r="D1657">
+        <v>1</v>
+      </c>
+      <c r="E1657">
+        <v>1</v>
+      </c>
+      <c r="F1657">
+        <v>33</v>
+      </c>
+      <c r="H1657" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1657">
+        <v>0</v>
+      </c>
+      <c r="J1657">
+        <v>0</v>
+      </c>
+      <c r="K1657">
+        <v>122.22</v>
+      </c>
+      <c r="L1657">
+        <v>27</v>
+      </c>
+      <c r="M1657">
+        <v>15</v>
+      </c>
+      <c r="N1657">
+        <v>5</v>
+      </c>
+      <c r="O1657">
+        <v>1</v>
+      </c>
+      <c r="P1657">
+        <v>18.54</v>
+      </c>
+      <c r="Q1657">
+        <v>0</v>
+      </c>
+      <c r="R1657">
+        <v>0</v>
+      </c>
+      <c r="S1657">
+        <v>0</v>
+      </c>
+      <c r="T1657">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1658" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1658">
+        <v>1</v>
+      </c>
+      <c r="D1658">
+        <v>1</v>
+      </c>
+      <c r="E1658">
+        <v>0</v>
+      </c>
+      <c r="F1658">
+        <v>4</v>
+      </c>
+      <c r="G1658">
+        <v>4</v>
+      </c>
+      <c r="H1658">
+        <v>4</v>
+      </c>
+      <c r="I1658">
+        <v>0</v>
+      </c>
+      <c r="J1658">
+        <v>0</v>
+      </c>
+      <c r="K1658">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1658">
+        <v>3</v>
+      </c>
+      <c r="M1658">
+        <v>2</v>
+      </c>
+      <c r="N1658">
+        <v>1</v>
+      </c>
+      <c r="O1658">
+        <v>0</v>
+      </c>
+      <c r="P1658">
+        <v>3.13</v>
+      </c>
+      <c r="Q1658">
+        <v>1</v>
+      </c>
+      <c r="R1658">
+        <v>0</v>
+      </c>
+      <c r="S1658">
+        <v>0</v>
+      </c>
+      <c r="T1658">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1659" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1659">
+        <v>1</v>
+      </c>
+      <c r="D1659">
+        <v>1</v>
+      </c>
+      <c r="E1659">
+        <v>0</v>
+      </c>
+      <c r="F1659">
+        <v>5</v>
+      </c>
+      <c r="G1659">
+        <v>5</v>
+      </c>
+      <c r="H1659">
+        <v>5</v>
+      </c>
+      <c r="I1659">
+        <v>0</v>
+      </c>
+      <c r="J1659">
+        <v>0</v>
+      </c>
+      <c r="K1659">
+        <v>100</v>
+      </c>
+      <c r="L1659">
+        <v>5</v>
+      </c>
+      <c r="M1659">
+        <v>2</v>
+      </c>
+      <c r="N1659">
+        <v>0</v>
+      </c>
+      <c r="O1659">
+        <v>0</v>
+      </c>
+      <c r="P1659">
+        <v>3.91</v>
+      </c>
+      <c r="Q1659">
+        <v>1</v>
+      </c>
+      <c r="R1659">
+        <v>0</v>
+      </c>
+      <c r="S1659">
+        <v>0</v>
+      </c>
+      <c r="T1659">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1660" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>551</v>
+      </c>
+      <c r="C1660">
+        <v>1</v>
+      </c>
+      <c r="D1660">
+        <v>1</v>
+      </c>
+      <c r="E1660">
+        <v>0</v>
+      </c>
+      <c r="F1660">
+        <v>6</v>
+      </c>
+      <c r="G1660">
+        <v>6</v>
+      </c>
+      <c r="H1660">
+        <v>6</v>
+      </c>
+      <c r="I1660">
+        <v>0</v>
+      </c>
+      <c r="J1660">
+        <v>0</v>
+      </c>
+      <c r="K1660">
+        <v>150</v>
+      </c>
+      <c r="L1660">
+        <v>4</v>
+      </c>
+      <c r="M1660">
+        <v>1</v>
+      </c>
+      <c r="N1660">
+        <v>1</v>
+      </c>
+      <c r="O1660">
+        <v>0</v>
+      </c>
+      <c r="P1660">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="Q1660">
+        <v>0</v>
+      </c>
+      <c r="R1660">
+        <v>1</v>
+      </c>
+      <c r="S1660">
+        <v>0</v>
+      </c>
+      <c r="T1660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1661" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>485</v>
+      </c>
+      <c r="C1661">
+        <v>1</v>
+      </c>
+      <c r="D1661">
+        <v>1</v>
+      </c>
+      <c r="E1661">
+        <v>1</v>
+      </c>
+      <c r="F1661">
+        <v>5</v>
+      </c>
+      <c r="H1661" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1661">
+        <v>0</v>
+      </c>
+      <c r="J1661">
+        <v>0</v>
+      </c>
+      <c r="K1661">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="L1661">
+        <v>7</v>
+      </c>
+      <c r="M1661">
+        <v>5</v>
+      </c>
+      <c r="N1661">
+        <v>1</v>
+      </c>
+      <c r="O1661">
+        <v>0</v>
+      </c>
+      <c r="P1661">
+        <v>3.91</v>
+      </c>
+      <c r="Q1661">
+        <v>0</v>
+      </c>
+      <c r="R1661">
+        <v>0</v>
+      </c>
+      <c r="S1661">
+        <v>0</v>
+      </c>
+      <c r="T1661">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1662" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>486</v>
+      </c>
+      <c r="C1662">
+        <v>1</v>
+      </c>
+      <c r="D1662">
+        <v>1</v>
+      </c>
+      <c r="E1662">
+        <v>0</v>
+      </c>
+      <c r="F1662">
+        <v>30</v>
+      </c>
+      <c r="G1662">
+        <v>30</v>
+      </c>
+      <c r="H1662">
+        <v>30</v>
+      </c>
+      <c r="I1662">
+        <v>0</v>
+      </c>
+      <c r="J1662">
+        <v>0</v>
+      </c>
+      <c r="K1662">
+        <v>142.86000000000001</v>
+      </c>
+      <c r="L1662">
+        <v>21</v>
+      </c>
+      <c r="M1662">
+        <v>8</v>
+      </c>
+      <c r="N1662">
+        <v>5</v>
+      </c>
+      <c r="O1662">
+        <v>0</v>
+      </c>
+      <c r="P1662">
+        <v>23.44</v>
+      </c>
+      <c r="Q1662">
+        <v>0</v>
+      </c>
+      <c r="R1662">
+        <v>0</v>
+      </c>
+      <c r="S1662">
+        <v>0</v>
+      </c>
+      <c r="T1662">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1663" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1663">
+        <v>1</v>
+      </c>
+      <c r="D1663">
+        <v>1</v>
+      </c>
+      <c r="E1663">
+        <v>0</v>
+      </c>
+      <c r="F1663">
+        <v>14</v>
+      </c>
+      <c r="G1663">
+        <v>14</v>
+      </c>
+      <c r="H1663">
+        <v>14</v>
+      </c>
+      <c r="I1663">
+        <v>0</v>
+      </c>
+      <c r="J1663">
+        <v>0</v>
+      </c>
+      <c r="K1663">
+        <v>87.5</v>
+      </c>
+      <c r="L1663">
+        <v>16</v>
+      </c>
+      <c r="M1663">
+        <v>7</v>
+      </c>
+      <c r="N1663">
+        <v>1</v>
+      </c>
+      <c r="O1663">
+        <v>0</v>
+      </c>
+      <c r="P1663">
+        <v>7.87</v>
+      </c>
+      <c r="Q1663">
+        <v>0</v>
+      </c>
+      <c r="R1663">
+        <v>0</v>
+      </c>
+      <c r="S1663">
+        <v>0</v>
+      </c>
+      <c r="T1663">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1664" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>452</v>
+      </c>
+      <c r="C1664">
+        <v>1</v>
+      </c>
+      <c r="D1664">
+        <v>1</v>
+      </c>
+      <c r="E1664">
+        <v>0</v>
+      </c>
+      <c r="F1664">
+        <v>21</v>
+      </c>
+      <c r="G1664">
+        <v>21</v>
+      </c>
+      <c r="H1664">
+        <v>21</v>
+      </c>
+      <c r="I1664">
+        <v>0</v>
+      </c>
+      <c r="J1664">
+        <v>0</v>
+      </c>
+      <c r="K1664">
+        <v>210</v>
+      </c>
+      <c r="L1664">
+        <v>10</v>
+      </c>
+      <c r="M1664">
+        <v>1</v>
+      </c>
+      <c r="N1664">
+        <v>4</v>
+      </c>
+      <c r="O1664">
+        <v>0</v>
+      </c>
+      <c r="P1664">
+        <v>11.8</v>
+      </c>
+      <c r="Q1664">
+        <v>0</v>
+      </c>
+      <c r="R1664">
+        <v>0</v>
+      </c>
+      <c r="S1664">
+        <v>0</v>
+      </c>
+      <c r="T1664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1665" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1665">
+        <v>1</v>
+      </c>
+      <c r="D1665">
+        <v>1</v>
+      </c>
+      <c r="E1665">
+        <v>0</v>
+      </c>
+      <c r="F1665">
+        <v>2</v>
+      </c>
+      <c r="G1665">
+        <v>2</v>
+      </c>
+      <c r="H1665">
+        <v>2</v>
+      </c>
+      <c r="I1665">
+        <v>0</v>
+      </c>
+      <c r="J1665">
+        <v>0</v>
+      </c>
+      <c r="K1665">
+        <v>50</v>
+      </c>
+      <c r="L1665">
+        <v>4</v>
+      </c>
+      <c r="M1665">
+        <v>2</v>
+      </c>
+      <c r="N1665">
+        <v>0</v>
+      </c>
+      <c r="O1665">
+        <v>0</v>
+      </c>
+      <c r="P1665">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="Q1665">
+        <v>0</v>
+      </c>
+      <c r="R1665">
+        <v>0</v>
+      </c>
+      <c r="S1665">
+        <v>0</v>
+      </c>
+      <c r="T1665">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1666" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1666">
+        <v>1</v>
+      </c>
+      <c r="D1666">
+        <v>1</v>
+      </c>
+      <c r="E1666">
+        <v>0</v>
+      </c>
+      <c r="F1666">
+        <v>1</v>
+      </c>
+      <c r="G1666">
+        <v>1</v>
+      </c>
+      <c r="H1666">
+        <v>1</v>
+      </c>
+      <c r="I1666">
+        <v>0</v>
+      </c>
+      <c r="J1666">
+        <v>0</v>
+      </c>
+      <c r="K1666">
+        <v>25</v>
+      </c>
+      <c r="L1666">
+        <v>4</v>
+      </c>
+      <c r="M1666">
+        <v>3</v>
+      </c>
+      <c r="N1666">
+        <v>0</v>
+      </c>
+      <c r="O1666">
+        <v>0</v>
+      </c>
+      <c r="P1666">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="Q1666">
+        <v>0</v>
+      </c>
+      <c r="R1666">
+        <v>0</v>
+      </c>
+      <c r="S1666">
+        <v>0</v>
+      </c>
+      <c r="T1666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1667" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1667">
+        <v>1</v>
+      </c>
+      <c r="D1667">
+        <v>1</v>
+      </c>
+      <c r="E1667">
+        <v>1</v>
+      </c>
+      <c r="F1667">
+        <v>5</v>
+      </c>
+      <c r="H1667" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1667">
+        <v>0</v>
+      </c>
+      <c r="J1667">
+        <v>0</v>
+      </c>
+      <c r="K1667">
+        <v>250</v>
+      </c>
+      <c r="L1667">
+        <v>2</v>
+      </c>
+      <c r="M1667">
+        <v>0</v>
+      </c>
+      <c r="N1667">
+        <v>0</v>
+      </c>
+      <c r="O1667">
+        <v>0</v>
+      </c>
+      <c r="P1667">
+        <v>2.81</v>
+      </c>
+      <c r="Q1667">
+        <v>0</v>
+      </c>
+      <c r="R1667">
+        <v>0</v>
+      </c>
+      <c r="S1667">
+        <v>0</v>
+      </c>
+      <c r="T1667">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1668" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1668">
+        <v>1</v>
+      </c>
+      <c r="D1668">
+        <v>1</v>
+      </c>
+      <c r="E1668">
+        <v>0</v>
+      </c>
+      <c r="F1668">
+        <v>14</v>
+      </c>
+      <c r="G1668">
+        <v>14</v>
+      </c>
+      <c r="H1668">
+        <v>14</v>
+      </c>
+      <c r="I1668">
+        <v>0</v>
+      </c>
+      <c r="J1668">
+        <v>0</v>
+      </c>
+      <c r="K1668">
+        <v>70</v>
+      </c>
+      <c r="L1668">
+        <v>20</v>
+      </c>
+      <c r="M1668">
+        <v>10</v>
+      </c>
+      <c r="N1668">
+        <v>1</v>
+      </c>
+      <c r="O1668">
+        <v>0</v>
+      </c>
+      <c r="P1668">
+        <v>10.94</v>
+      </c>
+      <c r="Q1668">
+        <v>1</v>
+      </c>
+      <c r="R1668">
+        <v>0</v>
+      </c>
+      <c r="S1668">
+        <v>0</v>
+      </c>
+      <c r="T1668">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1669" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>489</v>
+      </c>
+      <c r="C1669">
+        <v>1</v>
+      </c>
+      <c r="D1669">
+        <v>1</v>
+      </c>
+      <c r="E1669">
+        <v>0</v>
+      </c>
+      <c r="F1669">
+        <v>29</v>
+      </c>
+      <c r="G1669">
+        <v>29</v>
+      </c>
+      <c r="H1669">
+        <v>29</v>
+      </c>
+      <c r="I1669">
+        <v>0</v>
+      </c>
+      <c r="J1669">
+        <v>0</v>
+      </c>
+      <c r="K1669">
+        <v>107.41</v>
+      </c>
+      <c r="L1669">
+        <v>27</v>
+      </c>
+      <c r="M1669">
+        <v>12</v>
+      </c>
+      <c r="N1669">
+        <v>4</v>
+      </c>
+      <c r="O1669">
+        <v>0</v>
+      </c>
+      <c r="P1669">
+        <v>22.66</v>
+      </c>
+      <c r="Q1669">
+        <v>0</v>
+      </c>
+      <c r="R1669">
+        <v>0</v>
+      </c>
+      <c r="S1669">
+        <v>0</v>
+      </c>
+      <c r="T1669">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1670" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1670">
+        <v>1</v>
+      </c>
+      <c r="D1670">
+        <v>1</v>
+      </c>
+      <c r="E1670">
+        <v>0</v>
+      </c>
+      <c r="F1670">
+        <v>21</v>
+      </c>
+      <c r="G1670">
+        <v>21</v>
+      </c>
+      <c r="H1670">
+        <v>21</v>
+      </c>
+      <c r="I1670">
+        <v>0</v>
+      </c>
+      <c r="J1670">
+        <v>0</v>
+      </c>
+      <c r="K1670">
+        <v>131.25</v>
+      </c>
+      <c r="L1670">
+        <v>16</v>
+      </c>
+      <c r="M1670">
+        <v>8</v>
+      </c>
+      <c r="N1670">
+        <v>2</v>
+      </c>
+      <c r="O1670">
+        <v>1</v>
+      </c>
+      <c r="P1670">
+        <v>11.8</v>
+      </c>
+      <c r="Q1670">
+        <v>0</v>
+      </c>
+      <c r="R1670">
+        <v>1</v>
+      </c>
+      <c r="S1670">
+        <v>0</v>
+      </c>
+      <c r="T1670">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1671" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1671">
+        <v>1</v>
+      </c>
+      <c r="D1671">
+        <v>1</v>
+      </c>
+      <c r="E1671">
+        <v>0</v>
+      </c>
+      <c r="F1671">
+        <v>2</v>
+      </c>
+      <c r="G1671">
+        <v>2</v>
+      </c>
+      <c r="H1671">
+        <v>2</v>
+      </c>
+      <c r="I1671">
+        <v>0</v>
+      </c>
+      <c r="J1671">
+        <v>0</v>
+      </c>
+      <c r="K1671">
+        <v>50</v>
+      </c>
+      <c r="L1671">
+        <v>4</v>
+      </c>
+      <c r="M1671">
+        <v>2</v>
+      </c>
+      <c r="N1671">
+        <v>0</v>
+      </c>
+      <c r="O1671">
+        <v>0</v>
+      </c>
+      <c r="P1671">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="Q1671">
+        <v>0</v>
+      </c>
+      <c r="R1671">
+        <v>0</v>
+      </c>
+      <c r="S1671">
+        <v>0</v>
+      </c>
+      <c r="T1671">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1672" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1672">
+        <v>1</v>
+      </c>
+      <c r="D1672">
+        <v>1</v>
+      </c>
+      <c r="E1672">
+        <v>1</v>
+      </c>
+      <c r="F1672">
+        <v>26</v>
+      </c>
+      <c r="H1672" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1672">
+        <v>0</v>
+      </c>
+      <c r="J1672">
+        <v>0</v>
+      </c>
+      <c r="K1672">
+        <v>118.18</v>
+      </c>
+      <c r="L1672">
+        <v>22</v>
+      </c>
+      <c r="M1672">
+        <v>11</v>
+      </c>
+      <c r="N1672">
+        <v>3</v>
+      </c>
+      <c r="O1672">
+        <v>1</v>
+      </c>
+      <c r="P1672">
+        <v>21.49</v>
+      </c>
+      <c r="Q1672">
+        <v>1</v>
+      </c>
+      <c r="R1672">
+        <v>0</v>
+      </c>
+      <c r="S1672">
+        <v>0</v>
+      </c>
+      <c r="T1672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1673" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1673">
+        <v>1</v>
+      </c>
+      <c r="D1673">
+        <v>1</v>
+      </c>
+      <c r="E1673">
+        <v>1</v>
+      </c>
+      <c r="F1673">
+        <v>5</v>
+      </c>
+      <c r="H1673" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1673">
+        <v>0</v>
+      </c>
+      <c r="J1673">
+        <v>0</v>
+      </c>
+      <c r="K1673">
+        <v>55.56</v>
+      </c>
+      <c r="L1673">
+        <v>9</v>
+      </c>
+      <c r="M1673">
+        <v>7</v>
+      </c>
+      <c r="N1673">
+        <v>1</v>
+      </c>
+      <c r="O1673">
+        <v>0</v>
+      </c>
+      <c r="P1673">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q1673">
+        <v>0</v>
+      </c>
+      <c r="R1673">
+        <v>0</v>
+      </c>
+      <c r="S1673">
+        <v>0</v>
+      </c>
+      <c r="T1673">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1674" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>721</v>
+      </c>
+      <c r="C1674">
+        <v>1</v>
+      </c>
+      <c r="D1674">
+        <v>1</v>
+      </c>
+      <c r="E1674">
+        <v>0</v>
+      </c>
+      <c r="F1674">
+        <v>8</v>
+      </c>
+      <c r="G1674">
+        <v>8</v>
+      </c>
+      <c r="H1674">
+        <v>8</v>
+      </c>
+      <c r="I1674">
+        <v>0</v>
+      </c>
+      <c r="J1674">
+        <v>0</v>
+      </c>
+      <c r="K1674">
+        <v>53.33</v>
+      </c>
+      <c r="L1674">
+        <v>15</v>
+      </c>
+      <c r="M1674">
+        <v>10</v>
+      </c>
+      <c r="N1674">
+        <v>1</v>
+      </c>
+      <c r="O1674">
+        <v>0</v>
+      </c>
+      <c r="P1674">
+        <v>6.61</v>
+      </c>
+      <c r="Q1674">
+        <v>0</v>
+      </c>
+      <c r="R1674">
+        <v>0</v>
+      </c>
+      <c r="S1674">
+        <v>0</v>
+      </c>
+      <c r="T1674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1675" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1675">
+        <v>1</v>
+      </c>
+      <c r="D1675">
+        <v>1</v>
+      </c>
+      <c r="E1675">
+        <v>0</v>
+      </c>
+      <c r="F1675">
+        <v>15</v>
+      </c>
+      <c r="G1675">
+        <v>15</v>
+      </c>
+      <c r="H1675">
+        <v>15</v>
+      </c>
+      <c r="I1675">
+        <v>0</v>
+      </c>
+      <c r="J1675">
+        <v>0</v>
+      </c>
+      <c r="K1675">
+        <v>51.72</v>
+      </c>
+      <c r="L1675">
+        <v>29</v>
+      </c>
+      <c r="M1675">
+        <v>18</v>
+      </c>
+      <c r="N1675">
+        <v>0</v>
+      </c>
+      <c r="O1675">
+        <v>0</v>
+      </c>
+      <c r="P1675">
+        <v>12.4</v>
+      </c>
+      <c r="Q1675">
+        <v>0</v>
+      </c>
+      <c r="R1675">
+        <v>0</v>
+      </c>
+      <c r="S1675">
+        <v>0</v>
+      </c>
+      <c r="T1675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1676" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1676">
+        <v>1</v>
+      </c>
+      <c r="D1676">
+        <v>1</v>
+      </c>
+      <c r="E1676">
+        <v>0</v>
+      </c>
+      <c r="F1676">
+        <v>1</v>
+      </c>
+      <c r="G1676">
+        <v>1</v>
+      </c>
+      <c r="H1676">
+        <v>1</v>
+      </c>
+      <c r="I1676">
+        <v>0</v>
+      </c>
+      <c r="J1676">
+        <v>0</v>
+      </c>
+      <c r="K1676">
+        <v>11.11</v>
+      </c>
+      <c r="L1676">
+        <v>9</v>
+      </c>
+      <c r="M1676">
+        <v>8</v>
+      </c>
+      <c r="N1676">
+        <v>0</v>
+      </c>
+      <c r="O1676">
+        <v>0</v>
+      </c>
+      <c r="P1676">
+        <v>0.82</v>
+      </c>
+      <c r="Q1676">
+        <v>0</v>
+      </c>
+      <c r="R1676">
+        <v>0</v>
+      </c>
+      <c r="S1676">
+        <v>0</v>
+      </c>
+      <c r="T1676">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1677" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>722</v>
+      </c>
+      <c r="C1677">
+        <v>1</v>
+      </c>
+      <c r="D1677">
+        <v>1</v>
+      </c>
+      <c r="E1677">
+        <v>0</v>
+      </c>
+      <c r="F1677">
+        <v>2</v>
+      </c>
+      <c r="G1677">
+        <v>2</v>
+      </c>
+      <c r="H1677">
+        <v>2</v>
+      </c>
+      <c r="I1677">
+        <v>0</v>
+      </c>
+      <c r="J1677">
+        <v>0</v>
+      </c>
+      <c r="K1677">
+        <v>28.57</v>
+      </c>
+      <c r="L1677">
+        <v>7</v>
+      </c>
+      <c r="M1677">
+        <v>5</v>
+      </c>
+      <c r="N1677">
+        <v>0</v>
+      </c>
+      <c r="O1677">
+        <v>0</v>
+      </c>
+      <c r="P1677">
+        <v>1.65</v>
+      </c>
+      <c r="Q1677">
+        <v>0</v>
+      </c>
+      <c r="R1677">
+        <v>0</v>
+      </c>
+      <c r="S1677">
+        <v>0</v>
+      </c>
+      <c r="T1677">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1678" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1678">
+        <v>1</v>
+      </c>
+      <c r="D1678">
+        <v>1</v>
+      </c>
+      <c r="E1678">
+        <v>0</v>
+      </c>
+      <c r="F1678">
+        <v>0</v>
+      </c>
+      <c r="G1678">
+        <v>0</v>
+      </c>
+      <c r="H1678">
+        <v>0</v>
+      </c>
+      <c r="I1678">
+        <v>0</v>
+      </c>
+      <c r="J1678">
+        <v>0</v>
+      </c>
+      <c r="K1678">
+        <v>0</v>
+      </c>
+      <c r="L1678">
+        <v>1</v>
+      </c>
+      <c r="M1678">
+        <v>1</v>
+      </c>
+      <c r="N1678">
+        <v>0</v>
+      </c>
+      <c r="O1678">
+        <v>0</v>
+      </c>
+      <c r="P1678">
+        <v>0</v>
+      </c>
+      <c r="Q1678">
+        <v>0</v>
+      </c>
+      <c r="R1678">
+        <v>0</v>
+      </c>
+      <c r="S1678">
+        <v>0</v>
+      </c>
+      <c r="T1678">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1679" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1679">
+        <v>1</v>
+      </c>
+      <c r="D1679">
+        <v>1</v>
+      </c>
+      <c r="E1679">
+        <v>0</v>
+      </c>
+      <c r="F1679">
+        <v>10</v>
+      </c>
+      <c r="G1679">
+        <v>10</v>
+      </c>
+      <c r="H1679">
+        <v>10</v>
+      </c>
+      <c r="I1679">
+        <v>0</v>
+      </c>
+      <c r="J1679">
+        <v>0</v>
+      </c>
+      <c r="K1679">
+        <v>142.86000000000001</v>
+      </c>
+      <c r="L1679">
+        <v>7</v>
+      </c>
+      <c r="M1679">
+        <v>3</v>
+      </c>
+      <c r="N1679">
+        <v>0</v>
+      </c>
+      <c r="O1679">
+        <v>1</v>
+      </c>
+      <c r="P1679">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Q1679">
+        <v>0</v>
+      </c>
+      <c r="R1679">
+        <v>0</v>
+      </c>
+      <c r="S1679">
+        <v>0</v>
+      </c>
+      <c r="T1679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1680" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1680">
+        <v>1</v>
+      </c>
+      <c r="D1680">
+        <v>1</v>
+      </c>
+      <c r="E1680">
+        <v>1</v>
+      </c>
+      <c r="F1680">
+        <v>7</v>
+      </c>
+      <c r="H1680" t="s">
+        <v>316</v>
+      </c>
+      <c r="I1680">
+        <v>0</v>
+      </c>
+      <c r="J1680">
+        <v>0</v>
+      </c>
+      <c r="K1680">
+        <v>100</v>
+      </c>
+      <c r="L1680">
+        <v>7</v>
+      </c>
+      <c r="M1680">
+        <v>5</v>
+      </c>
+      <c r="N1680">
+        <v>0</v>
+      </c>
+      <c r="O1680">
+        <v>1</v>
+      </c>
+      <c r="P1680">
+        <v>5.74</v>
+      </c>
+      <c r="Q1680">
+        <v>0</v>
+      </c>
+      <c r="R1680">
+        <v>0</v>
+      </c>
+      <c r="S1680">
+        <v>0</v>
+      </c>
+      <c r="T1680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1681" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1681">
+        <v>1</v>
+      </c>
+      <c r="D1681">
+        <v>1</v>
+      </c>
+      <c r="E1681">
+        <v>0</v>
+      </c>
+      <c r="F1681">
+        <v>6</v>
+      </c>
+      <c r="G1681">
+        <v>6</v>
+      </c>
+      <c r="H1681">
+        <v>6</v>
+      </c>
+      <c r="I1681">
+        <v>0</v>
+      </c>
+      <c r="J1681">
+        <v>0</v>
+      </c>
+      <c r="K1681">
+        <v>120</v>
+      </c>
+      <c r="L1681">
+        <v>5</v>
+      </c>
+      <c r="M1681">
+        <v>2</v>
+      </c>
+      <c r="N1681">
+        <v>1</v>
+      </c>
+      <c r="O1681">
+        <v>0</v>
+      </c>
+      <c r="P1681">
+        <v>4.96</v>
+      </c>
+      <c r="Q1681">
+        <v>0</v>
+      </c>
+      <c r="R1681">
+        <v>0</v>
+      </c>
+      <c r="S1681">
+        <v>0</v>
+      </c>
+      <c r="T1681">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1682" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1682">
+        <v>1</v>
+      </c>
+      <c r="D1682">
+        <v>1</v>
+      </c>
+      <c r="E1682">
+        <v>0</v>
+      </c>
+      <c r="F1682">
+        <v>11</v>
+      </c>
+      <c r="G1682">
+        <v>11</v>
+      </c>
+      <c r="H1682">
+        <v>11</v>
+      </c>
+      <c r="I1682">
+        <v>0</v>
+      </c>
+      <c r="J1682">
+        <v>0</v>
+      </c>
+      <c r="K1682">
+        <v>73.33</v>
+      </c>
+      <c r="L1682">
+        <v>15</v>
+      </c>
+      <c r="M1682">
+        <v>10</v>
+      </c>
+      <c r="N1682">
+        <v>2</v>
+      </c>
+      <c r="O1682">
+        <v>0</v>
+      </c>
+      <c r="P1682">
+        <v>9.02</v>
+      </c>
+      <c r="Q1682">
+        <v>1</v>
+      </c>
+      <c r="R1682">
+        <v>0</v>
+      </c>
+      <c r="S1682">
+        <v>0</v>
+      </c>
+      <c r="T1682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1683" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1683">
+        <v>1</v>
+      </c>
+      <c r="D1683">
+        <v>1</v>
+      </c>
+      <c r="E1683">
+        <v>1</v>
+      </c>
+      <c r="F1683">
+        <v>1</v>
+      </c>
+      <c r="H1683" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1683">
+        <v>0</v>
+      </c>
+      <c r="J1683">
+        <v>0</v>
+      </c>
+      <c r="K1683">
+        <v>25</v>
+      </c>
+      <c r="L1683">
+        <v>4</v>
+      </c>
+      <c r="M1683">
+        <v>3</v>
+      </c>
+      <c r="N1683">
+        <v>0</v>
+      </c>
+      <c r="O1683">
+        <v>0</v>
+      </c>
+      <c r="P1683">
+        <v>0.83</v>
+      </c>
+      <c r="Q1683">
+        <v>0</v>
+      </c>
+      <c r="R1683">
+        <v>0</v>
+      </c>
+      <c r="S1683">
+        <v>0</v>
+      </c>
+      <c r="T1683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1684" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1684">
+        <v>1</v>
+      </c>
+      <c r="D1684">
+        <v>1</v>
+      </c>
+      <c r="E1684">
+        <v>0</v>
+      </c>
+      <c r="F1684">
+        <v>0</v>
+      </c>
+      <c r="G1684">
+        <v>0</v>
+      </c>
+      <c r="H1684">
+        <v>0</v>
+      </c>
+      <c r="I1684">
+        <v>0</v>
+      </c>
+      <c r="J1684">
+        <v>0</v>
+      </c>
+      <c r="K1684">
+        <v>0</v>
+      </c>
+      <c r="L1684">
+        <v>1</v>
+      </c>
+      <c r="M1684">
+        <v>1</v>
+      </c>
+      <c r="N1684">
+        <v>0</v>
+      </c>
+      <c r="O1684">
+        <v>0</v>
+      </c>
+      <c r="P1684">
+        <v>0</v>
+      </c>
+      <c r="Q1684">
+        <v>1</v>
+      </c>
+      <c r="R1684">
+        <v>0</v>
+      </c>
+      <c r="S1684">
+        <v>0</v>
+      </c>
+      <c r="T1684">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1685" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1685">
+        <v>1</v>
+      </c>
+      <c r="D1685">
+        <v>1</v>
+      </c>
+      <c r="E1685">
+        <v>0</v>
+      </c>
+      <c r="F1685">
+        <v>0</v>
+      </c>
+      <c r="G1685">
+        <v>0</v>
+      </c>
+      <c r="H1685">
+        <v>0</v>
+      </c>
+      <c r="I1685">
+        <v>0</v>
+      </c>
+      <c r="J1685">
+        <v>0</v>
+      </c>
+      <c r="K1685">
+        <v>0</v>
+      </c>
+      <c r="L1685">
+        <v>1</v>
+      </c>
+      <c r="M1685">
+        <v>1</v>
+      </c>
+      <c r="N1685">
+        <v>0</v>
+      </c>
+      <c r="O1685">
+        <v>0</v>
+      </c>
+      <c r="P1685">
+        <v>0</v>
+      </c>
+      <c r="Q1685">
+        <v>0</v>
+      </c>
+      <c r="R1685">
+        <v>0</v>
+      </c>
+      <c r="S1685">
+        <v>0</v>
+      </c>
+      <c r="T1685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1686" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1686">
+        <v>1</v>
+      </c>
+      <c r="D1686">
+        <v>1</v>
+      </c>
+      <c r="E1686">
+        <v>0</v>
+      </c>
+      <c r="F1686">
+        <v>15</v>
+      </c>
+      <c r="G1686">
+        <v>15</v>
+      </c>
+      <c r="H1686">
+        <v>15</v>
+      </c>
+      <c r="I1686">
+        <v>0</v>
+      </c>
+      <c r="J1686">
+        <v>0</v>
+      </c>
+      <c r="K1686">
+        <v>125</v>
+      </c>
+      <c r="L1686">
+        <v>12</v>
+      </c>
+      <c r="M1686">
+        <v>8</v>
+      </c>
+      <c r="N1686">
+        <v>2</v>
+      </c>
+      <c r="O1686">
+        <v>1</v>
+      </c>
+      <c r="P1686">
+        <v>12.3</v>
+      </c>
+      <c r="Q1686">
+        <v>0</v>
+      </c>
+      <c r="R1686">
+        <v>0</v>
+      </c>
+      <c r="S1686">
+        <v>0</v>
+      </c>
+      <c r="T1686">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1687" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>723</v>
+      </c>
+      <c r="C1687">
+        <v>1</v>
+      </c>
+      <c r="D1687">
+        <v>1</v>
+      </c>
+      <c r="E1687">
+        <v>0</v>
+      </c>
+      <c r="F1687">
+        <v>8</v>
+      </c>
+      <c r="G1687">
+        <v>8</v>
+      </c>
+      <c r="H1687">
+        <v>8</v>
+      </c>
+      <c r="I1687">
+        <v>0</v>
+      </c>
+      <c r="J1687">
+        <v>0</v>
+      </c>
+      <c r="K1687">
+        <v>50</v>
+      </c>
+      <c r="L1687">
+        <v>16</v>
+      </c>
+      <c r="M1687">
+        <v>11</v>
+      </c>
+      <c r="N1687">
+        <v>1</v>
+      </c>
+      <c r="O1687">
+        <v>0</v>
+      </c>
+      <c r="P1687">
+        <v>6.61</v>
+      </c>
+      <c r="Q1687">
+        <v>0</v>
+      </c>
+      <c r="R1687">
+        <v>0</v>
+      </c>
+      <c r="S1687">
+        <v>0</v>
+      </c>
+      <c r="T1687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1688" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1688">
+        <v>1</v>
+      </c>
+      <c r="D1688">
+        <v>0</v>
+      </c>
+      <c r="E1688">
+        <v>0</v>
+      </c>
+      <c r="F1688">
+        <v>0</v>
+      </c>
+      <c r="I1688">
+        <v>0</v>
+      </c>
+      <c r="J1688">
+        <v>0</v>
+      </c>
+      <c r="L1688">
+        <v>0</v>
+      </c>
+      <c r="M1688">
+        <v>0</v>
+      </c>
+      <c r="N1688">
+        <v>0</v>
+      </c>
+      <c r="O1688">
+        <v>0</v>
+      </c>
+      <c r="P1688">
+        <v>0</v>
+      </c>
+      <c r="Q1688">
+        <v>0</v>
+      </c>
+      <c r="R1688">
+        <v>0</v>
+      </c>
+      <c r="S1688">
+        <v>0</v>
+      </c>
+      <c r="T1688">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1689" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>691</v>
+      </c>
+      <c r="C1689">
+        <v>1</v>
+      </c>
+      <c r="D1689">
+        <v>1</v>
+      </c>
+      <c r="E1689">
+        <v>0</v>
+      </c>
+      <c r="F1689">
+        <v>8</v>
+      </c>
+      <c r="G1689">
+        <v>8</v>
+      </c>
+      <c r="H1689">
+        <v>8</v>
+      </c>
+      <c r="I1689">
+        <v>0</v>
+      </c>
+      <c r="J1689">
+        <v>0</v>
+      </c>
+      <c r="K1689">
+        <v>72.73</v>
+      </c>
+      <c r="L1689">
+        <v>11</v>
+      </c>
+      <c r="M1689">
+        <v>7</v>
+      </c>
+      <c r="N1689">
+        <v>1</v>
+      </c>
+      <c r="O1689">
+        <v>0</v>
+      </c>
+      <c r="P1689">
+        <v>6.61</v>
+      </c>
+      <c r="Q1689">
+        <v>0</v>
+      </c>
+      <c r="R1689">
+        <v>0</v>
+      </c>
+      <c r="S1689">
+        <v>0</v>
+      </c>
+      <c r="T1689">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1690" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>724</v>
+      </c>
+      <c r="C1690">
+        <v>1</v>
+      </c>
+      <c r="D1690">
+        <v>1</v>
+      </c>
+      <c r="E1690">
+        <v>0</v>
+      </c>
+      <c r="F1690">
+        <v>12</v>
+      </c>
+      <c r="G1690">
+        <v>12</v>
+      </c>
+      <c r="H1690">
+        <v>12</v>
+      </c>
+      <c r="I1690">
+        <v>0</v>
+      </c>
+      <c r="J1690">
+        <v>0</v>
+      </c>
+      <c r="K1690">
+        <v>120</v>
+      </c>
+      <c r="L1690">
+        <v>10</v>
+      </c>
+      <c r="M1690">
+        <v>3</v>
+      </c>
+      <c r="N1690">
+        <v>1</v>
+      </c>
+      <c r="O1690">
+        <v>0</v>
+      </c>
+      <c r="P1690">
+        <v>9.92</v>
+      </c>
+      <c r="Q1690">
+        <v>0</v>
+      </c>
+      <c r="R1690">
+        <v>0</v>
+      </c>
+      <c r="S1690">
+        <v>0</v>
+      </c>
+      <c r="T1690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1691" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1691">
+        <v>1</v>
+      </c>
+      <c r="D1691">
+        <v>1</v>
+      </c>
+      <c r="E1691">
+        <v>0</v>
+      </c>
+      <c r="F1691">
+        <v>8</v>
+      </c>
+      <c r="G1691">
+        <v>8</v>
+      </c>
+      <c r="H1691">
+        <v>8</v>
+      </c>
+      <c r="I1691">
+        <v>0</v>
+      </c>
+      <c r="J1691">
+        <v>0</v>
+      </c>
+      <c r="K1691">
+        <v>88.89</v>
+      </c>
+      <c r="L1691">
+        <v>9</v>
+      </c>
+      <c r="M1691">
+        <v>7</v>
+      </c>
+      <c r="N1691">
+        <v>2</v>
+      </c>
+      <c r="O1691">
+        <v>0</v>
+      </c>
+      <c r="P1691">
+        <v>6.56</v>
+      </c>
+      <c r="Q1691">
+        <v>0</v>
+      </c>
+      <c r="R1691">
+        <v>0</v>
+      </c>
+      <c r="S1691">
+        <v>0</v>
+      </c>
+      <c r="T1691">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1692" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1692">
+        <v>1</v>
+      </c>
+      <c r="D1692">
+        <v>1</v>
+      </c>
+      <c r="E1692">
+        <v>1</v>
+      </c>
+      <c r="F1692">
+        <v>33</v>
+      </c>
+      <c r="H1692" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1692">
+        <v>0</v>
+      </c>
+      <c r="J1692">
+        <v>0</v>
+      </c>
+      <c r="K1692">
+        <v>143.47999999999999</v>
+      </c>
+      <c r="L1692">
+        <v>23</v>
+      </c>
+      <c r="M1692">
+        <v>9</v>
+      </c>
+      <c r="N1692">
+        <v>4</v>
+      </c>
+      <c r="O1692">
+        <v>1</v>
+      </c>
+      <c r="P1692">
+        <v>27.05</v>
+      </c>
+      <c r="Q1692">
+        <v>0</v>
+      </c>
+      <c r="R1692">
+        <v>0</v>
+      </c>
+      <c r="S1692">
+        <v>0</v>
+      </c>
+      <c r="T1692">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1693" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>682</v>
+      </c>
+      <c r="C1693">
+        <v>1</v>
+      </c>
+      <c r="D1693">
+        <v>1</v>
+      </c>
+      <c r="E1693">
+        <v>0</v>
+      </c>
+      <c r="F1693">
+        <v>4</v>
+      </c>
+      <c r="G1693">
+        <v>4</v>
+      </c>
+      <c r="H1693">
+        <v>4</v>
+      </c>
+      <c r="I1693">
+        <v>0</v>
+      </c>
+      <c r="J1693">
+        <v>0</v>
+      </c>
+      <c r="K1693">
+        <v>50</v>
+      </c>
+      <c r="L1693">
+        <v>8</v>
+      </c>
+      <c r="M1693">
+        <v>4</v>
+      </c>
+      <c r="N1693">
+        <v>0</v>
+      </c>
+      <c r="O1693">
+        <v>0</v>
+      </c>
+      <c r="P1693">
+        <v>3.28</v>
+      </c>
+      <c r="Q1693">
+        <v>3</v>
+      </c>
+      <c r="R1693">
+        <v>0</v>
+      </c>
+      <c r="S1693">
+        <v>0</v>
+      </c>
+      <c r="T1693">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1694" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1694">
+        <v>1</v>
+      </c>
+      <c r="D1694">
+        <v>1</v>
+      </c>
+      <c r="E1694">
+        <v>0</v>
+      </c>
+      <c r="F1694">
+        <v>0</v>
+      </c>
+      <c r="G1694">
+        <v>0</v>
+      </c>
+      <c r="H1694">
+        <v>0</v>
+      </c>
+      <c r="I1694">
+        <v>0</v>
+      </c>
+      <c r="J1694">
+        <v>0</v>
+      </c>
+      <c r="K1694">
+        <v>0</v>
+      </c>
+      <c r="L1694">
+        <v>3</v>
+      </c>
+      <c r="M1694">
+        <v>3</v>
+      </c>
+      <c r="N1694">
+        <v>0</v>
+      </c>
+      <c r="O1694">
+        <v>0</v>
+      </c>
+      <c r="P1694">
+        <v>0</v>
+      </c>
+      <c r="Q1694">
+        <v>0</v>
+      </c>
+      <c r="R1694">
+        <v>0</v>
+      </c>
+      <c r="S1694">
+        <v>0</v>
+      </c>
+      <c r="T1694">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1695" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1695">
+        <v>1</v>
+      </c>
+      <c r="D1695">
+        <v>1</v>
+      </c>
+      <c r="E1695">
+        <v>0</v>
+      </c>
+      <c r="F1695">
+        <v>7</v>
+      </c>
+      <c r="G1695">
+        <v>7</v>
+      </c>
+      <c r="H1695">
+        <v>7</v>
+      </c>
+      <c r="I1695">
+        <v>0</v>
+      </c>
+      <c r="J1695">
+        <v>0</v>
+      </c>
+      <c r="K1695">
+        <v>140</v>
+      </c>
+      <c r="L1695">
+        <v>5</v>
+      </c>
+      <c r="M1695">
+        <v>2</v>
+      </c>
+      <c r="N1695">
+        <v>1</v>
+      </c>
+      <c r="O1695">
+        <v>0</v>
+      </c>
+      <c r="P1695">
+        <v>5.74</v>
+      </c>
+      <c r="Q1695">
+        <v>0</v>
+      </c>
+      <c r="R1695">
+        <v>0</v>
+      </c>
+      <c r="S1695">
+        <v>0</v>
+      </c>
+      <c r="T1695">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1696" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1696">
+        <v>1</v>
+      </c>
+      <c r="D1696">
+        <v>1</v>
+      </c>
+      <c r="E1696">
+        <v>0</v>
+      </c>
+      <c r="F1696">
+        <v>24</v>
+      </c>
+      <c r="G1696">
+        <v>24</v>
+      </c>
+      <c r="H1696">
+        <v>24</v>
+      </c>
+      <c r="I1696">
+        <v>0</v>
+      </c>
+      <c r="J1696">
+        <v>0</v>
+      </c>
+      <c r="K1696">
+        <v>72.73</v>
+      </c>
+      <c r="L1696">
+        <v>33</v>
+      </c>
+      <c r="M1696">
+        <v>19</v>
+      </c>
+      <c r="N1696">
+        <v>3</v>
+      </c>
+      <c r="O1696">
+        <v>0</v>
+      </c>
+      <c r="P1696">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="Q1696">
+        <v>0</v>
+      </c>
+      <c r="R1696">
+        <v>0</v>
+      </c>
+      <c r="S1696">
+        <v>0</v>
+      </c>
+      <c r="T1696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1697" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1697">
+        <v>1</v>
+      </c>
+      <c r="D1697">
+        <v>0</v>
+      </c>
+      <c r="E1697">
+        <v>0</v>
+      </c>
+      <c r="F1697">
+        <v>0</v>
+      </c>
+      <c r="I1697">
+        <v>0</v>
+      </c>
+      <c r="J1697">
+        <v>0</v>
+      </c>
+      <c r="L1697">
+        <v>0</v>
+      </c>
+      <c r="M1697">
+        <v>0</v>
+      </c>
+      <c r="N1697">
+        <v>0</v>
+      </c>
+      <c r="O1697">
+        <v>0</v>
+      </c>
+      <c r="P1697">
+        <v>0</v>
+      </c>
+      <c r="Q1697">
+        <v>0</v>
+      </c>
+      <c r="R1697">
+        <v>0</v>
+      </c>
+      <c r="S1697">
+        <v>0</v>
+      </c>
+      <c r="T1697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1698" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>633</v>
+      </c>
+      <c r="C1698">
+        <v>1</v>
+      </c>
+      <c r="D1698">
+        <v>1</v>
+      </c>
+      <c r="E1698">
+        <v>0</v>
+      </c>
+      <c r="F1698">
+        <v>3</v>
+      </c>
+      <c r="G1698">
+        <v>3</v>
+      </c>
+      <c r="H1698">
+        <v>3</v>
+      </c>
+      <c r="I1698">
+        <v>0</v>
+      </c>
+      <c r="J1698">
+        <v>0</v>
+      </c>
+      <c r="K1698">
+        <v>37.5</v>
+      </c>
+      <c r="L1698">
+        <v>8</v>
+      </c>
+      <c r="M1698">
+        <v>6</v>
+      </c>
+      <c r="N1698">
+        <v>0</v>
+      </c>
+      <c r="O1698">
+        <v>0</v>
+      </c>
+      <c r="P1698">
+        <v>2.44</v>
+      </c>
+      <c r="Q1698">
+        <v>0</v>
+      </c>
+      <c r="R1698">
+        <v>0</v>
+      </c>
+      <c r="S1698">
+        <v>0</v>
+      </c>
+      <c r="T1698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1699" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1699">
+        <v>1</v>
+      </c>
+      <c r="D1699">
+        <v>1</v>
+      </c>
+      <c r="E1699">
+        <v>1</v>
+      </c>
+      <c r="F1699">
+        <v>5</v>
+      </c>
+      <c r="H1699" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1699">
+        <v>0</v>
+      </c>
+      <c r="J1699">
+        <v>0</v>
+      </c>
+      <c r="K1699">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="L1699">
+        <v>7</v>
+      </c>
+      <c r="M1699">
+        <v>5</v>
+      </c>
+      <c r="N1699">
+        <v>1</v>
+      </c>
+      <c r="O1699">
+        <v>0</v>
+      </c>
+      <c r="P1699">
+        <v>4.07</v>
+      </c>
+      <c r="Q1699">
+        <v>0</v>
+      </c>
+      <c r="R1699">
+        <v>0</v>
+      </c>
+      <c r="S1699">
+        <v>0</v>
+      </c>
+      <c r="T1699">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1700" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1700">
+        <v>1</v>
+      </c>
+      <c r="D1700">
+        <v>0</v>
+      </c>
+      <c r="E1700">
+        <v>0</v>
+      </c>
+      <c r="F1700">
+        <v>0</v>
+      </c>
+      <c r="I1700">
+        <v>0</v>
+      </c>
+      <c r="J1700">
+        <v>0</v>
+      </c>
+      <c r="L1700">
+        <v>0</v>
+      </c>
+      <c r="M1700">
+        <v>0</v>
+      </c>
+      <c r="N1700">
+        <v>0</v>
+      </c>
+      <c r="O1700">
+        <v>0</v>
+      </c>
+      <c r="P1700">
+        <v>0</v>
+      </c>
+      <c r="Q1700">
+        <v>0</v>
+      </c>
+      <c r="R1700">
+        <v>0</v>
+      </c>
+      <c r="S1700">
+        <v>0</v>
+      </c>
+      <c r="T1700">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1701" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>418</v>
+      </c>
+      <c r="C1701">
+        <v>1</v>
+      </c>
+      <c r="D1701">
+        <v>1</v>
+      </c>
+      <c r="E1701">
+        <v>0</v>
+      </c>
+      <c r="F1701">
+        <v>4</v>
+      </c>
+      <c r="G1701">
+        <v>4</v>
+      </c>
+      <c r="H1701">
+        <v>4</v>
+      </c>
+      <c r="I1701">
+        <v>0</v>
+      </c>
+      <c r="J1701">
+        <v>0</v>
+      </c>
+      <c r="K1701">
+        <v>66.67</v>
+      </c>
+      <c r="L1701">
+        <v>6</v>
+      </c>
+      <c r="M1701">
+        <v>3</v>
+      </c>
+      <c r="N1701">
+        <v>0</v>
+      </c>
+      <c r="O1701">
+        <v>0</v>
+      </c>
+      <c r="P1701">
+        <v>3.28</v>
+      </c>
+      <c r="Q1701">
+        <v>0</v>
+      </c>
+      <c r="R1701">
+        <v>0</v>
+      </c>
+      <c r="S1701">
+        <v>0</v>
+      </c>
+      <c r="T1701">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1702" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1702">
+        <v>1</v>
+      </c>
+      <c r="D1702">
+        <v>1</v>
+      </c>
+      <c r="E1702">
+        <v>1</v>
+      </c>
+      <c r="F1702">
+        <v>7</v>
+      </c>
+      <c r="H1702" t="s">
+        <v>316</v>
+      </c>
+      <c r="I1702">
+        <v>0</v>
+      </c>
+      <c r="J1702">
+        <v>0</v>
+      </c>
+      <c r="K1702">
+        <v>46.67</v>
+      </c>
+      <c r="L1702">
+        <v>15</v>
+      </c>
+      <c r="M1702">
+        <v>8</v>
+      </c>
+      <c r="N1702">
+        <v>0</v>
+      </c>
+      <c r="O1702">
+        <v>0</v>
+      </c>
+      <c r="P1702">
+        <v>5.69</v>
+      </c>
+      <c r="Q1702">
+        <v>0</v>
+      </c>
+      <c r="R1702">
+        <v>1</v>
+      </c>
+      <c r="S1702">
+        <v>1</v>
+      </c>
+      <c r="T1702">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1703" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1703">
+        <v>1</v>
+      </c>
+      <c r="D1703">
+        <v>1</v>
+      </c>
+      <c r="E1703">
+        <v>0</v>
+      </c>
+      <c r="F1703">
+        <v>4</v>
+      </c>
+      <c r="G1703">
+        <v>4</v>
+      </c>
+      <c r="H1703">
+        <v>4</v>
+      </c>
+      <c r="I1703">
+        <v>0</v>
+      </c>
+      <c r="J1703">
+        <v>0</v>
+      </c>
+      <c r="K1703">
+        <v>100</v>
+      </c>
+      <c r="L1703">
+        <v>4</v>
+      </c>
+      <c r="M1703">
+        <v>3</v>
+      </c>
+      <c r="N1703">
+        <v>1</v>
+      </c>
+      <c r="O1703">
+        <v>0</v>
+      </c>
+      <c r="P1703">
+        <v>3.28</v>
+      </c>
+      <c r="Q1703">
+        <v>0</v>
+      </c>
+      <c r="R1703">
+        <v>0</v>
+      </c>
+      <c r="S1703">
+        <v>0</v>
+      </c>
+      <c r="T1703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1704" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>700</v>
+      </c>
+      <c r="C1704">
+        <v>1</v>
+      </c>
+      <c r="D1704">
+        <v>1</v>
+      </c>
+      <c r="E1704">
+        <v>0</v>
+      </c>
+      <c r="F1704">
+        <v>13</v>
+      </c>
+      <c r="G1704">
+        <v>13</v>
+      </c>
+      <c r="H1704">
+        <v>13</v>
+      </c>
+      <c r="I1704">
+        <v>0</v>
+      </c>
+      <c r="J1704">
+        <v>0</v>
+      </c>
+      <c r="K1704">
+        <v>162.5</v>
+      </c>
+      <c r="L1704">
+        <v>8</v>
+      </c>
+      <c r="M1704">
+        <v>4</v>
+      </c>
+      <c r="N1704">
+        <v>1</v>
+      </c>
+      <c r="O1704">
+        <v>1</v>
+      </c>
+      <c r="P1704">
+        <v>10.57</v>
+      </c>
+      <c r="Q1704">
+        <v>0</v>
+      </c>
+      <c r="R1704">
+        <v>0</v>
+      </c>
+      <c r="S1704">
+        <v>0</v>
+      </c>
+      <c r="T1704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1705" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1705">
+        <v>1</v>
+      </c>
+      <c r="D1705">
+        <v>1</v>
+      </c>
+      <c r="E1705">
+        <v>1</v>
+      </c>
+      <c r="F1705">
+        <v>30</v>
+      </c>
+      <c r="H1705" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1705">
+        <v>0</v>
+      </c>
+      <c r="J1705">
+        <v>0</v>
+      </c>
+      <c r="K1705">
+        <v>157.88999999999999</v>
+      </c>
+      <c r="L1705">
+        <v>19</v>
+      </c>
+      <c r="M1705">
+        <v>4</v>
+      </c>
+      <c r="N1705">
+        <v>3</v>
+      </c>
+      <c r="O1705">
+        <v>0</v>
+      </c>
+      <c r="P1705">
+        <v>24.39</v>
+      </c>
+      <c r="Q1705">
+        <v>0</v>
+      </c>
+      <c r="R1705">
+        <v>0</v>
+      </c>
+      <c r="S1705">
+        <v>0</v>
+      </c>
+      <c r="T1705">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1706" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1706">
+        <v>1</v>
+      </c>
+      <c r="D1706">
+        <v>1</v>
+      </c>
+      <c r="E1706">
+        <v>0</v>
+      </c>
+      <c r="F1706">
+        <v>7</v>
+      </c>
+      <c r="G1706">
+        <v>7</v>
+      </c>
+      <c r="H1706">
+        <v>7</v>
+      </c>
+      <c r="I1706">
+        <v>0</v>
+      </c>
+      <c r="J1706">
+        <v>0</v>
+      </c>
+      <c r="K1706">
+        <v>58.33</v>
+      </c>
+      <c r="L1706">
+        <v>12</v>
+      </c>
+      <c r="M1706">
+        <v>7</v>
+      </c>
+      <c r="N1706">
+        <v>0</v>
+      </c>
+      <c r="O1706">
+        <v>0</v>
+      </c>
+      <c r="P1706">
+        <v>5.69</v>
+      </c>
+      <c r="Q1706">
+        <v>0</v>
+      </c>
+      <c r="R1706">
+        <v>0</v>
+      </c>
+      <c r="S1706">
+        <v>0</v>
+      </c>
+      <c r="T1706">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1707" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>431</v>
+      </c>
+      <c r="C1707">
+        <v>1</v>
+      </c>
+      <c r="D1707">
+        <v>1</v>
+      </c>
+      <c r="E1707">
+        <v>0</v>
+      </c>
+      <c r="F1707">
+        <v>20</v>
+      </c>
+      <c r="G1707">
+        <v>20</v>
+      </c>
+      <c r="H1707">
+        <v>20</v>
+      </c>
+      <c r="I1707">
+        <v>0</v>
+      </c>
+      <c r="J1707">
+        <v>0</v>
+      </c>
+      <c r="K1707">
+        <v>125</v>
+      </c>
+      <c r="L1707">
+        <v>16</v>
+      </c>
+      <c r="M1707">
+        <v>9</v>
+      </c>
+      <c r="N1707">
+        <v>2</v>
+      </c>
+      <c r="O1707">
+        <v>1</v>
+      </c>
+      <c r="P1707">
+        <v>16.39</v>
+      </c>
+      <c r="Q1707">
+        <v>0</v>
+      </c>
+      <c r="R1707">
+        <v>0</v>
+      </c>
+      <c r="S1707">
+        <v>0</v>
+      </c>
+      <c r="T1707">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1708" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>677</v>
+      </c>
+      <c r="C1708">
+        <v>1</v>
+      </c>
+      <c r="D1708">
+        <v>1</v>
+      </c>
+      <c r="E1708">
+        <v>0</v>
+      </c>
+      <c r="F1708">
+        <v>8</v>
+      </c>
+      <c r="G1708">
+        <v>8</v>
+      </c>
+      <c r="H1708">
+        <v>8</v>
+      </c>
+      <c r="I1708">
+        <v>0</v>
+      </c>
+      <c r="J1708">
+        <v>0</v>
+      </c>
+      <c r="K1708">
+        <v>88.89</v>
+      </c>
+      <c r="L1708">
+        <v>9</v>
+      </c>
+      <c r="M1708">
+        <v>7</v>
+      </c>
+      <c r="N1708">
+        <v>2</v>
+      </c>
+      <c r="O1708">
+        <v>0</v>
+      </c>
+      <c r="P1708">
+        <v>6.56</v>
+      </c>
+      <c r="Q1708">
+        <v>0</v>
+      </c>
+      <c r="R1708">
+        <v>1</v>
+      </c>
+      <c r="S1708">
+        <v>0</v>
+      </c>
+      <c r="T1708">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1709" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1709">
+        <v>1</v>
+      </c>
+      <c r="D1709">
+        <v>1</v>
+      </c>
+      <c r="E1709">
+        <v>1</v>
+      </c>
+      <c r="F1709">
+        <v>6</v>
+      </c>
+      <c r="H1709" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1709">
+        <v>0</v>
+      </c>
+      <c r="J1709">
+        <v>0</v>
+      </c>
+      <c r="K1709">
+        <v>150</v>
+      </c>
+      <c r="L1709">
+        <v>4</v>
+      </c>
+      <c r="M1709">
+        <v>1</v>
+      </c>
+      <c r="N1709">
+        <v>1</v>
+      </c>
+      <c r="O1709">
+        <v>0</v>
+      </c>
+      <c r="P1709">
+        <v>4.92</v>
+      </c>
+      <c r="Q1709">
+        <v>0</v>
+      </c>
+      <c r="R1709">
+        <v>0</v>
+      </c>
+      <c r="S1709">
+        <v>0</v>
+      </c>
+      <c r="T1709">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1710" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>726</v>
+      </c>
+      <c r="C1710">
+        <v>1</v>
+      </c>
+      <c r="D1710">
+        <v>1</v>
+      </c>
+      <c r="E1710">
+        <v>0</v>
+      </c>
+      <c r="F1710">
+        <v>9</v>
+      </c>
+      <c r="G1710">
+        <v>9</v>
+      </c>
+      <c r="H1710">
+        <v>9</v>
+      </c>
+      <c r="I1710">
+        <v>0</v>
+      </c>
+      <c r="J1710">
+        <v>0</v>
+      </c>
+      <c r="K1710">
+        <v>128.57</v>
+      </c>
+      <c r="L1710">
+        <v>7</v>
+      </c>
+      <c r="M1710">
+        <v>4</v>
+      </c>
+      <c r="N1710">
+        <v>2</v>
+      </c>
+      <c r="O1710">
+        <v>0</v>
+      </c>
+      <c r="P1710">
+        <v>7.38</v>
+      </c>
+      <c r="Q1710">
+        <v>0</v>
+      </c>
+      <c r="R1710">
+        <v>0</v>
+      </c>
+      <c r="S1710">
+        <v>0</v>
+      </c>
+      <c r="T1710">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1711" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>504</v>
+      </c>
+      <c r="C1711">
+        <v>1</v>
+      </c>
+      <c r="D1711">
+        <v>1</v>
+      </c>
+      <c r="E1711">
+        <v>0</v>
+      </c>
+      <c r="F1711">
+        <v>4</v>
+      </c>
+      <c r="G1711">
+        <v>4</v>
+      </c>
+      <c r="H1711">
+        <v>4</v>
+      </c>
+      <c r="I1711">
+        <v>0</v>
+      </c>
+      <c r="J1711">
+        <v>0</v>
+      </c>
+      <c r="K1711">
+        <v>66.67</v>
+      </c>
+      <c r="L1711">
+        <v>6</v>
+      </c>
+      <c r="M1711">
+        <v>3</v>
+      </c>
+      <c r="N1711">
+        <v>0</v>
+      </c>
+      <c r="O1711">
+        <v>0</v>
+      </c>
+      <c r="P1711">
+        <v>3.28</v>
+      </c>
+      <c r="Q1711">
+        <v>0</v>
+      </c>
+      <c r="R1711">
+        <v>0</v>
+      </c>
+      <c r="S1711">
+        <v>0</v>
+      </c>
+      <c r="T1711">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1712" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>679</v>
+      </c>
+      <c r="C1712">
+        <v>1</v>
+      </c>
+      <c r="D1712">
+        <v>1</v>
+      </c>
+      <c r="E1712">
+        <v>0</v>
+      </c>
+      <c r="F1712">
+        <v>7</v>
+      </c>
+      <c r="G1712">
+        <v>7</v>
+      </c>
+      <c r="H1712">
+        <v>7</v>
+      </c>
+      <c r="I1712">
+        <v>0</v>
+      </c>
+      <c r="J1712">
+        <v>0</v>
+      </c>
+      <c r="K1712">
+        <v>53.85</v>
+      </c>
+      <c r="L1712">
+        <v>13</v>
+      </c>
+      <c r="M1712">
+        <v>9</v>
+      </c>
+      <c r="N1712">
+        <v>1</v>
+      </c>
+      <c r="O1712">
+        <v>0</v>
+      </c>
+      <c r="P1712">
+        <v>5.74</v>
+      </c>
+      <c r="Q1712">
+        <v>0</v>
+      </c>
+      <c r="R1712">
+        <v>0</v>
+      </c>
+      <c r="S1712">
+        <v>0</v>
+      </c>
+      <c r="T1712">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1713" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>727</v>
+      </c>
+      <c r="C1713">
+        <v>1</v>
+      </c>
+      <c r="D1713">
+        <v>1</v>
+      </c>
+      <c r="E1713">
+        <v>0</v>
+      </c>
+      <c r="F1713">
+        <v>3</v>
+      </c>
+      <c r="G1713">
+        <v>3</v>
+      </c>
+      <c r="H1713">
+        <v>3</v>
+      </c>
+      <c r="I1713">
+        <v>0</v>
+      </c>
+      <c r="J1713">
+        <v>0</v>
+      </c>
+      <c r="K1713">
+        <v>50</v>
+      </c>
+      <c r="L1713">
+        <v>6</v>
+      </c>
+      <c r="M1713">
+        <v>3</v>
+      </c>
+      <c r="N1713">
+        <v>0</v>
+      </c>
+      <c r="O1713">
+        <v>0</v>
+      </c>
+      <c r="P1713">
+        <v>2.46</v>
+      </c>
+      <c r="Q1713">
+        <v>0</v>
+      </c>
+      <c r="R1713">
+        <v>0</v>
+      </c>
+      <c r="S1713">
+        <v>0</v>
+      </c>
+      <c r="T1713">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1714" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1714">
+        <v>1</v>
+      </c>
+      <c r="D1714">
+        <v>0</v>
+      </c>
+      <c r="E1714">
+        <v>0</v>
+      </c>
+      <c r="F1714">
+        <v>0</v>
+      </c>
+      <c r="I1714">
+        <v>0</v>
+      </c>
+      <c r="J1714">
+        <v>0</v>
+      </c>
+      <c r="L1714">
+        <v>0</v>
+      </c>
+      <c r="M1714">
+        <v>0</v>
+      </c>
+      <c r="N1714">
+        <v>0</v>
+      </c>
+      <c r="O1714">
+        <v>0</v>
+      </c>
+      <c r="P1714">
+        <v>0</v>
+      </c>
+      <c r="Q1714">
+        <v>0</v>
+      </c>
+      <c r="R1714">
+        <v>0</v>
+      </c>
+      <c r="S1714">
+        <v>0</v>
+      </c>
+      <c r="T1714">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1715" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1715">
+        <v>1</v>
+      </c>
+      <c r="D1715">
+        <v>1</v>
+      </c>
+      <c r="E1715">
+        <v>0</v>
+      </c>
+      <c r="F1715">
+        <v>29</v>
+      </c>
+      <c r="G1715">
+        <v>29</v>
+      </c>
+      <c r="H1715">
+        <v>29</v>
+      </c>
+      <c r="I1715">
+        <v>0</v>
+      </c>
+      <c r="J1715">
+        <v>0</v>
+      </c>
+      <c r="K1715">
+        <v>96.67</v>
+      </c>
+      <c r="L1715">
+        <v>30</v>
+      </c>
+      <c r="M1715">
+        <v>16</v>
+      </c>
+      <c r="N1715">
+        <v>3</v>
+      </c>
+      <c r="O1715">
+        <v>1</v>
+      </c>
+      <c r="P1715">
+        <v>23.77</v>
+      </c>
+      <c r="Q1715">
+        <v>0</v>
+      </c>
+      <c r="R1715">
+        <v>0</v>
+      </c>
+      <c r="S1715">
+        <v>0</v>
+      </c>
+      <c r="T1715">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1716" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1716">
+        <v>1</v>
+      </c>
+      <c r="D1716">
+        <v>1</v>
+      </c>
+      <c r="E1716">
+        <v>0</v>
+      </c>
+      <c r="F1716">
+        <v>5</v>
+      </c>
+      <c r="G1716">
+        <v>5</v>
+      </c>
+      <c r="H1716">
+        <v>5</v>
+      </c>
+      <c r="I1716">
+        <v>0</v>
+      </c>
+      <c r="J1716">
+        <v>0</v>
+      </c>
+      <c r="K1716">
+        <v>33.33</v>
+      </c>
+      <c r="L1716">
+        <v>15</v>
+      </c>
+      <c r="M1716">
+        <v>11</v>
+      </c>
+      <c r="N1716">
+        <v>0</v>
+      </c>
+      <c r="O1716">
+        <v>0</v>
+      </c>
+      <c r="P1716">
+        <v>4.55</v>
+      </c>
+      <c r="Q1716">
+        <v>0</v>
+      </c>
+      <c r="R1716">
+        <v>0</v>
+      </c>
+      <c r="S1716">
+        <v>0</v>
+      </c>
+      <c r="T1716">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1717" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>663</v>
+      </c>
+      <c r="C1717">
+        <v>1</v>
+      </c>
+      <c r="D1717">
+        <v>1</v>
+      </c>
+      <c r="E1717">
+        <v>1</v>
+      </c>
+      <c r="F1717">
+        <v>32</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1717">
+        <v>0</v>
+      </c>
+      <c r="J1717">
+        <v>0</v>
+      </c>
+      <c r="K1717">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1717">
+        <v>24</v>
+      </c>
+      <c r="M1717">
+        <v>13</v>
+      </c>
+      <c r="N1717">
+        <v>5</v>
+      </c>
+      <c r="O1717">
+        <v>1</v>
+      </c>
+      <c r="P1717">
+        <v>20.38</v>
+      </c>
+      <c r="Q1717">
+        <v>0</v>
+      </c>
+      <c r="R1717">
+        <v>0</v>
+      </c>
+      <c r="S1717">
+        <v>0</v>
+      </c>
+      <c r="T1717">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1718" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1718">
+        <v>1</v>
+      </c>
+      <c r="D1718">
+        <v>1</v>
+      </c>
+      <c r="E1718">
+        <v>0</v>
+      </c>
+      <c r="F1718">
+        <v>22</v>
+      </c>
+      <c r="G1718">
+        <v>22</v>
+      </c>
+      <c r="H1718">
+        <v>22</v>
+      </c>
+      <c r="I1718">
+        <v>0</v>
+      </c>
+      <c r="J1718">
+        <v>0</v>
+      </c>
+      <c r="K1718">
+        <v>110</v>
+      </c>
+      <c r="L1718">
+        <v>20</v>
+      </c>
+      <c r="M1718">
+        <v>10</v>
+      </c>
+      <c r="N1718">
+        <v>4</v>
+      </c>
+      <c r="O1718">
+        <v>0</v>
+      </c>
+      <c r="P1718">
+        <v>20</v>
+      </c>
+      <c r="Q1718">
+        <v>0</v>
+      </c>
+      <c r="R1718">
+        <v>0</v>
+      </c>
+      <c r="S1718">
+        <v>0</v>
+      </c>
+      <c r="T1718">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1719" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1719">
+        <v>1</v>
+      </c>
+      <c r="D1719">
+        <v>1</v>
+      </c>
+      <c r="E1719">
+        <v>1</v>
+      </c>
+      <c r="F1719">
+        <v>31</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1719">
+        <v>0</v>
+      </c>
+      <c r="J1719">
+        <v>0</v>
+      </c>
+      <c r="K1719">
+        <v>129.16999999999999</v>
+      </c>
+      <c r="L1719">
+        <v>24</v>
+      </c>
+      <c r="M1719">
+        <v>4</v>
+      </c>
+      <c r="N1719">
+        <v>2</v>
+      </c>
+      <c r="O1719">
+        <v>0</v>
+      </c>
+      <c r="P1719">
+        <v>19.75</v>
+      </c>
+      <c r="Q1719">
+        <v>1</v>
+      </c>
+      <c r="R1719">
+        <v>0</v>
+      </c>
+      <c r="S1719">
+        <v>0</v>
+      </c>
+      <c r="T1719">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1720" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>417</v>
+      </c>
+      <c r="C1720">
+        <v>1</v>
+      </c>
+      <c r="D1720">
+        <v>0</v>
+      </c>
+      <c r="E1720">
+        <v>0</v>
+      </c>
+      <c r="F1720">
+        <v>0</v>
+      </c>
+      <c r="I1720">
+        <v>0</v>
+      </c>
+      <c r="J1720">
+        <v>0</v>
+      </c>
+      <c r="L1720">
+        <v>0</v>
+      </c>
+      <c r="M1720">
+        <v>0</v>
+      </c>
+      <c r="N1720">
+        <v>0</v>
+      </c>
+      <c r="O1720">
+        <v>0</v>
+      </c>
+      <c r="P1720">
+        <v>0</v>
+      </c>
+      <c r="Q1720">
+        <v>0</v>
+      </c>
+      <c r="R1720">
+        <v>0</v>
+      </c>
+      <c r="S1720">
+        <v>0</v>
+      </c>
+      <c r="T1720">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1721" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1721">
+        <v>1</v>
+      </c>
+      <c r="D1721">
+        <v>1</v>
+      </c>
+      <c r="E1721">
+        <v>0</v>
+      </c>
+      <c r="F1721">
+        <v>14</v>
+      </c>
+      <c r="G1721">
+        <v>14</v>
+      </c>
+      <c r="H1721">
+        <v>14</v>
+      </c>
+      <c r="I1721">
+        <v>0</v>
+      </c>
+      <c r="J1721">
+        <v>0</v>
+      </c>
+      <c r="K1721">
+        <v>100</v>
+      </c>
+      <c r="L1721">
+        <v>14</v>
+      </c>
+      <c r="M1721">
+        <v>7</v>
+      </c>
+      <c r="N1721">
+        <v>2</v>
+      </c>
+      <c r="O1721">
+        <v>0</v>
+      </c>
+      <c r="P1721">
+        <v>12.73</v>
+      </c>
+      <c r="Q1721">
+        <v>0</v>
+      </c>
+      <c r="R1721">
+        <v>0</v>
+      </c>
+      <c r="S1721">
+        <v>0</v>
+      </c>
+      <c r="T1721">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1722" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1722">
+        <v>1</v>
+      </c>
+      <c r="D1722">
+        <v>1</v>
+      </c>
+      <c r="E1722">
+        <v>0</v>
+      </c>
+      <c r="F1722">
+        <v>8</v>
+      </c>
+      <c r="G1722">
+        <v>8</v>
+      </c>
+      <c r="H1722">
+        <v>8</v>
+      </c>
+      <c r="I1722">
+        <v>0</v>
+      </c>
+      <c r="J1722">
+        <v>0</v>
+      </c>
+      <c r="K1722">
+        <v>53.33</v>
+      </c>
+      <c r="L1722">
+        <v>15</v>
+      </c>
+      <c r="M1722">
+        <v>8</v>
+      </c>
+      <c r="N1722">
+        <v>0</v>
+      </c>
+      <c r="O1722">
+        <v>0</v>
+      </c>
+      <c r="P1722">
+        <v>7.27</v>
+      </c>
+      <c r="Q1722">
+        <v>0</v>
+      </c>
+      <c r="R1722">
+        <v>0</v>
+      </c>
+      <c r="S1722">
+        <v>0</v>
+      </c>
+      <c r="T1722">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1723" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1723">
+        <v>1</v>
+      </c>
+      <c r="D1723">
+        <v>1</v>
+      </c>
+      <c r="E1723">
+        <v>0</v>
+      </c>
+      <c r="F1723">
+        <v>2</v>
+      </c>
+      <c r="G1723">
+        <v>2</v>
+      </c>
+      <c r="H1723">
+        <v>2</v>
+      </c>
+      <c r="I1723">
+        <v>0</v>
+      </c>
+      <c r="J1723">
+        <v>0</v>
+      </c>
+      <c r="K1723">
+        <v>33.33</v>
+      </c>
+      <c r="L1723">
+        <v>6</v>
+      </c>
+      <c r="M1723">
+        <v>4</v>
+      </c>
+      <c r="N1723">
+        <v>0</v>
+      </c>
+      <c r="O1723">
+        <v>0</v>
+      </c>
+      <c r="P1723">
+        <v>1.82</v>
+      </c>
+      <c r="Q1723">
+        <v>0</v>
+      </c>
+      <c r="R1723">
+        <v>0</v>
+      </c>
+      <c r="S1723">
+        <v>1</v>
+      </c>
+      <c r="T1723">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1724" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>671</v>
+      </c>
+      <c r="C1724">
+        <v>1</v>
+      </c>
+      <c r="D1724">
+        <v>1</v>
+      </c>
+      <c r="E1724">
+        <v>0</v>
+      </c>
+      <c r="F1724">
+        <v>26</v>
+      </c>
+      <c r="G1724">
+        <v>26</v>
+      </c>
+      <c r="H1724">
+        <v>26</v>
+      </c>
+      <c r="I1724">
+        <v>0</v>
+      </c>
+      <c r="J1724">
+        <v>0</v>
+      </c>
+      <c r="K1724">
+        <v>83.87</v>
+      </c>
+      <c r="L1724">
+        <v>31</v>
+      </c>
+      <c r="M1724">
+        <v>16</v>
+      </c>
+      <c r="N1724">
+        <v>2</v>
+      </c>
+      <c r="O1724">
+        <v>0</v>
+      </c>
+      <c r="P1724">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="Q1724">
+        <v>1</v>
+      </c>
+      <c r="R1724">
+        <v>0</v>
+      </c>
+      <c r="S1724">
+        <v>0</v>
+      </c>
+      <c r="T1724">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1725" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1725">
+        <v>1</v>
+      </c>
+      <c r="D1725">
+        <v>1</v>
+      </c>
+      <c r="E1725">
+        <v>0</v>
+      </c>
+      <c r="F1725">
+        <v>14</v>
+      </c>
+      <c r="G1725">
+        <v>14</v>
+      </c>
+      <c r="H1725">
+        <v>14</v>
+      </c>
+      <c r="I1725">
+        <v>0</v>
+      </c>
+      <c r="J1725">
+        <v>0</v>
+      </c>
+      <c r="K1725">
+        <v>100</v>
+      </c>
+      <c r="L1725">
+        <v>14</v>
+      </c>
+      <c r="M1725">
+        <v>6</v>
+      </c>
+      <c r="N1725">
+        <v>1</v>
+      </c>
+      <c r="O1725">
+        <v>0</v>
+      </c>
+      <c r="P1725">
+        <v>8.92</v>
+      </c>
+      <c r="Q1725">
+        <v>0</v>
+      </c>
+      <c r="R1725">
+        <v>0</v>
+      </c>
+      <c r="S1725">
+        <v>0</v>
+      </c>
+      <c r="T1725">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1726" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1726">
+        <v>1</v>
+      </c>
+      <c r="D1726">
+        <v>1</v>
+      </c>
+      <c r="E1726">
+        <v>0</v>
+      </c>
+      <c r="F1726">
+        <v>2</v>
+      </c>
+      <c r="G1726">
+        <v>2</v>
+      </c>
+      <c r="H1726">
+        <v>2</v>
+      </c>
+      <c r="I1726">
+        <v>0</v>
+      </c>
+      <c r="J1726">
+        <v>0</v>
+      </c>
+      <c r="K1726">
+        <v>100</v>
+      </c>
+      <c r="L1726">
+        <v>2</v>
+      </c>
+      <c r="M1726">
+        <v>0</v>
+      </c>
+      <c r="N1726">
+        <v>0</v>
+      </c>
+      <c r="O1726">
+        <v>0</v>
+      </c>
+      <c r="P1726">
+        <v>1.27</v>
+      </c>
+      <c r="Q1726">
+        <v>0</v>
+      </c>
+      <c r="R1726">
+        <v>0</v>
+      </c>
+      <c r="S1726">
+        <v>0</v>
+      </c>
+      <c r="T1726">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1727" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>440</v>
+      </c>
+      <c r="C1727">
+        <v>1</v>
+      </c>
+      <c r="D1727">
+        <v>0</v>
+      </c>
+      <c r="E1727">
+        <v>0</v>
+      </c>
+      <c r="F1727">
+        <v>0</v>
+      </c>
+      <c r="I1727">
+        <v>0</v>
+      </c>
+      <c r="J1727">
+        <v>0</v>
+      </c>
+      <c r="L1727">
+        <v>0</v>
+      </c>
+      <c r="M1727">
+        <v>0</v>
+      </c>
+      <c r="N1727">
+        <v>0</v>
+      </c>
+      <c r="O1727">
+        <v>0</v>
+      </c>
+      <c r="P1727">
+        <v>0</v>
+      </c>
+      <c r="Q1727">
+        <v>0</v>
+      </c>
+      <c r="R1727">
+        <v>0</v>
+      </c>
+      <c r="S1727">
+        <v>0</v>
+      </c>
+      <c r="T1727">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1728" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>665</v>
+      </c>
+      <c r="C1728">
+        <v>1</v>
+      </c>
+      <c r="D1728">
+        <v>0</v>
+      </c>
+      <c r="E1728">
+        <v>0</v>
+      </c>
+      <c r="F1728">
+        <v>0</v>
+      </c>
+      <c r="I1728">
+        <v>0</v>
+      </c>
+      <c r="J1728">
+        <v>0</v>
+      </c>
+      <c r="L1728">
+        <v>0</v>
+      </c>
+      <c r="M1728">
+        <v>0</v>
+      </c>
+      <c r="N1728">
+        <v>0</v>
+      </c>
+      <c r="O1728">
+        <v>0</v>
+      </c>
+      <c r="P1728">
+        <v>0</v>
+      </c>
+      <c r="Q1728">
+        <v>0</v>
+      </c>
+      <c r="R1728">
+        <v>0</v>
+      </c>
+      <c r="S1728">
+        <v>0</v>
+      </c>
+      <c r="T1728">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1729" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1729">
+        <v>1</v>
+      </c>
+      <c r="D1729">
+        <v>1</v>
+      </c>
+      <c r="E1729">
+        <v>1</v>
+      </c>
+      <c r="F1729">
+        <v>32</v>
+      </c>
+      <c r="H1729" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1729">
+        <v>0</v>
+      </c>
+      <c r="J1729">
+        <v>0</v>
+      </c>
+      <c r="K1729">
+        <v>128</v>
+      </c>
+      <c r="L1729">
+        <v>25</v>
+      </c>
+      <c r="M1729">
+        <v>9</v>
+      </c>
+      <c r="N1729">
+        <v>5</v>
+      </c>
+      <c r="O1729">
+        <v>0</v>
+      </c>
+      <c r="P1729">
+        <v>20.38</v>
+      </c>
+      <c r="Q1729">
+        <v>0</v>
+      </c>
+      <c r="R1729">
+        <v>0</v>
+      </c>
+      <c r="S1729">
+        <v>0</v>
+      </c>
+      <c r="T1729">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1730" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1730">
+        <v>1</v>
+      </c>
+      <c r="D1730">
+        <v>0</v>
+      </c>
+      <c r="E1730">
+        <v>0</v>
+      </c>
+      <c r="F1730">
+        <v>0</v>
+      </c>
+      <c r="I1730">
+        <v>0</v>
+      </c>
+      <c r="J1730">
+        <v>0</v>
+      </c>
+      <c r="L1730">
+        <v>0</v>
+      </c>
+      <c r="M1730">
+        <v>0</v>
+      </c>
+      <c r="N1730">
+        <v>0</v>
+      </c>
+      <c r="O1730">
+        <v>0</v>
+      </c>
+      <c r="P1730">
+        <v>0</v>
+      </c>
+      <c r="Q1730">
+        <v>1</v>
+      </c>
+      <c r="R1730">
+        <v>0</v>
+      </c>
+      <c r="S1730">
+        <v>0</v>
+      </c>
+      <c r="T1730">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1731" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>729</v>
+      </c>
+      <c r="C1731">
+        <v>1</v>
+      </c>
+      <c r="D1731">
+        <v>1</v>
+      </c>
+      <c r="E1731">
+        <v>0</v>
+      </c>
+      <c r="F1731">
+        <v>0</v>
+      </c>
+      <c r="G1731">
+        <v>0</v>
+      </c>
+      <c r="H1731">
+        <v>0</v>
+      </c>
+      <c r="I1731">
+        <v>0</v>
+      </c>
+      <c r="J1731">
+        <v>0</v>
+      </c>
+      <c r="K1731">
+        <v>0</v>
+      </c>
+      <c r="L1731">
+        <v>1</v>
+      </c>
+      <c r="M1731">
+        <v>1</v>
+      </c>
+      <c r="N1731">
+        <v>0</v>
+      </c>
+      <c r="O1731">
+        <v>0</v>
+      </c>
+      <c r="P1731">
+        <v>0</v>
+      </c>
+      <c r="Q1731">
+        <v>0</v>
+      </c>
+      <c r="R1731">
+        <v>0</v>
+      </c>
+      <c r="S1731">
+        <v>0</v>
+      </c>
+      <c r="T1731">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1732" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1732">
+        <v>1</v>
+      </c>
+      <c r="D1732">
+        <v>1</v>
+      </c>
+      <c r="E1732">
+        <v>0</v>
+      </c>
+      <c r="F1732">
+        <v>11</v>
+      </c>
+      <c r="G1732">
+        <v>11</v>
+      </c>
+      <c r="H1732">
+        <v>11</v>
+      </c>
+      <c r="I1732">
+        <v>0</v>
+      </c>
+      <c r="J1732">
+        <v>0</v>
+      </c>
+      <c r="K1732">
+        <v>122.22</v>
+      </c>
+      <c r="L1732">
+        <v>9</v>
+      </c>
+      <c r="M1732">
+        <v>4</v>
+      </c>
+      <c r="N1732">
+        <v>2</v>
+      </c>
+      <c r="O1732">
+        <v>0</v>
+      </c>
+      <c r="P1732">
+        <v>10</v>
+      </c>
+      <c r="Q1732">
+        <v>0</v>
+      </c>
+      <c r="R1732">
+        <v>0</v>
+      </c>
+      <c r="S1732">
+        <v>0</v>
+      </c>
+      <c r="T1732">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1733" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1733">
+        <v>1</v>
+      </c>
+      <c r="D1733">
+        <v>1</v>
+      </c>
+      <c r="E1733">
+        <v>0</v>
+      </c>
+      <c r="F1733">
+        <v>0</v>
+      </c>
+      <c r="G1733">
+        <v>0</v>
+      </c>
+      <c r="H1733">
+        <v>0</v>
+      </c>
+      <c r="I1733">
+        <v>0</v>
+      </c>
+      <c r="J1733">
+        <v>0</v>
+      </c>
+      <c r="K1733">
+        <v>0</v>
+      </c>
+      <c r="L1733">
+        <v>8</v>
+      </c>
+      <c r="M1733">
+        <v>8</v>
+      </c>
+      <c r="N1733">
+        <v>0</v>
+      </c>
+      <c r="O1733">
+        <v>0</v>
+      </c>
+      <c r="P1733">
+        <v>0</v>
+      </c>
+      <c r="Q1733">
+        <v>0</v>
+      </c>
+      <c r="R1733">
+        <v>0</v>
+      </c>
+      <c r="S1733">
+        <v>0</v>
+      </c>
+      <c r="T1733">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1734" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1734">
+        <v>1</v>
+      </c>
+      <c r="D1734">
+        <v>1</v>
+      </c>
+      <c r="E1734">
+        <v>0</v>
+      </c>
+      <c r="F1734">
+        <v>10</v>
+      </c>
+      <c r="G1734">
+        <v>10</v>
+      </c>
+      <c r="H1734">
+        <v>10</v>
+      </c>
+      <c r="I1734">
+        <v>0</v>
+      </c>
+      <c r="J1734">
+        <v>0</v>
+      </c>
+      <c r="K1734">
+        <v>166.67</v>
+      </c>
+      <c r="L1734">
+        <v>6</v>
+      </c>
+      <c r="M1734">
+        <v>2</v>
+      </c>
+      <c r="N1734">
+        <v>2</v>
+      </c>
+      <c r="O1734">
+        <v>0</v>
+      </c>
+      <c r="P1734">
+        <v>9.09</v>
+      </c>
+      <c r="Q1734">
+        <v>1</v>
+      </c>
+      <c r="R1734">
+        <v>0</v>
+      </c>
+      <c r="S1734">
+        <v>0</v>
+      </c>
+      <c r="T1734">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1735" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1735">
+        <v>1</v>
+      </c>
+      <c r="D1735">
+        <v>1</v>
+      </c>
+      <c r="E1735">
+        <v>1</v>
+      </c>
+      <c r="F1735">
+        <v>2</v>
+      </c>
+      <c r="H1735" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1735">
+        <v>0</v>
+      </c>
+      <c r="J1735">
+        <v>0</v>
+      </c>
+      <c r="K1735">
+        <v>200</v>
+      </c>
+      <c r="L1735">
+        <v>1</v>
+      </c>
+      <c r="M1735">
+        <v>0</v>
+      </c>
+      <c r="N1735">
+        <v>0</v>
+      </c>
+      <c r="O1735">
+        <v>0</v>
+      </c>
+      <c r="P1735">
+        <v>1.27</v>
+      </c>
+      <c r="Q1735">
+        <v>0</v>
+      </c>
+      <c r="R1735">
+        <v>0</v>
+      </c>
+      <c r="S1735">
+        <v>0</v>
+      </c>
+      <c r="T1735">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1736" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1736">
+        <v>1</v>
+      </c>
+      <c r="D1736">
+        <v>1</v>
+      </c>
+      <c r="E1736">
+        <v>1</v>
+      </c>
+      <c r="F1736">
+        <v>3</v>
+      </c>
+      <c r="H1736" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1736">
+        <v>0</v>
+      </c>
+      <c r="J1736">
+        <v>0</v>
+      </c>
+      <c r="K1736">
+        <v>25</v>
+      </c>
+      <c r="L1736">
+        <v>12</v>
+      </c>
+      <c r="M1736">
+        <v>9</v>
+      </c>
+      <c r="N1736">
+        <v>0</v>
+      </c>
+      <c r="O1736">
+        <v>0</v>
+      </c>
+      <c r="P1736">
+        <v>2.73</v>
+      </c>
+      <c r="Q1736">
+        <v>0</v>
+      </c>
+      <c r="R1736">
+        <v>0</v>
+      </c>
+      <c r="S1736">
+        <v>0</v>
+      </c>
+      <c r="T1736">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1737" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>429</v>
+      </c>
+      <c r="C1737">
+        <v>1</v>
+      </c>
+      <c r="D1737">
+        <v>1</v>
+      </c>
+      <c r="E1737">
+        <v>0</v>
+      </c>
+      <c r="F1737">
+        <v>3</v>
+      </c>
+      <c r="G1737">
+        <v>3</v>
+      </c>
+      <c r="H1737">
+        <v>3</v>
+      </c>
+      <c r="I1737">
+        <v>0</v>
+      </c>
+      <c r="J1737">
+        <v>0</v>
+      </c>
+      <c r="K1737">
+        <v>50</v>
+      </c>
+      <c r="L1737">
+        <v>6</v>
+      </c>
+      <c r="M1737">
+        <v>3</v>
+      </c>
+      <c r="N1737">
+        <v>0</v>
+      </c>
+      <c r="O1737">
+        <v>0</v>
+      </c>
+      <c r="P1737">
+        <v>2.73</v>
+      </c>
+      <c r="Q1737">
+        <v>0</v>
+      </c>
+      <c r="R1737">
+        <v>0</v>
+      </c>
+      <c r="S1737">
+        <v>0</v>
+      </c>
+      <c r="T1737">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1738" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1738">
+        <v>1</v>
+      </c>
+      <c r="D1738">
+        <v>1</v>
+      </c>
+      <c r="E1738">
+        <v>0</v>
+      </c>
+      <c r="F1738">
+        <v>26</v>
+      </c>
+      <c r="G1738">
+        <v>26</v>
+      </c>
+      <c r="H1738">
+        <v>26</v>
+      </c>
+      <c r="I1738">
+        <v>0</v>
+      </c>
+      <c r="J1738">
+        <v>0</v>
+      </c>
+      <c r="K1738">
+        <v>236.36</v>
+      </c>
+      <c r="L1738">
+        <v>11</v>
+      </c>
+      <c r="M1738">
+        <v>4</v>
+      </c>
+      <c r="N1738">
+        <v>3</v>
+      </c>
+      <c r="O1738">
+        <v>2</v>
+      </c>
+      <c r="P1738">
+        <v>17.22</v>
+      </c>
+      <c r="Q1738">
+        <v>0</v>
+      </c>
+      <c r="R1738">
+        <v>0</v>
+      </c>
+      <c r="S1738">
+        <v>0</v>
+      </c>
+      <c r="T1738">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1739" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1739">
+        <v>1</v>
+      </c>
+      <c r="D1739">
+        <v>1</v>
+      </c>
+      <c r="E1739">
+        <v>0</v>
+      </c>
+      <c r="F1739">
+        <v>12</v>
+      </c>
+      <c r="G1739">
+        <v>12</v>
+      </c>
+      <c r="H1739">
+        <v>12</v>
+      </c>
+      <c r="I1739">
+        <v>0</v>
+      </c>
+      <c r="J1739">
+        <v>0</v>
+      </c>
+      <c r="K1739">
+        <v>109.09</v>
+      </c>
+      <c r="L1739">
+        <v>11</v>
+      </c>
+      <c r="M1739">
+        <v>4</v>
+      </c>
+      <c r="N1739">
+        <v>1</v>
+      </c>
+      <c r="O1739">
+        <v>0</v>
+      </c>
+      <c r="P1739">
+        <v>7.89</v>
+      </c>
+      <c r="Q1739">
+        <v>0</v>
+      </c>
+      <c r="R1739">
+        <v>0</v>
+      </c>
+      <c r="S1739">
+        <v>0</v>
+      </c>
+      <c r="T1739">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1740" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1740">
+        <v>1</v>
+      </c>
+      <c r="D1740">
+        <v>1</v>
+      </c>
+      <c r="E1740">
+        <v>1</v>
+      </c>
+      <c r="F1740">
+        <v>28</v>
+      </c>
+      <c r="H1740" t="s">
+        <v>564</v>
+      </c>
+      <c r="I1740">
+        <v>0</v>
+      </c>
+      <c r="J1740">
+        <v>0</v>
+      </c>
+      <c r="K1740">
+        <v>121.74</v>
+      </c>
+      <c r="L1740">
+        <v>23</v>
+      </c>
+      <c r="M1740">
+        <v>9</v>
+      </c>
+      <c r="N1740">
+        <v>3</v>
+      </c>
+      <c r="O1740">
+        <v>0</v>
+      </c>
+      <c r="P1740">
+        <v>18.54</v>
+      </c>
+      <c r="Q1740">
+        <v>0</v>
+      </c>
+      <c r="R1740">
+        <v>0</v>
+      </c>
+      <c r="S1740">
+        <v>0</v>
+      </c>
+      <c r="T1740">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1741" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>384</v>
+      </c>
+      <c r="C1741">
+        <v>1</v>
+      </c>
+      <c r="D1741">
+        <v>1</v>
+      </c>
+      <c r="E1741">
+        <v>1</v>
+      </c>
+      <c r="F1741">
+        <v>3</v>
+      </c>
+      <c r="H1741" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1741">
+        <v>0</v>
+      </c>
+      <c r="J1741">
+        <v>0</v>
+      </c>
+      <c r="K1741">
+        <v>150</v>
+      </c>
+      <c r="L1741">
+        <v>2</v>
+      </c>
+      <c r="M1741">
+        <v>0</v>
+      </c>
+      <c r="N1741">
+        <v>0</v>
+      </c>
+      <c r="O1741">
+        <v>0</v>
+      </c>
+      <c r="P1741">
+        <v>1.97</v>
+      </c>
+      <c r="Q1741">
+        <v>0</v>
+      </c>
+      <c r="R1741">
+        <v>0</v>
+      </c>
+      <c r="S1741">
+        <v>0</v>
+      </c>
+      <c r="T1741">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1742" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1742">
+        <v>1</v>
+      </c>
+      <c r="D1742">
+        <v>1</v>
+      </c>
+      <c r="E1742">
+        <v>1</v>
+      </c>
+      <c r="F1742">
+        <v>32</v>
+      </c>
+      <c r="H1742" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1742">
+        <v>0</v>
+      </c>
+      <c r="J1742">
+        <v>0</v>
+      </c>
+      <c r="K1742">
+        <v>96.97</v>
+      </c>
+      <c r="L1742">
+        <v>33</v>
+      </c>
+      <c r="M1742">
+        <v>17</v>
+      </c>
+      <c r="N1742">
+        <v>4</v>
+      </c>
+      <c r="O1742">
+        <v>0</v>
+      </c>
+      <c r="P1742">
+        <v>21.19</v>
+      </c>
+      <c r="Q1742">
+        <v>1</v>
+      </c>
+      <c r="R1742">
+        <v>0</v>
+      </c>
+      <c r="S1742">
+        <v>0</v>
+      </c>
+      <c r="T1742">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1743" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>473</v>
+      </c>
+      <c r="C1743">
+        <v>1</v>
+      </c>
+      <c r="D1743">
+        <v>1</v>
+      </c>
+      <c r="E1743">
+        <v>1</v>
+      </c>
+      <c r="F1743">
+        <v>14</v>
+      </c>
+      <c r="H1743" t="s">
+        <v>205</v>
+      </c>
+      <c r="I1743">
+        <v>0</v>
+      </c>
+      <c r="J1743">
+        <v>0</v>
+      </c>
+      <c r="K1743">
+        <v>77.78</v>
+      </c>
+      <c r="L1743">
+        <v>18</v>
+      </c>
+      <c r="M1743">
+        <v>7</v>
+      </c>
+      <c r="N1743">
+        <v>0</v>
+      </c>
+      <c r="O1743">
+        <v>0</v>
+      </c>
+      <c r="P1743">
+        <v>9.27</v>
+      </c>
+      <c r="Q1743">
+        <v>0</v>
+      </c>
+      <c r="R1743">
+        <v>0</v>
+      </c>
+      <c r="S1743">
+        <v>0</v>
+      </c>
+      <c r="T1743">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1744" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1744">
+        <v>1</v>
+      </c>
+      <c r="D1744">
+        <v>1</v>
+      </c>
+      <c r="E1744">
+        <v>1</v>
+      </c>
+      <c r="F1744">
+        <v>32</v>
+      </c>
+      <c r="H1744" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1744">
+        <v>0</v>
+      </c>
+      <c r="J1744">
+        <v>0</v>
+      </c>
+      <c r="K1744">
+        <v>168.42</v>
+      </c>
+      <c r="L1744">
+        <v>19</v>
+      </c>
+      <c r="M1744">
+        <v>6</v>
+      </c>
+      <c r="N1744">
+        <v>3</v>
+      </c>
+      <c r="O1744">
+        <v>1</v>
+      </c>
+      <c r="P1744">
+        <v>21.05</v>
+      </c>
+      <c r="Q1744">
+        <v>1</v>
+      </c>
+      <c r="R1744">
+        <v>0</v>
+      </c>
+      <c r="S1744">
+        <v>0</v>
+      </c>
+      <c r="T1744">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1745" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>531</v>
+      </c>
+      <c r="C1745">
+        <v>1</v>
+      </c>
+      <c r="D1745">
+        <v>1</v>
+      </c>
+      <c r="E1745">
+        <v>0</v>
+      </c>
+      <c r="F1745">
+        <v>0</v>
+      </c>
+      <c r="G1745">
+        <v>0</v>
+      </c>
+      <c r="H1745">
+        <v>0</v>
+      </c>
+      <c r="I1745">
+        <v>0</v>
+      </c>
+      <c r="J1745">
+        <v>0</v>
+      </c>
+      <c r="K1745">
+        <v>0</v>
+      </c>
+      <c r="L1745">
+        <v>4</v>
+      </c>
+      <c r="M1745">
+        <v>4</v>
+      </c>
+      <c r="N1745">
+        <v>0</v>
+      </c>
+      <c r="O1745">
+        <v>0</v>
+      </c>
+      <c r="P1745">
+        <v>0</v>
+      </c>
+      <c r="Q1745">
+        <v>0</v>
+      </c>
+      <c r="R1745">
+        <v>0</v>
+      </c>
+      <c r="S1745">
+        <v>0</v>
+      </c>
+      <c r="T1745">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1746" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1746">
+        <v>1</v>
+      </c>
+      <c r="D1746">
+        <v>0</v>
+      </c>
+      <c r="E1746">
+        <v>0</v>
+      </c>
+      <c r="F1746">
+        <v>0</v>
+      </c>
+      <c r="I1746">
+        <v>0</v>
+      </c>
+      <c r="J1746">
+        <v>0</v>
+      </c>
+      <c r="L1746">
+        <v>0</v>
+      </c>
+      <c r="M1746">
+        <v>0</v>
+      </c>
+      <c r="N1746">
+        <v>0</v>
+      </c>
+      <c r="O1746">
+        <v>0</v>
+      </c>
+      <c r="P1746">
+        <v>0</v>
+      </c>
+      <c r="Q1746">
+        <v>0</v>
+      </c>
+      <c r="R1746">
+        <v>0</v>
+      </c>
+      <c r="S1746">
+        <v>0</v>
+      </c>
+      <c r="T1746">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1747" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>394</v>
+      </c>
+      <c r="C1747">
+        <v>1</v>
+      </c>
+      <c r="D1747">
+        <v>1</v>
+      </c>
+      <c r="E1747">
+        <v>0</v>
+      </c>
+      <c r="F1747">
+        <v>0</v>
+      </c>
+      <c r="G1747">
+        <v>0</v>
+      </c>
+      <c r="H1747">
+        <v>0</v>
+      </c>
+      <c r="I1747">
+        <v>0</v>
+      </c>
+      <c r="J1747">
+        <v>0</v>
+      </c>
+      <c r="K1747">
+        <v>0</v>
+      </c>
+      <c r="L1747">
+        <v>3</v>
+      </c>
+      <c r="M1747">
+        <v>3</v>
+      </c>
+      <c r="N1747">
+        <v>0</v>
+      </c>
+      <c r="O1747">
+        <v>0</v>
+      </c>
+      <c r="P1747">
+        <v>0</v>
+      </c>
+      <c r="Q1747">
+        <v>0</v>
+      </c>
+      <c r="R1747">
+        <v>0</v>
+      </c>
+      <c r="S1747">
+        <v>0</v>
+      </c>
+      <c r="T1747">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1748" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>532</v>
+      </c>
+      <c r="C1748">
+        <v>1</v>
+      </c>
+      <c r="D1748">
+        <v>1</v>
+      </c>
+      <c r="E1748">
+        <v>0</v>
+      </c>
+      <c r="F1748">
+        <v>2</v>
+      </c>
+      <c r="G1748">
+        <v>2</v>
+      </c>
+      <c r="H1748">
+        <v>2</v>
+      </c>
+      <c r="I1748">
+        <v>0</v>
+      </c>
+      <c r="J1748">
+        <v>0</v>
+      </c>
+      <c r="K1748">
+        <v>100</v>
+      </c>
+      <c r="L1748">
+        <v>2</v>
+      </c>
+      <c r="M1748">
+        <v>1</v>
+      </c>
+      <c r="N1748">
+        <v>0</v>
+      </c>
+      <c r="O1748">
+        <v>0</v>
+      </c>
+      <c r="P1748">
+        <v>1.32</v>
+      </c>
+      <c r="Q1748">
+        <v>0</v>
+      </c>
+      <c r="R1748">
+        <v>0</v>
+      </c>
+      <c r="S1748">
+        <v>0</v>
+      </c>
+      <c r="T1748">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1749" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1749">
+        <v>1</v>
+      </c>
+      <c r="D1749">
+        <v>0</v>
+      </c>
+      <c r="E1749">
+        <v>0</v>
+      </c>
+      <c r="F1749">
+        <v>0</v>
+      </c>
+      <c r="I1749">
+        <v>0</v>
+      </c>
+      <c r="J1749">
+        <v>0</v>
+      </c>
+      <c r="L1749">
+        <v>0</v>
+      </c>
+      <c r="M1749">
+        <v>0</v>
+      </c>
+      <c r="N1749">
+        <v>0</v>
+      </c>
+      <c r="O1749">
+        <v>0</v>
+      </c>
+      <c r="P1749">
+        <v>0</v>
+      </c>
+      <c r="Q1749">
+        <v>0</v>
+      </c>
+      <c r="R1749">
+        <v>0</v>
+      </c>
+      <c r="S1749">
+        <v>0</v>
+      </c>
+      <c r="T1749">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1750" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1750">
+        <v>1</v>
+      </c>
+      <c r="D1750">
+        <v>1</v>
+      </c>
+      <c r="E1750">
+        <v>0</v>
+      </c>
+      <c r="F1750">
+        <v>10</v>
+      </c>
+      <c r="G1750">
+        <v>10</v>
+      </c>
+      <c r="H1750">
+        <v>10</v>
+      </c>
+      <c r="I1750">
+        <v>0</v>
+      </c>
+      <c r="J1750">
+        <v>0</v>
+      </c>
+      <c r="K1750">
+        <v>58.82</v>
+      </c>
+      <c r="L1750">
+        <v>17</v>
+      </c>
+      <c r="M1750">
+        <v>10</v>
+      </c>
+      <c r="N1750">
+        <v>1</v>
+      </c>
+      <c r="O1750">
+        <v>0</v>
+      </c>
+      <c r="P1750">
+        <v>6.58</v>
+      </c>
+      <c r="Q1750">
+        <v>0</v>
+      </c>
+      <c r="R1750">
+        <v>0</v>
+      </c>
+      <c r="S1750">
+        <v>0</v>
+      </c>
+      <c r="T1750">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1751" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>367</v>
+      </c>
+      <c r="C1751">
+        <v>1</v>
+      </c>
+      <c r="D1751">
+        <v>1</v>
+      </c>
+      <c r="E1751">
+        <v>0</v>
+      </c>
+      <c r="F1751">
+        <v>22</v>
+      </c>
+      <c r="G1751">
+        <v>22</v>
+      </c>
+      <c r="H1751">
+        <v>22</v>
+      </c>
+      <c r="I1751">
+        <v>0</v>
+      </c>
+      <c r="J1751">
+        <v>0</v>
+      </c>
+      <c r="K1751">
+        <v>137.5</v>
+      </c>
+      <c r="L1751">
+        <v>16</v>
+      </c>
+      <c r="M1751">
+        <v>5</v>
+      </c>
+      <c r="N1751">
+        <v>1</v>
+      </c>
+      <c r="O1751">
+        <v>1</v>
+      </c>
+      <c r="P1751">
+        <v>14.57</v>
+      </c>
+      <c r="Q1751">
+        <v>0</v>
+      </c>
+      <c r="R1751">
+        <v>0</v>
+      </c>
+      <c r="S1751">
+        <v>0</v>
+      </c>
+      <c r="T1751">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1752" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>321</v>
+      </c>
+      <c r="C1752">
+        <v>1</v>
+      </c>
+      <c r="D1752">
+        <v>1</v>
+      </c>
+      <c r="E1752">
+        <v>1</v>
+      </c>
+      <c r="F1752">
+        <v>30</v>
+      </c>
+      <c r="H1752" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1752">
+        <v>0</v>
+      </c>
+      <c r="J1752">
+        <v>0</v>
+      </c>
+      <c r="K1752">
+        <v>115.38</v>
+      </c>
+      <c r="L1752">
+        <v>26</v>
+      </c>
+      <c r="M1752">
+        <v>8</v>
+      </c>
+      <c r="N1752">
+        <v>1</v>
+      </c>
+      <c r="O1752">
+        <v>1</v>
+      </c>
+      <c r="P1752">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="Q1752">
+        <v>0</v>
+      </c>
+      <c r="R1752">
+        <v>2</v>
+      </c>
+      <c r="S1752">
+        <v>0</v>
+      </c>
+      <c r="T1752">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1753" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1753">
+        <v>1</v>
+      </c>
+      <c r="D1753">
+        <v>0</v>
+      </c>
+      <c r="E1753">
+        <v>0</v>
+      </c>
+      <c r="F1753">
+        <v>0</v>
+      </c>
+      <c r="I1753">
+        <v>0</v>
+      </c>
+      <c r="J1753">
+        <v>0</v>
+      </c>
+      <c r="L1753">
+        <v>0</v>
+      </c>
+      <c r="M1753">
+        <v>0</v>
+      </c>
+      <c r="N1753">
+        <v>0</v>
+      </c>
+      <c r="O1753">
+        <v>0</v>
+      </c>
+      <c r="P1753">
+        <v>0</v>
+      </c>
+      <c r="Q1753">
+        <v>0</v>
+      </c>
+      <c r="R1753">
+        <v>0</v>
+      </c>
+      <c r="S1753">
+        <v>0</v>
+      </c>
+      <c r="T1753">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1754" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>731</v>
+      </c>
+      <c r="C1754">
+        <v>1</v>
+      </c>
+      <c r="D1754">
+        <v>1</v>
+      </c>
+      <c r="E1754">
+        <v>1</v>
+      </c>
+      <c r="F1754">
+        <v>31</v>
+      </c>
+      <c r="H1754" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1754">
+        <v>0</v>
+      </c>
+      <c r="J1754">
+        <v>0</v>
+      </c>
+      <c r="K1754">
+        <v>172.22</v>
+      </c>
+      <c r="L1754">
+        <v>18</v>
+      </c>
+      <c r="M1754">
+        <v>4</v>
+      </c>
+      <c r="N1754">
+        <v>3</v>
+      </c>
+      <c r="O1754">
+        <v>1</v>
+      </c>
+      <c r="P1754">
+        <v>20.39</v>
+      </c>
+      <c r="Q1754">
+        <v>0</v>
+      </c>
+      <c r="R1754">
+        <v>0</v>
+      </c>
+      <c r="S1754">
+        <v>0</v>
+      </c>
+      <c r="T1754">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1755" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>732</v>
+      </c>
+      <c r="C1755">
+        <v>1</v>
+      </c>
+      <c r="D1755">
+        <v>1</v>
+      </c>
+      <c r="E1755">
+        <v>0</v>
+      </c>
+      <c r="F1755">
+        <v>6</v>
+      </c>
+      <c r="G1755">
+        <v>6</v>
+      </c>
+      <c r="H1755">
+        <v>6</v>
+      </c>
+      <c r="I1755">
+        <v>0</v>
+      </c>
+      <c r="J1755">
+        <v>0</v>
+      </c>
+      <c r="K1755">
+        <v>85.71</v>
+      </c>
+      <c r="L1755">
+        <v>7</v>
+      </c>
+      <c r="M1755">
+        <v>4</v>
+      </c>
+      <c r="N1755">
+        <v>1</v>
+      </c>
+      <c r="O1755">
+        <v>0</v>
+      </c>
+      <c r="P1755">
+        <v>3.95</v>
+      </c>
+      <c r="Q1755">
+        <v>0</v>
+      </c>
+      <c r="R1755">
+        <v>0</v>
+      </c>
+      <c r="S1755">
+        <v>0</v>
+      </c>
+      <c r="T1755">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1756" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1756">
+        <v>1</v>
+      </c>
+      <c r="D1756">
+        <v>1</v>
+      </c>
+      <c r="E1756">
+        <v>1</v>
+      </c>
+      <c r="F1756">
+        <v>11</v>
+      </c>
+      <c r="H1756" t="s">
+        <v>221</v>
+      </c>
+      <c r="I1756">
+        <v>0</v>
+      </c>
+      <c r="J1756">
+        <v>0</v>
+      </c>
+      <c r="K1756">
+        <v>78.569999999999993</v>
+      </c>
+      <c r="L1756">
+        <v>14</v>
+      </c>
+      <c r="M1756">
+        <v>6</v>
+      </c>
+      <c r="N1756">
+        <v>0</v>
+      </c>
+      <c r="O1756">
+        <v>0</v>
+      </c>
+      <c r="P1756">
+        <v>7.24</v>
+      </c>
+      <c r="Q1756">
+        <v>0</v>
+      </c>
+      <c r="R1756">
+        <v>0</v>
+      </c>
+      <c r="S1756">
+        <v>0</v>
+      </c>
+      <c r="T1756">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1757" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1757">
+        <v>1</v>
+      </c>
+      <c r="D1757">
+        <v>1</v>
+      </c>
+      <c r="E1757">
+        <v>0</v>
+      </c>
+      <c r="F1757">
+        <v>0</v>
+      </c>
+      <c r="G1757">
+        <v>0</v>
+      </c>
+      <c r="H1757">
+        <v>0</v>
+      </c>
+      <c r="I1757">
+        <v>0</v>
+      </c>
+      <c r="J1757">
+        <v>0</v>
+      </c>
+      <c r="K1757">
+        <v>0</v>
+      </c>
+      <c r="L1757">
+        <v>4</v>
+      </c>
+      <c r="M1757">
+        <v>4</v>
+      </c>
+      <c r="N1757">
+        <v>0</v>
+      </c>
+      <c r="O1757">
+        <v>0</v>
+      </c>
+      <c r="P1757">
+        <v>0</v>
+      </c>
+      <c r="Q1757">
+        <v>0</v>
+      </c>
+      <c r="R1757">
+        <v>0</v>
+      </c>
+      <c r="S1757">
+        <v>0</v>
+      </c>
+      <c r="T1757">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1758" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>536</v>
+      </c>
+      <c r="C1758">
+        <v>1</v>
+      </c>
+      <c r="D1758">
+        <v>1</v>
+      </c>
+      <c r="E1758">
+        <v>0</v>
+      </c>
+      <c r="F1758">
+        <v>2</v>
+      </c>
+      <c r="G1758">
+        <v>2</v>
+      </c>
+      <c r="H1758">
+        <v>2</v>
+      </c>
+      <c r="I1758">
+        <v>0</v>
+      </c>
+      <c r="J1758">
+        <v>0</v>
+      </c>
+      <c r="K1758">
+        <v>100</v>
+      </c>
+      <c r="L1758">
+        <v>2</v>
+      </c>
+      <c r="M1758">
+        <v>1</v>
+      </c>
+      <c r="N1758">
+        <v>0</v>
+      </c>
+      <c r="O1758">
+        <v>0</v>
+      </c>
+      <c r="P1758">
+        <v>1.32</v>
+      </c>
+      <c r="Q1758">
+        <v>0</v>
+      </c>
+      <c r="R1758">
+        <v>0</v>
+      </c>
+      <c r="S1758">
+        <v>0</v>
+      </c>
+      <c r="T1758">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1759" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1759">
+        <v>1</v>
+      </c>
+      <c r="D1759">
+        <v>1</v>
+      </c>
+      <c r="E1759">
+        <v>0</v>
+      </c>
+      <c r="F1759">
+        <v>5</v>
+      </c>
+      <c r="G1759">
+        <v>5</v>
+      </c>
+      <c r="H1759">
+        <v>5</v>
+      </c>
+      <c r="I1759">
+        <v>0</v>
+      </c>
+      <c r="J1759">
+        <v>0</v>
+      </c>
+      <c r="K1759">
+        <v>166.67</v>
+      </c>
+      <c r="L1759">
+        <v>3</v>
+      </c>
+      <c r="M1759">
+        <v>1</v>
+      </c>
+      <c r="N1759">
+        <v>1</v>
+      </c>
+      <c r="O1759">
+        <v>0</v>
+      </c>
+      <c r="P1759">
+        <v>3.31</v>
+      </c>
+      <c r="Q1759">
+        <v>0</v>
+      </c>
+      <c r="R1759">
+        <v>0</v>
+      </c>
+      <c r="S1759">
+        <v>0</v>
+      </c>
+      <c r="T1759">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="A1628:T1656">

--- a/NV Play Midweek League batting stats for season.xlsx
+++ b/NV Play Midweek League batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3989" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4042" uniqueCount="736">
   <si>
     <t>Group</t>
   </si>
@@ -2219,6 +2219,15 @@
   <si>
     <t>Roshan Varghese</t>
   </si>
+  <si>
+    <t>Belfast Superkings MW XI v Ardent Blues MW1 XI, TBC - 23 July 2026</t>
+  </si>
+  <si>
+    <t>Thomas Varghese</t>
+  </si>
+  <si>
+    <t>Rijo George</t>
+  </si>
 </sst>
 </file>
 
@@ -3025,10 +3034,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1759"/>
+  <dimension ref="A1:U1781"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="97.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="61" customWidth="1"/>
     <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -108346,6 +108355,1298 @@
         <v>0</v>
       </c>
       <c r="T1759">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1760" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1760">
+        <v>1</v>
+      </c>
+      <c r="D1760">
+        <v>1</v>
+      </c>
+      <c r="E1760">
+        <v>1</v>
+      </c>
+      <c r="F1760">
+        <v>31</v>
+      </c>
+      <c r="H1760" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1760">
+        <v>0</v>
+      </c>
+      <c r="J1760">
+        <v>0</v>
+      </c>
+      <c r="K1760">
+        <v>182.35</v>
+      </c>
+      <c r="L1760">
+        <v>17</v>
+      </c>
+      <c r="M1760">
+        <v>7</v>
+      </c>
+      <c r="N1760">
+        <v>3</v>
+      </c>
+      <c r="O1760">
+        <v>2</v>
+      </c>
+      <c r="P1760">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="Q1760">
+        <v>0</v>
+      </c>
+      <c r="R1760">
+        <v>0</v>
+      </c>
+      <c r="S1760">
+        <v>0</v>
+      </c>
+      <c r="T1760">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1761" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1761">
+        <v>1</v>
+      </c>
+      <c r="D1761">
+        <v>1</v>
+      </c>
+      <c r="E1761">
+        <v>1</v>
+      </c>
+      <c r="F1761">
+        <v>33</v>
+      </c>
+      <c r="H1761" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1761">
+        <v>0</v>
+      </c>
+      <c r="J1761">
+        <v>0</v>
+      </c>
+      <c r="K1761">
+        <v>165</v>
+      </c>
+      <c r="L1761">
+        <v>20</v>
+      </c>
+      <c r="M1761">
+        <v>5</v>
+      </c>
+      <c r="N1761">
+        <v>4</v>
+      </c>
+      <c r="O1761">
+        <v>1</v>
+      </c>
+      <c r="P1761">
+        <v>17.93</v>
+      </c>
+      <c r="Q1761">
+        <v>0</v>
+      </c>
+      <c r="R1761">
+        <v>0</v>
+      </c>
+      <c r="S1761">
+        <v>0</v>
+      </c>
+      <c r="T1761">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1762" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1762">
+        <v>1</v>
+      </c>
+      <c r="D1762">
+        <v>1</v>
+      </c>
+      <c r="E1762">
+        <v>1</v>
+      </c>
+      <c r="F1762">
+        <v>22</v>
+      </c>
+      <c r="H1762" t="s">
+        <v>219</v>
+      </c>
+      <c r="I1762">
+        <v>0</v>
+      </c>
+      <c r="J1762">
+        <v>0</v>
+      </c>
+      <c r="K1762">
+        <v>70.97</v>
+      </c>
+      <c r="L1762">
+        <v>31</v>
+      </c>
+      <c r="M1762">
+        <v>15</v>
+      </c>
+      <c r="N1762">
+        <v>2</v>
+      </c>
+      <c r="O1762">
+        <v>0</v>
+      </c>
+      <c r="P1762">
+        <v>11.96</v>
+      </c>
+      <c r="Q1762">
+        <v>0</v>
+      </c>
+      <c r="R1762">
+        <v>0</v>
+      </c>
+      <c r="S1762">
+        <v>0</v>
+      </c>
+      <c r="T1762">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1763" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1763">
+        <v>1</v>
+      </c>
+      <c r="D1763">
+        <v>1</v>
+      </c>
+      <c r="E1763">
+        <v>0</v>
+      </c>
+      <c r="F1763">
+        <v>15</v>
+      </c>
+      <c r="G1763">
+        <v>15</v>
+      </c>
+      <c r="H1763">
+        <v>15</v>
+      </c>
+      <c r="I1763">
+        <v>0</v>
+      </c>
+      <c r="J1763">
+        <v>0</v>
+      </c>
+      <c r="K1763">
+        <v>136.36000000000001</v>
+      </c>
+      <c r="L1763">
+        <v>11</v>
+      </c>
+      <c r="M1763">
+        <v>4</v>
+      </c>
+      <c r="N1763">
+        <v>1</v>
+      </c>
+      <c r="O1763">
+        <v>1</v>
+      </c>
+      <c r="P1763">
+        <v>8.11</v>
+      </c>
+      <c r="Q1763">
+        <v>0</v>
+      </c>
+      <c r="R1763">
+        <v>1</v>
+      </c>
+      <c r="S1763">
+        <v>0</v>
+      </c>
+      <c r="T1763">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1764" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1764">
+        <v>1</v>
+      </c>
+      <c r="D1764">
+        <v>1</v>
+      </c>
+      <c r="E1764">
+        <v>0</v>
+      </c>
+      <c r="F1764">
+        <v>9</v>
+      </c>
+      <c r="G1764">
+        <v>9</v>
+      </c>
+      <c r="H1764">
+        <v>9</v>
+      </c>
+      <c r="I1764">
+        <v>0</v>
+      </c>
+      <c r="J1764">
+        <v>0</v>
+      </c>
+      <c r="K1764">
+        <v>90</v>
+      </c>
+      <c r="L1764">
+        <v>10</v>
+      </c>
+      <c r="M1764">
+        <v>4</v>
+      </c>
+      <c r="N1764">
+        <v>1</v>
+      </c>
+      <c r="O1764">
+        <v>0</v>
+      </c>
+      <c r="P1764">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="Q1764">
+        <v>0</v>
+      </c>
+      <c r="R1764">
+        <v>0</v>
+      </c>
+      <c r="S1764">
+        <v>0</v>
+      </c>
+      <c r="T1764">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1765" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1765">
+        <v>1</v>
+      </c>
+      <c r="D1765">
+        <v>1</v>
+      </c>
+      <c r="E1765">
+        <v>1</v>
+      </c>
+      <c r="F1765">
+        <v>32</v>
+      </c>
+      <c r="H1765" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1765">
+        <v>0</v>
+      </c>
+      <c r="J1765">
+        <v>0</v>
+      </c>
+      <c r="K1765">
+        <v>152.38</v>
+      </c>
+      <c r="L1765">
+        <v>21</v>
+      </c>
+      <c r="M1765">
+        <v>11</v>
+      </c>
+      <c r="N1765">
+        <v>4</v>
+      </c>
+      <c r="O1765">
+        <v>2</v>
+      </c>
+      <c r="P1765">
+        <v>17.3</v>
+      </c>
+      <c r="Q1765">
+        <v>0</v>
+      </c>
+      <c r="R1765">
+        <v>0</v>
+      </c>
+      <c r="S1765">
+        <v>0</v>
+      </c>
+      <c r="T1765">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1766" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>664</v>
+      </c>
+      <c r="C1766">
+        <v>1</v>
+      </c>
+      <c r="D1766">
+        <v>1</v>
+      </c>
+      <c r="E1766">
+        <v>1</v>
+      </c>
+      <c r="F1766">
+        <v>8</v>
+      </c>
+      <c r="H1766" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1766">
+        <v>0</v>
+      </c>
+      <c r="J1766">
+        <v>0</v>
+      </c>
+      <c r="K1766">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1766">
+        <v>6</v>
+      </c>
+      <c r="M1766">
+        <v>1</v>
+      </c>
+      <c r="N1766">
+        <v>1</v>
+      </c>
+      <c r="O1766">
+        <v>0</v>
+      </c>
+      <c r="P1766">
+        <v>4.32</v>
+      </c>
+      <c r="Q1766">
+        <v>0</v>
+      </c>
+      <c r="R1766">
+        <v>0</v>
+      </c>
+      <c r="S1766">
+        <v>0</v>
+      </c>
+      <c r="T1766">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1767" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>734</v>
+      </c>
+      <c r="C1767">
+        <v>1</v>
+      </c>
+      <c r="D1767">
+        <v>0</v>
+      </c>
+      <c r="E1767">
+        <v>0</v>
+      </c>
+      <c r="F1767">
+        <v>0</v>
+      </c>
+      <c r="I1767">
+        <v>0</v>
+      </c>
+      <c r="J1767">
+        <v>0</v>
+      </c>
+      <c r="L1767">
+        <v>0</v>
+      </c>
+      <c r="M1767">
+        <v>0</v>
+      </c>
+      <c r="N1767">
+        <v>0</v>
+      </c>
+      <c r="O1767">
+        <v>0</v>
+      </c>
+      <c r="P1767">
+        <v>0</v>
+      </c>
+      <c r="Q1767">
+        <v>0</v>
+      </c>
+      <c r="R1767">
+        <v>0</v>
+      </c>
+      <c r="S1767">
+        <v>0</v>
+      </c>
+      <c r="T1767">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1768" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1768">
+        <v>1</v>
+      </c>
+      <c r="D1768">
+        <v>1</v>
+      </c>
+      <c r="E1768">
+        <v>0</v>
+      </c>
+      <c r="F1768">
+        <v>12</v>
+      </c>
+      <c r="G1768">
+        <v>12</v>
+      </c>
+      <c r="H1768">
+        <v>12</v>
+      </c>
+      <c r="I1768">
+        <v>0</v>
+      </c>
+      <c r="J1768">
+        <v>0</v>
+      </c>
+      <c r="K1768">
+        <v>100</v>
+      </c>
+      <c r="L1768">
+        <v>12</v>
+      </c>
+      <c r="M1768">
+        <v>6</v>
+      </c>
+      <c r="N1768">
+        <v>2</v>
+      </c>
+      <c r="O1768">
+        <v>0</v>
+      </c>
+      <c r="P1768">
+        <v>6.52</v>
+      </c>
+      <c r="Q1768">
+        <v>0</v>
+      </c>
+      <c r="R1768">
+        <v>0</v>
+      </c>
+      <c r="S1768">
+        <v>0</v>
+      </c>
+      <c r="T1768">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1769" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1769">
+        <v>1</v>
+      </c>
+      <c r="D1769">
+        <v>1</v>
+      </c>
+      <c r="E1769">
+        <v>1</v>
+      </c>
+      <c r="F1769">
+        <v>15</v>
+      </c>
+      <c r="H1769" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1769">
+        <v>0</v>
+      </c>
+      <c r="J1769">
+        <v>0</v>
+      </c>
+      <c r="K1769">
+        <v>166.67</v>
+      </c>
+      <c r="L1769">
+        <v>9</v>
+      </c>
+      <c r="M1769">
+        <v>3</v>
+      </c>
+      <c r="N1769">
+        <v>1</v>
+      </c>
+      <c r="O1769">
+        <v>1</v>
+      </c>
+      <c r="P1769">
+        <v>8.11</v>
+      </c>
+      <c r="Q1769">
+        <v>0</v>
+      </c>
+      <c r="R1769">
+        <v>0</v>
+      </c>
+      <c r="S1769">
+        <v>0</v>
+      </c>
+      <c r="T1769">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1770" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1770">
+        <v>1</v>
+      </c>
+      <c r="D1770">
+        <v>0</v>
+      </c>
+      <c r="E1770">
+        <v>0</v>
+      </c>
+      <c r="F1770">
+        <v>0</v>
+      </c>
+      <c r="I1770">
+        <v>0</v>
+      </c>
+      <c r="J1770">
+        <v>0</v>
+      </c>
+      <c r="L1770">
+        <v>0</v>
+      </c>
+      <c r="M1770">
+        <v>0</v>
+      </c>
+      <c r="N1770">
+        <v>0</v>
+      </c>
+      <c r="O1770">
+        <v>0</v>
+      </c>
+      <c r="P1770">
+        <v>0</v>
+      </c>
+      <c r="Q1770">
+        <v>0</v>
+      </c>
+      <c r="R1770">
+        <v>0</v>
+      </c>
+      <c r="S1770">
+        <v>0</v>
+      </c>
+      <c r="T1770">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1771" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1771">
+        <v>1</v>
+      </c>
+      <c r="D1771">
+        <v>1</v>
+      </c>
+      <c r="E1771">
+        <v>1</v>
+      </c>
+      <c r="F1771">
+        <v>33</v>
+      </c>
+      <c r="H1771" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1771">
+        <v>0</v>
+      </c>
+      <c r="J1771">
+        <v>0</v>
+      </c>
+      <c r="K1771">
+        <v>206.25</v>
+      </c>
+      <c r="L1771">
+        <v>16</v>
+      </c>
+      <c r="M1771">
+        <v>4</v>
+      </c>
+      <c r="N1771">
+        <v>5</v>
+      </c>
+      <c r="O1771">
+        <v>1</v>
+      </c>
+      <c r="P1771">
+        <v>17.93</v>
+      </c>
+      <c r="Q1771">
+        <v>0</v>
+      </c>
+      <c r="R1771">
+        <v>0</v>
+      </c>
+      <c r="S1771">
+        <v>0</v>
+      </c>
+      <c r="T1771">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1772" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>659</v>
+      </c>
+      <c r="C1772">
+        <v>1</v>
+      </c>
+      <c r="D1772">
+        <v>0</v>
+      </c>
+      <c r="E1772">
+        <v>0</v>
+      </c>
+      <c r="F1772">
+        <v>0</v>
+      </c>
+      <c r="I1772">
+        <v>0</v>
+      </c>
+      <c r="J1772">
+        <v>0</v>
+      </c>
+      <c r="L1772">
+        <v>0</v>
+      </c>
+      <c r="M1772">
+        <v>0</v>
+      </c>
+      <c r="N1772">
+        <v>0</v>
+      </c>
+      <c r="O1772">
+        <v>0</v>
+      </c>
+      <c r="P1772">
+        <v>0</v>
+      </c>
+      <c r="Q1772">
+        <v>0</v>
+      </c>
+      <c r="R1772">
+        <v>0</v>
+      </c>
+      <c r="S1772">
+        <v>0</v>
+      </c>
+      <c r="T1772">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1773" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>735</v>
+      </c>
+      <c r="C1773">
+        <v>1</v>
+      </c>
+      <c r="D1773">
+        <v>1</v>
+      </c>
+      <c r="E1773">
+        <v>0</v>
+      </c>
+      <c r="F1773">
+        <v>1</v>
+      </c>
+      <c r="G1773">
+        <v>1</v>
+      </c>
+      <c r="H1773">
+        <v>1</v>
+      </c>
+      <c r="I1773">
+        <v>0</v>
+      </c>
+      <c r="J1773">
+        <v>0</v>
+      </c>
+      <c r="K1773">
+        <v>25</v>
+      </c>
+      <c r="L1773">
+        <v>4</v>
+      </c>
+      <c r="M1773">
+        <v>3</v>
+      </c>
+      <c r="N1773">
+        <v>0</v>
+      </c>
+      <c r="O1773">
+        <v>0</v>
+      </c>
+      <c r="P1773">
+        <v>0.54</v>
+      </c>
+      <c r="Q1773">
+        <v>0</v>
+      </c>
+      <c r="R1773">
+        <v>0</v>
+      </c>
+      <c r="S1773">
+        <v>0</v>
+      </c>
+      <c r="T1773">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1774" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1774">
+        <v>1</v>
+      </c>
+      <c r="D1774">
+        <v>1</v>
+      </c>
+      <c r="E1774">
+        <v>0</v>
+      </c>
+      <c r="F1774">
+        <v>9</v>
+      </c>
+      <c r="G1774">
+        <v>9</v>
+      </c>
+      <c r="H1774">
+        <v>9</v>
+      </c>
+      <c r="I1774">
+        <v>0</v>
+      </c>
+      <c r="J1774">
+        <v>0</v>
+      </c>
+      <c r="K1774">
+        <v>112.5</v>
+      </c>
+      <c r="L1774">
+        <v>8</v>
+      </c>
+      <c r="M1774">
+        <v>5</v>
+      </c>
+      <c r="N1774">
+        <v>2</v>
+      </c>
+      <c r="O1774">
+        <v>0</v>
+      </c>
+      <c r="P1774">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="Q1774">
+        <v>0</v>
+      </c>
+      <c r="R1774">
+        <v>0</v>
+      </c>
+      <c r="S1774">
+        <v>0</v>
+      </c>
+      <c r="T1774">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1775" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>523</v>
+      </c>
+      <c r="C1775">
+        <v>1</v>
+      </c>
+      <c r="D1775">
+        <v>1</v>
+      </c>
+      <c r="E1775">
+        <v>0</v>
+      </c>
+      <c r="F1775">
+        <v>27</v>
+      </c>
+      <c r="G1775">
+        <v>27</v>
+      </c>
+      <c r="H1775">
+        <v>27</v>
+      </c>
+      <c r="I1775">
+        <v>0</v>
+      </c>
+      <c r="J1775">
+        <v>0</v>
+      </c>
+      <c r="K1775">
+        <v>135</v>
+      </c>
+      <c r="L1775">
+        <v>20</v>
+      </c>
+      <c r="M1775">
+        <v>8</v>
+      </c>
+      <c r="N1775">
+        <v>3</v>
+      </c>
+      <c r="O1775">
+        <v>1</v>
+      </c>
+      <c r="P1775">
+        <v>14.59</v>
+      </c>
+      <c r="Q1775">
+        <v>0</v>
+      </c>
+      <c r="R1775">
+        <v>0</v>
+      </c>
+      <c r="S1775">
+        <v>0</v>
+      </c>
+      <c r="T1775">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1776" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>648</v>
+      </c>
+      <c r="C1776">
+        <v>1</v>
+      </c>
+      <c r="D1776">
+        <v>1</v>
+      </c>
+      <c r="E1776">
+        <v>1</v>
+      </c>
+      <c r="F1776">
+        <v>20</v>
+      </c>
+      <c r="H1776" t="s">
+        <v>545</v>
+      </c>
+      <c r="I1776">
+        <v>0</v>
+      </c>
+      <c r="J1776">
+        <v>0</v>
+      </c>
+      <c r="K1776">
+        <v>125</v>
+      </c>
+      <c r="L1776">
+        <v>16</v>
+      </c>
+      <c r="M1776">
+        <v>6</v>
+      </c>
+      <c r="N1776">
+        <v>3</v>
+      </c>
+      <c r="O1776">
+        <v>0</v>
+      </c>
+      <c r="P1776">
+        <v>10.87</v>
+      </c>
+      <c r="Q1776">
+        <v>0</v>
+      </c>
+      <c r="R1776">
+        <v>0</v>
+      </c>
+      <c r="S1776">
+        <v>0</v>
+      </c>
+      <c r="T1776">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1777" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>526</v>
+      </c>
+      <c r="C1777">
+        <v>1</v>
+      </c>
+      <c r="D1777">
+        <v>1</v>
+      </c>
+      <c r="E1777">
+        <v>0</v>
+      </c>
+      <c r="F1777">
+        <v>11</v>
+      </c>
+      <c r="G1777">
+        <v>11</v>
+      </c>
+      <c r="H1777">
+        <v>11</v>
+      </c>
+      <c r="I1777">
+        <v>0</v>
+      </c>
+      <c r="J1777">
+        <v>0</v>
+      </c>
+      <c r="K1777">
+        <v>157.13999999999999</v>
+      </c>
+      <c r="L1777">
+        <v>7</v>
+      </c>
+      <c r="M1777">
+        <v>3</v>
+      </c>
+      <c r="N1777">
+        <v>2</v>
+      </c>
+      <c r="O1777">
+        <v>0</v>
+      </c>
+      <c r="P1777">
+        <v>5.95</v>
+      </c>
+      <c r="Q1777">
+        <v>0</v>
+      </c>
+      <c r="R1777">
+        <v>0</v>
+      </c>
+      <c r="S1777">
+        <v>0</v>
+      </c>
+      <c r="T1777">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1778" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1778">
+        <v>1</v>
+      </c>
+      <c r="D1778">
+        <v>0</v>
+      </c>
+      <c r="E1778">
+        <v>0</v>
+      </c>
+      <c r="F1778">
+        <v>0</v>
+      </c>
+      <c r="I1778">
+        <v>0</v>
+      </c>
+      <c r="J1778">
+        <v>0</v>
+      </c>
+      <c r="L1778">
+        <v>0</v>
+      </c>
+      <c r="M1778">
+        <v>0</v>
+      </c>
+      <c r="N1778">
+        <v>0</v>
+      </c>
+      <c r="O1778">
+        <v>0</v>
+      </c>
+      <c r="P1778">
+        <v>0</v>
+      </c>
+      <c r="Q1778">
+        <v>0</v>
+      </c>
+      <c r="R1778">
+        <v>0</v>
+      </c>
+      <c r="S1778">
+        <v>0</v>
+      </c>
+      <c r="T1778">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1779" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1779">
+        <v>1</v>
+      </c>
+      <c r="D1779">
+        <v>1</v>
+      </c>
+      <c r="E1779">
+        <v>0</v>
+      </c>
+      <c r="F1779">
+        <v>10</v>
+      </c>
+      <c r="G1779">
+        <v>10</v>
+      </c>
+      <c r="H1779">
+        <v>10</v>
+      </c>
+      <c r="I1779">
+        <v>0</v>
+      </c>
+      <c r="J1779">
+        <v>0</v>
+      </c>
+      <c r="K1779">
+        <v>125</v>
+      </c>
+      <c r="L1779">
+        <v>8</v>
+      </c>
+      <c r="M1779">
+        <v>6</v>
+      </c>
+      <c r="N1779">
+        <v>1</v>
+      </c>
+      <c r="O1779">
+        <v>1</v>
+      </c>
+      <c r="P1779">
+        <v>5.43</v>
+      </c>
+      <c r="Q1779">
+        <v>0</v>
+      </c>
+      <c r="R1779">
+        <v>0</v>
+      </c>
+      <c r="S1779">
+        <v>0</v>
+      </c>
+      <c r="T1779">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1780" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1780">
+        <v>1</v>
+      </c>
+      <c r="D1780">
+        <v>1</v>
+      </c>
+      <c r="E1780">
+        <v>1</v>
+      </c>
+      <c r="F1780">
+        <v>35</v>
+      </c>
+      <c r="H1780" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1780">
+        <v>0</v>
+      </c>
+      <c r="J1780">
+        <v>0</v>
+      </c>
+      <c r="K1780">
+        <v>250</v>
+      </c>
+      <c r="L1780">
+        <v>14</v>
+      </c>
+      <c r="M1780">
+        <v>3</v>
+      </c>
+      <c r="N1780">
+        <v>3</v>
+      </c>
+      <c r="O1780">
+        <v>3</v>
+      </c>
+      <c r="P1780">
+        <v>19.02</v>
+      </c>
+      <c r="Q1780">
+        <v>0</v>
+      </c>
+      <c r="R1780">
+        <v>0</v>
+      </c>
+      <c r="S1780">
+        <v>0</v>
+      </c>
+      <c r="T1780">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1781" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>575</v>
+      </c>
+      <c r="C1781">
+        <v>1</v>
+      </c>
+      <c r="D1781">
+        <v>0</v>
+      </c>
+      <c r="E1781">
+        <v>0</v>
+      </c>
+      <c r="F1781">
+        <v>0</v>
+      </c>
+      <c r="I1781">
+        <v>0</v>
+      </c>
+      <c r="J1781">
+        <v>0</v>
+      </c>
+      <c r="L1781">
+        <v>0</v>
+      </c>
+      <c r="M1781">
+        <v>0</v>
+      </c>
+      <c r="N1781">
+        <v>0</v>
+      </c>
+      <c r="O1781">
+        <v>0</v>
+      </c>
+      <c r="P1781">
+        <v>0</v>
+      </c>
+      <c r="Q1781">
+        <v>0</v>
+      </c>
+      <c r="R1781">
+        <v>0</v>
+      </c>
+      <c r="S1781">
+        <v>0</v>
+      </c>
+      <c r="T1781">
         <v>0</v>
       </c>
     </row>

--- a/NV Play Midweek League batting stats for season.xlsx
+++ b/NV Play Midweek League batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4042" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4141" uniqueCount="739">
   <si>
     <t>Group</t>
   </si>
@@ -2225,6 +2225,18 @@
   <si>
     <t>Mohan Vijayakumar</t>
   </si>
+  <si>
+    <t>Downpatrick MW XI v Dunmurry MW2 XI, The Meadow - 29 July 2026</t>
+  </si>
+  <si>
+    <t>Onkar Jadhav</t>
+  </si>
+  <si>
+    <t>Sidharth Kumar</t>
+  </si>
+  <si>
+    <t>Muckamore MW1 XI v Arches MW XI, Moylena - 29 July 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -3031,7 +3043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1781"/>
+  <dimension ref="A1:U1825"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61" customWidth="1"/>
@@ -109647,6 +109659,2638 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1782" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1782" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1782">
+        <v>1</v>
+      </c>
+      <c r="D1782">
+        <v>1</v>
+      </c>
+      <c r="E1782">
+        <v>1</v>
+      </c>
+      <c r="F1782">
+        <v>19</v>
+      </c>
+      <c r="H1782" t="s">
+        <v>560</v>
+      </c>
+      <c r="I1782">
+        <v>0</v>
+      </c>
+      <c r="J1782">
+        <v>0</v>
+      </c>
+      <c r="K1782">
+        <v>211.11</v>
+      </c>
+      <c r="L1782">
+        <v>9</v>
+      </c>
+      <c r="M1782">
+        <v>1</v>
+      </c>
+      <c r="N1782">
+        <v>3</v>
+      </c>
+      <c r="O1782">
+        <v>0</v>
+      </c>
+      <c r="P1782">
+        <v>12.84</v>
+      </c>
+      <c r="Q1782">
+        <v>0</v>
+      </c>
+      <c r="R1782">
+        <v>0</v>
+      </c>
+      <c r="S1782">
+        <v>0</v>
+      </c>
+      <c r="T1782">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1783" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1783">
+        <v>1</v>
+      </c>
+      <c r="D1783">
+        <v>0</v>
+      </c>
+      <c r="E1783">
+        <v>0</v>
+      </c>
+      <c r="F1783">
+        <v>0</v>
+      </c>
+      <c r="I1783">
+        <v>0</v>
+      </c>
+      <c r="J1783">
+        <v>0</v>
+      </c>
+      <c r="L1783">
+        <v>0</v>
+      </c>
+      <c r="M1783">
+        <v>0</v>
+      </c>
+      <c r="N1783">
+        <v>0</v>
+      </c>
+      <c r="O1783">
+        <v>0</v>
+      </c>
+      <c r="P1783">
+        <v>0</v>
+      </c>
+      <c r="Q1783">
+        <v>0</v>
+      </c>
+      <c r="R1783">
+        <v>0</v>
+      </c>
+      <c r="S1783">
+        <v>0</v>
+      </c>
+      <c r="T1783">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1784" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1784">
+        <v>1</v>
+      </c>
+      <c r="D1784">
+        <v>1</v>
+      </c>
+      <c r="E1784">
+        <v>0</v>
+      </c>
+      <c r="F1784">
+        <v>7</v>
+      </c>
+      <c r="G1784">
+        <v>7</v>
+      </c>
+      <c r="H1784">
+        <v>7</v>
+      </c>
+      <c r="I1784">
+        <v>0</v>
+      </c>
+      <c r="J1784">
+        <v>0</v>
+      </c>
+      <c r="K1784">
+        <v>100</v>
+      </c>
+      <c r="L1784">
+        <v>7</v>
+      </c>
+      <c r="M1784">
+        <v>4</v>
+      </c>
+      <c r="N1784">
+        <v>0</v>
+      </c>
+      <c r="O1784">
+        <v>0</v>
+      </c>
+      <c r="P1784">
+        <v>4.7</v>
+      </c>
+      <c r="Q1784">
+        <v>0</v>
+      </c>
+      <c r="R1784">
+        <v>0</v>
+      </c>
+      <c r="S1784">
+        <v>0</v>
+      </c>
+      <c r="T1784">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1785" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>542</v>
+      </c>
+      <c r="C1785">
+        <v>1</v>
+      </c>
+      <c r="D1785">
+        <v>1</v>
+      </c>
+      <c r="E1785">
+        <v>0</v>
+      </c>
+      <c r="F1785">
+        <v>1</v>
+      </c>
+      <c r="G1785">
+        <v>1</v>
+      </c>
+      <c r="H1785">
+        <v>1</v>
+      </c>
+      <c r="I1785">
+        <v>0</v>
+      </c>
+      <c r="J1785">
+        <v>0</v>
+      </c>
+      <c r="K1785">
+        <v>50</v>
+      </c>
+      <c r="L1785">
+        <v>2</v>
+      </c>
+      <c r="M1785">
+        <v>1</v>
+      </c>
+      <c r="N1785">
+        <v>0</v>
+      </c>
+      <c r="O1785">
+        <v>0</v>
+      </c>
+      <c r="P1785">
+        <v>0.68</v>
+      </c>
+      <c r="Q1785">
+        <v>0</v>
+      </c>
+      <c r="R1785">
+        <v>0</v>
+      </c>
+      <c r="S1785">
+        <v>0</v>
+      </c>
+      <c r="T1785">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1786" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>736</v>
+      </c>
+      <c r="C1786">
+        <v>1</v>
+      </c>
+      <c r="D1786">
+        <v>1</v>
+      </c>
+      <c r="E1786">
+        <v>0</v>
+      </c>
+      <c r="F1786">
+        <v>19</v>
+      </c>
+      <c r="G1786">
+        <v>19</v>
+      </c>
+      <c r="H1786">
+        <v>19</v>
+      </c>
+      <c r="I1786">
+        <v>0</v>
+      </c>
+      <c r="J1786">
+        <v>0</v>
+      </c>
+      <c r="K1786">
+        <v>190</v>
+      </c>
+      <c r="L1786">
+        <v>10</v>
+      </c>
+      <c r="M1786">
+        <v>4</v>
+      </c>
+      <c r="N1786">
+        <v>1</v>
+      </c>
+      <c r="O1786">
+        <v>2</v>
+      </c>
+      <c r="P1786">
+        <v>12.75</v>
+      </c>
+      <c r="Q1786">
+        <v>0</v>
+      </c>
+      <c r="R1786">
+        <v>2</v>
+      </c>
+      <c r="S1786">
+        <v>0</v>
+      </c>
+      <c r="T1786">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1787" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1787">
+        <v>1</v>
+      </c>
+      <c r="D1787">
+        <v>1</v>
+      </c>
+      <c r="E1787">
+        <v>1</v>
+      </c>
+      <c r="F1787">
+        <v>3</v>
+      </c>
+      <c r="H1787" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1787">
+        <v>0</v>
+      </c>
+      <c r="J1787">
+        <v>0</v>
+      </c>
+      <c r="K1787">
+        <v>100</v>
+      </c>
+      <c r="L1787">
+        <v>3</v>
+      </c>
+      <c r="M1787">
+        <v>1</v>
+      </c>
+      <c r="N1787">
+        <v>0</v>
+      </c>
+      <c r="O1787">
+        <v>0</v>
+      </c>
+      <c r="P1787">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="Q1787">
+        <v>0</v>
+      </c>
+      <c r="R1787">
+        <v>0</v>
+      </c>
+      <c r="S1787">
+        <v>0</v>
+      </c>
+      <c r="T1787">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1788" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1788">
+        <v>1</v>
+      </c>
+      <c r="D1788">
+        <v>1</v>
+      </c>
+      <c r="E1788">
+        <v>0</v>
+      </c>
+      <c r="F1788">
+        <v>0</v>
+      </c>
+      <c r="G1788">
+        <v>0</v>
+      </c>
+      <c r="H1788">
+        <v>0</v>
+      </c>
+      <c r="I1788">
+        <v>0</v>
+      </c>
+      <c r="J1788">
+        <v>0</v>
+      </c>
+      <c r="K1788">
+        <v>0</v>
+      </c>
+      <c r="L1788">
+        <v>1</v>
+      </c>
+      <c r="M1788">
+        <v>1</v>
+      </c>
+      <c r="N1788">
+        <v>0</v>
+      </c>
+      <c r="O1788">
+        <v>0</v>
+      </c>
+      <c r="P1788">
+        <v>0</v>
+      </c>
+      <c r="Q1788">
+        <v>0</v>
+      </c>
+      <c r="R1788">
+        <v>0</v>
+      </c>
+      <c r="S1788">
+        <v>0</v>
+      </c>
+      <c r="T1788">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1789" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>613</v>
+      </c>
+      <c r="C1789">
+        <v>1</v>
+      </c>
+      <c r="D1789">
+        <v>1</v>
+      </c>
+      <c r="E1789">
+        <v>1</v>
+      </c>
+      <c r="F1789">
+        <v>3</v>
+      </c>
+      <c r="H1789" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1789">
+        <v>0</v>
+      </c>
+      <c r="J1789">
+        <v>0</v>
+      </c>
+      <c r="K1789">
+        <v>100</v>
+      </c>
+      <c r="L1789">
+        <v>3</v>
+      </c>
+      <c r="M1789">
+        <v>1</v>
+      </c>
+      <c r="N1789">
+        <v>0</v>
+      </c>
+      <c r="O1789">
+        <v>0</v>
+      </c>
+      <c r="P1789">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="Q1789">
+        <v>0</v>
+      </c>
+      <c r="R1789">
+        <v>0</v>
+      </c>
+      <c r="S1789">
+        <v>0</v>
+      </c>
+      <c r="T1789">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1790" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1790">
+        <v>1</v>
+      </c>
+      <c r="D1790">
+        <v>1</v>
+      </c>
+      <c r="E1790">
+        <v>0</v>
+      </c>
+      <c r="F1790">
+        <v>17</v>
+      </c>
+      <c r="G1790">
+        <v>17</v>
+      </c>
+      <c r="H1790">
+        <v>17</v>
+      </c>
+      <c r="I1790">
+        <v>0</v>
+      </c>
+      <c r="J1790">
+        <v>0</v>
+      </c>
+      <c r="K1790">
+        <v>170</v>
+      </c>
+      <c r="L1790">
+        <v>10</v>
+      </c>
+      <c r="M1790">
+        <v>3</v>
+      </c>
+      <c r="N1790">
+        <v>3</v>
+      </c>
+      <c r="O1790">
+        <v>0</v>
+      </c>
+      <c r="P1790">
+        <v>11.49</v>
+      </c>
+      <c r="Q1790">
+        <v>0</v>
+      </c>
+      <c r="R1790">
+        <v>0</v>
+      </c>
+      <c r="S1790">
+        <v>0</v>
+      </c>
+      <c r="T1790">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1791" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1791">
+        <v>1</v>
+      </c>
+      <c r="D1791">
+        <v>1</v>
+      </c>
+      <c r="E1791">
+        <v>0</v>
+      </c>
+      <c r="F1791">
+        <v>26</v>
+      </c>
+      <c r="G1791">
+        <v>26</v>
+      </c>
+      <c r="H1791">
+        <v>26</v>
+      </c>
+      <c r="I1791">
+        <v>0</v>
+      </c>
+      <c r="J1791">
+        <v>0</v>
+      </c>
+      <c r="K1791">
+        <v>89.66</v>
+      </c>
+      <c r="L1791">
+        <v>29</v>
+      </c>
+      <c r="M1791">
+        <v>13</v>
+      </c>
+      <c r="N1791">
+        <v>1</v>
+      </c>
+      <c r="O1791">
+        <v>1</v>
+      </c>
+      <c r="P1791">
+        <v>17.57</v>
+      </c>
+      <c r="Q1791">
+        <v>0</v>
+      </c>
+      <c r="R1791">
+        <v>0</v>
+      </c>
+      <c r="S1791">
+        <v>0</v>
+      </c>
+      <c r="T1791">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1792" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1792">
+        <v>1</v>
+      </c>
+      <c r="D1792">
+        <v>1</v>
+      </c>
+      <c r="E1792">
+        <v>0</v>
+      </c>
+      <c r="F1792">
+        <v>15</v>
+      </c>
+      <c r="G1792">
+        <v>15</v>
+      </c>
+      <c r="H1792">
+        <v>15</v>
+      </c>
+      <c r="I1792">
+        <v>0</v>
+      </c>
+      <c r="J1792">
+        <v>0</v>
+      </c>
+      <c r="K1792">
+        <v>100</v>
+      </c>
+      <c r="L1792">
+        <v>15</v>
+      </c>
+      <c r="M1792">
+        <v>8</v>
+      </c>
+      <c r="N1792">
+        <v>2</v>
+      </c>
+      <c r="O1792">
+        <v>0</v>
+      </c>
+      <c r="P1792">
+        <v>10.07</v>
+      </c>
+      <c r="Q1792">
+        <v>0</v>
+      </c>
+      <c r="R1792">
+        <v>0</v>
+      </c>
+      <c r="S1792">
+        <v>0</v>
+      </c>
+      <c r="T1792">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1793" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1793">
+        <v>1</v>
+      </c>
+      <c r="D1793">
+        <v>1</v>
+      </c>
+      <c r="E1793">
+        <v>1</v>
+      </c>
+      <c r="F1793">
+        <v>31</v>
+      </c>
+      <c r="H1793" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1793">
+        <v>0</v>
+      </c>
+      <c r="J1793">
+        <v>0</v>
+      </c>
+      <c r="K1793">
+        <v>124</v>
+      </c>
+      <c r="L1793">
+        <v>25</v>
+      </c>
+      <c r="M1793">
+        <v>11</v>
+      </c>
+      <c r="N1793">
+        <v>1</v>
+      </c>
+      <c r="O1793">
+        <v>2</v>
+      </c>
+      <c r="P1793">
+        <v>20.81</v>
+      </c>
+      <c r="Q1793">
+        <v>0</v>
+      </c>
+      <c r="R1793">
+        <v>0</v>
+      </c>
+      <c r="S1793">
+        <v>0</v>
+      </c>
+      <c r="T1793">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1794" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1794">
+        <v>1</v>
+      </c>
+      <c r="D1794">
+        <v>1</v>
+      </c>
+      <c r="E1794">
+        <v>1</v>
+      </c>
+      <c r="F1794">
+        <v>30</v>
+      </c>
+      <c r="H1794" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1794">
+        <v>0</v>
+      </c>
+      <c r="J1794">
+        <v>0</v>
+      </c>
+      <c r="K1794">
+        <v>115.38</v>
+      </c>
+      <c r="L1794">
+        <v>26</v>
+      </c>
+      <c r="M1794">
+        <v>13</v>
+      </c>
+      <c r="N1794">
+        <v>4</v>
+      </c>
+      <c r="O1794">
+        <v>1</v>
+      </c>
+      <c r="P1794">
+        <v>20.13</v>
+      </c>
+      <c r="Q1794">
+        <v>0</v>
+      </c>
+      <c r="R1794">
+        <v>0</v>
+      </c>
+      <c r="S1794">
+        <v>0</v>
+      </c>
+      <c r="T1794">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1795" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>694</v>
+      </c>
+      <c r="C1795">
+        <v>1</v>
+      </c>
+      <c r="D1795">
+        <v>1</v>
+      </c>
+      <c r="E1795">
+        <v>0</v>
+      </c>
+      <c r="F1795">
+        <v>3</v>
+      </c>
+      <c r="G1795">
+        <v>3</v>
+      </c>
+      <c r="H1795">
+        <v>3</v>
+      </c>
+      <c r="I1795">
+        <v>0</v>
+      </c>
+      <c r="J1795">
+        <v>0</v>
+      </c>
+      <c r="K1795">
+        <v>100</v>
+      </c>
+      <c r="L1795">
+        <v>3</v>
+      </c>
+      <c r="M1795">
+        <v>0</v>
+      </c>
+      <c r="N1795">
+        <v>0</v>
+      </c>
+      <c r="O1795">
+        <v>0</v>
+      </c>
+      <c r="P1795">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="Q1795">
+        <v>0</v>
+      </c>
+      <c r="R1795">
+        <v>0</v>
+      </c>
+      <c r="S1795">
+        <v>0</v>
+      </c>
+      <c r="T1795">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1796" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1796">
+        <v>1</v>
+      </c>
+      <c r="D1796">
+        <v>1</v>
+      </c>
+      <c r="E1796">
+        <v>0</v>
+      </c>
+      <c r="F1796">
+        <v>7</v>
+      </c>
+      <c r="G1796">
+        <v>7</v>
+      </c>
+      <c r="H1796">
+        <v>7</v>
+      </c>
+      <c r="I1796">
+        <v>0</v>
+      </c>
+      <c r="J1796">
+        <v>0</v>
+      </c>
+      <c r="K1796">
+        <v>87.5</v>
+      </c>
+      <c r="L1796">
+        <v>8</v>
+      </c>
+      <c r="M1796">
+        <v>6</v>
+      </c>
+      <c r="N1796">
+        <v>1</v>
+      </c>
+      <c r="O1796">
+        <v>0</v>
+      </c>
+      <c r="P1796">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="Q1796">
+        <v>0</v>
+      </c>
+      <c r="R1796">
+        <v>1</v>
+      </c>
+      <c r="S1796">
+        <v>0</v>
+      </c>
+      <c r="T1796">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1797" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1797">
+        <v>1</v>
+      </c>
+      <c r="D1797">
+        <v>0</v>
+      </c>
+      <c r="E1797">
+        <v>0</v>
+      </c>
+      <c r="F1797">
+        <v>0</v>
+      </c>
+      <c r="I1797">
+        <v>0</v>
+      </c>
+      <c r="J1797">
+        <v>0</v>
+      </c>
+      <c r="L1797">
+        <v>0</v>
+      </c>
+      <c r="M1797">
+        <v>0</v>
+      </c>
+      <c r="N1797">
+        <v>0</v>
+      </c>
+      <c r="O1797">
+        <v>0</v>
+      </c>
+      <c r="P1797">
+        <v>0</v>
+      </c>
+      <c r="Q1797">
+        <v>1</v>
+      </c>
+      <c r="R1797">
+        <v>0</v>
+      </c>
+      <c r="S1797">
+        <v>0</v>
+      </c>
+      <c r="T1797">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1798" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>737</v>
+      </c>
+      <c r="C1798">
+        <v>1</v>
+      </c>
+      <c r="D1798">
+        <v>1</v>
+      </c>
+      <c r="E1798">
+        <v>0</v>
+      </c>
+      <c r="F1798">
+        <v>28</v>
+      </c>
+      <c r="G1798">
+        <v>28</v>
+      </c>
+      <c r="H1798">
+        <v>28</v>
+      </c>
+      <c r="I1798">
+        <v>0</v>
+      </c>
+      <c r="J1798">
+        <v>0</v>
+      </c>
+      <c r="K1798">
+        <v>90.32</v>
+      </c>
+      <c r="L1798">
+        <v>31</v>
+      </c>
+      <c r="M1798">
+        <v>15</v>
+      </c>
+      <c r="N1798">
+        <v>2</v>
+      </c>
+      <c r="O1798">
+        <v>1</v>
+      </c>
+      <c r="P1798">
+        <v>18.920000000000002</v>
+      </c>
+      <c r="Q1798">
+        <v>0</v>
+      </c>
+      <c r="R1798">
+        <v>0</v>
+      </c>
+      <c r="S1798">
+        <v>0</v>
+      </c>
+      <c r="T1798">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1799" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1799">
+        <v>1</v>
+      </c>
+      <c r="D1799">
+        <v>1</v>
+      </c>
+      <c r="E1799">
+        <v>0</v>
+      </c>
+      <c r="F1799">
+        <v>17</v>
+      </c>
+      <c r="G1799">
+        <v>17</v>
+      </c>
+      <c r="H1799">
+        <v>17</v>
+      </c>
+      <c r="I1799">
+        <v>0</v>
+      </c>
+      <c r="J1799">
+        <v>0</v>
+      </c>
+      <c r="K1799">
+        <v>121.43</v>
+      </c>
+      <c r="L1799">
+        <v>14</v>
+      </c>
+      <c r="M1799">
+        <v>5</v>
+      </c>
+      <c r="N1799">
+        <v>1</v>
+      </c>
+      <c r="O1799">
+        <v>1</v>
+      </c>
+      <c r="P1799">
+        <v>11.41</v>
+      </c>
+      <c r="Q1799">
+        <v>0</v>
+      </c>
+      <c r="R1799">
+        <v>0</v>
+      </c>
+      <c r="S1799">
+        <v>0</v>
+      </c>
+      <c r="T1799">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1800" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1800">
+        <v>1</v>
+      </c>
+      <c r="D1800">
+        <v>1</v>
+      </c>
+      <c r="E1800">
+        <v>0</v>
+      </c>
+      <c r="F1800">
+        <v>1</v>
+      </c>
+      <c r="G1800">
+        <v>1</v>
+      </c>
+      <c r="H1800">
+        <v>1</v>
+      </c>
+      <c r="I1800">
+        <v>0</v>
+      </c>
+      <c r="J1800">
+        <v>0</v>
+      </c>
+      <c r="K1800">
+        <v>14.29</v>
+      </c>
+      <c r="L1800">
+        <v>7</v>
+      </c>
+      <c r="M1800">
+        <v>6</v>
+      </c>
+      <c r="N1800">
+        <v>0</v>
+      </c>
+      <c r="O1800">
+        <v>0</v>
+      </c>
+      <c r="P1800">
+        <v>0.68</v>
+      </c>
+      <c r="Q1800">
+        <v>0</v>
+      </c>
+      <c r="R1800">
+        <v>0</v>
+      </c>
+      <c r="S1800">
+        <v>0</v>
+      </c>
+      <c r="T1800">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1801" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1801" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1801">
+        <v>1</v>
+      </c>
+      <c r="D1801">
+        <v>1</v>
+      </c>
+      <c r="E1801">
+        <v>1</v>
+      </c>
+      <c r="F1801">
+        <v>10</v>
+      </c>
+      <c r="H1801" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1801">
+        <v>0</v>
+      </c>
+      <c r="J1801">
+        <v>0</v>
+      </c>
+      <c r="K1801">
+        <v>83.33</v>
+      </c>
+      <c r="L1801">
+        <v>12</v>
+      </c>
+      <c r="M1801">
+        <v>6</v>
+      </c>
+      <c r="N1801">
+        <v>1</v>
+      </c>
+      <c r="O1801">
+        <v>0</v>
+      </c>
+      <c r="P1801">
+        <v>6.71</v>
+      </c>
+      <c r="Q1801">
+        <v>0</v>
+      </c>
+      <c r="R1801">
+        <v>0</v>
+      </c>
+      <c r="S1801">
+        <v>0</v>
+      </c>
+      <c r="T1801">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1802" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1802" t="s">
+        <v>586</v>
+      </c>
+      <c r="C1802">
+        <v>1</v>
+      </c>
+      <c r="D1802">
+        <v>1</v>
+      </c>
+      <c r="E1802">
+        <v>0</v>
+      </c>
+      <c r="F1802">
+        <v>30</v>
+      </c>
+      <c r="G1802">
+        <v>30</v>
+      </c>
+      <c r="H1802">
+        <v>30</v>
+      </c>
+      <c r="I1802">
+        <v>0</v>
+      </c>
+      <c r="J1802">
+        <v>0</v>
+      </c>
+      <c r="K1802">
+        <v>250</v>
+      </c>
+      <c r="L1802">
+        <v>12</v>
+      </c>
+      <c r="M1802">
+        <v>3</v>
+      </c>
+      <c r="N1802">
+        <v>5</v>
+      </c>
+      <c r="O1802">
+        <v>1</v>
+      </c>
+      <c r="P1802">
+        <v>20.27</v>
+      </c>
+      <c r="Q1802">
+        <v>1</v>
+      </c>
+      <c r="R1802">
+        <v>0</v>
+      </c>
+      <c r="S1802">
+        <v>0</v>
+      </c>
+      <c r="T1802">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1803" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1803" t="s">
+        <v>680</v>
+      </c>
+      <c r="C1803">
+        <v>1</v>
+      </c>
+      <c r="D1803">
+        <v>0</v>
+      </c>
+      <c r="E1803">
+        <v>0</v>
+      </c>
+      <c r="F1803">
+        <v>0</v>
+      </c>
+      <c r="I1803">
+        <v>0</v>
+      </c>
+      <c r="J1803">
+        <v>0</v>
+      </c>
+      <c r="L1803">
+        <v>0</v>
+      </c>
+      <c r="M1803">
+        <v>0</v>
+      </c>
+      <c r="N1803">
+        <v>0</v>
+      </c>
+      <c r="O1803">
+        <v>0</v>
+      </c>
+      <c r="P1803">
+        <v>0</v>
+      </c>
+      <c r="Q1803">
+        <v>0</v>
+      </c>
+      <c r="R1803">
+        <v>0</v>
+      </c>
+      <c r="S1803">
+        <v>0</v>
+      </c>
+      <c r="T1803">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1804" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1804" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1804">
+        <v>1</v>
+      </c>
+      <c r="D1804">
+        <v>1</v>
+      </c>
+      <c r="E1804">
+        <v>1</v>
+      </c>
+      <c r="F1804">
+        <v>22</v>
+      </c>
+      <c r="H1804" t="s">
+        <v>219</v>
+      </c>
+      <c r="I1804">
+        <v>0</v>
+      </c>
+      <c r="J1804">
+        <v>0</v>
+      </c>
+      <c r="K1804">
+        <v>146.66999999999999</v>
+      </c>
+      <c r="L1804">
+        <v>15</v>
+      </c>
+      <c r="M1804">
+        <v>4</v>
+      </c>
+      <c r="N1804">
+        <v>1</v>
+      </c>
+      <c r="O1804">
+        <v>1</v>
+      </c>
+      <c r="P1804">
+        <v>13.02</v>
+      </c>
+      <c r="Q1804">
+        <v>0</v>
+      </c>
+      <c r="R1804">
+        <v>0</v>
+      </c>
+      <c r="S1804">
+        <v>0</v>
+      </c>
+      <c r="T1804">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1805" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1805" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1805">
+        <v>1</v>
+      </c>
+      <c r="D1805">
+        <v>0</v>
+      </c>
+      <c r="E1805">
+        <v>0</v>
+      </c>
+      <c r="F1805">
+        <v>0</v>
+      </c>
+      <c r="I1805">
+        <v>0</v>
+      </c>
+      <c r="J1805">
+        <v>0</v>
+      </c>
+      <c r="L1805">
+        <v>0</v>
+      </c>
+      <c r="M1805">
+        <v>0</v>
+      </c>
+      <c r="N1805">
+        <v>0</v>
+      </c>
+      <c r="O1805">
+        <v>0</v>
+      </c>
+      <c r="P1805">
+        <v>0</v>
+      </c>
+      <c r="Q1805">
+        <v>0</v>
+      </c>
+      <c r="R1805">
+        <v>0</v>
+      </c>
+      <c r="S1805">
+        <v>0</v>
+      </c>
+      <c r="T1805">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1806" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1806" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1806">
+        <v>1</v>
+      </c>
+      <c r="D1806">
+        <v>1</v>
+      </c>
+      <c r="E1806">
+        <v>0</v>
+      </c>
+      <c r="F1806">
+        <v>32</v>
+      </c>
+      <c r="G1806">
+        <v>32</v>
+      </c>
+      <c r="H1806">
+        <v>32</v>
+      </c>
+      <c r="I1806">
+        <v>0</v>
+      </c>
+      <c r="J1806">
+        <v>0</v>
+      </c>
+      <c r="K1806">
+        <v>114.29</v>
+      </c>
+      <c r="L1806">
+        <v>28</v>
+      </c>
+      <c r="M1806">
+        <v>11</v>
+      </c>
+      <c r="N1806">
+        <v>3</v>
+      </c>
+      <c r="O1806">
+        <v>1</v>
+      </c>
+      <c r="P1806">
+        <v>20.51</v>
+      </c>
+      <c r="Q1806">
+        <v>0</v>
+      </c>
+      <c r="R1806">
+        <v>0</v>
+      </c>
+      <c r="S1806">
+        <v>0</v>
+      </c>
+      <c r="T1806">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1807" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1807" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1807">
+        <v>1</v>
+      </c>
+      <c r="D1807">
+        <v>1</v>
+      </c>
+      <c r="E1807">
+        <v>1</v>
+      </c>
+      <c r="F1807">
+        <v>12</v>
+      </c>
+      <c r="H1807" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1807">
+        <v>0</v>
+      </c>
+      <c r="J1807">
+        <v>0</v>
+      </c>
+      <c r="K1807">
+        <v>60</v>
+      </c>
+      <c r="L1807">
+        <v>20</v>
+      </c>
+      <c r="M1807">
+        <v>10</v>
+      </c>
+      <c r="N1807">
+        <v>0</v>
+      </c>
+      <c r="O1807">
+        <v>0</v>
+      </c>
+      <c r="P1807">
+        <v>7.69</v>
+      </c>
+      <c r="Q1807">
+        <v>2</v>
+      </c>
+      <c r="R1807">
+        <v>0</v>
+      </c>
+      <c r="S1807">
+        <v>0</v>
+      </c>
+      <c r="T1807">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1808" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1808" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1808">
+        <v>1</v>
+      </c>
+      <c r="D1808">
+        <v>1</v>
+      </c>
+      <c r="E1808">
+        <v>1</v>
+      </c>
+      <c r="F1808">
+        <v>3</v>
+      </c>
+      <c r="H1808" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1808">
+        <v>0</v>
+      </c>
+      <c r="J1808">
+        <v>0</v>
+      </c>
+      <c r="K1808">
+        <v>30</v>
+      </c>
+      <c r="L1808">
+        <v>10</v>
+      </c>
+      <c r="M1808">
+        <v>7</v>
+      </c>
+      <c r="N1808">
+        <v>0</v>
+      </c>
+      <c r="O1808">
+        <v>0</v>
+      </c>
+      <c r="P1808">
+        <v>1.92</v>
+      </c>
+      <c r="Q1808">
+        <v>0</v>
+      </c>
+      <c r="R1808">
+        <v>0</v>
+      </c>
+      <c r="S1808">
+        <v>0</v>
+      </c>
+      <c r="T1808">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1809" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1809" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1809">
+        <v>1</v>
+      </c>
+      <c r="D1809">
+        <v>1</v>
+      </c>
+      <c r="E1809">
+        <v>0</v>
+      </c>
+      <c r="F1809">
+        <v>7</v>
+      </c>
+      <c r="G1809">
+        <v>7</v>
+      </c>
+      <c r="H1809">
+        <v>7</v>
+      </c>
+      <c r="I1809">
+        <v>0</v>
+      </c>
+      <c r="J1809">
+        <v>0</v>
+      </c>
+      <c r="K1809">
+        <v>100</v>
+      </c>
+      <c r="L1809">
+        <v>7</v>
+      </c>
+      <c r="M1809">
+        <v>3</v>
+      </c>
+      <c r="N1809">
+        <v>1</v>
+      </c>
+      <c r="O1809">
+        <v>0</v>
+      </c>
+      <c r="P1809">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="Q1809">
+        <v>0</v>
+      </c>
+      <c r="R1809">
+        <v>0</v>
+      </c>
+      <c r="S1809">
+        <v>0</v>
+      </c>
+      <c r="T1809">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1810" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1810" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1810">
+        <v>1</v>
+      </c>
+      <c r="D1810">
+        <v>1</v>
+      </c>
+      <c r="E1810">
+        <v>0</v>
+      </c>
+      <c r="F1810">
+        <v>0</v>
+      </c>
+      <c r="G1810">
+        <v>0</v>
+      </c>
+      <c r="H1810">
+        <v>0</v>
+      </c>
+      <c r="I1810">
+        <v>0</v>
+      </c>
+      <c r="J1810">
+        <v>0</v>
+      </c>
+      <c r="K1810">
+        <v>0</v>
+      </c>
+      <c r="L1810">
+        <v>2</v>
+      </c>
+      <c r="M1810">
+        <v>2</v>
+      </c>
+      <c r="N1810">
+        <v>0</v>
+      </c>
+      <c r="O1810">
+        <v>0</v>
+      </c>
+      <c r="P1810">
+        <v>0</v>
+      </c>
+      <c r="Q1810">
+        <v>0</v>
+      </c>
+      <c r="R1810">
+        <v>0</v>
+      </c>
+      <c r="S1810">
+        <v>0</v>
+      </c>
+      <c r="T1810">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1811" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1811" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1811">
+        <v>1</v>
+      </c>
+      <c r="D1811">
+        <v>0</v>
+      </c>
+      <c r="E1811">
+        <v>0</v>
+      </c>
+      <c r="F1811">
+        <v>0</v>
+      </c>
+      <c r="I1811">
+        <v>0</v>
+      </c>
+      <c r="J1811">
+        <v>0</v>
+      </c>
+      <c r="L1811">
+        <v>0</v>
+      </c>
+      <c r="M1811">
+        <v>0</v>
+      </c>
+      <c r="N1811">
+        <v>0</v>
+      </c>
+      <c r="O1811">
+        <v>0</v>
+      </c>
+      <c r="P1811">
+        <v>0</v>
+      </c>
+      <c r="Q1811">
+        <v>0</v>
+      </c>
+      <c r="R1811">
+        <v>0</v>
+      </c>
+      <c r="S1811">
+        <v>0</v>
+      </c>
+      <c r="T1811">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1812" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1812" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1812">
+        <v>1</v>
+      </c>
+      <c r="D1812">
+        <v>1</v>
+      </c>
+      <c r="E1812">
+        <v>0</v>
+      </c>
+      <c r="F1812">
+        <v>29</v>
+      </c>
+      <c r="G1812">
+        <v>29</v>
+      </c>
+      <c r="H1812">
+        <v>29</v>
+      </c>
+      <c r="I1812">
+        <v>0</v>
+      </c>
+      <c r="J1812">
+        <v>0</v>
+      </c>
+      <c r="K1812">
+        <v>241.67</v>
+      </c>
+      <c r="L1812">
+        <v>12</v>
+      </c>
+      <c r="M1812">
+        <v>4</v>
+      </c>
+      <c r="N1812">
+        <v>0</v>
+      </c>
+      <c r="O1812">
+        <v>4</v>
+      </c>
+      <c r="P1812">
+        <v>17.16</v>
+      </c>
+      <c r="Q1812">
+        <v>0</v>
+      </c>
+      <c r="R1812">
+        <v>0</v>
+      </c>
+      <c r="S1812">
+        <v>0</v>
+      </c>
+      <c r="T1812">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1813" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1813" t="s">
+        <v>698</v>
+      </c>
+      <c r="C1813">
+        <v>1</v>
+      </c>
+      <c r="D1813">
+        <v>1</v>
+      </c>
+      <c r="E1813">
+        <v>0</v>
+      </c>
+      <c r="F1813">
+        <v>6</v>
+      </c>
+      <c r="G1813">
+        <v>6</v>
+      </c>
+      <c r="H1813">
+        <v>6</v>
+      </c>
+      <c r="I1813">
+        <v>0</v>
+      </c>
+      <c r="J1813">
+        <v>0</v>
+      </c>
+      <c r="K1813">
+        <v>150</v>
+      </c>
+      <c r="L1813">
+        <v>4</v>
+      </c>
+      <c r="M1813">
+        <v>2</v>
+      </c>
+      <c r="N1813">
+        <v>1</v>
+      </c>
+      <c r="O1813">
+        <v>0</v>
+      </c>
+      <c r="P1813">
+        <v>3.85</v>
+      </c>
+      <c r="Q1813">
+        <v>0</v>
+      </c>
+      <c r="R1813">
+        <v>0</v>
+      </c>
+      <c r="S1813">
+        <v>0</v>
+      </c>
+      <c r="T1813">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1814" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1814" t="s">
+        <v>715</v>
+      </c>
+      <c r="C1814">
+        <v>1</v>
+      </c>
+      <c r="D1814">
+        <v>1</v>
+      </c>
+      <c r="E1814">
+        <v>0</v>
+      </c>
+      <c r="F1814">
+        <v>12</v>
+      </c>
+      <c r="G1814">
+        <v>12</v>
+      </c>
+      <c r="H1814">
+        <v>12</v>
+      </c>
+      <c r="I1814">
+        <v>0</v>
+      </c>
+      <c r="J1814">
+        <v>0</v>
+      </c>
+      <c r="K1814">
+        <v>300</v>
+      </c>
+      <c r="L1814">
+        <v>4</v>
+      </c>
+      <c r="M1814">
+        <v>2</v>
+      </c>
+      <c r="N1814">
+        <v>0</v>
+      </c>
+      <c r="O1814">
+        <v>2</v>
+      </c>
+      <c r="P1814">
+        <v>7.69</v>
+      </c>
+      <c r="Q1814">
+        <v>0</v>
+      </c>
+      <c r="R1814">
+        <v>0</v>
+      </c>
+      <c r="S1814">
+        <v>0</v>
+      </c>
+      <c r="T1814">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1815" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1815" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1815">
+        <v>1</v>
+      </c>
+      <c r="D1815">
+        <v>1</v>
+      </c>
+      <c r="E1815">
+        <v>1</v>
+      </c>
+      <c r="F1815">
+        <v>1</v>
+      </c>
+      <c r="H1815" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1815">
+        <v>0</v>
+      </c>
+      <c r="J1815">
+        <v>0</v>
+      </c>
+      <c r="K1815">
+        <v>100</v>
+      </c>
+      <c r="L1815">
+        <v>1</v>
+      </c>
+      <c r="M1815">
+        <v>0</v>
+      </c>
+      <c r="N1815">
+        <v>0</v>
+      </c>
+      <c r="O1815">
+        <v>0</v>
+      </c>
+      <c r="P1815">
+        <v>0.59</v>
+      </c>
+      <c r="Q1815">
+        <v>0</v>
+      </c>
+      <c r="R1815">
+        <v>0</v>
+      </c>
+      <c r="S1815">
+        <v>0</v>
+      </c>
+      <c r="T1815">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1816" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1816" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1816">
+        <v>1</v>
+      </c>
+      <c r="D1816">
+        <v>1</v>
+      </c>
+      <c r="E1816">
+        <v>0</v>
+      </c>
+      <c r="F1816">
+        <v>31</v>
+      </c>
+      <c r="G1816">
+        <v>31</v>
+      </c>
+      <c r="H1816">
+        <v>31</v>
+      </c>
+      <c r="I1816">
+        <v>0</v>
+      </c>
+      <c r="J1816">
+        <v>0</v>
+      </c>
+      <c r="K1816">
+        <v>124</v>
+      </c>
+      <c r="L1816">
+        <v>25</v>
+      </c>
+      <c r="M1816">
+        <v>9</v>
+      </c>
+      <c r="N1816">
+        <v>2</v>
+      </c>
+      <c r="O1816">
+        <v>1</v>
+      </c>
+      <c r="P1816">
+        <v>19.87</v>
+      </c>
+      <c r="Q1816">
+        <v>0</v>
+      </c>
+      <c r="R1816">
+        <v>0</v>
+      </c>
+      <c r="S1816">
+        <v>0</v>
+      </c>
+      <c r="T1816">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1817" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1817" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1817">
+        <v>1</v>
+      </c>
+      <c r="D1817">
+        <v>0</v>
+      </c>
+      <c r="E1817">
+        <v>0</v>
+      </c>
+      <c r="F1817">
+        <v>0</v>
+      </c>
+      <c r="I1817">
+        <v>0</v>
+      </c>
+      <c r="J1817">
+        <v>0</v>
+      </c>
+      <c r="L1817">
+        <v>0</v>
+      </c>
+      <c r="M1817">
+        <v>0</v>
+      </c>
+      <c r="N1817">
+        <v>0</v>
+      </c>
+      <c r="O1817">
+        <v>0</v>
+      </c>
+      <c r="P1817">
+        <v>0</v>
+      </c>
+      <c r="Q1817">
+        <v>0</v>
+      </c>
+      <c r="R1817">
+        <v>0</v>
+      </c>
+      <c r="S1817">
+        <v>0</v>
+      </c>
+      <c r="T1817">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1818" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1818" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1818">
+        <v>1</v>
+      </c>
+      <c r="D1818">
+        <v>1</v>
+      </c>
+      <c r="E1818">
+        <v>0</v>
+      </c>
+      <c r="F1818">
+        <v>6</v>
+      </c>
+      <c r="G1818">
+        <v>6</v>
+      </c>
+      <c r="H1818">
+        <v>6</v>
+      </c>
+      <c r="I1818">
+        <v>0</v>
+      </c>
+      <c r="J1818">
+        <v>0</v>
+      </c>
+      <c r="K1818">
+        <v>150</v>
+      </c>
+      <c r="L1818">
+        <v>4</v>
+      </c>
+      <c r="M1818">
+        <v>2</v>
+      </c>
+      <c r="N1818">
+        <v>1</v>
+      </c>
+      <c r="O1818">
+        <v>0</v>
+      </c>
+      <c r="P1818">
+        <v>3.55</v>
+      </c>
+      <c r="Q1818">
+        <v>0</v>
+      </c>
+      <c r="R1818">
+        <v>0</v>
+      </c>
+      <c r="S1818">
+        <v>0</v>
+      </c>
+      <c r="T1818">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1819" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1819" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1819">
+        <v>1</v>
+      </c>
+      <c r="D1819">
+        <v>1</v>
+      </c>
+      <c r="E1819">
+        <v>0</v>
+      </c>
+      <c r="F1819">
+        <v>5</v>
+      </c>
+      <c r="G1819">
+        <v>5</v>
+      </c>
+      <c r="H1819">
+        <v>5</v>
+      </c>
+      <c r="I1819">
+        <v>0</v>
+      </c>
+      <c r="J1819">
+        <v>0</v>
+      </c>
+      <c r="K1819">
+        <v>50</v>
+      </c>
+      <c r="L1819">
+        <v>10</v>
+      </c>
+      <c r="M1819">
+        <v>5</v>
+      </c>
+      <c r="N1819">
+        <v>0</v>
+      </c>
+      <c r="O1819">
+        <v>0</v>
+      </c>
+      <c r="P1819">
+        <v>2.96</v>
+      </c>
+      <c r="Q1819">
+        <v>0</v>
+      </c>
+      <c r="R1819">
+        <v>0</v>
+      </c>
+      <c r="S1819">
+        <v>0</v>
+      </c>
+      <c r="T1819">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1820" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1820" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1820">
+        <v>1</v>
+      </c>
+      <c r="D1820">
+        <v>1</v>
+      </c>
+      <c r="E1820">
+        <v>0</v>
+      </c>
+      <c r="F1820">
+        <v>25</v>
+      </c>
+      <c r="G1820">
+        <v>25</v>
+      </c>
+      <c r="H1820">
+        <v>25</v>
+      </c>
+      <c r="I1820">
+        <v>0</v>
+      </c>
+      <c r="J1820">
+        <v>0</v>
+      </c>
+      <c r="K1820">
+        <v>78.13</v>
+      </c>
+      <c r="L1820">
+        <v>32</v>
+      </c>
+      <c r="M1820">
+        <v>17</v>
+      </c>
+      <c r="N1820">
+        <v>3</v>
+      </c>
+      <c r="O1820">
+        <v>0</v>
+      </c>
+      <c r="P1820">
+        <v>14.79</v>
+      </c>
+      <c r="Q1820">
+        <v>0</v>
+      </c>
+      <c r="R1820">
+        <v>0</v>
+      </c>
+      <c r="S1820">
+        <v>0</v>
+      </c>
+      <c r="T1820">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1821" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1821" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1821">
+        <v>1</v>
+      </c>
+      <c r="D1821">
+        <v>0</v>
+      </c>
+      <c r="E1821">
+        <v>0</v>
+      </c>
+      <c r="F1821">
+        <v>0</v>
+      </c>
+      <c r="I1821">
+        <v>0</v>
+      </c>
+      <c r="J1821">
+        <v>0</v>
+      </c>
+      <c r="L1821">
+        <v>0</v>
+      </c>
+      <c r="M1821">
+        <v>0</v>
+      </c>
+      <c r="N1821">
+        <v>0</v>
+      </c>
+      <c r="O1821">
+        <v>0</v>
+      </c>
+      <c r="P1821">
+        <v>0</v>
+      </c>
+      <c r="Q1821">
+        <v>0</v>
+      </c>
+      <c r="R1821">
+        <v>0</v>
+      </c>
+      <c r="S1821">
+        <v>0</v>
+      </c>
+      <c r="T1821">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1822" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1822" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1822">
+        <v>1</v>
+      </c>
+      <c r="D1822">
+        <v>1</v>
+      </c>
+      <c r="E1822">
+        <v>1</v>
+      </c>
+      <c r="F1822">
+        <v>30</v>
+      </c>
+      <c r="H1822" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1822">
+        <v>0</v>
+      </c>
+      <c r="J1822">
+        <v>0</v>
+      </c>
+      <c r="K1822">
+        <v>115.38</v>
+      </c>
+      <c r="L1822">
+        <v>26</v>
+      </c>
+      <c r="M1822">
+        <v>12</v>
+      </c>
+      <c r="N1822">
+        <v>0</v>
+      </c>
+      <c r="O1822">
+        <v>3</v>
+      </c>
+      <c r="P1822">
+        <v>17.75</v>
+      </c>
+      <c r="Q1822">
+        <v>0</v>
+      </c>
+      <c r="R1822">
+        <v>1</v>
+      </c>
+      <c r="S1822">
+        <v>0</v>
+      </c>
+      <c r="T1822">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1823" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1823" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1823">
+        <v>1</v>
+      </c>
+      <c r="D1823">
+        <v>1</v>
+      </c>
+      <c r="E1823">
+        <v>0</v>
+      </c>
+      <c r="F1823">
+        <v>18</v>
+      </c>
+      <c r="G1823">
+        <v>18</v>
+      </c>
+      <c r="H1823">
+        <v>18</v>
+      </c>
+      <c r="I1823">
+        <v>0</v>
+      </c>
+      <c r="J1823">
+        <v>0</v>
+      </c>
+      <c r="K1823">
+        <v>100</v>
+      </c>
+      <c r="L1823">
+        <v>18</v>
+      </c>
+      <c r="M1823">
+        <v>9</v>
+      </c>
+      <c r="N1823">
+        <v>3</v>
+      </c>
+      <c r="O1823">
+        <v>0</v>
+      </c>
+      <c r="P1823">
+        <v>11.54</v>
+      </c>
+      <c r="Q1823">
+        <v>1</v>
+      </c>
+      <c r="R1823">
+        <v>0</v>
+      </c>
+      <c r="S1823">
+        <v>0</v>
+      </c>
+      <c r="T1823">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1824" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1824" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1824">
+        <v>1</v>
+      </c>
+      <c r="D1824">
+        <v>1</v>
+      </c>
+      <c r="E1824">
+        <v>0</v>
+      </c>
+      <c r="F1824">
+        <v>23</v>
+      </c>
+      <c r="G1824">
+        <v>23</v>
+      </c>
+      <c r="H1824">
+        <v>23</v>
+      </c>
+      <c r="I1824">
+        <v>0</v>
+      </c>
+      <c r="J1824">
+        <v>0</v>
+      </c>
+      <c r="K1824">
+        <v>164.29</v>
+      </c>
+      <c r="L1824">
+        <v>14</v>
+      </c>
+      <c r="M1824">
+        <v>7</v>
+      </c>
+      <c r="N1824">
+        <v>2</v>
+      </c>
+      <c r="O1824">
+        <v>2</v>
+      </c>
+      <c r="P1824">
+        <v>13.61</v>
+      </c>
+      <c r="Q1824">
+        <v>0</v>
+      </c>
+      <c r="R1824">
+        <v>0</v>
+      </c>
+      <c r="S1824">
+        <v>0</v>
+      </c>
+      <c r="T1824">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1825" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1825" t="s">
+        <v>510</v>
+      </c>
+      <c r="C1825">
+        <v>1</v>
+      </c>
+      <c r="D1825">
+        <v>1</v>
+      </c>
+      <c r="E1825">
+        <v>0</v>
+      </c>
+      <c r="F1825">
+        <v>20</v>
+      </c>
+      <c r="G1825">
+        <v>20</v>
+      </c>
+      <c r="H1825">
+        <v>20</v>
+      </c>
+      <c r="I1825">
+        <v>0</v>
+      </c>
+      <c r="J1825">
+        <v>0</v>
+      </c>
+      <c r="K1825">
+        <v>200</v>
+      </c>
+      <c r="L1825">
+        <v>10</v>
+      </c>
+      <c r="M1825">
+        <v>4</v>
+      </c>
+      <c r="N1825">
+        <v>1</v>
+      </c>
+      <c r="O1825">
+        <v>2</v>
+      </c>
+      <c r="P1825">
+        <v>12.82</v>
+      </c>
+      <c r="Q1825">
+        <v>0</v>
+      </c>
+      <c r="R1825">
+        <v>0</v>
+      </c>
+      <c r="S1825">
+        <v>0</v>
+      </c>
+      <c r="T1825">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A1628:T1656">
     <sortCondition ref="B1628:B1656"/>

--- a/NV Play Midweek League batting stats for season.xlsx
+++ b/NV Play Midweek League batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4141" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4189" uniqueCount="741">
   <si>
     <t>Group</t>
   </si>
@@ -2237,6 +2237,12 @@
   <si>
     <t>Muckamore MW1 XI v Arches MW XI, Moylena - 29 July 2026</t>
   </si>
+  <si>
+    <t>Arches MW XI v Dunmurry MW2 XI, City of Belfast Playing Fields (Dunmurry) - 6 August 2026</t>
+  </si>
+  <si>
+    <t>Purvik Prasad</t>
+  </si>
 </sst>
 </file>
 
@@ -3043,7 +3049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1825"/>
+  <dimension ref="A1:U1847"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61" customWidth="1"/>
@@ -112291,6 +112297,1346 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1826" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1826" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1826" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1826">
+        <v>1</v>
+      </c>
+      <c r="D1826">
+        <v>1</v>
+      </c>
+      <c r="E1826">
+        <v>0</v>
+      </c>
+      <c r="F1826">
+        <v>10</v>
+      </c>
+      <c r="G1826">
+        <v>10</v>
+      </c>
+      <c r="H1826">
+        <v>10</v>
+      </c>
+      <c r="I1826">
+        <v>0</v>
+      </c>
+      <c r="J1826">
+        <v>0</v>
+      </c>
+      <c r="K1826">
+        <v>111.11</v>
+      </c>
+      <c r="L1826">
+        <v>9</v>
+      </c>
+      <c r="M1826">
+        <v>3</v>
+      </c>
+      <c r="N1826">
+        <v>1</v>
+      </c>
+      <c r="O1826">
+        <v>0</v>
+      </c>
+      <c r="P1826">
+        <v>5.24</v>
+      </c>
+      <c r="Q1826">
+        <v>0</v>
+      </c>
+      <c r="R1826">
+        <v>0</v>
+      </c>
+      <c r="S1826">
+        <v>0</v>
+      </c>
+      <c r="T1826">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1827" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1827" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1827">
+        <v>1</v>
+      </c>
+      <c r="D1827">
+        <v>1</v>
+      </c>
+      <c r="E1827">
+        <v>0</v>
+      </c>
+      <c r="F1827">
+        <v>5</v>
+      </c>
+      <c r="G1827">
+        <v>5</v>
+      </c>
+      <c r="H1827">
+        <v>5</v>
+      </c>
+      <c r="I1827">
+        <v>0</v>
+      </c>
+      <c r="J1827">
+        <v>0</v>
+      </c>
+      <c r="K1827">
+        <v>83.33</v>
+      </c>
+      <c r="L1827">
+        <v>6</v>
+      </c>
+      <c r="M1827">
+        <v>4</v>
+      </c>
+      <c r="N1827">
+        <v>1</v>
+      </c>
+      <c r="O1827">
+        <v>0</v>
+      </c>
+      <c r="P1827">
+        <v>5.56</v>
+      </c>
+      <c r="Q1827">
+        <v>0</v>
+      </c>
+      <c r="R1827">
+        <v>0</v>
+      </c>
+      <c r="S1827">
+        <v>0</v>
+      </c>
+      <c r="T1827">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1828" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1828" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1828">
+        <v>1</v>
+      </c>
+      <c r="D1828">
+        <v>1</v>
+      </c>
+      <c r="E1828">
+        <v>0</v>
+      </c>
+      <c r="F1828">
+        <v>30</v>
+      </c>
+      <c r="G1828">
+        <v>30</v>
+      </c>
+      <c r="H1828">
+        <v>30</v>
+      </c>
+      <c r="I1828">
+        <v>0</v>
+      </c>
+      <c r="J1828">
+        <v>0</v>
+      </c>
+      <c r="K1828">
+        <v>166.67</v>
+      </c>
+      <c r="L1828">
+        <v>18</v>
+      </c>
+      <c r="M1828">
+        <v>9</v>
+      </c>
+      <c r="N1828">
+        <v>1</v>
+      </c>
+      <c r="O1828">
+        <v>3</v>
+      </c>
+      <c r="P1828">
+        <v>15.71</v>
+      </c>
+      <c r="Q1828">
+        <v>0</v>
+      </c>
+      <c r="R1828">
+        <v>0</v>
+      </c>
+      <c r="S1828">
+        <v>0</v>
+      </c>
+      <c r="T1828">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1829" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1829" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1829">
+        <v>1</v>
+      </c>
+      <c r="D1829">
+        <v>1</v>
+      </c>
+      <c r="E1829">
+        <v>0</v>
+      </c>
+      <c r="F1829">
+        <v>9</v>
+      </c>
+      <c r="G1829">
+        <v>9</v>
+      </c>
+      <c r="H1829">
+        <v>9</v>
+      </c>
+      <c r="I1829">
+        <v>0</v>
+      </c>
+      <c r="J1829">
+        <v>0</v>
+      </c>
+      <c r="K1829">
+        <v>69.23</v>
+      </c>
+      <c r="L1829">
+        <v>13</v>
+      </c>
+      <c r="M1829">
+        <v>10</v>
+      </c>
+      <c r="N1829">
+        <v>2</v>
+      </c>
+      <c r="O1829">
+        <v>0</v>
+      </c>
+      <c r="P1829">
+        <v>10</v>
+      </c>
+      <c r="Q1829">
+        <v>1</v>
+      </c>
+      <c r="R1829">
+        <v>0</v>
+      </c>
+      <c r="S1829">
+        <v>0</v>
+      </c>
+      <c r="T1829">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1830" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1830" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1830">
+        <v>1</v>
+      </c>
+      <c r="D1830">
+        <v>1</v>
+      </c>
+      <c r="E1830">
+        <v>0</v>
+      </c>
+      <c r="F1830">
+        <v>5</v>
+      </c>
+      <c r="G1830">
+        <v>5</v>
+      </c>
+      <c r="H1830">
+        <v>5</v>
+      </c>
+      <c r="I1830">
+        <v>0</v>
+      </c>
+      <c r="J1830">
+        <v>0</v>
+      </c>
+      <c r="K1830">
+        <v>33.33</v>
+      </c>
+      <c r="L1830">
+        <v>15</v>
+      </c>
+      <c r="M1830">
+        <v>11</v>
+      </c>
+      <c r="N1830">
+        <v>0</v>
+      </c>
+      <c r="O1830">
+        <v>0</v>
+      </c>
+      <c r="P1830">
+        <v>5.56</v>
+      </c>
+      <c r="Q1830">
+        <v>0</v>
+      </c>
+      <c r="R1830">
+        <v>0</v>
+      </c>
+      <c r="S1830">
+        <v>0</v>
+      </c>
+      <c r="T1830">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1831" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1831" t="s">
+        <v>736</v>
+      </c>
+      <c r="C1831">
+        <v>1</v>
+      </c>
+      <c r="D1831">
+        <v>1</v>
+      </c>
+      <c r="E1831">
+        <v>1</v>
+      </c>
+      <c r="F1831">
+        <v>30</v>
+      </c>
+      <c r="H1831" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1831">
+        <v>0</v>
+      </c>
+      <c r="J1831">
+        <v>0</v>
+      </c>
+      <c r="K1831">
+        <v>150</v>
+      </c>
+      <c r="L1831">
+        <v>20</v>
+      </c>
+      <c r="M1831">
+        <v>5</v>
+      </c>
+      <c r="N1831">
+        <v>3</v>
+      </c>
+      <c r="O1831">
+        <v>1</v>
+      </c>
+      <c r="P1831">
+        <v>15.71</v>
+      </c>
+      <c r="Q1831">
+        <v>0</v>
+      </c>
+      <c r="R1831">
+        <v>0</v>
+      </c>
+      <c r="S1831">
+        <v>0</v>
+      </c>
+      <c r="T1831">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1832" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1832" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1832">
+        <v>1</v>
+      </c>
+      <c r="D1832">
+        <v>1</v>
+      </c>
+      <c r="E1832">
+        <v>0</v>
+      </c>
+      <c r="F1832">
+        <v>3</v>
+      </c>
+      <c r="G1832">
+        <v>3</v>
+      </c>
+      <c r="H1832">
+        <v>3</v>
+      </c>
+      <c r="I1832">
+        <v>0</v>
+      </c>
+      <c r="J1832">
+        <v>0</v>
+      </c>
+      <c r="K1832">
+        <v>75</v>
+      </c>
+      <c r="L1832">
+        <v>4</v>
+      </c>
+      <c r="M1832">
+        <v>2</v>
+      </c>
+      <c r="N1832">
+        <v>0</v>
+      </c>
+      <c r="O1832">
+        <v>0</v>
+      </c>
+      <c r="P1832">
+        <v>1.57</v>
+      </c>
+      <c r="Q1832">
+        <v>0</v>
+      </c>
+      <c r="R1832">
+        <v>0</v>
+      </c>
+      <c r="S1832">
+        <v>0</v>
+      </c>
+      <c r="T1832">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1833" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1833" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1833">
+        <v>1</v>
+      </c>
+      <c r="D1833">
+        <v>1</v>
+      </c>
+      <c r="E1833">
+        <v>0</v>
+      </c>
+      <c r="F1833">
+        <v>3</v>
+      </c>
+      <c r="G1833">
+        <v>3</v>
+      </c>
+      <c r="H1833">
+        <v>3</v>
+      </c>
+      <c r="I1833">
+        <v>0</v>
+      </c>
+      <c r="J1833">
+        <v>0</v>
+      </c>
+      <c r="K1833">
+        <v>27.27</v>
+      </c>
+      <c r="L1833">
+        <v>11</v>
+      </c>
+      <c r="M1833">
+        <v>8</v>
+      </c>
+      <c r="N1833">
+        <v>0</v>
+      </c>
+      <c r="O1833">
+        <v>0</v>
+      </c>
+      <c r="P1833">
+        <v>3.33</v>
+      </c>
+      <c r="Q1833">
+        <v>0</v>
+      </c>
+      <c r="R1833">
+        <v>0</v>
+      </c>
+      <c r="S1833">
+        <v>0</v>
+      </c>
+      <c r="T1833">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1834" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1834" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1834">
+        <v>1</v>
+      </c>
+      <c r="D1834">
+        <v>1</v>
+      </c>
+      <c r="E1834">
+        <v>0</v>
+      </c>
+      <c r="F1834">
+        <v>10</v>
+      </c>
+      <c r="G1834">
+        <v>10</v>
+      </c>
+      <c r="H1834">
+        <v>10</v>
+      </c>
+      <c r="I1834">
+        <v>0</v>
+      </c>
+      <c r="J1834">
+        <v>0</v>
+      </c>
+      <c r="K1834">
+        <v>76.92</v>
+      </c>
+      <c r="L1834">
+        <v>13</v>
+      </c>
+      <c r="M1834">
+        <v>8</v>
+      </c>
+      <c r="N1834">
+        <v>0</v>
+      </c>
+      <c r="O1834">
+        <v>1</v>
+      </c>
+      <c r="P1834">
+        <v>11.11</v>
+      </c>
+      <c r="Q1834">
+        <v>0</v>
+      </c>
+      <c r="R1834">
+        <v>0</v>
+      </c>
+      <c r="S1834">
+        <v>0</v>
+      </c>
+      <c r="T1834">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1835" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1835" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1835">
+        <v>1</v>
+      </c>
+      <c r="D1835">
+        <v>1</v>
+      </c>
+      <c r="E1835">
+        <v>0</v>
+      </c>
+      <c r="F1835">
+        <v>8</v>
+      </c>
+      <c r="G1835">
+        <v>8</v>
+      </c>
+      <c r="H1835">
+        <v>8</v>
+      </c>
+      <c r="I1835">
+        <v>0</v>
+      </c>
+      <c r="J1835">
+        <v>0</v>
+      </c>
+      <c r="K1835">
+        <v>66.67</v>
+      </c>
+      <c r="L1835">
+        <v>12</v>
+      </c>
+      <c r="M1835">
+        <v>5</v>
+      </c>
+      <c r="N1835">
+        <v>0</v>
+      </c>
+      <c r="O1835">
+        <v>0</v>
+      </c>
+      <c r="P1835">
+        <v>8.89</v>
+      </c>
+      <c r="Q1835">
+        <v>0</v>
+      </c>
+      <c r="R1835">
+        <v>0</v>
+      </c>
+      <c r="S1835">
+        <v>0</v>
+      </c>
+      <c r="T1835">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1836" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1836" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1836">
+        <v>1</v>
+      </c>
+      <c r="D1836">
+        <v>1</v>
+      </c>
+      <c r="E1836">
+        <v>0</v>
+      </c>
+      <c r="F1836">
+        <v>33</v>
+      </c>
+      <c r="G1836">
+        <v>33</v>
+      </c>
+      <c r="H1836">
+        <v>33</v>
+      </c>
+      <c r="I1836">
+        <v>0</v>
+      </c>
+      <c r="J1836">
+        <v>0</v>
+      </c>
+      <c r="K1836">
+        <v>206.25</v>
+      </c>
+      <c r="L1836">
+        <v>16</v>
+      </c>
+      <c r="M1836">
+        <v>4</v>
+      </c>
+      <c r="N1836">
+        <v>5</v>
+      </c>
+      <c r="O1836">
+        <v>1</v>
+      </c>
+      <c r="P1836">
+        <v>17.28</v>
+      </c>
+      <c r="Q1836">
+        <v>3</v>
+      </c>
+      <c r="R1836">
+        <v>0</v>
+      </c>
+      <c r="S1836">
+        <v>0</v>
+      </c>
+      <c r="T1836">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1837" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1837" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1837">
+        <v>1</v>
+      </c>
+      <c r="D1837">
+        <v>1</v>
+      </c>
+      <c r="E1837">
+        <v>0</v>
+      </c>
+      <c r="F1837">
+        <v>1</v>
+      </c>
+      <c r="G1837">
+        <v>1</v>
+      </c>
+      <c r="H1837">
+        <v>1</v>
+      </c>
+      <c r="I1837">
+        <v>0</v>
+      </c>
+      <c r="J1837">
+        <v>0</v>
+      </c>
+      <c r="K1837">
+        <v>25</v>
+      </c>
+      <c r="L1837">
+        <v>4</v>
+      </c>
+      <c r="M1837">
+        <v>3</v>
+      </c>
+      <c r="N1837">
+        <v>0</v>
+      </c>
+      <c r="O1837">
+        <v>0</v>
+      </c>
+      <c r="P1837">
+        <v>0.52</v>
+      </c>
+      <c r="Q1837">
+        <v>1</v>
+      </c>
+      <c r="R1837">
+        <v>0</v>
+      </c>
+      <c r="S1837">
+        <v>0</v>
+      </c>
+      <c r="T1837">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1838" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1838" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1838">
+        <v>1</v>
+      </c>
+      <c r="D1838">
+        <v>1</v>
+      </c>
+      <c r="E1838">
+        <v>0</v>
+      </c>
+      <c r="F1838">
+        <v>31</v>
+      </c>
+      <c r="G1838">
+        <v>31</v>
+      </c>
+      <c r="H1838">
+        <v>31</v>
+      </c>
+      <c r="I1838">
+        <v>0</v>
+      </c>
+      <c r="J1838">
+        <v>0</v>
+      </c>
+      <c r="K1838">
+        <v>134.78</v>
+      </c>
+      <c r="L1838">
+        <v>23</v>
+      </c>
+      <c r="M1838">
+        <v>8</v>
+      </c>
+      <c r="N1838">
+        <v>4</v>
+      </c>
+      <c r="O1838">
+        <v>0</v>
+      </c>
+      <c r="P1838">
+        <v>16.23</v>
+      </c>
+      <c r="Q1838">
+        <v>1</v>
+      </c>
+      <c r="R1838">
+        <v>0</v>
+      </c>
+      <c r="S1838">
+        <v>0</v>
+      </c>
+      <c r="T1838">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1839" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1839" t="s">
+        <v>740</v>
+      </c>
+      <c r="C1839">
+        <v>1</v>
+      </c>
+      <c r="D1839">
+        <v>1</v>
+      </c>
+      <c r="E1839">
+        <v>0</v>
+      </c>
+      <c r="F1839">
+        <v>4</v>
+      </c>
+      <c r="G1839">
+        <v>4</v>
+      </c>
+      <c r="H1839">
+        <v>4</v>
+      </c>
+      <c r="I1839">
+        <v>0</v>
+      </c>
+      <c r="J1839">
+        <v>0</v>
+      </c>
+      <c r="K1839">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1839">
+        <v>3</v>
+      </c>
+      <c r="M1839">
+        <v>2</v>
+      </c>
+      <c r="N1839">
+        <v>1</v>
+      </c>
+      <c r="O1839">
+        <v>0</v>
+      </c>
+      <c r="P1839">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="Q1839">
+        <v>0</v>
+      </c>
+      <c r="R1839">
+        <v>0</v>
+      </c>
+      <c r="S1839">
+        <v>0</v>
+      </c>
+      <c r="T1839">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1840" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1840" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1840">
+        <v>1</v>
+      </c>
+      <c r="D1840">
+        <v>1</v>
+      </c>
+      <c r="E1840">
+        <v>0</v>
+      </c>
+      <c r="F1840">
+        <v>0</v>
+      </c>
+      <c r="G1840">
+        <v>0</v>
+      </c>
+      <c r="H1840">
+        <v>0</v>
+      </c>
+      <c r="I1840">
+        <v>0</v>
+      </c>
+      <c r="J1840">
+        <v>0</v>
+      </c>
+      <c r="L1840">
+        <v>0</v>
+      </c>
+      <c r="M1840">
+        <v>0</v>
+      </c>
+      <c r="N1840">
+        <v>0</v>
+      </c>
+      <c r="O1840">
+        <v>0</v>
+      </c>
+      <c r="P1840">
+        <v>0</v>
+      </c>
+      <c r="Q1840">
+        <v>0</v>
+      </c>
+      <c r="R1840">
+        <v>0</v>
+      </c>
+      <c r="S1840">
+        <v>0</v>
+      </c>
+      <c r="T1840">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1841" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1841" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1841">
+        <v>1</v>
+      </c>
+      <c r="D1841">
+        <v>0</v>
+      </c>
+      <c r="E1841">
+        <v>0</v>
+      </c>
+      <c r="F1841">
+        <v>0</v>
+      </c>
+      <c r="I1841">
+        <v>0</v>
+      </c>
+      <c r="J1841">
+        <v>0</v>
+      </c>
+      <c r="L1841">
+        <v>0</v>
+      </c>
+      <c r="M1841">
+        <v>0</v>
+      </c>
+      <c r="N1841">
+        <v>0</v>
+      </c>
+      <c r="O1841">
+        <v>0</v>
+      </c>
+      <c r="P1841">
+        <v>0</v>
+      </c>
+      <c r="Q1841">
+        <v>0</v>
+      </c>
+      <c r="R1841">
+        <v>0</v>
+      </c>
+      <c r="S1841">
+        <v>0</v>
+      </c>
+      <c r="T1841">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1842" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1842" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1842">
+        <v>1</v>
+      </c>
+      <c r="D1842">
+        <v>1</v>
+      </c>
+      <c r="E1842">
+        <v>1</v>
+      </c>
+      <c r="F1842">
+        <v>1</v>
+      </c>
+      <c r="H1842" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1842">
+        <v>0</v>
+      </c>
+      <c r="J1842">
+        <v>0</v>
+      </c>
+      <c r="K1842">
+        <v>100</v>
+      </c>
+      <c r="L1842">
+        <v>1</v>
+      </c>
+      <c r="M1842">
+        <v>0</v>
+      </c>
+      <c r="N1842">
+        <v>0</v>
+      </c>
+      <c r="O1842">
+        <v>0</v>
+      </c>
+      <c r="P1842">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="Q1842">
+        <v>0</v>
+      </c>
+      <c r="R1842">
+        <v>0</v>
+      </c>
+      <c r="S1842">
+        <v>0</v>
+      </c>
+      <c r="T1842">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1843" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1843" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1843">
+        <v>1</v>
+      </c>
+      <c r="D1843">
+        <v>1</v>
+      </c>
+      <c r="E1843">
+        <v>0</v>
+      </c>
+      <c r="F1843">
+        <v>1</v>
+      </c>
+      <c r="G1843">
+        <v>1</v>
+      </c>
+      <c r="H1843">
+        <v>1</v>
+      </c>
+      <c r="I1843">
+        <v>0</v>
+      </c>
+      <c r="J1843">
+        <v>0</v>
+      </c>
+      <c r="K1843">
+        <v>20</v>
+      </c>
+      <c r="L1843">
+        <v>5</v>
+      </c>
+      <c r="M1843">
+        <v>4</v>
+      </c>
+      <c r="N1843">
+        <v>0</v>
+      </c>
+      <c r="O1843">
+        <v>0</v>
+      </c>
+      <c r="P1843">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="Q1843">
+        <v>0</v>
+      </c>
+      <c r="R1843">
+        <v>0</v>
+      </c>
+      <c r="S1843">
+        <v>0</v>
+      </c>
+      <c r="T1843">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1844" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1844" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1844">
+        <v>1</v>
+      </c>
+      <c r="D1844">
+        <v>1</v>
+      </c>
+      <c r="E1844">
+        <v>1</v>
+      </c>
+      <c r="F1844">
+        <v>31</v>
+      </c>
+      <c r="H1844" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1844">
+        <v>0</v>
+      </c>
+      <c r="J1844">
+        <v>0</v>
+      </c>
+      <c r="K1844">
+        <v>147.62</v>
+      </c>
+      <c r="L1844">
+        <v>21</v>
+      </c>
+      <c r="M1844">
+        <v>4</v>
+      </c>
+      <c r="N1844">
+        <v>4</v>
+      </c>
+      <c r="O1844">
+        <v>0</v>
+      </c>
+      <c r="P1844">
+        <v>16.23</v>
+      </c>
+      <c r="Q1844">
+        <v>0</v>
+      </c>
+      <c r="R1844">
+        <v>0</v>
+      </c>
+      <c r="S1844">
+        <v>0</v>
+      </c>
+      <c r="T1844">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1845" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1845" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1845">
+        <v>1</v>
+      </c>
+      <c r="D1845">
+        <v>1</v>
+      </c>
+      <c r="E1845">
+        <v>0</v>
+      </c>
+      <c r="F1845">
+        <v>2</v>
+      </c>
+      <c r="G1845">
+        <v>2</v>
+      </c>
+      <c r="H1845">
+        <v>2</v>
+      </c>
+      <c r="I1845">
+        <v>0</v>
+      </c>
+      <c r="J1845">
+        <v>0</v>
+      </c>
+      <c r="K1845">
+        <v>100</v>
+      </c>
+      <c r="L1845">
+        <v>2</v>
+      </c>
+      <c r="M1845">
+        <v>1</v>
+      </c>
+      <c r="N1845">
+        <v>0</v>
+      </c>
+      <c r="O1845">
+        <v>0</v>
+      </c>
+      <c r="P1845">
+        <v>1.05</v>
+      </c>
+      <c r="Q1845">
+        <v>0</v>
+      </c>
+      <c r="R1845">
+        <v>0</v>
+      </c>
+      <c r="S1845">
+        <v>0</v>
+      </c>
+      <c r="T1845">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1846" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1846" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1846">
+        <v>1</v>
+      </c>
+      <c r="D1846">
+        <v>1</v>
+      </c>
+      <c r="E1846">
+        <v>0</v>
+      </c>
+      <c r="F1846">
+        <v>35</v>
+      </c>
+      <c r="G1846">
+        <v>35</v>
+      </c>
+      <c r="H1846">
+        <v>35</v>
+      </c>
+      <c r="I1846">
+        <v>0</v>
+      </c>
+      <c r="J1846">
+        <v>0</v>
+      </c>
+      <c r="K1846">
+        <v>218.75</v>
+      </c>
+      <c r="L1846">
+        <v>16</v>
+      </c>
+      <c r="M1846">
+        <v>7</v>
+      </c>
+      <c r="N1846">
+        <v>2</v>
+      </c>
+      <c r="O1846">
+        <v>4</v>
+      </c>
+      <c r="P1846">
+        <v>38.89</v>
+      </c>
+      <c r="Q1846">
+        <v>1</v>
+      </c>
+      <c r="R1846">
+        <v>0</v>
+      </c>
+      <c r="S1846">
+        <v>0</v>
+      </c>
+      <c r="T1846">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1847" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1847" t="s">
+        <v>680</v>
+      </c>
+      <c r="C1847">
+        <v>1</v>
+      </c>
+      <c r="D1847">
+        <v>1</v>
+      </c>
+      <c r="E1847">
+        <v>1</v>
+      </c>
+      <c r="F1847">
+        <v>0</v>
+      </c>
+      <c r="H1847" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1847">
+        <v>0</v>
+      </c>
+      <c r="J1847">
+        <v>0</v>
+      </c>
+      <c r="K1847">
+        <v>0</v>
+      </c>
+      <c r="L1847">
+        <v>3</v>
+      </c>
+      <c r="M1847">
+        <v>3</v>
+      </c>
+      <c r="N1847">
+        <v>0</v>
+      </c>
+      <c r="O1847">
+        <v>0</v>
+      </c>
+      <c r="P1847">
+        <v>0</v>
+      </c>
+      <c r="Q1847">
+        <v>0</v>
+      </c>
+      <c r="R1847">
+        <v>0</v>
+      </c>
+      <c r="S1847">
+        <v>0</v>
+      </c>
+      <c r="T1847">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A1628:T1656">
     <sortCondition ref="B1628:B1656"/>

--- a/NV Play Midweek League batting stats for season.xlsx
+++ b/NV Play Midweek League batting stats for season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\-Midweek League-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD3FE2F-4FD6-4F25-978D-FF71800FBC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB413D1F-3247-465B-B06F-6FB24CDD9E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="1500" windowWidth="29655" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30255" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20260529-000138-batting-stats-g" sheetId="1" r:id="rId1"/>
@@ -1753,9 +1753,6 @@
     <t>Josh Williams</t>
   </si>
   <si>
-    <t>Alec Stuart</t>
-  </si>
-  <si>
     <t>Arches MW XI v Cliftonville Academy MW XI, TBC - 30 June 2026</t>
   </si>
   <si>
@@ -2237,6 +2234,9 @@
   </si>
   <si>
     <t>Purvik Prasad</t>
+  </si>
+  <si>
+    <t>Alex Stuart</t>
   </si>
 </sst>
 </file>
@@ -3952,7 +3952,7 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -5138,7 +5138,7 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -12398,7 +12398,7 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -12451,7 +12451,7 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -14283,7 +14283,7 @@
         <v>197</v>
       </c>
       <c r="B188" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -16823,7 +16823,7 @@
         <v>241</v>
       </c>
       <c r="B231" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -16947,7 +16947,7 @@
         <v>241</v>
       </c>
       <c r="B233" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -19904,7 +19904,7 @@
         <v>267</v>
       </c>
       <c r="B282" t="s">
-        <v>577</v>
+        <v>738</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -24189,7 +24189,7 @@
         <v>289</v>
       </c>
       <c r="B353" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -24307,7 +24307,7 @@
         <v>297</v>
       </c>
       <c r="B355" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -25588,7 +25588,7 @@
     </row>
     <row r="376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B376" t="s">
         <v>310</v>
@@ -25641,7 +25641,7 @@
     </row>
     <row r="377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B377" t="s">
         <v>418</v>
@@ -25703,7 +25703,7 @@
     </row>
     <row r="378" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B378" t="s">
         <v>419</v>
@@ -25765,7 +25765,7 @@
     </row>
     <row r="379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B379" t="s">
         <v>311</v>
@@ -25827,7 +25827,7 @@
     </row>
     <row r="380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B380" t="s">
         <v>420</v>
@@ -25889,7 +25889,7 @@
     </row>
     <row r="381" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B381" t="s">
         <v>185</v>
@@ -25951,7 +25951,7 @@
     </row>
     <row r="382" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B382" t="s">
         <v>187</v>
@@ -26013,7 +26013,7 @@
     </row>
     <row r="383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B383" t="s">
         <v>312</v>
@@ -26072,7 +26072,7 @@
     </row>
     <row r="384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B384" t="s">
         <v>313</v>
@@ -26125,7 +26125,7 @@
     </row>
     <row r="385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B385" t="s">
         <v>190</v>
@@ -26187,7 +26187,7 @@
     </row>
     <row r="386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B386" t="s">
         <v>191</v>
@@ -26246,7 +26246,7 @@
     </row>
     <row r="387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B387" t="s">
         <v>315</v>
@@ -26299,7 +26299,7 @@
     </row>
     <row r="388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B388" t="s">
         <v>316</v>
@@ -26352,7 +26352,7 @@
     </row>
     <row r="389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B389" t="s">
         <v>317</v>
@@ -26414,7 +26414,7 @@
     </row>
     <row r="390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B390" t="s">
         <v>405</v>
@@ -26473,7 +26473,7 @@
     </row>
     <row r="391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B391" t="s">
         <v>385</v>
@@ -26532,7 +26532,7 @@
     </row>
     <row r="392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B392" t="s">
         <v>318</v>
@@ -26594,7 +26594,7 @@
     </row>
     <row r="393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B393" t="s">
         <v>319</v>
@@ -26647,7 +26647,7 @@
     </row>
     <row r="394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B394" t="s">
         <v>320</v>
@@ -26700,7 +26700,7 @@
     </row>
     <row r="395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B395" t="s">
         <v>321</v>
@@ -26753,7 +26753,7 @@
     </row>
     <row r="396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B396" t="s">
         <v>194</v>
@@ -26815,7 +26815,7 @@
     </row>
     <row r="397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B397" t="s">
         <v>195</v>
@@ -28193,7 +28193,7 @@
         <v>329</v>
       </c>
       <c r="B420" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C420">
         <v>1</v>
@@ -33472,7 +33472,7 @@
         <v>366</v>
       </c>
       <c r="B508" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C508">
         <v>1</v>
@@ -35637,7 +35637,7 @@
         <v>371</v>
       </c>
       <c r="B545" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C545">
         <v>1</v>
@@ -36044,7 +36044,7 @@
     </row>
     <row r="552" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B552" t="s">
         <v>378</v>
@@ -36106,7 +36106,7 @@
     </row>
     <row r="553" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B553" t="s">
         <v>310</v>
@@ -36168,7 +36168,7 @@
     </row>
     <row r="554" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B554" t="s">
         <v>379</v>
@@ -36230,7 +36230,7 @@
     </row>
     <row r="555" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B555" t="s">
         <v>399</v>
@@ -36283,7 +36283,7 @@
     </row>
     <row r="556" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B556" t="s">
         <v>380</v>
@@ -36345,7 +36345,7 @@
     </row>
     <row r="557" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B557" t="s">
         <v>400</v>
@@ -36407,7 +36407,7 @@
     </row>
     <row r="558" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B558" t="s">
         <v>401</v>
@@ -36469,7 +36469,7 @@
     </row>
     <row r="559" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B559" t="s">
         <v>402</v>
@@ -36531,7 +36531,7 @@
     </row>
     <row r="560" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B560" t="s">
         <v>381</v>
@@ -36593,7 +36593,7 @@
     </row>
     <row r="561" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B561" t="s">
         <v>403</v>
@@ -36655,7 +36655,7 @@
     </row>
     <row r="562" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B562" t="s">
         <v>404</v>
@@ -36717,7 +36717,7 @@
     </row>
     <row r="563" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B563" t="s">
         <v>382</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="564" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B564" t="s">
         <v>383</v>
@@ -36841,7 +36841,7 @@
     </row>
     <row r="565" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B565" t="s">
         <v>315</v>
@@ -36903,7 +36903,7 @@
     </row>
     <row r="566" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B566" t="s">
         <v>316</v>
@@ -36962,7 +36962,7 @@
     </row>
     <row r="567" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B567" t="s">
         <v>405</v>
@@ -37024,7 +37024,7 @@
     </row>
     <row r="568" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B568" t="s">
         <v>352</v>
@@ -37083,7 +37083,7 @@
     </row>
     <row r="569" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B569" t="s">
         <v>353</v>
@@ -37145,7 +37145,7 @@
     </row>
     <row r="570" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B570" t="s">
         <v>384</v>
@@ -37207,7 +37207,7 @@
     </row>
     <row r="571" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B571" t="s">
         <v>385</v>
@@ -37269,7 +37269,7 @@
     </row>
     <row r="572" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B572" t="s">
         <v>269</v>
@@ -37328,7 +37328,7 @@
     </row>
     <row r="573" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B573" t="s">
         <v>355</v>
@@ -49222,7 +49222,7 @@
     </row>
     <row r="772" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B772" t="s">
         <v>200</v>
@@ -49275,7 +49275,7 @@
     </row>
     <row r="773" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B773" t="s">
         <v>160</v>
@@ -49337,7 +49337,7 @@
     </row>
     <row r="774" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B774" t="s">
         <v>555</v>
@@ -49390,7 +49390,7 @@
     </row>
     <row r="775" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B775" t="s">
         <v>224</v>
@@ -49452,7 +49452,7 @@
     </row>
     <row r="776" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B776" t="s">
         <v>226</v>
@@ -49514,7 +49514,7 @@
     </row>
     <row r="777" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B777" t="s">
         <v>227</v>
@@ -49576,7 +49576,7 @@
     </row>
     <row r="778" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B778" t="s">
         <v>229</v>
@@ -49638,7 +49638,7 @@
     </row>
     <row r="779" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B779" t="s">
         <v>230</v>
@@ -49697,7 +49697,7 @@
     </row>
     <row r="780" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B780" t="s">
         <v>205</v>
@@ -49756,7 +49756,7 @@
     </row>
     <row r="781" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B781" t="s">
         <v>231</v>
@@ -49818,7 +49818,7 @@
     </row>
     <row r="782" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B782" t="s">
         <v>375</v>
@@ -49877,7 +49877,7 @@
     </row>
     <row r="783" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B783" t="s">
         <v>292</v>
@@ -49930,7 +49930,7 @@
     </row>
     <row r="784" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B784" t="s">
         <v>293</v>
@@ -49992,7 +49992,7 @@
     </row>
     <row r="785" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B785" t="s">
         <v>557</v>
@@ -50054,7 +50054,7 @@
     </row>
     <row r="786" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B786" t="s">
         <v>234</v>
@@ -50116,10 +50116,10 @@
     </row>
     <row r="787" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
+        <v>608</v>
+      </c>
+      <c r="B787" t="s">
         <v>609</v>
-      </c>
-      <c r="B787" t="s">
-        <v>610</v>
       </c>
       <c r="C787">
         <v>1</v>
@@ -50178,7 +50178,7 @@
     </row>
     <row r="788" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B788" t="s">
         <v>235</v>
@@ -50240,7 +50240,7 @@
     </row>
     <row r="789" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B789" t="s">
         <v>207</v>
@@ -50302,7 +50302,7 @@
     </row>
     <row r="790" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B790" t="s">
         <v>208</v>
@@ -50364,7 +50364,7 @@
     </row>
     <row r="791" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B791" t="s">
         <v>238</v>
@@ -50426,7 +50426,7 @@
     </row>
     <row r="792" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B792" t="s">
         <v>574</v>
@@ -50482,10 +50482,10 @@
     </row>
     <row r="793" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B793" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C793">
         <v>1</v>
@@ -57842,7 +57842,7 @@
         <v>538</v>
       </c>
       <c r="B915" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C915">
         <v>1</v>
@@ -58090,7 +58090,7 @@
         <v>538</v>
       </c>
       <c r="B919" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C919">
         <v>1</v>
@@ -58447,7 +58447,7 @@
         <v>538</v>
       </c>
       <c r="B925" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C925">
         <v>1</v>
@@ -59722,7 +59722,7 @@
         <v>542</v>
       </c>
       <c r="B946" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C946">
         <v>1</v>
@@ -63779,7 +63779,7 @@
     </row>
     <row r="1014" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1014" t="s">
         <v>248</v>
@@ -63838,10 +63838,10 @@
     </row>
     <row r="1015" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
+        <v>577</v>
+      </c>
+      <c r="B1015" t="s">
         <v>578</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>579</v>
       </c>
       <c r="C1015">
         <v>1</v>
@@ -63897,7 +63897,7 @@
     </row>
     <row r="1016" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1016" t="s">
         <v>71</v>
@@ -63956,10 +63956,10 @@
     </row>
     <row r="1017" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1017" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C1017">
         <v>1</v>
@@ -64018,7 +64018,7 @@
     </row>
     <row r="1018" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1018" t="s">
         <v>250</v>
@@ -64071,7 +64071,7 @@
     </row>
     <row r="1019" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1019" t="s">
         <v>430</v>
@@ -64130,7 +64130,7 @@
     </row>
     <row r="1020" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1020" t="s">
         <v>252</v>
@@ -64189,7 +64189,7 @@
     </row>
     <row r="1021" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1021" t="s">
         <v>367</v>
@@ -64242,7 +64242,7 @@
     </row>
     <row r="1022" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1022" t="s">
         <v>78</v>
@@ -64304,7 +64304,7 @@
     </row>
     <row r="1023" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1023" t="s">
         <v>255</v>
@@ -64357,7 +64357,7 @@
     </row>
     <row r="1024" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1024" t="s">
         <v>257</v>
@@ -64419,7 +64419,7 @@
     </row>
     <row r="1025" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1025" t="s">
         <v>258</v>
@@ -64481,7 +64481,7 @@
     </row>
     <row r="1026" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1026" t="s">
         <v>261</v>
@@ -64543,7 +64543,7 @@
     </row>
     <row r="1027" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1027" t="s">
         <v>506</v>
@@ -64605,7 +64605,7 @@
     </row>
     <row r="1028" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1028" t="s">
         <v>262</v>
@@ -64658,7 +64658,7 @@
     </row>
     <row r="1029" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1029" t="s">
         <v>264</v>
@@ -64717,7 +64717,7 @@
     </row>
     <row r="1030" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1030" t="s">
         <v>287</v>
@@ -64770,7 +64770,7 @@
     </row>
     <row r="1031" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1031" t="s">
         <v>265</v>
@@ -64829,7 +64829,7 @@
     </row>
     <row r="1032" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1032" t="s">
         <v>89</v>
@@ -64891,7 +64891,7 @@
     </row>
     <row r="1033" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1033" t="s">
         <v>90</v>
@@ -64944,10 +64944,10 @@
     </row>
     <row r="1034" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1034" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C1034">
         <v>1</v>
@@ -65003,7 +65003,7 @@
     </row>
     <row r="1035" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B1035" t="s">
         <v>288</v>
@@ -65065,7 +65065,7 @@
     </row>
     <row r="1036" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1036" t="s">
         <v>386</v>
@@ -65127,7 +65127,7 @@
     </row>
     <row r="1037" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1037" t="s">
         <v>46</v>
@@ -65186,7 +65186,7 @@
     </row>
     <row r="1038" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1038" t="s">
         <v>406</v>
@@ -65239,7 +65239,7 @@
     </row>
     <row r="1039" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1039" t="s">
         <v>388</v>
@@ -65298,10 +65298,10 @@
     </row>
     <row r="1040" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
+        <v>581</v>
+      </c>
+      <c r="B1040" t="s">
         <v>582</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>583</v>
       </c>
       <c r="C1040">
         <v>1</v>
@@ -65360,7 +65360,7 @@
     </row>
     <row r="1041" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1041" t="s">
         <v>357</v>
@@ -65422,7 +65422,7 @@
     </row>
     <row r="1042" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1042" t="s">
         <v>469</v>
@@ -65484,7 +65484,7 @@
     </row>
     <row r="1043" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1043" t="s">
         <v>301</v>
@@ -65537,7 +65537,7 @@
     </row>
     <row r="1044" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1044" t="s">
         <v>359</v>
@@ -65599,7 +65599,7 @@
     </row>
     <row r="1045" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1045" t="s">
         <v>390</v>
@@ -65658,7 +65658,7 @@
     </row>
     <row r="1046" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1046" t="s">
         <v>528</v>
@@ -65720,7 +65720,7 @@
     </row>
     <row r="1047" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1047" t="s">
         <v>304</v>
@@ -65782,7 +65782,7 @@
     </row>
     <row r="1048" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1048" t="s">
         <v>569</v>
@@ -65844,7 +65844,7 @@
     </row>
     <row r="1049" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1049" t="s">
         <v>364</v>
@@ -65903,7 +65903,7 @@
     </row>
     <row r="1050" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1050" t="s">
         <v>63</v>
@@ -65965,7 +65965,7 @@
     </row>
     <row r="1051" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1051" t="s">
         <v>64</v>
@@ -66024,7 +66024,7 @@
     </row>
     <row r="1052" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1052" t="s">
         <v>65</v>
@@ -66086,10 +66086,10 @@
     </row>
     <row r="1053" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1053" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C1053">
         <v>1</v>
@@ -66148,7 +66148,7 @@
     </row>
     <row r="1054" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1054" t="s">
         <v>393</v>
@@ -66201,7 +66201,7 @@
     </row>
     <row r="1055" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1055" t="s">
         <v>532</v>
@@ -66263,7 +66263,7 @@
     </row>
     <row r="1056" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1056" t="s">
         <v>394</v>
@@ -66325,7 +66325,7 @@
     </row>
     <row r="1057" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B1057" t="s">
         <v>309</v>
@@ -66384,7 +66384,7 @@
     </row>
     <row r="1058" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1058" t="s">
         <v>21</v>
@@ -66446,7 +66446,7 @@
     </row>
     <row r="1059" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1059" t="s">
         <v>134</v>
@@ -66505,10 +66505,10 @@
     </row>
     <row r="1060" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1060" t="s">
         <v>585</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>586</v>
       </c>
       <c r="C1060">
         <v>1</v>
@@ -66558,7 +66558,7 @@
     </row>
     <row r="1061" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1061" t="s">
         <v>98</v>
@@ -66620,7 +66620,7 @@
     </row>
     <row r="1062" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1062" t="s">
         <v>478</v>
@@ -66682,7 +66682,7 @@
     </row>
     <row r="1063" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1063" t="s">
         <v>479</v>
@@ -66741,7 +66741,7 @@
     </row>
     <row r="1064" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1064" t="s">
         <v>545</v>
@@ -66800,7 +66800,7 @@
     </row>
     <row r="1065" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1065" t="s">
         <v>104</v>
@@ -66862,7 +66862,7 @@
     </row>
     <row r="1066" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1066" t="s">
         <v>253</v>
@@ -66924,7 +66924,7 @@
     </row>
     <row r="1067" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1067" t="s">
         <v>535</v>
@@ -66986,10 +66986,10 @@
     </row>
     <row r="1068" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1068" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C1068">
         <v>1</v>
@@ -67048,7 +67048,7 @@
     </row>
     <row r="1069" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1069" t="s">
         <v>546</v>
@@ -67110,7 +67110,7 @@
     </row>
     <row r="1070" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1070" t="s">
         <v>547</v>
@@ -67172,7 +67172,7 @@
     </row>
     <row r="1071" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1071" t="s">
         <v>143</v>
@@ -67234,7 +67234,7 @@
     </row>
     <row r="1072" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1072" t="s">
         <v>145</v>
@@ -67296,7 +67296,7 @@
     </row>
     <row r="1073" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1073" t="s">
         <v>38</v>
@@ -67358,7 +67358,7 @@
     </row>
     <row r="1074" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1074" t="s">
         <v>40</v>
@@ -67420,7 +67420,7 @@
     </row>
     <row r="1075" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1075" t="s">
         <v>483</v>
@@ -67482,7 +67482,7 @@
     </row>
     <row r="1076" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1076" t="s">
         <v>108</v>
@@ -67541,10 +67541,10 @@
     </row>
     <row r="1077" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1077" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C1077">
         <v>1</v>
@@ -67603,7 +67603,7 @@
     </row>
     <row r="1078" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1078" t="s">
         <v>152</v>
@@ -67662,7 +67662,7 @@
     </row>
     <row r="1079" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B1079" t="s">
         <v>43</v>
@@ -67724,7 +67724,7 @@
     </row>
     <row r="1080" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1080" t="s">
         <v>437</v>
@@ -67789,7 +67789,7 @@
     </row>
     <row r="1081" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1081" t="s">
         <v>217</v>
@@ -67851,7 +67851,7 @@
     </row>
     <row r="1082" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1082" t="s">
         <v>221</v>
@@ -67910,7 +67910,7 @@
     </row>
     <row r="1083" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1083" t="s">
         <v>23</v>
@@ -67975,7 +67975,7 @@
     </row>
     <row r="1084" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1084" t="s">
         <v>24</v>
@@ -68034,7 +68034,7 @@
     </row>
     <row r="1085" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1085" t="s">
         <v>337</v>
@@ -68096,7 +68096,7 @@
     </row>
     <row r="1086" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1086" t="s">
         <v>26</v>
@@ -68158,7 +68158,7 @@
     </row>
     <row r="1087" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1087" t="s">
         <v>31</v>
@@ -68220,10 +68220,10 @@
     </row>
     <row r="1088" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1088" t="s">
         <v>612</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>613</v>
       </c>
       <c r="C1088">
         <v>1</v>
@@ -68282,7 +68282,7 @@
     </row>
     <row r="1089" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1089" t="s">
         <v>518</v>
@@ -68335,7 +68335,7 @@
     </row>
     <row r="1090" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1090" t="s">
         <v>32</v>
@@ -68397,7 +68397,7 @@
     </row>
     <row r="1091" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1091" t="s">
         <v>36</v>
@@ -68462,7 +68462,7 @@
     </row>
     <row r="1092" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1092" t="s">
         <v>37</v>
@@ -68515,7 +68515,7 @@
     </row>
     <row r="1093" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1093" t="s">
         <v>519</v>
@@ -68577,7 +68577,7 @@
     </row>
     <row r="1094" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1094" t="s">
         <v>520</v>
@@ -68633,10 +68633,10 @@
     </row>
     <row r="1095" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1095" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C1095">
         <v>1</v>
@@ -68698,10 +68698,10 @@
     </row>
     <row r="1096" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1096" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C1096">
         <v>1</v>
@@ -68751,7 +68751,7 @@
     </row>
     <row r="1097" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1097" t="s">
         <v>522</v>
@@ -68813,7 +68813,7 @@
     </row>
     <row r="1098" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1098" t="s">
         <v>433</v>
@@ -68869,7 +68869,7 @@
     </row>
     <row r="1099" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1099" t="s">
         <v>561</v>
@@ -68928,7 +68928,7 @@
     </row>
     <row r="1100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1100" t="s">
         <v>523</v>
@@ -68981,7 +68981,7 @@
     </row>
     <row r="1101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B1101" t="s">
         <v>571</v>
@@ -69034,7 +69034,7 @@
     </row>
     <row r="1102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1102" t="s">
         <v>181</v>
@@ -69096,10 +69096,10 @@
     </row>
     <row r="1103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1103" t="s">
         <v>589</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>590</v>
       </c>
       <c r="C1103">
         <v>1</v>
@@ -69158,10 +69158,10 @@
     </row>
     <row r="1104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1104" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C1104">
         <v>1</v>
@@ -69214,10 +69214,10 @@
     </row>
     <row r="1105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1105" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C1105">
         <v>1</v>
@@ -69276,10 +69276,10 @@
     </row>
     <row r="1106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1106" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C1106">
         <v>1</v>
@@ -69338,7 +69338,7 @@
     </row>
     <row r="1107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1107" t="s">
         <v>387</v>
@@ -69391,7 +69391,7 @@
     </row>
     <row r="1108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1108" t="s">
         <v>300</v>
@@ -69453,7 +69453,7 @@
     </row>
     <row r="1109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1109" t="s">
         <v>188</v>
@@ -69515,7 +69515,7 @@
     </row>
     <row r="1110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1110" t="s">
         <v>189</v>
@@ -69577,7 +69577,7 @@
     </row>
     <row r="1111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1111" t="s">
         <v>434</v>
@@ -69636,7 +69636,7 @@
     </row>
     <row r="1112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1112" t="s">
         <v>389</v>
@@ -69698,7 +69698,7 @@
     </row>
     <row r="1113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1113" t="s">
         <v>192</v>
@@ -69751,7 +69751,7 @@
     </row>
     <row r="1114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1114" t="s">
         <v>435</v>
@@ -69813,10 +69813,10 @@
     </row>
     <row r="1115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1115" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C1115">
         <v>1</v>
@@ -69866,7 +69866,7 @@
     </row>
     <row r="1116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1116" t="s">
         <v>363</v>
@@ -69928,7 +69928,7 @@
     </row>
     <row r="1117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1117" t="s">
         <v>529</v>
@@ -69990,7 +69990,7 @@
     </row>
     <row r="1118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1118" t="s">
         <v>303</v>
@@ -70049,7 +70049,7 @@
     </row>
     <row r="1119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1119" t="s">
         <v>306</v>
@@ -70111,7 +70111,7 @@
     </row>
     <row r="1120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1120" t="s">
         <v>307</v>
@@ -70164,7 +70164,7 @@
     </row>
     <row r="1121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1121" t="s">
         <v>458</v>
@@ -70217,10 +70217,10 @@
     </row>
     <row r="1122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1122" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C1122">
         <v>1</v>
@@ -70270,7 +70270,7 @@
     </row>
     <row r="1123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1123" t="s">
         <v>391</v>
@@ -70329,7 +70329,7 @@
     </row>
     <row r="1124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1124" t="s">
         <v>465</v>
@@ -70391,7 +70391,7 @@
     </row>
     <row r="1125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1125" t="s">
         <v>48</v>
@@ -70453,7 +70453,7 @@
     </row>
     <row r="1126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1126" t="s">
         <v>428</v>
@@ -70512,7 +70512,7 @@
     </row>
     <row r="1127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1127" t="s">
         <v>50</v>
@@ -70574,7 +70574,7 @@
     </row>
     <row r="1128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1128" t="s">
         <v>400</v>
@@ -70636,7 +70636,7 @@
     </row>
     <row r="1129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1129" t="s">
         <v>347</v>
@@ -70695,7 +70695,7 @@
     </row>
     <row r="1130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1130" t="s">
         <v>404</v>
@@ -70754,7 +70754,7 @@
     </row>
     <row r="1131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1131" t="s">
         <v>348</v>
@@ -70816,7 +70816,7 @@
     </row>
     <row r="1132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1132" t="s">
         <v>407</v>
@@ -70878,7 +70878,7 @@
     </row>
     <row r="1133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1133" t="s">
         <v>53</v>
@@ -70940,7 +70940,7 @@
     </row>
     <row r="1134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1134" t="s">
         <v>56</v>
@@ -71002,10 +71002,10 @@
     </row>
     <row r="1135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1135" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C1135">
         <v>1</v>
@@ -71061,7 +71061,7 @@
     </row>
     <row r="1136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1136" t="s">
         <v>147</v>
@@ -71117,10 +71117,10 @@
     </row>
     <row r="1137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1137" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C1137">
         <v>1</v>
@@ -71170,10 +71170,10 @@
     </row>
     <row r="1138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
+        <v>595</v>
+      </c>
+      <c r="B1138" t="s">
         <v>596</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>597</v>
       </c>
       <c r="C1138">
         <v>1</v>
@@ -71232,7 +71232,7 @@
     </row>
     <row r="1139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1139" t="s">
         <v>352</v>
@@ -71291,7 +71291,7 @@
     </row>
     <row r="1140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1140" t="s">
         <v>472</v>
@@ -71353,7 +71353,7 @@
     </row>
     <row r="1141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1141" t="s">
         <v>61</v>
@@ -71415,7 +71415,7 @@
     </row>
     <row r="1142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1142" t="s">
         <v>269</v>
@@ -71477,7 +71477,7 @@
     </row>
     <row r="1143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1143" t="s">
         <v>355</v>
@@ -71539,7 +71539,7 @@
     </row>
     <row r="1144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1144" t="s">
         <v>151</v>
@@ -71601,10 +71601,10 @@
     </row>
     <row r="1145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B1145" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C1145">
         <v>1</v>
@@ -71663,10 +71663,10 @@
     </row>
     <row r="1146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1146" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C1146">
         <v>1</v>
@@ -71725,7 +71725,7 @@
     </row>
     <row r="1147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1147" t="s">
         <v>93</v>
@@ -71784,7 +71784,7 @@
     </row>
     <row r="1148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1148" t="s">
         <v>68</v>
@@ -71846,7 +71846,7 @@
     </row>
     <row r="1149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1149" t="s">
         <v>408</v>
@@ -71905,7 +71905,7 @@
     </row>
     <row r="1150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1150" t="s">
         <v>429</v>
@@ -71967,7 +71967,7 @@
     </row>
     <row r="1151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1151" t="s">
         <v>96</v>
@@ -72026,10 +72026,10 @@
     </row>
     <row r="1152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1152" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C1152">
         <v>1</v>
@@ -72088,7 +72088,7 @@
     </row>
     <row r="1153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1153" t="s">
         <v>283</v>
@@ -72150,10 +72150,10 @@
     </row>
     <row r="1154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1154" t="s">
         <v>599</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>600</v>
       </c>
       <c r="C1154">
         <v>1</v>
@@ -72212,7 +72212,7 @@
     </row>
     <row r="1155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1155" t="s">
         <v>100</v>
@@ -72274,7 +72274,7 @@
     </row>
     <row r="1156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1156" t="s">
         <v>446</v>
@@ -72336,7 +72336,7 @@
     </row>
     <row r="1157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1157" t="s">
         <v>73</v>
@@ -72398,7 +72398,7 @@
     </row>
     <row r="1158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1158" t="s">
         <v>101</v>
@@ -72460,7 +72460,7 @@
     </row>
     <row r="1159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1159" t="s">
         <v>461</v>
@@ -72522,10 +72522,10 @@
     </row>
     <row r="1160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1160" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C1160">
         <v>1</v>
@@ -72575,7 +72575,7 @@
     </row>
     <row r="1161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1161" t="s">
         <v>75</v>
@@ -72628,7 +72628,7 @@
     </row>
     <row r="1162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1162" t="s">
         <v>409</v>
@@ -72690,10 +72690,10 @@
     </row>
     <row r="1163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1163" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C1163">
         <v>1</v>
@@ -72749,7 +72749,7 @@
     </row>
     <row r="1164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1164" t="s">
         <v>79</v>
@@ -72808,7 +72808,7 @@
     </row>
     <row r="1165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1165" t="s">
         <v>278</v>
@@ -72861,7 +72861,7 @@
     </row>
     <row r="1166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1166" t="s">
         <v>88</v>
@@ -72923,7 +72923,7 @@
     </row>
     <row r="1167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1167" t="s">
         <v>432</v>
@@ -72985,7 +72985,7 @@
     </row>
     <row r="1168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1168" t="s">
         <v>465</v>
@@ -73047,7 +73047,7 @@
     </row>
     <row r="1169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1169" t="s">
         <v>135</v>
@@ -73106,7 +73106,7 @@
     </row>
     <row r="1170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1170" t="s">
         <v>514</v>
@@ -73165,7 +73165,7 @@
     </row>
     <row r="1171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1171" t="s">
         <v>300</v>
@@ -73227,7 +73227,7 @@
     </row>
     <row r="1172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1172" t="s">
         <v>50</v>
@@ -73289,10 +73289,10 @@
     </row>
     <row r="1173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1173" t="s">
         <v>618</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>619</v>
       </c>
       <c r="C1173">
         <v>1</v>
@@ -73351,7 +73351,7 @@
     </row>
     <row r="1174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1174" t="s">
         <v>56</v>
@@ -73404,7 +73404,7 @@
     </row>
     <row r="1175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1175" t="s">
         <v>435</v>
@@ -73463,7 +73463,7 @@
     </row>
     <row r="1176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1176" t="s">
         <v>456</v>
@@ -73525,7 +73525,7 @@
     </row>
     <row r="1177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1177" t="s">
         <v>529</v>
@@ -73587,7 +73587,7 @@
     </row>
     <row r="1178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1178" t="s">
         <v>302</v>
@@ -73649,10 +73649,10 @@
     </row>
     <row r="1179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1179" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C1179">
         <v>1</v>
@@ -73711,7 +73711,7 @@
     </row>
     <row r="1180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1180" t="s">
         <v>303</v>
@@ -73773,7 +73773,7 @@
     </row>
     <row r="1181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1181" t="s">
         <v>148</v>
@@ -73835,7 +73835,7 @@
     </row>
     <row r="1182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1182" t="s">
         <v>306</v>
@@ -73897,7 +73897,7 @@
     </row>
     <row r="1183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1183" t="s">
         <v>564</v>
@@ -73956,7 +73956,7 @@
     </row>
     <row r="1184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1184" t="s">
         <v>484</v>
@@ -74018,7 +74018,7 @@
     </row>
     <row r="1185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1185" t="s">
         <v>458</v>
@@ -74077,7 +74077,7 @@
     </row>
     <row r="1186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1186" t="s">
         <v>472</v>
@@ -74139,10 +74139,10 @@
     </row>
     <row r="1187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1187" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C1187">
         <v>1</v>
@@ -74192,7 +74192,7 @@
     </row>
     <row r="1188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1188" t="s">
         <v>61</v>
@@ -74254,7 +74254,7 @@
     </row>
     <row r="1189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1189" t="s">
         <v>151</v>
@@ -74316,7 +74316,7 @@
     </row>
     <row r="1190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1190" t="s">
         <v>378</v>
@@ -74378,10 +74378,10 @@
     </row>
     <row r="1191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
+        <v>620</v>
+      </c>
+      <c r="B1191" t="s">
         <v>621</v>
-      </c>
-      <c r="B1191" t="s">
-        <v>622</v>
       </c>
       <c r="C1191">
         <v>1</v>
@@ -74440,7 +74440,7 @@
     </row>
     <row r="1192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1192" t="s">
         <v>310</v>
@@ -74502,7 +74502,7 @@
     </row>
     <row r="1193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1193" t="s">
         <v>46</v>
@@ -74561,7 +74561,7 @@
     </row>
     <row r="1194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1194" t="s">
         <v>380</v>
@@ -74620,10 +74620,10 @@
     </row>
     <row r="1195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1195" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C1195">
         <v>1</v>
@@ -74682,7 +74682,7 @@
     </row>
     <row r="1196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1196" t="s">
         <v>301</v>
@@ -74744,7 +74744,7 @@
     </row>
     <row r="1197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1197" t="s">
         <v>313</v>
@@ -74806,10 +74806,10 @@
     </row>
     <row r="1198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1198" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C1198">
         <v>1</v>
@@ -74859,7 +74859,7 @@
     </row>
     <row r="1199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1199" t="s">
         <v>315</v>
@@ -74921,7 +74921,7 @@
     </row>
     <row r="1200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1200" t="s">
         <v>491</v>
@@ -74983,7 +74983,7 @@
     </row>
     <row r="1201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1201" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1201" t="s">
         <v>304</v>
@@ -75042,7 +75042,7 @@
     </row>
     <row r="1202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1202" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1202" t="s">
         <v>60</v>
@@ -75101,10 +75101,10 @@
     </row>
     <row r="1203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1203" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C1203">
         <v>1</v>
@@ -75163,10 +75163,10 @@
     </row>
     <row r="1204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1204" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C1204">
         <v>1</v>
@@ -75225,7 +75225,7 @@
     </row>
     <row r="1205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1205" t="s">
         <v>385</v>
@@ -75287,7 +75287,7 @@
     </row>
     <row r="1206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1206" t="s">
         <v>320</v>
@@ -75349,10 +75349,10 @@
     </row>
     <row r="1207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1207" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C1207">
         <v>1</v>
@@ -75411,7 +75411,7 @@
     </row>
     <row r="1208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1208" t="s">
         <v>64</v>
@@ -75473,7 +75473,7 @@
     </row>
     <row r="1209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1209" t="s">
         <v>65</v>
@@ -75532,10 +75532,10 @@
     </row>
     <row r="1210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1210" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1210" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C1210">
         <v>1</v>
@@ -75594,7 +75594,7 @@
     </row>
     <row r="1211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B1211" t="s">
         <v>309</v>
@@ -75656,7 +75656,7 @@
     </row>
     <row r="1212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1212" t="s">
         <v>437</v>
@@ -75718,7 +75718,7 @@
     </row>
     <row r="1213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1213" t="s">
         <v>23</v>
@@ -75780,7 +75780,7 @@
     </row>
     <row r="1214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1214" t="s">
         <v>160</v>
@@ -75842,7 +75842,7 @@
     </row>
     <row r="1215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1215" t="s">
         <v>24</v>
@@ -75904,7 +75904,7 @@
     </row>
     <row r="1216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1216" t="s">
         <v>337</v>
@@ -75966,7 +75966,7 @@
     </row>
     <row r="1217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1217" t="s">
         <v>26</v>
@@ -76028,7 +76028,7 @@
     </row>
     <row r="1218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1218" t="s">
         <v>31</v>
@@ -76090,7 +76090,7 @@
     </row>
     <row r="1219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1219" t="s">
         <v>227</v>
@@ -76149,10 +76149,10 @@
     </row>
     <row r="1220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
+        <v>627</v>
+      </c>
+      <c r="B1220" t="s">
         <v>628</v>
-      </c>
-      <c r="B1220" t="s">
-        <v>629</v>
       </c>
       <c r="C1220">
         <v>1</v>
@@ -76208,7 +76208,7 @@
     </row>
     <row r="1221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1221" t="s">
         <v>229</v>
@@ -76270,7 +76270,7 @@
     </row>
     <row r="1222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1222" t="s">
         <v>230</v>
@@ -76332,7 +76332,7 @@
     </row>
     <row r="1223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1223" t="s">
         <v>231</v>
@@ -76394,7 +76394,7 @@
     </row>
     <row r="1224" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1224" t="s">
         <v>550</v>
@@ -76447,7 +76447,7 @@
     </row>
     <row r="1225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1225" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1225" t="s">
         <v>32</v>
@@ -76509,7 +76509,7 @@
     </row>
     <row r="1226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1226" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1226" t="s">
         <v>34</v>
@@ -76568,7 +76568,7 @@
     </row>
     <row r="1227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1227" t="s">
         <v>234</v>
@@ -76630,7 +76630,7 @@
     </row>
     <row r="1228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1228" t="s">
         <v>36</v>
@@ -76689,10 +76689,10 @@
     </row>
     <row r="1229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1229" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1229" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C1229">
         <v>1</v>
@@ -76742,7 +76742,7 @@
     </row>
     <row r="1230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1230" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1230" t="s">
         <v>238</v>
@@ -76801,7 +76801,7 @@
     </row>
     <row r="1231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1231" t="s">
         <v>476</v>
@@ -76863,10 +76863,10 @@
     </row>
     <row r="1232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B1232" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C1232">
         <v>1</v>
@@ -76925,7 +76925,7 @@
     </row>
     <row r="1233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1233" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1233" t="s">
         <v>134</v>
@@ -76987,10 +76987,10 @@
     </row>
     <row r="1234" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1234" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1234" t="s">
         <v>632</v>
-      </c>
-      <c r="B1234" t="s">
-        <v>633</v>
       </c>
       <c r="C1234">
         <v>1</v>
@@ -77040,10 +77040,10 @@
     </row>
     <row r="1235" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1235" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1235" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C1235">
         <v>1</v>
@@ -77102,7 +77102,7 @@
     </row>
     <row r="1236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1236" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1236" t="s">
         <v>71</v>
@@ -77164,7 +77164,7 @@
     </row>
     <row r="1237" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1237" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1237" t="s">
         <v>138</v>
@@ -77226,7 +77226,7 @@
     </row>
     <row r="1238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1238" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1238" t="s">
         <v>72</v>
@@ -77285,7 +77285,7 @@
     </row>
     <row r="1239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1239" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1239" t="s">
         <v>430</v>
@@ -77347,7 +77347,7 @@
     </row>
     <row r="1240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1240" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1240" t="s">
         <v>140</v>
@@ -77409,7 +77409,7 @@
     </row>
     <row r="1241" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1241" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1241" t="s">
         <v>78</v>
@@ -77471,10 +77471,10 @@
     </row>
     <row r="1242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1242" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1242" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C1242">
         <v>1</v>
@@ -77530,10 +77530,10 @@
     </row>
     <row r="1243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1243" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1243" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C1243">
         <v>1</v>
@@ -77583,7 +77583,7 @@
     </row>
     <row r="1244" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1244" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1244" t="s">
         <v>144</v>
@@ -77642,10 +77642,10 @@
     </row>
     <row r="1245" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1245" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1245" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C1245">
         <v>1</v>
@@ -77704,7 +77704,7 @@
     </row>
     <row r="1246" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1246" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1246" t="s">
         <v>174</v>
@@ -77763,7 +77763,7 @@
     </row>
     <row r="1247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1247" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1247" t="s">
         <v>246</v>
@@ -77825,7 +77825,7 @@
     </row>
     <row r="1248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1248" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1248" t="s">
         <v>42</v>
@@ -77878,7 +77878,7 @@
     </row>
     <row r="1249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1249" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1249" t="s">
         <v>287</v>
@@ -77931,10 +77931,10 @@
     </row>
     <row r="1250" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1250" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1250" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C1250">
         <v>1</v>
@@ -77993,7 +77993,7 @@
     </row>
     <row r="1251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1251" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1251" t="s">
         <v>154</v>
@@ -78055,10 +78055,10 @@
     </row>
     <row r="1252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1252" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1252" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C1252">
         <v>1</v>
@@ -78108,10 +78108,10 @@
     </row>
     <row r="1253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1253" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1253" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C1253">
         <v>1</v>
@@ -78167,7 +78167,7 @@
     </row>
     <row r="1254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1254" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1254" t="s">
         <v>288</v>
@@ -78229,7 +78229,7 @@
     </row>
     <row r="1255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1255" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1255" t="s">
         <v>22</v>
@@ -78288,10 +78288,10 @@
     </row>
     <row r="1256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1256" t="s">
+        <v>638</v>
+      </c>
+      <c r="B1256" t="s">
         <v>639</v>
-      </c>
-      <c r="B1256" t="s">
-        <v>640</v>
       </c>
       <c r="C1256">
         <v>1</v>
@@ -78350,7 +78350,7 @@
     </row>
     <row r="1257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1257" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1257" t="s">
         <v>251</v>
@@ -78409,7 +78409,7 @@
     </row>
     <row r="1258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1258" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1258" t="s">
         <v>253</v>
@@ -78468,7 +78468,7 @@
     </row>
     <row r="1259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1259" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1259" t="s">
         <v>205</v>
@@ -78521,7 +78521,7 @@
     </row>
     <row r="1260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1260" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1260" t="s">
         <v>375</v>
@@ -78583,7 +78583,7 @@
     </row>
     <row r="1261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1261" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1261" t="s">
         <v>293</v>
@@ -78636,10 +78636,10 @@
     </row>
     <row r="1262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1262" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1262" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C1262">
         <v>1</v>
@@ -78695,10 +78695,10 @@
     </row>
     <row r="1263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1263" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1263" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C1263">
         <v>1</v>
@@ -78757,10 +78757,10 @@
     </row>
     <row r="1264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1264" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1264" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C1264">
         <v>1</v>
@@ -78816,7 +78816,7 @@
     </row>
     <row r="1265" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1265" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1265" t="s">
         <v>423</v>
@@ -78869,7 +78869,7 @@
     </row>
     <row r="1266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1266" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1266" t="s">
         <v>244</v>
@@ -78931,7 +78931,7 @@
     </row>
     <row r="1267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1267" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1267" t="s">
         <v>376</v>
@@ -78990,7 +78990,7 @@
     </row>
     <row r="1268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1268" t="s">
         <v>209</v>
@@ -79052,10 +79052,10 @@
     </row>
     <row r="1269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1269" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1269" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C1269">
         <v>1</v>
@@ -79114,7 +79114,7 @@
     </row>
     <row r="1270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1270" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1270" t="s">
         <v>38</v>
@@ -79176,10 +79176,10 @@
     </row>
     <row r="1271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1271" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1271" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C1271">
         <v>1</v>
@@ -79238,10 +79238,10 @@
     </row>
     <row r="1272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1272" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C1272">
         <v>1</v>
@@ -79300,7 +79300,7 @@
     </row>
     <row r="1273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1273" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1273" t="s">
         <v>296</v>
@@ -79353,7 +79353,7 @@
     </row>
     <row r="1274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1274" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1274" t="s">
         <v>43</v>
@@ -79415,10 +79415,10 @@
     </row>
     <row r="1275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1275" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B1275" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C1275">
         <v>1</v>
@@ -79477,7 +79477,7 @@
     </row>
     <row r="1276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1276" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1276" t="s">
         <v>248</v>
@@ -79539,7 +79539,7 @@
     </row>
     <row r="1277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1277" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1277" t="s">
         <v>162</v>
@@ -79592,7 +79592,7 @@
     </row>
     <row r="1278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1278" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1278" t="s">
         <v>250</v>
@@ -79651,7 +79651,7 @@
     </row>
     <row r="1279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1279" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1279" t="s">
         <v>252</v>
@@ -79710,7 +79710,7 @@
     </row>
     <row r="1280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1280" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1280" t="s">
         <v>367</v>
@@ -79772,10 +79772,10 @@
     </row>
     <row r="1281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1281" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1281" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C1281">
         <v>1</v>
@@ -79828,10 +79828,10 @@
     </row>
     <row r="1282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1282" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1282" t="s">
         <v>646</v>
-      </c>
-      <c r="B1282" t="s">
-        <v>647</v>
       </c>
       <c r="C1282">
         <v>1</v>
@@ -79887,7 +79887,7 @@
     </row>
     <row r="1283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1283" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1283" t="s">
         <v>255</v>
@@ -79949,7 +79949,7 @@
     </row>
     <row r="1284" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1284" t="s">
         <v>448</v>
@@ -80008,7 +80008,7 @@
     </row>
     <row r="1285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1285" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1285" t="s">
         <v>257</v>
@@ -80070,7 +80070,7 @@
     </row>
     <row r="1286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1286" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1286" t="s">
         <v>258</v>
@@ -80132,7 +80132,7 @@
     </row>
     <row r="1287" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1287" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1287" t="s">
         <v>170</v>
@@ -80194,7 +80194,7 @@
     </row>
     <row r="1288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1288" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1288" t="s">
         <v>172</v>
@@ -80256,7 +80256,7 @@
     </row>
     <row r="1289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1289" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1289" t="s">
         <v>261</v>
@@ -80318,7 +80318,7 @@
     </row>
     <row r="1290" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1290" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1290" t="s">
         <v>262</v>
@@ -80371,7 +80371,7 @@
     </row>
     <row r="1291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1291" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1291" t="s">
         <v>175</v>
@@ -80430,7 +80430,7 @@
     </row>
     <row r="1292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1292" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1292" t="s">
         <v>177</v>
@@ -80483,7 +80483,7 @@
     </row>
     <row r="1293" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1293" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1293" t="s">
         <v>264</v>
@@ -80545,7 +80545,7 @@
     </row>
     <row r="1294" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1294" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1294" t="s">
         <v>179</v>
@@ -80598,7 +80598,7 @@
     </row>
     <row r="1295" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1295" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1295" t="s">
         <v>417</v>
@@ -80651,10 +80651,10 @@
     </row>
     <row r="1296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1296" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1296" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C1296">
         <v>1</v>
@@ -80713,7 +80713,7 @@
     </row>
     <row r="1297" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1297" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1297" t="s">
         <v>508</v>
@@ -80766,7 +80766,7 @@
     </row>
     <row r="1298" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1298" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1298" t="s">
         <v>135</v>
@@ -80819,7 +80819,7 @@
     </row>
     <row r="1299" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1299" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1299" t="s">
         <v>159</v>
@@ -80878,10 +80878,10 @@
     </row>
     <row r="1300" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1300" t="s">
+        <v>648</v>
+      </c>
+      <c r="B1300" t="s">
         <v>649</v>
-      </c>
-      <c r="B1300" t="s">
-        <v>650</v>
       </c>
       <c r="C1300">
         <v>1</v>
@@ -80937,7 +80937,7 @@
     </row>
     <row r="1301" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1301" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1301" t="s">
         <v>162</v>
@@ -80999,7 +80999,7 @@
     </row>
     <row r="1302" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1302" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1302" t="s">
         <v>142</v>
@@ -81058,7 +81058,7 @@
     </row>
     <row r="1303" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1303" t="s">
         <v>417</v>
@@ -81120,10 +81120,10 @@
     </row>
     <row r="1304" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1304" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1304" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C1304">
         <v>1</v>
@@ -81182,10 +81182,10 @@
     </row>
     <row r="1305" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1305" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1305" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C1305">
         <v>1</v>
@@ -81241,7 +81241,7 @@
     </row>
     <row r="1306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1306" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1306" t="s">
         <v>147</v>
@@ -81300,7 +81300,7 @@
     </row>
     <row r="1307" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1307" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1307" t="s">
         <v>170</v>
@@ -81362,7 +81362,7 @@
     </row>
     <row r="1308" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1308" t="s">
         <v>59</v>
@@ -81421,10 +81421,10 @@
     </row>
     <row r="1309" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1309" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1309" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C1309">
         <v>1</v>
@@ -81483,7 +81483,7 @@
     </row>
     <row r="1310" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1310" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1310" t="s">
         <v>172</v>
@@ -81545,7 +81545,7 @@
     </row>
     <row r="1311" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1311" t="s">
         <v>149</v>
@@ -81598,7 +81598,7 @@
     </row>
     <row r="1312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1312" t="s">
         <v>484</v>
@@ -81660,7 +81660,7 @@
     </row>
     <row r="1313" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1313" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1313" t="s">
         <v>175</v>
@@ -81722,7 +81722,7 @@
     </row>
     <row r="1314" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1314" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1314" t="s">
         <v>61</v>
@@ -81775,7 +81775,7 @@
     </row>
     <row r="1315" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1315" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1315" t="s">
         <v>179</v>
@@ -81834,7 +81834,7 @@
     </row>
     <row r="1316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1316" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1316" t="s">
         <v>62</v>
@@ -81896,7 +81896,7 @@
     </row>
     <row r="1317" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1317" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1317" t="s">
         <v>151</v>
@@ -81949,10 +81949,10 @@
     </row>
     <row r="1318" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1318" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C1318">
         <v>1</v>
@@ -82008,7 +82008,7 @@
     </row>
     <row r="1319" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1319" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B1319" t="s">
         <v>156</v>
@@ -82070,7 +82070,7 @@
     </row>
     <row r="1320" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1320" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1320" t="s">
         <v>21</v>
@@ -82132,7 +82132,7 @@
     </row>
     <row r="1321" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1321" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1321" t="s">
         <v>22</v>
@@ -82185,7 +82185,7 @@
     </row>
     <row r="1322" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1322" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1322" t="s">
         <v>201</v>
@@ -82247,10 +82247,10 @@
     </row>
     <row r="1323" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1323" t="s">
+        <v>652</v>
+      </c>
+      <c r="B1323" t="s">
         <v>653</v>
-      </c>
-      <c r="B1323" t="s">
-        <v>654</v>
       </c>
       <c r="C1323">
         <v>1</v>
@@ -82309,7 +82309,7 @@
     </row>
     <row r="1324" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1324" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1324" t="s">
         <v>202</v>
@@ -82371,7 +82371,7 @@
     </row>
     <row r="1325" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1325" t="s">
         <v>339</v>
@@ -82430,7 +82430,7 @@
     </row>
     <row r="1326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1326" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1326" t="s">
         <v>340</v>
@@ -82492,7 +82492,7 @@
     </row>
     <row r="1327" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1327" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1327" t="s">
         <v>140</v>
@@ -82545,10 +82545,10 @@
     </row>
     <row r="1328" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1328" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1328" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C1328">
         <v>1</v>
@@ -82598,7 +82598,7 @@
     </row>
     <row r="1329" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1329" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1329" t="s">
         <v>211</v>
@@ -82660,7 +82660,7 @@
     </row>
     <row r="1330" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1330" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1330" t="s">
         <v>38</v>
@@ -82719,10 +82719,10 @@
     </row>
     <row r="1331" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1331" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1331" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C1331">
         <v>1</v>
@@ -82781,7 +82781,7 @@
     </row>
     <row r="1332" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1332" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1332" t="s">
         <v>212</v>
@@ -82834,7 +82834,7 @@
     </row>
     <row r="1333" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1333" t="s">
         <v>462</v>
@@ -82893,7 +82893,7 @@
     </row>
     <row r="1334" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1334" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1334" t="s">
         <v>174</v>
@@ -82946,7 +82946,7 @@
     </row>
     <row r="1335" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1335" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1335" t="s">
         <v>246</v>
@@ -83005,7 +83005,7 @@
     </row>
     <row r="1336" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1336" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1336" t="s">
         <v>499</v>
@@ -83067,10 +83067,10 @@
     </row>
     <row r="1337" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1337" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1337" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C1337">
         <v>1</v>
@@ -83126,7 +83126,7 @@
     </row>
     <row r="1338" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1338" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1338" t="s">
         <v>215</v>
@@ -83179,7 +83179,7 @@
     </row>
     <row r="1339" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1339" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1339" t="s">
         <v>43</v>
@@ -83232,7 +83232,7 @@
     </row>
     <row r="1340" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1340" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1340" t="s">
         <v>424</v>
@@ -83291,7 +83291,7 @@
     </row>
     <row r="1341" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1341" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B1341" t="s">
         <v>425</v>
@@ -83353,7 +83353,7 @@
     </row>
     <row r="1342" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1342" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1342" t="s">
         <v>217</v>
@@ -83412,7 +83412,7 @@
     </row>
     <row r="1343" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1343" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1343" t="s">
         <v>221</v>
@@ -83474,7 +83474,7 @@
     </row>
     <row r="1344" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1344" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1344" t="s">
         <v>222</v>
@@ -83536,10 +83536,10 @@
     </row>
     <row r="1345" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1345" t="s">
+        <v>657</v>
+      </c>
+      <c r="B1345" t="s">
         <v>658</v>
-      </c>
-      <c r="B1345" t="s">
-        <v>659</v>
       </c>
       <c r="C1345">
         <v>1</v>
@@ -83598,10 +83598,10 @@
     </row>
     <row r="1346" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1346" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1346" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C1346">
         <v>1</v>
@@ -83651,7 +83651,7 @@
     </row>
     <row r="1347" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1347" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1347" t="s">
         <v>120</v>
@@ -83713,7 +83713,7 @@
     </row>
     <row r="1348" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1348" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1348" t="s">
         <v>413</v>
@@ -83775,10 +83775,10 @@
     </row>
     <row r="1349" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1349" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1349" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C1349">
         <v>1</v>
@@ -83834,7 +83834,7 @@
     </row>
     <row r="1350" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1350" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1350" t="s">
         <v>232</v>
@@ -83896,10 +83896,10 @@
     </row>
     <row r="1351" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1351" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1351" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1351">
         <v>1</v>
@@ -83955,7 +83955,7 @@
     </row>
     <row r="1352" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1352" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1352" t="s">
         <v>124</v>
@@ -84011,7 +84011,7 @@
     </row>
     <row r="1353" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1353" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1353" t="s">
         <v>326</v>
@@ -84073,7 +84073,7 @@
     </row>
     <row r="1354" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1354" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1354" t="s">
         <v>125</v>
@@ -84135,7 +84135,7 @@
     </row>
     <row r="1355" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1355" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1355" t="s">
         <v>327</v>
@@ -84188,10 +84188,10 @@
     </row>
     <row r="1356" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1356" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1356" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C1356">
         <v>1</v>
@@ -84250,7 +84250,7 @@
     </row>
     <row r="1357" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1357" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1357" t="s">
         <v>126</v>
@@ -84309,7 +84309,7 @@
     </row>
     <row r="1358" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1358" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1358" t="s">
         <v>328</v>
@@ -84371,7 +84371,7 @@
     </row>
     <row r="1359" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1359" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1359" t="s">
         <v>519</v>
@@ -84430,7 +84430,7 @@
     </row>
     <row r="1360" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1360" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1360" t="s">
         <v>522</v>
@@ -84489,7 +84489,7 @@
     </row>
     <row r="1361" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1361" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1361" t="s">
         <v>433</v>
@@ -84551,10 +84551,10 @@
     </row>
     <row r="1362" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1362" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1362" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C1362">
         <v>1</v>
@@ -84604,7 +84604,7 @@
     </row>
     <row r="1363" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1363" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B1363" t="s">
         <v>571</v>
@@ -84657,7 +84657,7 @@
     </row>
     <row r="1364" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1364" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1364" t="s">
         <v>378</v>
@@ -84719,7 +84719,7 @@
     </row>
     <row r="1365" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1365" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1365" t="s">
         <v>181</v>
@@ -84781,7 +84781,7 @@
     </row>
     <row r="1366" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1366" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1366" t="s">
         <v>310</v>
@@ -84840,7 +84840,7 @@
     </row>
     <row r="1367" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1367" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1367" t="s">
         <v>182</v>
@@ -84899,7 +84899,7 @@
     </row>
     <row r="1368" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1368" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1368" t="s">
         <v>183</v>
@@ -84961,7 +84961,7 @@
     </row>
     <row r="1369" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1369" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1369" t="s">
         <v>387</v>
@@ -85014,7 +85014,7 @@
     </row>
     <row r="1370" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1370" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1370" t="s">
         <v>184</v>
@@ -85073,7 +85073,7 @@
     </row>
     <row r="1371" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1371" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1371" t="s">
         <v>345</v>
@@ -85135,10 +85135,10 @@
     </row>
     <row r="1372" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1372" t="s">
+        <v>662</v>
+      </c>
+      <c r="B1372" t="s">
         <v>663</v>
-      </c>
-      <c r="B1372" t="s">
-        <v>664</v>
       </c>
       <c r="C1372">
         <v>1</v>
@@ -85197,7 +85197,7 @@
     </row>
     <row r="1373" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1373" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1373" t="s">
         <v>313</v>
@@ -85256,7 +85256,7 @@
     </row>
     <row r="1374" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1374" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1374" t="s">
         <v>188</v>
@@ -85318,7 +85318,7 @@
     </row>
     <row r="1375" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1375" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1375" t="s">
         <v>189</v>
@@ -85380,7 +85380,7 @@
     </row>
     <row r="1376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1376" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1376" t="s">
         <v>315</v>
@@ -85433,7 +85433,7 @@
     </row>
     <row r="1377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1377" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1377" t="s">
         <v>363</v>
@@ -85495,7 +85495,7 @@
     </row>
     <row r="1378" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1378" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1378" t="s">
         <v>316</v>
@@ -85557,10 +85557,10 @@
     </row>
     <row r="1379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1379" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1379" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C1379">
         <v>1</v>
@@ -85619,7 +85619,7 @@
     </row>
     <row r="1380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1380" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1380" t="s">
         <v>384</v>
@@ -85678,7 +85678,7 @@
     </row>
     <row r="1381" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1381" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1381" t="s">
         <v>385</v>
@@ -85737,7 +85737,7 @@
     </row>
     <row r="1382" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1382" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1382" t="s">
         <v>391</v>
@@ -85799,7 +85799,7 @@
     </row>
     <row r="1383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1383" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1383" t="s">
         <v>320</v>
@@ -85852,10 +85852,10 @@
     </row>
     <row r="1384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1384" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1384" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C1384">
         <v>1</v>
@@ -85914,7 +85914,7 @@
     </row>
     <row r="1385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1385" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1385" t="s">
         <v>392</v>
@@ -85967,7 +85967,7 @@
     </row>
     <row r="1386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1386" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1386" t="s">
         <v>437</v>
@@ -86020,7 +86020,7 @@
     </row>
     <row r="1387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1387" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1387" t="s">
         <v>118</v>
@@ -86082,7 +86082,7 @@
     </row>
     <row r="1388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1388" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1388" t="s">
         <v>372</v>
@@ -86144,7 +86144,7 @@
     </row>
     <row r="1389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1389" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1389" t="s">
         <v>23</v>
@@ -86206,7 +86206,7 @@
     </row>
     <row r="1390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1390" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1390" t="s">
         <v>24</v>
@@ -86268,7 +86268,7 @@
     </row>
     <row r="1391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1391" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1391" t="s">
         <v>337</v>
@@ -86330,7 +86330,7 @@
     </row>
     <row r="1392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1392" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1392" t="s">
         <v>119</v>
@@ -86389,7 +86389,7 @@
     </row>
     <row r="1393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1393" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1393" t="s">
         <v>31</v>
@@ -86451,7 +86451,7 @@
     </row>
     <row r="1394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1394" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1394" t="s">
         <v>123</v>
@@ -86513,7 +86513,7 @@
     </row>
     <row r="1395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1395" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1395" t="s">
         <v>32</v>
@@ -86572,7 +86572,7 @@
     </row>
     <row r="1396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1396" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1396" t="s">
         <v>34</v>
@@ -86631,7 +86631,7 @@
     </row>
     <row r="1397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1397" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1397" t="s">
         <v>559</v>
@@ -86690,10 +86690,10 @@
     </row>
     <row r="1398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
+        <v>670</v>
+      </c>
+      <c r="B1398" t="s">
         <v>671</v>
-      </c>
-      <c r="B1398" t="s">
-        <v>672</v>
       </c>
       <c r="C1398">
         <v>1</v>
@@ -86752,7 +86752,7 @@
     </row>
     <row r="1399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1399" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1399" t="s">
         <v>427</v>
@@ -86814,10 +86814,10 @@
     </row>
     <row r="1400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1400" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1400" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C1400">
         <v>1</v>
@@ -86876,7 +86876,7 @@
     </row>
     <row r="1401" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1401" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1401" t="s">
         <v>128</v>
@@ -86938,10 +86938,10 @@
     </row>
     <row r="1402" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1402" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1402" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C1402">
         <v>1</v>
@@ -86997,7 +86997,7 @@
     </row>
     <row r="1403" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1403" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1403" t="s">
         <v>398</v>
@@ -87059,7 +87059,7 @@
     </row>
     <row r="1404" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1404" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1404" t="s">
         <v>500</v>
@@ -87118,7 +87118,7 @@
     </row>
     <row r="1405" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1405" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1405" t="s">
         <v>476</v>
@@ -87177,10 +87177,10 @@
     </row>
     <row r="1406" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1406" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1406" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C1406">
         <v>1</v>
@@ -87239,7 +87239,7 @@
     </row>
     <row r="1407" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1407" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B1407" t="s">
         <v>44</v>
@@ -87301,7 +87301,7 @@
     </row>
     <row r="1408" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1408" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1408" t="s">
         <v>135</v>
@@ -87360,7 +87360,7 @@
     </row>
     <row r="1409" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1409" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1409" t="s">
         <v>248</v>
@@ -87422,10 +87422,10 @@
     </row>
     <row r="1410" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1410" t="s">
+        <v>675</v>
+      </c>
+      <c r="B1410" t="s">
         <v>676</v>
-      </c>
-      <c r="B1410" t="s">
-        <v>677</v>
       </c>
       <c r="C1410">
         <v>1</v>
@@ -87484,7 +87484,7 @@
     </row>
     <row r="1411" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1411" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1411" t="s">
         <v>250</v>
@@ -87543,7 +87543,7 @@
     </row>
     <row r="1412" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1412" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1412" t="s">
         <v>252</v>
@@ -87605,7 +87605,7 @@
     </row>
     <row r="1413" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1413" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1413" t="s">
         <v>333</v>
@@ -87664,7 +87664,7 @@
     </row>
     <row r="1414" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1414" t="s">
         <v>367</v>
@@ -87723,7 +87723,7 @@
     </row>
     <row r="1415" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1415" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1415" t="s">
         <v>54</v>
@@ -87785,7 +87785,7 @@
     </row>
     <row r="1416" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1416" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1416" t="s">
         <v>255</v>
@@ -87838,7 +87838,7 @@
     </row>
     <row r="1417" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1417" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1417" t="s">
         <v>448</v>
@@ -87897,7 +87897,7 @@
     </row>
     <row r="1418" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1418" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1418" t="s">
         <v>257</v>
@@ -87959,7 +87959,7 @@
     </row>
     <row r="1419" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1419" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1419" t="s">
         <v>258</v>
@@ -88021,7 +88021,7 @@
     </row>
     <row r="1420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1420" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1420" t="s">
         <v>147</v>
@@ -88080,7 +88080,7 @@
     </row>
     <row r="1421" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1421" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1421" t="s">
         <v>261</v>
@@ -88139,7 +88139,7 @@
     </row>
     <row r="1422" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1422" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1422" t="s">
         <v>149</v>
@@ -88192,7 +88192,7 @@
     </row>
     <row r="1423" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1423" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1423" t="s">
         <v>484</v>
@@ -88254,7 +88254,7 @@
     </row>
     <row r="1424" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1424" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1424" t="s">
         <v>262</v>
@@ -88307,7 +88307,7 @@
     </row>
     <row r="1425" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1425" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1425" t="s">
         <v>264</v>
@@ -88369,7 +88369,7 @@
     </row>
     <row r="1426" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1426" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1426" t="s">
         <v>61</v>
@@ -88431,7 +88431,7 @@
     </row>
     <row r="1427" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1427" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1427" t="s">
         <v>62</v>
@@ -88493,7 +88493,7 @@
     </row>
     <row r="1428" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1428" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1428" t="s">
         <v>151</v>
@@ -88555,10 +88555,10 @@
     </row>
     <row r="1429" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1429" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B1429" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C1429">
         <v>1</v>
@@ -88617,7 +88617,7 @@
     </row>
     <row r="1430" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1430" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1430" t="s">
         <v>134</v>
@@ -88676,10 +88676,10 @@
     </row>
     <row r="1431" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1431" t="s">
+        <v>678</v>
+      </c>
+      <c r="B1431" t="s">
         <v>679</v>
-      </c>
-      <c r="B1431" t="s">
-        <v>680</v>
       </c>
       <c r="C1431">
         <v>1</v>
@@ -88729,7 +88729,7 @@
     </row>
     <row r="1432" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1432" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1432" t="s">
         <v>249</v>
@@ -88791,7 +88791,7 @@
     </row>
     <row r="1433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1433" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1433" t="s">
         <v>138</v>
@@ -88853,7 +88853,7 @@
     </row>
     <row r="1434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1434" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1434" t="s">
         <v>162</v>
@@ -88906,7 +88906,7 @@
     </row>
     <row r="1435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1435" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1435" t="s">
         <v>140</v>
@@ -88968,7 +88968,7 @@
     </row>
     <row r="1436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1436" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1436" t="s">
         <v>168</v>
@@ -89021,10 +89021,10 @@
     </row>
     <row r="1437" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1437" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1437" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C1437">
         <v>1</v>
@@ -89083,7 +89083,7 @@
     </row>
     <row r="1438" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1438" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1438" t="s">
         <v>244</v>
@@ -89145,10 +89145,10 @@
     </row>
     <row r="1439" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1439" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1439" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C1439">
         <v>1</v>
@@ -89207,10 +89207,10 @@
     </row>
     <row r="1440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1440" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1440" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C1440">
         <v>1</v>
@@ -89269,10 +89269,10 @@
     </row>
     <row r="1441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1441" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1441" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C1441">
         <v>1</v>
@@ -89331,7 +89331,7 @@
     </row>
     <row r="1442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1442" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1442" t="s">
         <v>170</v>
@@ -89393,7 +89393,7 @@
     </row>
     <row r="1443" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1443" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1443" t="s">
         <v>172</v>
@@ -89455,7 +89455,7 @@
     </row>
     <row r="1444" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1444" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1444" t="s">
         <v>175</v>
@@ -89514,7 +89514,7 @@
     </row>
     <row r="1445" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1445" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1445" t="s">
         <v>507</v>
@@ -89567,7 +89567,7 @@
     </row>
     <row r="1446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1446" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1446" t="s">
         <v>42</v>
@@ -89626,7 +89626,7 @@
     </row>
     <row r="1447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1447" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1447" t="s">
         <v>179</v>
@@ -89685,10 +89685,10 @@
     </row>
     <row r="1448" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1448" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1448" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C1448">
         <v>1</v>
@@ -89738,10 +89738,10 @@
     </row>
     <row r="1449" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1449" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1449" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C1449">
         <v>1</v>
@@ -89797,7 +89797,7 @@
     </row>
     <row r="1450" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1450" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1450" t="s">
         <v>152</v>
@@ -89859,10 +89859,10 @@
     </row>
     <row r="1451" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1451" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B1451" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C1451">
         <v>1</v>
@@ -89921,7 +89921,7 @@
     </row>
     <row r="1452" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1452" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1452" t="s">
         <v>568</v>
@@ -89983,7 +89983,7 @@
     </row>
     <row r="1453" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1453" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1453" t="s">
         <v>408</v>
@@ -90042,10 +90042,10 @@
     </row>
     <row r="1454" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1454" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1454" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C1454">
         <v>1</v>
@@ -90101,10 +90101,10 @@
     </row>
     <row r="1455" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1455" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1455" t="s">
         <v>684</v>
-      </c>
-      <c r="B1455" t="s">
-        <v>685</v>
       </c>
       <c r="C1455">
         <v>1</v>
@@ -90163,7 +90163,7 @@
     </row>
     <row r="1456" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1456" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1456" t="s">
         <v>98</v>
@@ -90225,7 +90225,7 @@
     </row>
     <row r="1457" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1457" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1457" t="s">
         <v>478</v>
@@ -90287,7 +90287,7 @@
     </row>
     <row r="1458" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1458" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1458" t="s">
         <v>545</v>
@@ -90346,7 +90346,7 @@
     </row>
     <row r="1459" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1459" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1459" t="s">
         <v>73</v>
@@ -90408,10 +90408,10 @@
     </row>
     <row r="1460" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1460" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1460" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C1460">
         <v>1</v>
@@ -90467,7 +90467,7 @@
     </row>
     <row r="1461" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1461" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1461" t="s">
         <v>461</v>
@@ -90526,7 +90526,7 @@
     </row>
     <row r="1462" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1462" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1462" t="s">
         <v>75</v>
@@ -90579,7 +90579,7 @@
     </row>
     <row r="1463" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1463" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1463" t="s">
         <v>409</v>
@@ -90641,7 +90641,7 @@
     </row>
     <row r="1464" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1464" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1464" t="s">
         <v>547</v>
@@ -90703,7 +90703,7 @@
     </row>
     <row r="1465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1465" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1465" t="s">
         <v>276</v>
@@ -90765,7 +90765,7 @@
     </row>
     <row r="1466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1466" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1466" t="s">
         <v>511</v>
@@ -90827,7 +90827,7 @@
     </row>
     <row r="1467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1467" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1467" t="s">
         <v>277</v>
@@ -90880,7 +90880,7 @@
     </row>
     <row r="1468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1468" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1468" t="s">
         <v>108</v>
@@ -90942,7 +90942,7 @@
     </row>
     <row r="1469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1469" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1469" t="s">
         <v>485</v>
@@ -91001,10 +91001,10 @@
     </row>
     <row r="1470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1470" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1470" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C1470">
         <v>1</v>
@@ -91060,10 +91060,10 @@
     </row>
     <row r="1471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1471" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1471" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C1471">
         <v>1</v>
@@ -91122,7 +91122,7 @@
     </row>
     <row r="1472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1472" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1472" t="s">
         <v>110</v>
@@ -91184,7 +91184,7 @@
     </row>
     <row r="1473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1473" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B1473" t="s">
         <v>88</v>
@@ -91237,7 +91237,7 @@
     </row>
     <row r="1474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1474" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1474" t="s">
         <v>310</v>
@@ -91296,10 +91296,10 @@
     </row>
     <row r="1475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1475" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1475" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C1475">
         <v>1</v>
@@ -91355,10 +91355,10 @@
     </row>
     <row r="1476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1476" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1476" t="s">
         <v>688</v>
-      </c>
-      <c r="B1476" t="s">
-        <v>689</v>
       </c>
       <c r="C1476">
         <v>1</v>
@@ -91417,7 +91417,7 @@
     </row>
     <row r="1477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1477" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1477" t="s">
         <v>311</v>
@@ -91479,7 +91479,7 @@
     </row>
     <row r="1478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1478" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1478" t="s">
         <v>379</v>
@@ -91541,7 +91541,7 @@
     </row>
     <row r="1479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1479" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1479" t="s">
         <v>380</v>
@@ -91600,7 +91600,7 @@
     </row>
     <row r="1480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1480" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1480" t="s">
         <v>572</v>
@@ -91659,7 +91659,7 @@
     </row>
     <row r="1481" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1481" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1481" t="s">
         <v>383</v>
@@ -91721,7 +91721,7 @@
     </row>
     <row r="1482" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1482" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1482" t="s">
         <v>313</v>
@@ -91774,7 +91774,7 @@
     </row>
     <row r="1483" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1483" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1483" t="s">
         <v>435</v>
@@ -91833,7 +91833,7 @@
     </row>
     <row r="1484" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1484" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1484" t="s">
         <v>456</v>
@@ -91895,7 +91895,7 @@
     </row>
     <row r="1485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1485" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1485" t="s">
         <v>529</v>
@@ -91954,7 +91954,7 @@
     </row>
     <row r="1486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1486" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1486" t="s">
         <v>303</v>
@@ -92007,7 +92007,7 @@
     </row>
     <row r="1487" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1487" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1487" t="s">
         <v>405</v>
@@ -92069,7 +92069,7 @@
     </row>
     <row r="1488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1488" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1488" t="s">
         <v>305</v>
@@ -92128,7 +92128,7 @@
     </row>
     <row r="1489" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1489" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1489" t="s">
         <v>306</v>
@@ -92181,7 +92181,7 @@
     </row>
     <row r="1490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1490" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1490" t="s">
         <v>564</v>
@@ -92243,10 +92243,10 @@
     </row>
     <row r="1491" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1491" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1491" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C1491">
         <v>1</v>
@@ -92305,7 +92305,7 @@
     </row>
     <row r="1492" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1492" t="s">
         <v>385</v>
@@ -92367,7 +92367,7 @@
     </row>
     <row r="1493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1493" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1493" t="s">
         <v>307</v>
@@ -92420,7 +92420,7 @@
     </row>
     <row r="1494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1494" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1494" t="s">
         <v>458</v>
@@ -92473,10 +92473,10 @@
     </row>
     <row r="1495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1495" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1495" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C1495">
         <v>1</v>
@@ -92535,7 +92535,7 @@
     </row>
     <row r="1496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1496" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1496" t="s">
         <v>46</v>
@@ -92597,10 +92597,10 @@
     </row>
     <row r="1497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1497" t="s">
         <v>690</v>
-      </c>
-      <c r="B1497" t="s">
-        <v>691</v>
       </c>
       <c r="C1497">
         <v>1</v>
@@ -92656,7 +92656,7 @@
     </row>
     <row r="1498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1498" t="s">
         <v>182</v>
@@ -92718,7 +92718,7 @@
     </row>
     <row r="1499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1499" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1499" t="s">
         <v>183</v>
@@ -92780,7 +92780,7 @@
     </row>
     <row r="1500" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1500" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1500" t="s">
         <v>387</v>
@@ -92842,7 +92842,7 @@
     </row>
     <row r="1501" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1501" t="s">
         <v>184</v>
@@ -92904,7 +92904,7 @@
     </row>
     <row r="1502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1502" t="s">
         <v>186</v>
@@ -92966,7 +92966,7 @@
     </row>
     <row r="1503" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1503" t="s">
         <v>301</v>
@@ -93025,7 +93025,7 @@
     </row>
     <row r="1504" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1504" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1504" t="s">
         <v>188</v>
@@ -93087,7 +93087,7 @@
     </row>
     <row r="1505" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1505" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1505" t="s">
         <v>189</v>
@@ -93149,10 +93149,10 @@
     </row>
     <row r="1506" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1506" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1506" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C1506">
         <v>1</v>
@@ -93202,7 +93202,7 @@
     </row>
     <row r="1507" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1507" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1507" t="s">
         <v>491</v>
@@ -93261,7 +93261,7 @@
     </row>
     <row r="1508" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1508" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1508" t="s">
         <v>363</v>
@@ -93323,7 +93323,7 @@
     </row>
     <row r="1509" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1509" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1509" t="s">
         <v>304</v>
@@ -93385,10 +93385,10 @@
     </row>
     <row r="1510" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1510" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1510" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C1510">
         <v>1</v>
@@ -93447,7 +93447,7 @@
     </row>
     <row r="1511" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1511" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1511" t="s">
         <v>60</v>
@@ -93509,7 +93509,7 @@
     </row>
     <row r="1512" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1512" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1512" t="s">
         <v>441</v>
@@ -93571,7 +93571,7 @@
     </row>
     <row r="1513" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1513" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1513" t="s">
         <v>391</v>
@@ -93633,7 +93633,7 @@
     </row>
     <row r="1514" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1514" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1514" t="s">
         <v>64</v>
@@ -93686,7 +93686,7 @@
     </row>
     <row r="1515" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1515" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1515" t="s">
         <v>65</v>
@@ -93748,10 +93748,10 @@
     </row>
     <row r="1516" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1516" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1516" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C1516">
         <v>1</v>
@@ -93810,7 +93810,7 @@
     </row>
     <row r="1517" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1517" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B1517" t="s">
         <v>309</v>
@@ -93872,7 +93872,7 @@
     </row>
     <row r="1518" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1518" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1518" t="s">
         <v>115</v>
@@ -93934,7 +93934,7 @@
     </row>
     <row r="1519" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1519" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1519" t="s">
         <v>116</v>
@@ -93996,7 +93996,7 @@
     </row>
     <row r="1520" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1520" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1520" t="s">
         <v>200</v>
@@ -94049,10 +94049,10 @@
     </row>
     <row r="1521" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1521" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1521" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C1521">
         <v>1</v>
@@ -94111,7 +94111,7 @@
     </row>
     <row r="1522" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1522" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1522" t="s">
         <v>556</v>
@@ -94170,7 +94170,7 @@
     </row>
     <row r="1523" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1523" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1523" t="s">
         <v>120</v>
@@ -94232,7 +94232,7 @@
     </row>
     <row r="1524" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1524" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1524" t="s">
         <v>413</v>
@@ -94291,7 +94291,7 @@
     </row>
     <row r="1525" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1525" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1525" t="s">
         <v>205</v>
@@ -94353,10 +94353,10 @@
     </row>
     <row r="1526" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1526" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1526" t="s">
         <v>693</v>
-      </c>
-      <c r="B1526" t="s">
-        <v>694</v>
       </c>
       <c r="C1526">
         <v>1</v>
@@ -94415,10 +94415,10 @@
     </row>
     <row r="1527" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1527" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1527" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1527">
         <v>1</v>
@@ -94474,7 +94474,7 @@
     </row>
     <row r="1528" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1528" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1528" t="s">
         <v>326</v>
@@ -94533,7 +94533,7 @@
     </row>
     <row r="1529" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1529" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1529" t="s">
         <v>375</v>
@@ -94595,7 +94595,7 @@
     </row>
     <row r="1530" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1530" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1530" t="s">
         <v>125</v>
@@ -94657,7 +94657,7 @@
     </row>
     <row r="1531" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1531" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1531" t="s">
         <v>293</v>
@@ -94716,10 +94716,10 @@
     </row>
     <row r="1532" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1532" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1532" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C1532">
         <v>1</v>
@@ -94778,10 +94778,10 @@
     </row>
     <row r="1533" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1533" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1533" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C1533">
         <v>1</v>
@@ -94831,7 +94831,7 @@
     </row>
     <row r="1534" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1534" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1534" t="s">
         <v>126</v>
@@ -94893,7 +94893,7 @@
     </row>
     <row r="1535" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1535" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1535" t="s">
         <v>207</v>
@@ -94955,7 +94955,7 @@
     </row>
     <row r="1536" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1536" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1536" t="s">
         <v>376</v>
@@ -95017,7 +95017,7 @@
     </row>
     <row r="1537" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1537" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1537" t="s">
         <v>209</v>
@@ -95076,7 +95076,7 @@
     </row>
     <row r="1538" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1538" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1538" t="s">
         <v>130</v>
@@ -95138,7 +95138,7 @@
     </row>
     <row r="1539" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1539" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B1539" t="s">
         <v>567</v>
@@ -95200,7 +95200,7 @@
     </row>
     <row r="1540" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1540" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1540" t="s">
         <v>22</v>
@@ -95262,7 +95262,7 @@
     </row>
     <row r="1541" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1541" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1541" t="s">
         <v>134</v>
@@ -95321,7 +95321,7 @@
     </row>
     <row r="1542" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1542" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1542" t="s">
         <v>223</v>
@@ -95380,7 +95380,7 @@
     </row>
     <row r="1543" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1543" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1543" t="s">
         <v>249</v>
@@ -95439,7 +95439,7 @@
     </row>
     <row r="1544" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1544" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1544" t="s">
         <v>226</v>
@@ -95498,7 +95498,7 @@
     </row>
     <row r="1545" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1545" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1545" t="s">
         <v>227</v>
@@ -95551,7 +95551,7 @@
     </row>
     <row r="1546" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1546" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1546" t="s">
         <v>229</v>
@@ -95604,7 +95604,7 @@
     </row>
     <row r="1547" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1547" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1547" t="s">
         <v>230</v>
@@ -95666,7 +95666,7 @@
     </row>
     <row r="1548" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1548" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1548" t="s">
         <v>231</v>
@@ -95725,7 +95725,7 @@
     </row>
     <row r="1549" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1549" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1549" t="s">
         <v>254</v>
@@ -95787,10 +95787,10 @@
     </row>
     <row r="1550" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1550" t="s">
+        <v>694</v>
+      </c>
+      <c r="B1550" t="s">
         <v>695</v>
-      </c>
-      <c r="B1550" t="s">
-        <v>696</v>
       </c>
       <c r="C1550">
         <v>1</v>
@@ -95849,7 +95849,7 @@
     </row>
     <row r="1551" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1551" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1551" t="s">
         <v>234</v>
@@ -95911,7 +95911,7 @@
     </row>
     <row r="1552" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1552" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1552" t="s">
         <v>235</v>
@@ -95964,7 +95964,7 @@
     </row>
     <row r="1553" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1553" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1553" t="s">
         <v>144</v>
@@ -96026,10 +96026,10 @@
     </row>
     <row r="1554" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1554" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1554" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C1554">
         <v>1</v>
@@ -96085,7 +96085,7 @@
     </row>
     <row r="1555" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1555" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1555" t="s">
         <v>244</v>
@@ -96147,10 +96147,10 @@
     </row>
     <row r="1556" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1556" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1556" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C1556">
         <v>1</v>
@@ -96206,7 +96206,7 @@
     </row>
     <row r="1557" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1557" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1557" t="s">
         <v>38</v>
@@ -96265,7 +96265,7 @@
     </row>
     <row r="1558" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1558" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1558" t="s">
         <v>40</v>
@@ -96327,7 +96327,7 @@
     </row>
     <row r="1559" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1559" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1559" t="s">
         <v>238</v>
@@ -96389,7 +96389,7 @@
     </row>
     <row r="1560" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1560" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1560" t="s">
         <v>574</v>
@@ -96442,7 +96442,7 @@
     </row>
     <row r="1561" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1561" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B1561" t="s">
         <v>43</v>
@@ -96504,7 +96504,7 @@
     </row>
     <row r="1562" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1562" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1562" t="s">
         <v>135</v>
@@ -96566,10 +96566,10 @@
     </row>
     <row r="1563" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1563" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1563" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C1563">
         <v>1</v>
@@ -96628,7 +96628,7 @@
     </row>
     <row r="1564" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1564" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1564" t="s">
         <v>69</v>
@@ -96690,7 +96690,7 @@
     </row>
     <row r="1565" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1565" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1565" t="s">
         <v>137</v>
@@ -96752,10 +96752,10 @@
     </row>
     <row r="1566" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1566" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1566" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C1566">
         <v>1</v>
@@ -96814,7 +96814,7 @@
     </row>
     <row r="1567" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1567" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1567" t="s">
         <v>284</v>
@@ -96876,10 +96876,10 @@
     </row>
     <row r="1568" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1568" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1568" t="s">
         <v>698</v>
-      </c>
-      <c r="B1568" t="s">
-        <v>699</v>
       </c>
       <c r="C1568">
         <v>1</v>
@@ -96935,7 +96935,7 @@
     </row>
     <row r="1569" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1569" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1569" t="s">
         <v>430</v>
@@ -96997,7 +96997,7 @@
     </row>
     <row r="1570" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1570" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1570" t="s">
         <v>333</v>
@@ -97059,7 +97059,7 @@
     </row>
     <row r="1571" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1571" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1571" t="s">
         <v>54</v>
@@ -97118,7 +97118,7 @@
     </row>
     <row r="1572" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1572" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1572" t="s">
         <v>78</v>
@@ -97180,7 +97180,7 @@
     </row>
     <row r="1573" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1573" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1573" t="s">
         <v>147</v>
@@ -97239,7 +97239,7 @@
     </row>
     <row r="1574" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1574" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1574" t="s">
         <v>503</v>
@@ -97298,10 +97298,10 @@
     </row>
     <row r="1575" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1575" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1575" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C1575">
         <v>1</v>
@@ -97360,7 +97360,7 @@
     </row>
     <row r="1576" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1576" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1576" t="s">
         <v>506</v>
@@ -97419,7 +97419,7 @@
     </row>
     <row r="1577" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1577" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1577" t="s">
         <v>62</v>
@@ -97481,7 +97481,7 @@
     </row>
     <row r="1578" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1578" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1578" t="s">
         <v>151</v>
@@ -97543,7 +97543,7 @@
     </row>
     <row r="1579" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1579" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1579" t="s">
         <v>287</v>
@@ -97602,7 +97602,7 @@
     </row>
     <row r="1580" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1580" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1580" t="s">
         <v>156</v>
@@ -97664,10 +97664,10 @@
     </row>
     <row r="1581" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1581" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1581" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C1581">
         <v>1</v>
@@ -97723,7 +97723,7 @@
     </row>
     <row r="1582" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1582" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1582" t="s">
         <v>89</v>
@@ -97785,7 +97785,7 @@
     </row>
     <row r="1583" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1583" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B1583" t="s">
         <v>288</v>
@@ -97847,7 +97847,7 @@
     </row>
     <row r="1584" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1584" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1584" t="s">
         <v>222</v>
@@ -97906,7 +97906,7 @@
     </row>
     <row r="1585" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1585" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1585" t="s">
         <v>201</v>
@@ -97968,7 +97968,7 @@
     </row>
     <row r="1586" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1586" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1586" t="s">
         <v>517</v>
@@ -98027,7 +98027,7 @@
     </row>
     <row r="1587" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1587" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1587" t="s">
         <v>202</v>
@@ -98089,7 +98089,7 @@
     </row>
     <row r="1588" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1588" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1588" t="s">
         <v>339</v>
@@ -98148,10 +98148,10 @@
     </row>
     <row r="1589" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1589" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1589" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C1589">
         <v>1</v>
@@ -98210,7 +98210,7 @@
     </row>
     <row r="1590" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1590" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1590" t="s">
         <v>203</v>
@@ -98272,7 +98272,7 @@
     </row>
     <row r="1591" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1591" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1591" t="s">
         <v>518</v>
@@ -98325,7 +98325,7 @@
     </row>
     <row r="1592" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1592" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1592" t="s">
         <v>340</v>
@@ -98384,10 +98384,10 @@
     </row>
     <row r="1593" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1593" t="s">
+        <v>700</v>
+      </c>
+      <c r="B1593" t="s">
         <v>701</v>
-      </c>
-      <c r="B1593" t="s">
-        <v>702</v>
       </c>
       <c r="C1593">
         <v>1</v>
@@ -98443,7 +98443,7 @@
     </row>
     <row r="1594" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1594" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1594" t="s">
         <v>232</v>
@@ -98502,7 +98502,7 @@
     </row>
     <row r="1595" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1595" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1595" t="s">
         <v>211</v>
@@ -98564,7 +98564,7 @@
     </row>
     <row r="1596" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1596" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1596" t="s">
         <v>237</v>
@@ -98626,7 +98626,7 @@
     </row>
     <row r="1597" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1597" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1597" t="s">
         <v>212</v>
@@ -98688,7 +98688,7 @@
     </row>
     <row r="1598" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1598" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1598" t="s">
         <v>519</v>
@@ -98750,10 +98750,10 @@
     </row>
     <row r="1599" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1599" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1599" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C1599">
         <v>1</v>
@@ -98812,7 +98812,7 @@
     </row>
     <row r="1600" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1600" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1600" t="s">
         <v>522</v>
@@ -98871,7 +98871,7 @@
     </row>
     <row r="1601" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1601" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1601" t="s">
         <v>433</v>
@@ -98924,7 +98924,7 @@
     </row>
     <row r="1602" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1602" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1602" t="s">
         <v>499</v>
@@ -98983,7 +98983,7 @@
     </row>
     <row r="1603" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1603" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1603" t="s">
         <v>424</v>
@@ -99045,7 +99045,7 @@
     </row>
     <row r="1604" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1604" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1604" t="s">
         <v>425</v>
@@ -99107,7 +99107,7 @@
     </row>
     <row r="1605" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1605" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B1605" t="s">
         <v>571</v>
@@ -99160,7 +99160,7 @@
     </row>
     <row r="1606" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1606" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1606" t="s">
         <v>378</v>
@@ -99222,7 +99222,7 @@
     </row>
     <row r="1607" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1607" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1607" t="s">
         <v>513</v>
@@ -99281,7 +99281,7 @@
     </row>
     <row r="1608" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1608" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1608" t="s">
         <v>310</v>
@@ -99340,10 +99340,10 @@
     </row>
     <row r="1609" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1609" t="s">
+        <v>702</v>
+      </c>
+      <c r="B1609" t="s">
         <v>703</v>
-      </c>
-      <c r="B1609" t="s">
-        <v>704</v>
       </c>
       <c r="C1609">
         <v>1</v>
@@ -99393,7 +99393,7 @@
     </row>
     <row r="1610" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1610" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1610" t="s">
         <v>514</v>
@@ -99455,7 +99455,7 @@
     </row>
     <row r="1611" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1611" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1611" t="s">
         <v>48</v>
@@ -99511,10 +99511,10 @@
     </row>
     <row r="1612" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1612" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1612" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C1612">
         <v>1</v>
@@ -99564,7 +99564,7 @@
     </row>
     <row r="1613" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1613" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1613" t="s">
         <v>50</v>
@@ -99623,7 +99623,7 @@
     </row>
     <row r="1614" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1614" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1614" t="s">
         <v>382</v>
@@ -99676,7 +99676,7 @@
     </row>
     <row r="1615" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1615" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1615" t="s">
         <v>383</v>
@@ -99735,10 +99735,10 @@
     </row>
     <row r="1616" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1616" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1616" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C1616">
         <v>1</v>
@@ -99788,7 +99788,7 @@
     </row>
     <row r="1617" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1617" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1617" t="s">
         <v>313</v>
@@ -99841,7 +99841,7 @@
     </row>
     <row r="1618" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1618" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1618" t="s">
         <v>407</v>
@@ -99900,7 +99900,7 @@
     </row>
     <row r="1619" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1619" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1619" t="s">
         <v>56</v>
@@ -99953,7 +99953,7 @@
     </row>
     <row r="1620" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1620" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1620" t="s">
         <v>316</v>
@@ -100006,7 +100006,7 @@
     </row>
     <row r="1621" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1621" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1621" t="s">
         <v>405</v>
@@ -100068,7 +100068,7 @@
     </row>
     <row r="1622" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1622" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1622" t="s">
         <v>384</v>
@@ -100121,7 +100121,7 @@
     </row>
     <row r="1623" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1623" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1623" t="s">
         <v>385</v>
@@ -100180,7 +100180,7 @@
     </row>
     <row r="1624" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1624" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1624" t="s">
         <v>472</v>
@@ -100239,7 +100239,7 @@
     </row>
     <row r="1625" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1625" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1625" t="s">
         <v>319</v>
@@ -100301,7 +100301,7 @@
     </row>
     <row r="1626" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1626" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1626" t="s">
         <v>61</v>
@@ -100363,10 +100363,10 @@
     </row>
     <row r="1627" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1627" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B1627" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C1627">
         <v>1</v>
@@ -100425,10 +100425,10 @@
     </row>
     <row r="1628" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1628" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1628" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C1628">
         <v>1</v>
@@ -100487,10 +100487,10 @@
     </row>
     <row r="1629" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1629" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1629" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C1629">
         <v>1</v>
@@ -100540,7 +100540,7 @@
     </row>
     <row r="1630" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1630" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1630" t="s">
         <v>97</v>
@@ -100593,7 +100593,7 @@
     </row>
     <row r="1631" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1631" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1631" t="s">
         <v>283</v>
@@ -100655,7 +100655,7 @@
     </row>
     <row r="1632" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1632" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1632" t="s">
         <v>101</v>
@@ -100708,7 +100708,7 @@
     </row>
     <row r="1633" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1633" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1633" t="s">
         <v>445</v>
@@ -100767,10 +100767,10 @@
     </row>
     <row r="1634" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1634" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1634" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C1634">
         <v>1</v>
@@ -100826,10 +100826,10 @@
     </row>
     <row r="1635" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1635" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1635" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C1635">
         <v>1</v>
@@ -100879,7 +100879,7 @@
     </row>
     <row r="1636" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1636" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1636" t="s">
         <v>244</v>
@@ -100941,7 +100941,7 @@
     </row>
     <row r="1637" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1637" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1637" t="s">
         <v>140</v>
@@ -101003,10 +101003,10 @@
     </row>
     <row r="1638" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1638" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1638" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C1638">
         <v>1</v>
@@ -101062,10 +101062,10 @@
     </row>
     <row r="1639" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1639" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1639" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C1639">
         <v>1</v>
@@ -101124,10 +101124,10 @@
     </row>
     <row r="1640" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1640" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1640" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C1640">
         <v>1</v>
@@ -101186,7 +101186,7 @@
     </row>
     <row r="1641" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1641" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1641" t="s">
         <v>444</v>
@@ -101245,7 +101245,7 @@
     </row>
     <row r="1642" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1642" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1642" t="s">
         <v>134</v>
@@ -101307,10 +101307,10 @@
     </row>
     <row r="1643" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1643" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1643" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C1643">
         <v>1</v>
@@ -101369,7 +101369,7 @@
     </row>
     <row r="1644" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1644" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1644" t="s">
         <v>100</v>
@@ -101431,10 +101431,10 @@
     </row>
     <row r="1645" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1645" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1645" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C1645">
         <v>1</v>
@@ -101493,7 +101493,7 @@
     </row>
     <row r="1646" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1646" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1646" t="s">
         <v>143</v>
@@ -101555,10 +101555,10 @@
     </row>
     <row r="1647" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1647" t="s">
+        <v>706</v>
+      </c>
+      <c r="B1647" t="s">
         <v>707</v>
-      </c>
-      <c r="B1647" t="s">
-        <v>708</v>
       </c>
       <c r="C1647">
         <v>1</v>
@@ -101608,7 +101608,7 @@
     </row>
     <row r="1648" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1648" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1648" t="s">
         <v>152</v>
@@ -101670,7 +101670,7 @@
     </row>
     <row r="1649" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1649" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1649" t="s">
         <v>43</v>
@@ -101729,7 +101729,7 @@
     </row>
     <row r="1650" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1650" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1650" t="s">
         <v>248</v>
@@ -101788,7 +101788,7 @@
     </row>
     <row r="1651" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1651" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1651" t="s">
         <v>478</v>
@@ -101850,7 +101850,7 @@
     </row>
     <row r="1652" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1652" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1652" t="s">
         <v>545</v>
@@ -101912,7 +101912,7 @@
     </row>
     <row r="1653" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1653" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1653" t="s">
         <v>479</v>
@@ -101974,7 +101974,7 @@
     </row>
     <row r="1654" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1654" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1654" t="s">
         <v>250</v>
@@ -102036,10 +102036,10 @@
     </row>
     <row r="1655" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1655" t="s">
+        <v>713</v>
+      </c>
+      <c r="B1655" t="s">
         <v>714</v>
-      </c>
-      <c r="B1655" t="s">
-        <v>715</v>
       </c>
       <c r="C1655">
         <v>1</v>
@@ -102098,7 +102098,7 @@
     </row>
     <row r="1656" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1656" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1656" t="s">
         <v>252</v>
@@ -102157,7 +102157,7 @@
     </row>
     <row r="1657" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1657" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1657" t="s">
         <v>367</v>
@@ -102216,7 +102216,7 @@
     </row>
     <row r="1658" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1658" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1658" t="s">
         <v>546</v>
@@ -102278,7 +102278,7 @@
     </row>
     <row r="1659" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1659" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1659" t="s">
         <v>105</v>
@@ -102340,7 +102340,7 @@
     </row>
     <row r="1660" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1660" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1660" t="s">
         <v>547</v>
@@ -102402,7 +102402,7 @@
     </row>
     <row r="1661" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1661" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1661" t="s">
         <v>481</v>
@@ -102461,7 +102461,7 @@
     </row>
     <row r="1662" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1662" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1662" t="s">
         <v>482</v>
@@ -102523,7 +102523,7 @@
     </row>
     <row r="1663" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1663" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1663" t="s">
         <v>255</v>
@@ -102585,7 +102585,7 @@
     </row>
     <row r="1664" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1664" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1664" t="s">
         <v>448</v>
@@ -102647,7 +102647,7 @@
     </row>
     <row r="1665" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1665" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1665" t="s">
         <v>258</v>
@@ -102709,7 +102709,7 @@
     </row>
     <row r="1666" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1666" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1666" t="s">
         <v>261</v>
@@ -102771,7 +102771,7 @@
     </row>
     <row r="1667" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1667" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1667" t="s">
         <v>262</v>
@@ -102830,7 +102830,7 @@
     </row>
     <row r="1668" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1668" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1668" t="s">
         <v>108</v>
@@ -102892,7 +102892,7 @@
     </row>
     <row r="1669" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1669" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1669" t="s">
         <v>485</v>
@@ -102954,7 +102954,7 @@
     </row>
     <row r="1670" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1670" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1670" t="s">
         <v>264</v>
@@ -103016,7 +103016,7 @@
     </row>
     <row r="1671" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1671" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B1671" t="s">
         <v>265</v>
@@ -103078,7 +103078,7 @@
     </row>
     <row r="1672" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1672" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1672" t="s">
         <v>408</v>
@@ -103137,7 +103137,7 @@
     </row>
     <row r="1673" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1673" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1673" t="s">
         <v>135</v>
@@ -103196,10 +103196,10 @@
     </row>
     <row r="1674" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1674" t="s">
+        <v>715</v>
+      </c>
+      <c r="B1674" t="s">
         <v>716</v>
-      </c>
-      <c r="B1674" t="s">
-        <v>717</v>
       </c>
       <c r="C1674">
         <v>1</v>
@@ -103258,7 +103258,7 @@
     </row>
     <row r="1675" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1675" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1675" t="s">
         <v>274</v>
@@ -103320,7 +103320,7 @@
     </row>
     <row r="1676" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1676" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1676" t="s">
         <v>137</v>
@@ -103382,10 +103382,10 @@
     </row>
     <row r="1677" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1677" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1677" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C1677">
         <v>1</v>
@@ -103444,7 +103444,7 @@
     </row>
     <row r="1678" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1678" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1678" t="s">
         <v>73</v>
@@ -103506,7 +103506,7 @@
     </row>
     <row r="1679" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1679" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1679" t="s">
         <v>50</v>
@@ -103568,7 +103568,7 @@
     </row>
     <row r="1680" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1680" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1680" t="s">
         <v>333</v>
@@ -103627,7 +103627,7 @@
     </row>
     <row r="1681" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1681" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1681" t="s">
         <v>409</v>
@@ -103689,7 +103689,7 @@
     </row>
     <row r="1682" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1682" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1682" t="s">
         <v>407</v>
@@ -103751,7 +103751,7 @@
     </row>
     <row r="1683" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1683" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1683" t="s">
         <v>79</v>
@@ -103810,7 +103810,7 @@
     </row>
     <row r="1684" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1684" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1684" t="s">
         <v>147</v>
@@ -103872,7 +103872,7 @@
     </row>
     <row r="1685" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1685" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1685" t="s">
         <v>277</v>
@@ -103934,7 +103934,7 @@
     </row>
     <row r="1686" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1686" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1686" t="s">
         <v>148</v>
@@ -103996,10 +103996,10 @@
     </row>
     <row r="1687" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1687" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1687" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1687">
         <v>1</v>
@@ -104058,7 +104058,7 @@
     </row>
     <row r="1688" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1688" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1688" t="s">
         <v>149</v>
@@ -104111,10 +104111,10 @@
     </row>
     <row r="1689" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1689" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1689" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C1689">
         <v>1</v>
@@ -104173,10 +104173,10 @@
     </row>
     <row r="1690" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1690" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1690" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C1690">
         <v>1</v>
@@ -104235,7 +104235,7 @@
     </row>
     <row r="1691" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1691" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1691" t="s">
         <v>61</v>
@@ -104297,7 +104297,7 @@
     </row>
     <row r="1692" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1692" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1692" t="s">
         <v>62</v>
@@ -104356,10 +104356,10 @@
     </row>
     <row r="1693" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1693" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B1693" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C1693">
         <v>1</v>
@@ -104418,7 +104418,7 @@
     </row>
     <row r="1694" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1694" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1694" t="s">
         <v>160</v>
@@ -104480,7 +104480,7 @@
     </row>
     <row r="1695" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1695" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1695" t="s">
         <v>119</v>
@@ -104542,7 +104542,7 @@
     </row>
     <row r="1696" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1696" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1696" t="s">
         <v>226</v>
@@ -104604,7 +104604,7 @@
     </row>
     <row r="1697" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1697" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1697" t="s">
         <v>227</v>
@@ -104657,10 +104657,10 @@
     </row>
     <row r="1698" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1698" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1698" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C1698">
         <v>1</v>
@@ -104719,7 +104719,7 @@
     </row>
     <row r="1699" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1699" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1699" t="s">
         <v>229</v>
@@ -104778,7 +104778,7 @@
     </row>
     <row r="1700" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1700" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1700" t="s">
         <v>230</v>
@@ -104831,7 +104831,7 @@
     </row>
     <row r="1701" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1701" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1701" t="s">
         <v>414</v>
@@ -104893,7 +104893,7 @@
     </row>
     <row r="1702" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1702" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1702" t="s">
         <v>231</v>
@@ -104952,7 +104952,7 @@
     </row>
     <row r="1703" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1703" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1703" t="s">
         <v>123</v>
@@ -105014,10 +105014,10 @@
     </row>
     <row r="1704" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1704" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1704" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C1704">
         <v>1</v>
@@ -105076,7 +105076,7 @@
     </row>
     <row r="1705" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1705" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1705" t="s">
         <v>234</v>
@@ -105135,7 +105135,7 @@
     </row>
     <row r="1706" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1706" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1706" t="s">
         <v>235</v>
@@ -105197,7 +105197,7 @@
     </row>
     <row r="1707" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1707" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1707" t="s">
         <v>427</v>
@@ -105259,10 +105259,10 @@
     </row>
     <row r="1708" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1708" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1708" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C1708">
         <v>1</v>
@@ -105321,7 +105321,7 @@
     </row>
     <row r="1709" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1709" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1709" t="s">
         <v>128</v>
@@ -105380,10 +105380,10 @@
     </row>
     <row r="1710" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1710" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1710" t="s">
         <v>721</v>
-      </c>
-      <c r="B1710" t="s">
-        <v>722</v>
       </c>
       <c r="C1710">
         <v>1</v>
@@ -105442,7 +105442,7 @@
     </row>
     <row r="1711" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1711" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1711" t="s">
         <v>500</v>
@@ -105504,10 +105504,10 @@
     </row>
     <row r="1712" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1712" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1712" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C1712">
         <v>1</v>
@@ -105566,10 +105566,10 @@
     </row>
     <row r="1713" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1713" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1713" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C1713">
         <v>1</v>
@@ -105628,7 +105628,7 @@
     </row>
     <row r="1714" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1714" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1714" t="s">
         <v>574</v>
@@ -105681,7 +105681,7 @@
     </row>
     <row r="1715" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1715" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B1715" t="s">
         <v>132</v>
@@ -105743,7 +105743,7 @@
     </row>
     <row r="1716" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1716" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1716" t="s">
         <v>201</v>
@@ -105805,10 +105805,10 @@
     </row>
     <row r="1717" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1717" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1717" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C1717">
         <v>1</v>
@@ -105864,7 +105864,7 @@
     </row>
     <row r="1718" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1718" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1718" t="s">
         <v>202</v>
@@ -105926,7 +105926,7 @@
     </row>
     <row r="1719" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1719" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1719" t="s">
         <v>120</v>
@@ -105985,7 +105985,7 @@
     </row>
     <row r="1720" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1720" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1720" t="s">
         <v>413</v>
@@ -106038,7 +106038,7 @@
     </row>
     <row r="1721" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1721" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1721" t="s">
         <v>339</v>
@@ -106100,7 +106100,7 @@
     </row>
     <row r="1722" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1722" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1722" t="s">
         <v>203</v>
@@ -106162,7 +106162,7 @@
     </row>
     <row r="1723" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1723" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1723" t="s">
         <v>340</v>
@@ -106224,10 +106224,10 @@
     </row>
     <row r="1724" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1724" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1724" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1724">
         <v>1</v>
@@ -106286,7 +106286,7 @@
     </row>
     <row r="1725" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1725" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1725" t="s">
         <v>326</v>
@@ -106348,7 +106348,7 @@
     </row>
     <row r="1726" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1726" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1726" t="s">
         <v>125</v>
@@ -106410,7 +106410,7 @@
     </row>
     <row r="1727" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1727" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1727" t="s">
         <v>436</v>
@@ -106463,10 +106463,10 @@
     </row>
     <row r="1728" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1728" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1728" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C1728">
         <v>1</v>
@@ -106516,7 +106516,7 @@
     </row>
     <row r="1729" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1729" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1729" t="s">
         <v>126</v>
@@ -106575,7 +106575,7 @@
     </row>
     <row r="1730" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1730" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1730" t="s">
         <v>328</v>
@@ -106628,10 +106628,10 @@
     </row>
     <row r="1731" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1731" t="s">
+        <v>723</v>
+      </c>
+      <c r="B1731" t="s">
         <v>724</v>
-      </c>
-      <c r="B1731" t="s">
-        <v>725</v>
       </c>
       <c r="C1731">
         <v>1</v>
@@ -106690,7 +106690,7 @@
     </row>
     <row r="1732" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1732" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1732" t="s">
         <v>211</v>
@@ -106752,7 +106752,7 @@
     </row>
     <row r="1733" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1733" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1733" t="s">
         <v>212</v>
@@ -106814,7 +106814,7 @@
     </row>
     <row r="1734" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1734" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1734" t="s">
         <v>499</v>
@@ -106876,7 +106876,7 @@
     </row>
     <row r="1735" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1735" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1735" t="s">
         <v>130</v>
@@ -106935,7 +106935,7 @@
     </row>
     <row r="1736" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1736" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1736" t="s">
         <v>215</v>
@@ -106994,7 +106994,7 @@
     </row>
     <row r="1737" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1737" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1737" t="s">
         <v>425</v>
@@ -107056,7 +107056,7 @@
     </row>
     <row r="1738" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1738" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1738" t="s">
         <v>386</v>
@@ -107118,7 +107118,7 @@
     </row>
     <row r="1739" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1739" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1739" t="s">
         <v>311</v>
@@ -107180,7 +107180,7 @@
     </row>
     <row r="1740" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1740" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1740" t="s">
         <v>388</v>
@@ -107239,7 +107239,7 @@
     </row>
     <row r="1741" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1741" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1741" t="s">
         <v>380</v>
@@ -107298,7 +107298,7 @@
     </row>
     <row r="1742" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1742" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1742" t="s">
         <v>357</v>
@@ -107357,7 +107357,7 @@
     </row>
     <row r="1743" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1743" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1743" t="s">
         <v>469</v>
@@ -107416,7 +107416,7 @@
     </row>
     <row r="1744" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1744" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1744" t="s">
         <v>383</v>
@@ -107475,7 +107475,7 @@
     </row>
     <row r="1745" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1745" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1745" t="s">
         <v>527</v>
@@ -107537,7 +107537,7 @@
     </row>
     <row r="1746" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1746" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1746" t="s">
         <v>313</v>
@@ -107590,7 +107590,7 @@
     </row>
     <row r="1747" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1747" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1747" t="s">
         <v>390</v>
@@ -107652,7 +107652,7 @@
     </row>
     <row r="1748" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1748" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1748" t="s">
         <v>528</v>
@@ -107714,7 +107714,7 @@
     </row>
     <row r="1749" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1749" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1749" t="s">
         <v>316</v>
@@ -107767,7 +107767,7 @@
     </row>
     <row r="1750" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1750" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1750" t="s">
         <v>405</v>
@@ -107829,7 +107829,7 @@
     </row>
     <row r="1751" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1751" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1751" t="s">
         <v>364</v>
@@ -107891,7 +107891,7 @@
     </row>
     <row r="1752" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1752" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1752" t="s">
         <v>319</v>
@@ -107950,7 +107950,7 @@
     </row>
     <row r="1753" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1753" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1753" t="s">
         <v>320</v>
@@ -108003,10 +108003,10 @@
     </row>
     <row r="1754" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1754" t="s">
+        <v>725</v>
+      </c>
+      <c r="B1754" t="s">
         <v>726</v>
-      </c>
-      <c r="B1754" t="s">
-        <v>727</v>
       </c>
       <c r="C1754">
         <v>1</v>
@@ -108062,10 +108062,10 @@
     </row>
     <row r="1755" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1755" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1755" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C1755">
         <v>1</v>
@@ -108124,10 +108124,10 @@
     </row>
     <row r="1756" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1756" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1756" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C1756">
         <v>1</v>
@@ -108183,7 +108183,7 @@
     </row>
     <row r="1757" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1757" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1757" t="s">
         <v>393</v>
@@ -108245,7 +108245,7 @@
     </row>
     <row r="1758" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1758" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1758" t="s">
         <v>532</v>
@@ -108307,7 +108307,7 @@
     </row>
     <row r="1759" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1759" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B1759" t="s">
         <v>365</v>
@@ -108369,7 +108369,7 @@
     </row>
     <row r="1760" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1760" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1760" t="s">
         <v>217</v>
@@ -108428,7 +108428,7 @@
     </row>
     <row r="1761" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1761" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1761" t="s">
         <v>22</v>
@@ -108487,7 +108487,7 @@
     </row>
     <row r="1762" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1762" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1762" t="s">
         <v>134</v>
@@ -108546,7 +108546,7 @@
     </row>
     <row r="1763" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1763" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1763" t="s">
         <v>221</v>
@@ -108608,7 +108608,7 @@
     </row>
     <row r="1764" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1764" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1764" t="s">
         <v>222</v>
@@ -108670,7 +108670,7 @@
     </row>
     <row r="1765" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1765" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1765" t="s">
         <v>517</v>
@@ -108729,10 +108729,10 @@
     </row>
     <row r="1766" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1766" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1766" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C1766">
         <v>1</v>
@@ -108788,10 +108788,10 @@
     </row>
     <row r="1767" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1767" t="s">
+        <v>728</v>
+      </c>
+      <c r="B1767" t="s">
         <v>729</v>
-      </c>
-      <c r="B1767" t="s">
-        <v>730</v>
       </c>
       <c r="C1767">
         <v>1</v>
@@ -108841,7 +108841,7 @@
     </row>
     <row r="1768" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1768" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1768" t="s">
         <v>251</v>
@@ -108903,7 +108903,7 @@
     </row>
     <row r="1769" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1769" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1769" t="s">
         <v>232</v>
@@ -108962,7 +108962,7 @@
     </row>
     <row r="1770" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1770" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1770" t="s">
         <v>243</v>
@@ -109015,7 +109015,7 @@
     </row>
     <row r="1771" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1771" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1771" t="s">
         <v>146</v>
@@ -109074,10 +109074,10 @@
     </row>
     <row r="1772" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1772" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1772" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C1772">
         <v>1</v>
@@ -109127,10 +109127,10 @@
     </row>
     <row r="1773" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1773" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1773" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C1773">
         <v>1</v>
@@ -109189,7 +109189,7 @@
     </row>
     <row r="1774" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1774" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1774" t="s">
         <v>237</v>
@@ -109251,7 +109251,7 @@
     </row>
     <row r="1775" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1775" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1775" t="s">
         <v>519</v>
@@ -109313,10 +109313,10 @@
     </row>
     <row r="1776" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1776" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1776" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C1776">
         <v>1</v>
@@ -109372,7 +109372,7 @@
     </row>
     <row r="1777" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1777" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1777" t="s">
         <v>522</v>
@@ -109434,7 +109434,7 @@
     </row>
     <row r="1778" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1778" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1778" t="s">
         <v>433</v>
@@ -109487,7 +109487,7 @@
     </row>
     <row r="1779" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1779" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1779" t="s">
         <v>246</v>
@@ -109549,7 +109549,7 @@
     </row>
     <row r="1780" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1780" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1780" t="s">
         <v>43</v>
@@ -109608,7 +109608,7 @@
     </row>
     <row r="1781" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1781" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B1781" t="s">
         <v>571</v>
@@ -109661,7 +109661,7 @@
     </row>
     <row r="1782" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1782" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1782" t="s">
         <v>46</v>
@@ -109720,7 +109720,7 @@
     </row>
     <row r="1783" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1783" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1783" t="s">
         <v>135</v>
@@ -109773,7 +109773,7 @@
     </row>
     <row r="1784" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1784" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1784" t="s">
         <v>137</v>
@@ -109835,7 +109835,7 @@
     </row>
     <row r="1785" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1785" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1785" t="s">
         <v>540</v>
@@ -109897,10 +109897,10 @@
     </row>
     <row r="1786" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1786" t="s">
+        <v>732</v>
+      </c>
+      <c r="B1786" t="s">
         <v>733</v>
-      </c>
-      <c r="B1786" t="s">
-        <v>734</v>
       </c>
       <c r="C1786">
         <v>1</v>
@@ -109959,7 +109959,7 @@
     </row>
     <row r="1787" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1787" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1787" t="s">
         <v>333</v>
@@ -110018,7 +110018,7 @@
     </row>
     <row r="1788" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1788" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1788" t="s">
         <v>301</v>
@@ -110080,10 +110080,10 @@
     </row>
     <row r="1789" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1789" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1789" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C1789">
         <v>1</v>
@@ -110139,7 +110139,7 @@
     </row>
     <row r="1790" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1790" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1790" t="s">
         <v>491</v>
@@ -110201,7 +110201,7 @@
     </row>
     <row r="1791" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1791" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1791" t="s">
         <v>304</v>
@@ -110263,7 +110263,7 @@
     </row>
     <row r="1792" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1792" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1792" t="s">
         <v>147</v>
@@ -110325,7 +110325,7 @@
     </row>
     <row r="1793" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1793" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1793" t="s">
         <v>148</v>
@@ -110384,7 +110384,7 @@
     </row>
     <row r="1794" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1794" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1794" t="s">
         <v>59</v>
@@ -110443,10 +110443,10 @@
     </row>
     <row r="1795" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1795" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1795" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C1795">
         <v>1</v>
@@ -110505,7 +110505,7 @@
     </row>
     <row r="1796" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1796" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1796" t="s">
         <v>60</v>
@@ -110567,7 +110567,7 @@
     </row>
     <row r="1797" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1797" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1797" t="s">
         <v>149</v>
@@ -110620,10 +110620,10 @@
     </row>
     <row r="1798" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1798" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1798" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C1798">
         <v>1</v>
@@ -110682,7 +110682,7 @@
     </row>
     <row r="1799" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1799" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1799" t="s">
         <v>62</v>
@@ -110744,7 +110744,7 @@
     </row>
     <row r="1800" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1800" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1800" t="s">
         <v>64</v>
@@ -110806,7 +110806,7 @@
     </row>
     <row r="1801" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1801" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1801" t="s">
         <v>156</v>
@@ -110865,10 +110865,10 @@
     </row>
     <row r="1802" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1802" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1802" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C1802">
         <v>1</v>
@@ -110927,10 +110927,10 @@
     </row>
     <row r="1803" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1803" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1803" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C1803">
         <v>1</v>
@@ -110980,7 +110980,7 @@
     </row>
     <row r="1804" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1804" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1804" t="s">
         <v>248</v>
@@ -111039,7 +111039,7 @@
     </row>
     <row r="1805" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1805" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1805" t="s">
         <v>250</v>
@@ -111092,7 +111092,7 @@
     </row>
     <row r="1806" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1806" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1806" t="s">
         <v>226</v>
@@ -111154,10 +111154,10 @@
     </row>
     <row r="1807" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1807" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1807" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C1807">
         <v>1</v>
@@ -111213,7 +111213,7 @@
     </row>
     <row r="1808" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1808" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1808" t="s">
         <v>229</v>
@@ -111272,7 +111272,7 @@
     </row>
     <row r="1809" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1809" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1809" t="s">
         <v>252</v>
@@ -111334,7 +111334,7 @@
     </row>
     <row r="1810" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1810" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1810" t="s">
         <v>230</v>
@@ -111396,7 +111396,7 @@
     </row>
     <row r="1811" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1811" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1811" t="s">
         <v>231</v>
@@ -111449,7 +111449,7 @@
     </row>
     <row r="1812" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1812" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1812" t="s">
         <v>367</v>
@@ -111511,10 +111511,10 @@
     </row>
     <row r="1813" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1813" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1813" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C1813">
         <v>1</v>
@@ -111573,10 +111573,10 @@
     </row>
     <row r="1814" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1814" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1814" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C1814">
         <v>1</v>
@@ -111635,7 +111635,7 @@
     </row>
     <row r="1815" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1815" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1815" t="s">
         <v>255</v>
@@ -111694,7 +111694,7 @@
     </row>
     <row r="1816" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1816" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1816" t="s">
         <v>234</v>
@@ -111756,7 +111756,7 @@
     </row>
     <row r="1817" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1817" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1817" t="s">
         <v>235</v>
@@ -111809,7 +111809,7 @@
     </row>
     <row r="1818" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1818" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1818" t="s">
         <v>448</v>
@@ -111871,7 +111871,7 @@
     </row>
     <row r="1819" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1819" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1819" t="s">
         <v>258</v>
@@ -111933,7 +111933,7 @@
     </row>
     <row r="1820" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1820" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1820" t="s">
         <v>261</v>
@@ -111995,7 +111995,7 @@
     </row>
     <row r="1821" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1821" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1821" t="s">
         <v>262</v>
@@ -112048,7 +112048,7 @@
     </row>
     <row r="1822" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1822" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1822" t="s">
         <v>264</v>
@@ -112107,7 +112107,7 @@
     </row>
     <row r="1823" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1823" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1823" t="s">
         <v>238</v>
@@ -112169,7 +112169,7 @@
     </row>
     <row r="1824" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1824" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1824" t="s">
         <v>265</v>
@@ -112231,7 +112231,7 @@
     </row>
     <row r="1825" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1825" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B1825" t="s">
         <v>508</v>
@@ -112293,7 +112293,7 @@
     </row>
     <row r="1826" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1826" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1826" t="s">
         <v>135</v>
@@ -112355,7 +112355,7 @@
     </row>
     <row r="1827" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1827" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1827" t="s">
         <v>248</v>
@@ -112417,7 +112417,7 @@
     </row>
     <row r="1828" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1828" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1828" t="s">
         <v>137</v>
@@ -112479,7 +112479,7 @@
     </row>
     <row r="1829" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1829" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1829" t="s">
         <v>250</v>
@@ -112541,7 +112541,7 @@
     </row>
     <row r="1830" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1830" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1830" t="s">
         <v>252</v>
@@ -112603,10 +112603,10 @@
     </row>
     <row r="1831" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1831" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1831" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C1831">
         <v>1</v>
@@ -112662,7 +112662,7 @@
     </row>
     <row r="1832" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1832" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1832" t="s">
         <v>333</v>
@@ -112724,7 +112724,7 @@
     </row>
     <row r="1833" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1833" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1833" t="s">
         <v>367</v>
@@ -112786,7 +112786,7 @@
     </row>
     <row r="1834" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1834" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1834" t="s">
         <v>448</v>
@@ -112848,7 +112848,7 @@
     </row>
     <row r="1835" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1835" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1835" t="s">
         <v>258</v>
@@ -112910,7 +112910,7 @@
     </row>
     <row r="1836" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1836" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1836" t="s">
         <v>147</v>
@@ -112972,7 +112972,7 @@
     </row>
     <row r="1837" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1837" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1837" t="s">
         <v>148</v>
@@ -113034,7 +113034,7 @@
     </row>
     <row r="1838" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1838" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1838" t="s">
         <v>59</v>
@@ -113096,10 +113096,10 @@
     </row>
     <row r="1839" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1839" t="s">
+        <v>736</v>
+      </c>
+      <c r="B1839" t="s">
         <v>737</v>
-      </c>
-      <c r="B1839" t="s">
-        <v>738</v>
       </c>
       <c r="C1839">
         <v>1</v>
@@ -113158,7 +113158,7 @@
     </row>
     <row r="1840" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1840" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1840" t="s">
         <v>261</v>
@@ -113217,7 +113217,7 @@
     </row>
     <row r="1841" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1841" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1841" t="s">
         <v>149</v>
@@ -113270,7 +113270,7 @@
     </row>
     <row r="1842" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1842" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1842" t="s">
         <v>262</v>
@@ -113329,7 +113329,7 @@
     </row>
     <row r="1843" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1843" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1843" t="s">
         <v>264</v>
@@ -113391,7 +113391,7 @@
     </row>
     <row r="1844" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1844" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1844" t="s">
         <v>62</v>
@@ -113450,7 +113450,7 @@
     </row>
     <row r="1845" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1845" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1845" t="s">
         <v>156</v>
@@ -113512,7 +113512,7 @@
     </row>
     <row r="1846" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1846" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1846" t="s">
         <v>265</v>
@@ -113574,10 +113574,10 @@
     </row>
     <row r="1847" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1847" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B1847" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C1847">
         <v>1</v>
